--- a/planilhas/Contabilidade Condominio.xlsx
+++ b/planilhas/Contabilidade Condominio.xlsx
@@ -5,7 +5,7 @@
   <sheets>
     <sheet state="hidden" name="CAPA Explicações" sheetId="1" r:id="rId4"/>
     <sheet state="visible" name="Fluxo de caixa 2024" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="FLUXO DE CAIXA 2025" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="Fluxo de caixa 2025" sheetId="3" r:id="rId6"/>
     <sheet state="visible" name="TaxaCondominio" sheetId="4" r:id="rId7"/>
     <sheet state="hidden" name="Manutenções" sheetId="5" r:id="rId8"/>
   </sheets>
@@ -1000,7 +1000,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="153">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1242,9 +1242,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf borderId="36" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="36" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf borderId="36" fillId="0" fontId="17" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="36" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="34" fillId="10" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1314,6 +1320,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="25" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5090,7 +5099,7 @@
       </c>
       <c r="J6" s="82">
         <f t="shared" si="3"/>
-        <v>4068.8</v>
+        <v>4073.87</v>
       </c>
       <c r="K6" s="82" t="str">
         <f>'Fluxo de caixa 2024'!V31</f>
@@ -5158,19 +5167,19 @@
       </c>
       <c r="J8" s="86">
         <f t="shared" si="5"/>
-        <v>868.99</v>
+        <v>874.06</v>
       </c>
       <c r="K8" s="86">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="L8" s="86">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="M8" s="86">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
@@ -5213,41 +5222,38 @@
         <f>TaxaCondominio!V10</f>
         <v>450</v>
       </c>
-      <c r="K9" s="89">
-        <f>TaxaCondominio!W10</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="89">
-        <f>TaxaCondominio!X10</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="89">
-        <f>TaxaCondominio!Y10</f>
-        <v>0</v>
+      <c r="K9" s="90">
+        <v>600.0</v>
+      </c>
+      <c r="L9" s="90">
+        <v>600.0</v>
+      </c>
+      <c r="M9" s="90">
+        <v>600.0</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
       <c r="A10" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="90"/>
-      <c r="C10" s="90"/>
-      <c r="D10" s="90"/>
-      <c r="E10" s="90"/>
-      <c r="F10" s="91"/>
-      <c r="G10" s="91"/>
-      <c r="H10" s="90"/>
-      <c r="I10" s="90"/>
-      <c r="J10" s="90">
-        <v>418.99</v>
-      </c>
-      <c r="K10" s="90">
+      <c r="B10" s="91"/>
+      <c r="C10" s="91"/>
+      <c r="D10" s="91"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="92"/>
+      <c r="G10" s="92"/>
+      <c r="H10" s="91"/>
+      <c r="I10" s="91"/>
+      <c r="J10" s="93">
+        <v>424.06</v>
+      </c>
+      <c r="K10" s="91">
         <v>0.0</v>
       </c>
-      <c r="L10" s="90">
+      <c r="L10" s="91">
         <v>0.0</v>
       </c>
-      <c r="M10" s="90">
+      <c r="M10" s="91">
         <v>0.0</v>
       </c>
     </row>
@@ -5282,54 +5288,54 @@
       <c r="M12" s="84"/>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="92" t="s">
+      <c r="A13" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="93">
+      <c r="B13" s="95">
         <f>SUM(B14:B15)</f>
         <v>0</v>
       </c>
-      <c r="C13" s="93" t="str">
+      <c r="C13" s="95" t="str">
         <f>C14</f>
         <v/>
       </c>
-      <c r="D13" s="93">
+      <c r="D13" s="95">
         <f t="shared" ref="D13:M13" si="6">SUM(D14:D15)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="93">
+      <c r="E13" s="95">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F13" s="93">
+      <c r="F13" s="95">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G13" s="93">
+      <c r="G13" s="95">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H13" s="93">
+      <c r="H13" s="95">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I13" s="93">
+      <c r="I13" s="95">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J13" s="93">
+      <c r="J13" s="95">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="K13" s="93">
+      <c r="K13" s="95">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="L13" s="93">
+      <c r="L13" s="95">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="M13" s="93">
+      <c r="M13" s="95">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -5338,18 +5344,18 @@
       <c r="A14" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="94"/>
-      <c r="C14" s="94"/>
-      <c r="D14" s="94"/>
-      <c r="E14" s="94"/>
-      <c r="F14" s="94"/>
-      <c r="G14" s="94"/>
-      <c r="H14" s="94"/>
-      <c r="I14" s="94"/>
-      <c r="J14" s="94"/>
-      <c r="K14" s="94"/>
-      <c r="L14" s="94"/>
-      <c r="M14" s="94"/>
+      <c r="B14" s="96"/>
+      <c r="C14" s="96"/>
+      <c r="D14" s="96"/>
+      <c r="E14" s="96"/>
+      <c r="F14" s="96"/>
+      <c r="G14" s="96"/>
+      <c r="H14" s="96"/>
+      <c r="I14" s="96"/>
+      <c r="J14" s="96"/>
+      <c r="K14" s="96"/>
+      <c r="L14" s="96"/>
+      <c r="M14" s="96"/>
     </row>
     <row r="15" ht="12.75" customHeight="1">
       <c r="A15" s="76"/>
@@ -5367,179 +5373,188 @@
       <c r="M15" s="84"/>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="A16" s="92" t="s">
+      <c r="A16" s="94" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="93">
+      <c r="B16" s="95">
         <f t="shared" ref="B16:C16" si="7">B17+B18+B19</f>
         <v>324.07</v>
       </c>
-      <c r="C16" s="93">
+      <c r="C16" s="95">
         <f t="shared" si="7"/>
         <v>334.17</v>
       </c>
-      <c r="D16" s="93">
+      <c r="D16" s="95">
         <f t="shared" ref="D16:M16" si="8">SUM(D17:D20)</f>
         <v>334.82</v>
       </c>
-      <c r="E16" s="93">
+      <c r="E16" s="95">
         <f t="shared" si="8"/>
         <v>233.37</v>
       </c>
-      <c r="F16" s="93">
+      <c r="F16" s="95">
         <f t="shared" si="8"/>
         <v>333.85</v>
       </c>
-      <c r="G16" s="93">
+      <c r="G16" s="95">
         <f t="shared" si="8"/>
         <v>335.38</v>
       </c>
-      <c r="H16" s="93">
+      <c r="H16" s="95">
         <f t="shared" si="8"/>
         <v>336.31</v>
       </c>
-      <c r="I16" s="93">
+      <c r="I16" s="95">
         <f t="shared" si="8"/>
         <v>236.67</v>
       </c>
-      <c r="J16" s="93">
+      <c r="J16" s="95">
         <f t="shared" si="8"/>
         <v>243.72</v>
       </c>
-      <c r="K16" s="93">
+      <c r="K16" s="95">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L16" s="93">
+        <v>301.3733333</v>
+      </c>
+      <c r="L16" s="95">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="M16" s="93">
+        <v>301.3733333</v>
+      </c>
+      <c r="M16" s="95">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>301.3733333</v>
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1">
       <c r="A17" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="95">
+      <c r="B17" s="97">
         <v>76.5</v>
       </c>
-      <c r="C17" s="95">
+      <c r="C17" s="97">
         <v>76.3</v>
       </c>
-      <c r="D17" s="95">
+      <c r="D17" s="97">
         <v>76.3</v>
       </c>
-      <c r="E17" s="95">
+      <c r="E17" s="97">
         <v>76.3</v>
       </c>
-      <c r="F17" s="95">
+      <c r="F17" s="97">
         <v>76.3</v>
       </c>
-      <c r="G17" s="95">
+      <c r="G17" s="97">
         <v>76.3</v>
       </c>
-      <c r="H17" s="95">
+      <c r="H17" s="97">
         <v>76.3</v>
       </c>
-      <c r="I17" s="95">
+      <c r="I17" s="97">
         <v>76.3</v>
       </c>
-      <c r="J17" s="95">
+      <c r="J17" s="97">
         <v>76.3</v>
       </c>
-      <c r="K17" s="95">
-        <v>0.0</v>
-      </c>
-      <c r="L17" s="95">
-        <v>0.0</v>
-      </c>
-      <c r="M17" s="95">
-        <v>0.0</v>
+      <c r="K17" s="97">
+        <f t="shared" ref="K17:K19" si="9">AVERAGE(B17:J17)</f>
+        <v>76.32222222</v>
+      </c>
+      <c r="L17" s="97">
+        <f t="shared" ref="L17:L19" si="10">AVERAGE(B17:J17)</f>
+        <v>76.32222222</v>
+      </c>
+      <c r="M17" s="97">
+        <f t="shared" ref="M17:M19" si="11">AVERAGE(B17:J17)</f>
+        <v>76.32222222</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1">
       <c r="A18" s="87" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="95">
+      <c r="B18" s="97">
         <v>47.57</v>
       </c>
-      <c r="C18" s="95">
+      <c r="C18" s="97">
         <v>57.87</v>
       </c>
-      <c r="D18" s="95">
+      <c r="D18" s="97">
         <v>58.52</v>
       </c>
-      <c r="E18" s="95">
+      <c r="E18" s="97">
         <v>57.07</v>
       </c>
-      <c r="F18" s="95">
+      <c r="F18" s="97">
         <v>57.55</v>
       </c>
-      <c r="G18" s="95">
+      <c r="G18" s="97">
         <v>59.08</v>
       </c>
-      <c r="H18" s="95">
+      <c r="H18" s="97">
         <v>60.01</v>
       </c>
-      <c r="I18" s="95">
+      <c r="I18" s="97">
         <v>60.37</v>
       </c>
-      <c r="J18" s="95">
+      <c r="J18" s="97">
         <v>67.42</v>
       </c>
-      <c r="K18" s="95">
-        <v>0.0</v>
-      </c>
-      <c r="L18" s="95">
-        <v>0.0</v>
-      </c>
-      <c r="M18" s="95">
-        <v>0.0</v>
+      <c r="K18" s="97">
+        <f t="shared" si="9"/>
+        <v>58.38444444</v>
+      </c>
+      <c r="L18" s="97">
+        <f t="shared" si="10"/>
+        <v>58.38444444</v>
+      </c>
+      <c r="M18" s="97">
+        <f t="shared" si="11"/>
+        <v>58.38444444</v>
       </c>
     </row>
     <row r="19" ht="12.75" customHeight="1">
       <c r="A19" s="87" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="94">
+      <c r="B19" s="96">
         <v>200.0</v>
       </c>
-      <c r="C19" s="94">
+      <c r="C19" s="96">
         <v>200.0</v>
       </c>
-      <c r="D19" s="94">
+      <c r="D19" s="96">
         <v>200.0</v>
       </c>
-      <c r="E19" s="94">
+      <c r="E19" s="96">
         <v>100.0</v>
       </c>
-      <c r="F19" s="94">
+      <c r="F19" s="96">
         <v>200.0</v>
       </c>
-      <c r="G19" s="94">
+      <c r="G19" s="96">
         <v>200.0</v>
       </c>
-      <c r="H19" s="94">
+      <c r="H19" s="96">
         <v>200.0</v>
       </c>
-      <c r="I19" s="94">
+      <c r="I19" s="96">
         <v>100.0</v>
       </c>
-      <c r="J19" s="94">
+      <c r="J19" s="96">
         <v>100.0</v>
       </c>
-      <c r="K19" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="L19" s="94">
-        <v>0.0</v>
-      </c>
-      <c r="M19" s="94">
-        <v>0.0</v>
+      <c r="K19" s="97">
+        <f t="shared" si="9"/>
+        <v>166.6666667</v>
+      </c>
+      <c r="L19" s="97">
+        <f t="shared" si="10"/>
+        <v>166.6666667</v>
+      </c>
+      <c r="M19" s="97">
+        <f t="shared" si="11"/>
+        <v>166.6666667</v>
       </c>
     </row>
     <row r="20" ht="12.75" customHeight="1">
@@ -5558,55 +5573,55 @@
       <c r="M20" s="84"/>
     </row>
     <row r="21" ht="12.75" customHeight="1">
-      <c r="A21" s="92" t="s">
+      <c r="A21" s="94" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="93">
+      <c r="B21" s="95">
         <f>B22+B23+B24</f>
         <v>310</v>
       </c>
-      <c r="C21" s="93">
-        <f t="shared" ref="C21:M21" si="9">SUM(C22:C25)</f>
+      <c r="C21" s="95">
+        <f t="shared" ref="C21:M21" si="12">SUM(C22:C25)</f>
         <v>0</v>
       </c>
-      <c r="D21" s="93">
-        <f t="shared" si="9"/>
+      <c r="D21" s="95">
+        <f t="shared" si="12"/>
         <v>1000</v>
       </c>
-      <c r="E21" s="93">
-        <f t="shared" si="9"/>
+      <c r="E21" s="95">
+        <f t="shared" si="12"/>
         <v>150</v>
       </c>
-      <c r="F21" s="93">
-        <f t="shared" si="9"/>
+      <c r="F21" s="95">
+        <f t="shared" si="12"/>
         <v>600</v>
       </c>
-      <c r="G21" s="93">
-        <f t="shared" si="9"/>
+      <c r="G21" s="95">
+        <f t="shared" si="12"/>
         <v>150</v>
       </c>
-      <c r="H21" s="93">
-        <f t="shared" si="9"/>
+      <c r="H21" s="95">
+        <f t="shared" si="12"/>
         <v>150</v>
       </c>
-      <c r="I21" s="93">
-        <f t="shared" si="9"/>
+      <c r="I21" s="95">
+        <f t="shared" si="12"/>
         <v>150</v>
       </c>
-      <c r="J21" s="93">
-        <f t="shared" si="9"/>
+      <c r="J21" s="95">
+        <f t="shared" si="12"/>
         <v>195</v>
       </c>
-      <c r="K21" s="93">
-        <f t="shared" si="9"/>
+      <c r="K21" s="95">
+        <f t="shared" si="12"/>
         <v>150</v>
       </c>
-      <c r="L21" s="93">
-        <f t="shared" si="9"/>
+      <c r="L21" s="95">
+        <f t="shared" si="12"/>
         <v>150</v>
       </c>
-      <c r="M21" s="93">
-        <f t="shared" si="9"/>
+      <c r="M21" s="95">
+        <f t="shared" si="12"/>
         <v>150</v>
       </c>
     </row>
@@ -5614,40 +5629,40 @@
       <c r="A22" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="95">
+      <c r="B22" s="97">
         <v>0.0</v>
       </c>
-      <c r="C22" s="94">
+      <c r="C22" s="96">
         <v>0.0</v>
       </c>
-      <c r="D22" s="94">
+      <c r="D22" s="96">
         <v>0.0</v>
       </c>
-      <c r="E22" s="94">
+      <c r="E22" s="96">
         <v>0.0</v>
       </c>
-      <c r="F22" s="94">
+      <c r="F22" s="96">
         <v>0.0</v>
       </c>
-      <c r="G22" s="94">
+      <c r="G22" s="96">
         <v>0.0</v>
       </c>
-      <c r="H22" s="94">
+      <c r="H22" s="96">
         <v>0.0</v>
       </c>
-      <c r="I22" s="94">
+      <c r="I22" s="96">
         <v>0.0</v>
       </c>
-      <c r="J22" s="94">
+      <c r="J22" s="96">
         <v>0.0</v>
       </c>
-      <c r="K22" s="94">
+      <c r="K22" s="96">
         <v>0.0</v>
       </c>
-      <c r="L22" s="94">
+      <c r="L22" s="96">
         <v>0.0</v>
       </c>
-      <c r="M22" s="94">
+      <c r="M22" s="96">
         <v>0.0</v>
       </c>
     </row>
@@ -5655,81 +5670,81 @@
       <c r="A23" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="B23" s="95">
+      <c r="B23" s="97">
         <v>310.0</v>
       </c>
-      <c r="C23" s="95">
+      <c r="C23" s="97">
         <v>0.0</v>
       </c>
-      <c r="D23" s="95">
+      <c r="D23" s="97">
         <v>1000.0</v>
       </c>
-      <c r="E23" s="95">
+      <c r="E23" s="97">
         <v>0.0</v>
       </c>
-      <c r="F23" s="95">
+      <c r="F23" s="97">
         <v>450.0</v>
       </c>
-      <c r="G23" s="95">
+      <c r="G23" s="97">
         <v>0.0</v>
       </c>
-      <c r="H23" s="95">
+      <c r="H23" s="97">
         <v>0.0</v>
       </c>
-      <c r="I23" s="95">
+      <c r="I23" s="97">
         <v>0.0</v>
       </c>
-      <c r="J23" s="95">
+      <c r="J23" s="97">
         <v>45.0</v>
       </c>
-      <c r="K23" s="95">
+      <c r="K23" s="97">
         <v>0.0</v>
       </c>
-      <c r="L23" s="95">
+      <c r="L23" s="97">
         <v>0.0</v>
       </c>
-      <c r="M23" s="95">
+      <c r="M23" s="97">
         <v>0.0</v>
       </c>
     </row>
     <row r="24" ht="12.75" customHeight="1">
-      <c r="A24" s="96" t="s">
+      <c r="A24" s="98" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="95">
+      <c r="B24" s="97">
         <v>0.0</v>
       </c>
-      <c r="C24" s="95">
+      <c r="C24" s="97">
         <v>0.0</v>
       </c>
-      <c r="D24" s="95">
+      <c r="D24" s="97">
         <v>0.0</v>
       </c>
-      <c r="E24" s="95">
+      <c r="E24" s="97">
         <v>150.0</v>
       </c>
-      <c r="F24" s="95">
+      <c r="F24" s="97">
         <v>150.0</v>
       </c>
-      <c r="G24" s="95">
+      <c r="G24" s="97">
         <v>150.0</v>
       </c>
-      <c r="H24" s="95">
+      <c r="H24" s="97">
         <v>150.0</v>
       </c>
-      <c r="I24" s="95">
+      <c r="I24" s="97">
         <v>150.0</v>
       </c>
-      <c r="J24" s="95">
+      <c r="J24" s="97">
         <v>150.0</v>
       </c>
-      <c r="K24" s="97">
+      <c r="K24" s="99">
         <v>150.0</v>
       </c>
-      <c r="L24" s="97">
+      <c r="L24" s="99">
         <v>150.0</v>
       </c>
-      <c r="M24" s="97">
+      <c r="M24" s="99">
         <v>150.0</v>
       </c>
     </row>
@@ -5749,123 +5764,123 @@
       <c r="M25" s="84"/>
     </row>
     <row r="26" ht="12.75" customHeight="1">
-      <c r="A26" s="98" t="s">
+      <c r="A26" s="100" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="99"/>
-      <c r="C26" s="99"/>
-      <c r="D26" s="99"/>
-      <c r="E26" s="99"/>
-      <c r="F26" s="99"/>
-      <c r="G26" s="99"/>
-      <c r="H26" s="99"/>
-      <c r="I26" s="99"/>
-      <c r="J26" s="99"/>
-      <c r="K26" s="99"/>
-      <c r="L26" s="99"/>
-      <c r="M26" s="99"/>
+      <c r="B26" s="101"/>
+      <c r="C26" s="101"/>
+      <c r="D26" s="101"/>
+      <c r="E26" s="101"/>
+      <c r="F26" s="101"/>
+      <c r="G26" s="101"/>
+      <c r="H26" s="101"/>
+      <c r="I26" s="101"/>
+      <c r="J26" s="101"/>
+      <c r="K26" s="101"/>
+      <c r="L26" s="101"/>
+      <c r="M26" s="101"/>
     </row>
     <row r="27" ht="12.75" customHeight="1">
       <c r="A27" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="95">
-        <f>'Fluxo de caixa 2024'!M31+'FLUXO DE CAIXA 2025'!B8</f>
+      <c r="B27" s="97">
+        <f>'Fluxo de caixa 2024'!M31+'Fluxo de caixa 2025'!B8</f>
         <v>4417.17</v>
       </c>
-      <c r="C27" s="95">
+      <c r="C27" s="97">
         <f>C8+B31</f>
         <v>4383.1</v>
       </c>
-      <c r="D27" s="95">
+      <c r="D27" s="97">
         <v>0.0</v>
       </c>
-      <c r="E27" s="95">
+      <c r="E27" s="97">
         <f>E8</f>
         <v>600</v>
       </c>
-      <c r="F27" s="95">
+      <c r="F27" s="97">
         <f>F8+E31</f>
         <v>4130.74</v>
       </c>
-      <c r="G27" s="95">
+      <c r="G27" s="97">
         <f>F31+G8</f>
         <v>3796.89</v>
       </c>
-      <c r="H27" s="95">
+      <c r="H27" s="97">
         <f>G31+H9</f>
         <v>3911.51</v>
       </c>
-      <c r="I27" s="95">
+      <c r="I27" s="97">
         <f>I8+H31</f>
         <v>4025.2</v>
       </c>
-      <c r="J27" s="95">
-        <f t="shared" ref="J27:M27" si="10">I31+J8</f>
-        <v>4507.52</v>
-      </c>
-      <c r="K27" s="95">
-        <f t="shared" si="10"/>
-        <v>4068.8</v>
-      </c>
-      <c r="L27" s="95">
-        <f t="shared" si="10"/>
-        <v>3918.8</v>
-      </c>
-      <c r="M27" s="95">
-        <f t="shared" si="10"/>
-        <v>3768.8</v>
+      <c r="J27" s="97">
+        <f t="shared" ref="J27:M27" si="13">I31+J8</f>
+        <v>4512.59</v>
+      </c>
+      <c r="K27" s="97">
+        <f t="shared" si="13"/>
+        <v>4673.87</v>
+      </c>
+      <c r="L27" s="97">
+        <f t="shared" si="13"/>
+        <v>4822.496667</v>
+      </c>
+      <c r="M27" s="97">
+        <f t="shared" si="13"/>
+        <v>4971.123333</v>
       </c>
     </row>
     <row r="28" ht="12.75" customHeight="1">
       <c r="A28" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="95" t="str">
-        <f t="shared" ref="B28:E28" si="11">B10</f>
+      <c r="B28" s="97" t="str">
+        <f t="shared" ref="B28:E28" si="14">B10</f>
         <v/>
       </c>
-      <c r="C28" s="95" t="str">
-        <f t="shared" si="11"/>
+      <c r="C28" s="97" t="str">
+        <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="D28" s="95" t="str">
-        <f t="shared" si="11"/>
+      <c r="D28" s="97" t="str">
+        <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="E28" s="95" t="str">
-        <f t="shared" si="11"/>
+      <c r="E28" s="97" t="str">
+        <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="F28" s="95">
+      <c r="F28" s="97">
         <f>F13</f>
         <v>0</v>
       </c>
-      <c r="G28" s="95">
+      <c r="G28" s="97">
         <v>0.0</v>
       </c>
-      <c r="H28" s="95" t="str">
+      <c r="H28" s="97" t="str">
         <f>H10</f>
         <v/>
       </c>
-      <c r="I28" s="95">
+      <c r="I28" s="97">
         <f>I13</f>
         <v>0</v>
       </c>
-      <c r="J28" s="95">
-        <f t="shared" ref="J28:M28" si="12">J10</f>
-        <v>418.99</v>
-      </c>
-      <c r="K28" s="95">
-        <f t="shared" si="12"/>
+      <c r="J28" s="97">
+        <f t="shared" ref="J28:M28" si="15">J10</f>
+        <v>424.06</v>
+      </c>
+      <c r="K28" s="97">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="L28" s="95">
-        <f t="shared" si="12"/>
+      <c r="L28" s="97">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="M28" s="95">
-        <f t="shared" si="12"/>
+      <c r="M28" s="97">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -5873,105 +5888,105 @@
       <c r="A29" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="95">
-        <f t="shared" ref="B29:M29" si="13">B16</f>
+      <c r="B29" s="97">
+        <f t="shared" ref="B29:M29" si="16">B16</f>
         <v>324.07</v>
       </c>
-      <c r="C29" s="95">
-        <f t="shared" si="13"/>
+      <c r="C29" s="97">
+        <f t="shared" si="16"/>
         <v>334.17</v>
       </c>
-      <c r="D29" s="95">
-        <f t="shared" si="13"/>
+      <c r="D29" s="97">
+        <f t="shared" si="16"/>
         <v>334.82</v>
       </c>
-      <c r="E29" s="95">
-        <f t="shared" si="13"/>
+      <c r="E29" s="97">
+        <f t="shared" si="16"/>
         <v>233.37</v>
       </c>
-      <c r="F29" s="95">
-        <f t="shared" si="13"/>
+      <c r="F29" s="97">
+        <f t="shared" si="16"/>
         <v>333.85</v>
       </c>
-      <c r="G29" s="95">
-        <f t="shared" si="13"/>
+      <c r="G29" s="97">
+        <f t="shared" si="16"/>
         <v>335.38</v>
       </c>
-      <c r="H29" s="95">
-        <f t="shared" si="13"/>
+      <c r="H29" s="97">
+        <f t="shared" si="16"/>
         <v>336.31</v>
       </c>
-      <c r="I29" s="95">
-        <f t="shared" si="13"/>
+      <c r="I29" s="97">
+        <f t="shared" si="16"/>
         <v>236.67</v>
       </c>
-      <c r="J29" s="95">
-        <f t="shared" si="13"/>
+      <c r="J29" s="97">
+        <f t="shared" si="16"/>
         <v>243.72</v>
       </c>
-      <c r="K29" s="95">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="L29" s="95">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="M29" s="95">
-        <f t="shared" si="13"/>
-        <v>0</v>
+      <c r="K29" s="97">
+        <f t="shared" si="16"/>
+        <v>301.3733333</v>
+      </c>
+      <c r="L29" s="97">
+        <f t="shared" si="16"/>
+        <v>301.3733333</v>
+      </c>
+      <c r="M29" s="97">
+        <f t="shared" si="16"/>
+        <v>301.3733333</v>
       </c>
     </row>
     <row r="30" ht="12.75" customHeight="1">
       <c r="A30" s="87" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="95">
-        <f t="shared" ref="B30:M30" si="14">B21</f>
+      <c r="B30" s="97">
+        <f t="shared" ref="B30:M30" si="17">B21</f>
         <v>310</v>
       </c>
-      <c r="C30" s="95">
-        <f t="shared" si="14"/>
+      <c r="C30" s="97">
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="D30" s="95">
-        <f t="shared" si="14"/>
+      <c r="D30" s="97">
+        <f t="shared" si="17"/>
         <v>1000</v>
       </c>
-      <c r="E30" s="95">
-        <f t="shared" si="14"/>
+      <c r="E30" s="97">
+        <f t="shared" si="17"/>
         <v>150</v>
       </c>
-      <c r="F30" s="95">
-        <f t="shared" si="14"/>
+      <c r="F30" s="97">
+        <f t="shared" si="17"/>
         <v>600</v>
       </c>
-      <c r="G30" s="95">
-        <f t="shared" si="14"/>
+      <c r="G30" s="97">
+        <f t="shared" si="17"/>
         <v>150</v>
       </c>
-      <c r="H30" s="95">
-        <f t="shared" si="14"/>
+      <c r="H30" s="97">
+        <f t="shared" si="17"/>
         <v>150</v>
       </c>
-      <c r="I30" s="95">
-        <f t="shared" si="14"/>
+      <c r="I30" s="97">
+        <f t="shared" si="17"/>
         <v>150</v>
       </c>
-      <c r="J30" s="95">
-        <f t="shared" si="14"/>
+      <c r="J30" s="97">
+        <f t="shared" si="17"/>
         <v>195</v>
       </c>
-      <c r="K30" s="95">
-        <f t="shared" si="14"/>
+      <c r="K30" s="97">
+        <f t="shared" si="17"/>
         <v>150</v>
       </c>
-      <c r="L30" s="95">
-        <f t="shared" si="14"/>
+      <c r="L30" s="97">
+        <f t="shared" si="17"/>
         <v>150</v>
       </c>
-      <c r="M30" s="95">
-        <f t="shared" si="14"/>
+      <c r="M30" s="97">
+        <f t="shared" si="17"/>
         <v>150</v>
       </c>
     </row>
@@ -5979,90 +5994,98 @@
       <c r="A31" s="87" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="100">
+      <c r="B31" s="102">
         <f>B27-B29-B30</f>
         <v>3783.1</v>
       </c>
-      <c r="C31" s="100">
+      <c r="C31" s="102">
         <f>C27+C28-C29-C30</f>
         <v>4048.93</v>
       </c>
-      <c r="D31" s="100">
-        <f t="shared" ref="D31:E31" si="15">C31+D8-D16-D21</f>
+      <c r="D31" s="102">
+        <f t="shared" ref="D31:E31" si="18">C31+D8-D16-D21</f>
         <v>3314.11</v>
       </c>
-      <c r="E31" s="95">
-        <f t="shared" si="15"/>
+      <c r="E31" s="97">
+        <f t="shared" si="18"/>
         <v>3530.74</v>
       </c>
-      <c r="F31" s="95">
+      <c r="F31" s="97">
         <f>F27+F28-F29-F30</f>
         <v>3196.89</v>
       </c>
-      <c r="G31" s="95">
+      <c r="G31" s="97">
         <f>G27-G29-G30</f>
         <v>3311.51</v>
       </c>
-      <c r="H31" s="95">
-        <f t="shared" ref="H31:I31" si="16">H27+H28-H29-H30</f>
+      <c r="H31" s="97">
+        <f t="shared" ref="H31:I31" si="19">H27+H28-H29-H30</f>
         <v>3425.2</v>
       </c>
-      <c r="I31" s="95">
-        <f t="shared" si="16"/>
+      <c r="I31" s="97">
+        <f t="shared" si="19"/>
         <v>3638.53</v>
       </c>
-      <c r="J31" s="95">
+      <c r="J31" s="97">
         <f>J27-J29-J30</f>
-        <v>4068.8</v>
-      </c>
-      <c r="K31" s="95">
-        <f t="shared" ref="K31:M31" si="17">K27+K28-K29-K30</f>
-        <v>3918.8</v>
-      </c>
-      <c r="L31" s="95">
-        <f t="shared" si="17"/>
-        <v>3768.8</v>
-      </c>
-      <c r="M31" s="95">
-        <f t="shared" si="17"/>
-        <v>3618.8</v>
+        <v>4073.87</v>
+      </c>
+      <c r="K31" s="97">
+        <f t="shared" ref="K31:M31" si="20">K27+K28-K29-K30</f>
+        <v>4222.496667</v>
+      </c>
+      <c r="L31" s="97">
+        <f t="shared" si="20"/>
+        <v>4371.123333</v>
+      </c>
+      <c r="M31" s="97">
+        <f t="shared" si="20"/>
+        <v>4519.75</v>
       </c>
     </row>
     <row r="32" ht="12.75" customHeight="1"/>
     <row r="33" ht="12.75" customHeight="1">
-      <c r="A33" s="101" t="s">
+      <c r="A33" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="102">
+      <c r="D33" s="104">
         <v>-3000.0</v>
       </c>
-      <c r="E33" s="103">
+      <c r="E33" s="105">
         <f>D33+E24</f>
         <v>-2850</v>
       </c>
-      <c r="F33" s="103">
-        <f t="shared" ref="F33:G33" si="18">SUM(E33+F24)</f>
+      <c r="F33" s="105">
+        <f t="shared" ref="F33:G33" si="21">SUM(E33+F24)</f>
         <v>-2700</v>
       </c>
-      <c r="G33" s="104">
-        <f t="shared" si="18"/>
+      <c r="G33" s="106">
+        <f t="shared" si="21"/>
         <v>-2550</v>
       </c>
-      <c r="H33" s="103">
+      <c r="H33" s="105">
         <f>SUM(G33+H21)</f>
         <v>-2400</v>
       </c>
-      <c r="I33" s="103">
-        <f t="shared" ref="I33:K33" si="19">H33+150</f>
+      <c r="I33" s="105">
+        <f t="shared" ref="I33:M33" si="22">H33+150</f>
         <v>-2250</v>
       </c>
-      <c r="J33" s="103">
-        <f t="shared" si="19"/>
+      <c r="J33" s="105">
+        <f t="shared" si="22"/>
         <v>-2100</v>
       </c>
-      <c r="K33" s="103">
-        <f t="shared" si="19"/>
+      <c r="K33" s="105">
+        <f t="shared" si="22"/>
         <v>-1950</v>
+      </c>
+      <c r="L33" s="105">
+        <f t="shared" si="22"/>
+        <v>-1800</v>
+      </c>
+      <c r="M33" s="105">
+        <f t="shared" si="22"/>
+        <v>-1650</v>
       </c>
     </row>
     <row r="34" ht="12.75" customHeight="1"/>
@@ -7077,3941 +7100,3943 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="107" t="s">
         <v>44</v>
       </c>
-      <c r="N1" s="106"/>
+      <c r="N1" s="108"/>
     </row>
     <row r="2" ht="21.0" customHeight="1">
-      <c r="A2" s="105" t="s">
+      <c r="A2" s="107" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="107">
+      <c r="B2" s="109">
         <v>4.0</v>
       </c>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="108"/>
-      <c r="G2" s="108"/>
-      <c r="H2" s="108"/>
-      <c r="I2" s="108"/>
-      <c r="J2" s="108"/>
-      <c r="K2" s="108"/>
-      <c r="L2" s="108"/>
-      <c r="M2" s="108"/>
-      <c r="N2" s="106"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="110"/>
+      <c r="F2" s="110"/>
+      <c r="G2" s="110"/>
+      <c r="H2" s="110"/>
+      <c r="I2" s="110"/>
+      <c r="J2" s="110"/>
+      <c r="K2" s="110"/>
+      <c r="L2" s="110"/>
+      <c r="M2" s="110"/>
+      <c r="N2" s="108"/>
     </row>
     <row r="3" ht="15.0" customHeight="1">
-      <c r="A3" s="108"/>
-      <c r="B3" s="109"/>
-      <c r="C3" s="109"/>
-      <c r="D3" s="109"/>
-      <c r="E3" s="109"/>
-      <c r="F3" s="109"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="109"/>
-      <c r="I3" s="109"/>
-      <c r="J3" s="109"/>
-      <c r="K3" s="109"/>
-      <c r="L3" s="109"/>
-      <c r="M3" s="109"/>
-      <c r="N3" s="109"/>
-      <c r="O3" s="109"/>
-      <c r="P3" s="109"/>
-      <c r="Q3" s="109"/>
-      <c r="R3" s="109"/>
-      <c r="S3" s="109"/>
-      <c r="T3" s="109"/>
-      <c r="U3" s="109"/>
-      <c r="V3" s="109"/>
-      <c r="W3" s="109"/>
-      <c r="X3" s="109"/>
-      <c r="Y3" s="109"/>
-      <c r="Z3" s="109"/>
+      <c r="A3" s="110"/>
+      <c r="B3" s="111"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="111"/>
+      <c r="F3" s="111"/>
+      <c r="G3" s="111"/>
+      <c r="H3" s="111"/>
+      <c r="I3" s="111"/>
+      <c r="J3" s="111"/>
+      <c r="K3" s="111"/>
+      <c r="L3" s="111"/>
+      <c r="M3" s="111"/>
+      <c r="N3" s="111"/>
+      <c r="O3" s="111"/>
+      <c r="P3" s="111"/>
+      <c r="Q3" s="111"/>
+      <c r="R3" s="111"/>
+      <c r="S3" s="111"/>
+      <c r="T3" s="111"/>
+      <c r="U3" s="111"/>
+      <c r="V3" s="111"/>
+      <c r="W3" s="111"/>
+      <c r="X3" s="111"/>
+      <c r="Y3" s="111"/>
+      <c r="Z3" s="111"/>
     </row>
     <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="105" t="s">
+      <c r="A4" s="107" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="110" t="str">
+      <c r="B4" s="112" t="str">
         <f>CONCATENATE("Janeiro/",'Fluxo de caixa 2024'!$H$2)</f>
         <v>Janeiro/2024</v>
       </c>
-      <c r="C4" s="110" t="str">
+      <c r="C4" s="112" t="str">
         <f>CONCATENATE("Fevereiro/",'Fluxo de caixa 2024'!$H$2)</f>
         <v>Fevereiro/2024</v>
       </c>
-      <c r="D4" s="110" t="str">
+      <c r="D4" s="112" t="str">
         <f>CONCATENATE("Março/",'Fluxo de caixa 2024'!$H$2)</f>
         <v>Março/2024</v>
       </c>
-      <c r="E4" s="110" t="str">
+      <c r="E4" s="112" t="str">
         <f>CONCATENATE("Abril/",'Fluxo de caixa 2024'!$H$2)</f>
         <v>Abril/2024</v>
       </c>
-      <c r="F4" s="110" t="str">
+      <c r="F4" s="112" t="str">
         <f>CONCATENATE("Maio/",'Fluxo de caixa 2024'!$H$2)</f>
         <v>Maio/2024</v>
       </c>
-      <c r="G4" s="110" t="str">
+      <c r="G4" s="112" t="str">
         <f>CONCATENATE("Junho/",'Fluxo de caixa 2024'!$H$2)</f>
         <v>Junho/2024</v>
       </c>
-      <c r="H4" s="110" t="str">
+      <c r="H4" s="112" t="str">
         <f>CONCATENATE("Julho/",'Fluxo de caixa 2024'!$H$2)</f>
         <v>Julho/2024</v>
       </c>
-      <c r="I4" s="110" t="str">
+      <c r="I4" s="112" t="str">
         <f>CONCATENATE("Agosto/",'Fluxo de caixa 2024'!$H$2)</f>
         <v>Agosto/2024</v>
       </c>
-      <c r="J4" s="110" t="str">
+      <c r="J4" s="112" t="str">
         <f>CONCATENATE("Setembro/",'Fluxo de caixa 2024'!$H$2)</f>
         <v>Setembro/2024</v>
       </c>
-      <c r="K4" s="110" t="str">
+      <c r="K4" s="112" t="str">
         <f>CONCATENATE("Outubro/",'Fluxo de caixa 2024'!$H$2)</f>
         <v>Outubro/2024</v>
       </c>
-      <c r="L4" s="110" t="str">
+      <c r="L4" s="112" t="str">
         <f>CONCATENATE("Novembro/",'Fluxo de caixa 2024'!$H$2)</f>
         <v>Novembro/2024</v>
       </c>
-      <c r="M4" s="110" t="str">
+      <c r="M4" s="112" t="str">
         <f>CONCATENATE("Dezembro/",'Fluxo de caixa 2024'!$H$2)</f>
         <v>Dezembro/2024</v>
       </c>
-      <c r="N4" s="111">
+      <c r="N4" s="113">
         <v>45658.0</v>
       </c>
-      <c r="O4" s="111">
+      <c r="O4" s="113">
         <v>45689.0</v>
       </c>
-      <c r="P4" s="111">
+      <c r="P4" s="113">
         <v>45717.0</v>
       </c>
-      <c r="Q4" s="111">
+      <c r="Q4" s="113">
         <v>45748.0</v>
       </c>
-      <c r="R4" s="111">
+      <c r="R4" s="113">
         <v>45778.0</v>
       </c>
-      <c r="S4" s="111">
+      <c r="S4" s="113">
         <v>45809.0</v>
       </c>
-      <c r="T4" s="111">
+      <c r="T4" s="113">
         <v>45839.0</v>
       </c>
-      <c r="U4" s="111">
+      <c r="U4" s="113">
         <v>45870.0</v>
       </c>
-      <c r="V4" s="111">
+      <c r="V4" s="113">
         <v>45901.0</v>
       </c>
-      <c r="W4" s="111">
+      <c r="W4" s="113">
         <v>45931.0</v>
       </c>
-      <c r="X4" s="111">
+      <c r="X4" s="113">
         <v>45962.0</v>
       </c>
-      <c r="Y4" s="111">
+      <c r="Y4" s="113">
         <v>45992.0</v>
       </c>
-      <c r="Z4" s="111">
+      <c r="Z4" s="113">
         <v>46023.0</v>
       </c>
     </row>
     <row r="5" ht="19.5" customHeight="1">
-      <c r="A5" s="108">
+      <c r="A5" s="110">
         <v>1.0</v>
       </c>
-      <c r="B5" s="112">
+      <c r="B5" s="114">
         <v>0.0</v>
       </c>
-      <c r="C5" s="112">
+      <c r="C5" s="114">
         <v>150.0</v>
       </c>
-      <c r="D5" s="112">
+      <c r="D5" s="114">
         <v>150.0</v>
       </c>
-      <c r="E5" s="112">
+      <c r="E5" s="114">
         <v>150.0</v>
       </c>
-      <c r="F5" s="112">
+      <c r="F5" s="114">
         <v>150.0</v>
       </c>
-      <c r="G5" s="112">
+      <c r="G5" s="114">
         <v>150.0</v>
       </c>
-      <c r="H5" s="112">
+      <c r="H5" s="114">
         <v>150.0</v>
       </c>
-      <c r="I5" s="112">
+      <c r="I5" s="114">
         <v>150.0</v>
       </c>
-      <c r="J5" s="112">
+      <c r="J5" s="114">
         <v>150.0</v>
       </c>
-      <c r="K5" s="112">
+      <c r="K5" s="114">
         <v>150.0</v>
       </c>
-      <c r="L5" s="112">
+      <c r="L5" s="114">
         <v>150.0</v>
       </c>
-      <c r="M5" s="112">
+      <c r="M5" s="114">
         <v>150.0</v>
       </c>
-      <c r="N5" s="113">
+      <c r="N5" s="115">
         <v>150.0</v>
       </c>
-      <c r="O5" s="114">
+      <c r="O5" s="116">
         <v>150.0</v>
       </c>
-      <c r="P5" s="115">
+      <c r="P5" s="117">
         <v>150.0</v>
       </c>
-      <c r="Q5" s="115">
+      <c r="Q5" s="117">
         <v>150.0</v>
       </c>
-      <c r="R5" s="115">
+      <c r="R5" s="117">
         <v>150.0</v>
       </c>
-      <c r="S5" s="115">
+      <c r="S5" s="117">
         <v>150.0</v>
       </c>
-      <c r="T5" s="115">
+      <c r="T5" s="117">
         <v>150.0</v>
       </c>
-      <c r="U5" s="115">
+      <c r="U5" s="117">
         <v>150.0</v>
       </c>
-      <c r="V5" s="116">
+      <c r="V5" s="118">
         <v>150.0</v>
       </c>
-      <c r="W5" s="117"/>
-      <c r="X5" s="117"/>
-      <c r="Y5" s="117"/>
-      <c r="Z5" s="117"/>
+      <c r="W5" s="119"/>
+      <c r="X5" s="119"/>
+      <c r="Y5" s="119"/>
+      <c r="Z5" s="119"/>
     </row>
     <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="108">
+      <c r="A6" s="110">
         <v>2.0</v>
       </c>
-      <c r="B6" s="112">
+      <c r="B6" s="114">
         <v>0.0</v>
       </c>
-      <c r="C6" s="112">
+      <c r="C6" s="114">
         <v>150.0</v>
       </c>
-      <c r="D6" s="112">
+      <c r="D6" s="114">
         <v>150.0</v>
       </c>
-      <c r="E6" s="112">
+      <c r="E6" s="114">
         <v>150.0</v>
       </c>
-      <c r="F6" s="112">
+      <c r="F6" s="114">
         <v>150.0</v>
       </c>
-      <c r="G6" s="112">
+      <c r="G6" s="114">
         <v>150.0</v>
       </c>
-      <c r="H6" s="112">
+      <c r="H6" s="114">
         <v>150.0</v>
       </c>
-      <c r="I6" s="112">
+      <c r="I6" s="114">
         <v>150.0</v>
       </c>
-      <c r="J6" s="112">
+      <c r="J6" s="114">
         <v>150.0</v>
       </c>
-      <c r="K6" s="112">
+      <c r="K6" s="114">
         <v>150.0</v>
       </c>
-      <c r="L6" s="112">
+      <c r="L6" s="114">
         <v>150.0</v>
       </c>
-      <c r="M6" s="112">
+      <c r="M6" s="114">
         <v>150.0</v>
       </c>
-      <c r="N6" s="113">
+      <c r="N6" s="115">
         <v>150.0</v>
       </c>
-      <c r="O6" s="114">
+      <c r="O6" s="116">
         <v>150.0</v>
       </c>
-      <c r="P6" s="115">
+      <c r="P6" s="117">
         <v>150.0</v>
       </c>
-      <c r="Q6" s="115">
+      <c r="Q6" s="117">
         <v>150.0</v>
       </c>
-      <c r="R6" s="115">
+      <c r="R6" s="117">
         <v>150.0</v>
       </c>
-      <c r="S6" s="115">
+      <c r="S6" s="117">
         <v>150.0</v>
       </c>
-      <c r="T6" s="115">
+      <c r="T6" s="117">
         <v>150.0</v>
       </c>
-      <c r="U6" s="115">
+      <c r="U6" s="117">
         <v>150.0</v>
       </c>
-      <c r="V6" s="117"/>
-      <c r="W6" s="117"/>
-      <c r="X6" s="117"/>
-      <c r="Y6" s="117"/>
-      <c r="Z6" s="117"/>
+      <c r="V6" s="120">
+        <v>150.0</v>
+      </c>
+      <c r="W6" s="119"/>
+      <c r="X6" s="119"/>
+      <c r="Y6" s="119"/>
+      <c r="Z6" s="119"/>
     </row>
     <row r="7" ht="19.5" customHeight="1">
-      <c r="A7" s="108">
+      <c r="A7" s="110">
         <v>3.0</v>
       </c>
-      <c r="B7" s="112">
+      <c r="B7" s="114">
         <v>0.0</v>
       </c>
-      <c r="C7" s="112">
+      <c r="C7" s="114">
         <v>150.0</v>
       </c>
-      <c r="D7" s="112">
+      <c r="D7" s="114">
         <v>150.0</v>
       </c>
-      <c r="E7" s="112">
+      <c r="E7" s="114">
         <v>150.0</v>
       </c>
-      <c r="F7" s="112">
+      <c r="F7" s="114">
         <v>150.0</v>
       </c>
-      <c r="G7" s="112">
+      <c r="G7" s="114">
         <v>150.0</v>
       </c>
-      <c r="H7" s="112">
+      <c r="H7" s="114">
         <v>150.0</v>
       </c>
-      <c r="I7" s="112">
+      <c r="I7" s="114">
         <v>150.0</v>
       </c>
-      <c r="J7" s="112">
+      <c r="J7" s="114">
         <v>150.0</v>
       </c>
-      <c r="K7" s="112">
+      <c r="K7" s="114">
         <v>150.0</v>
       </c>
-      <c r="L7" s="112">
+      <c r="L7" s="114">
         <v>150.0</v>
       </c>
-      <c r="M7" s="112">
+      <c r="M7" s="114">
         <v>150.0</v>
       </c>
-      <c r="N7" s="113">
+      <c r="N7" s="115">
         <v>150.0</v>
       </c>
-      <c r="O7" s="118">
+      <c r="O7" s="121">
         <v>150.0</v>
       </c>
-      <c r="P7" s="115">
+      <c r="P7" s="117">
         <v>150.0</v>
       </c>
-      <c r="Q7" s="115">
+      <c r="Q7" s="117">
         <v>150.0</v>
       </c>
-      <c r="R7" s="115">
+      <c r="R7" s="117">
         <v>150.0</v>
       </c>
-      <c r="S7" s="115">
+      <c r="S7" s="117">
         <v>150.0</v>
       </c>
-      <c r="T7" s="115">
+      <c r="T7" s="117">
         <v>150.0</v>
       </c>
-      <c r="U7" s="115">
+      <c r="U7" s="117">
         <v>150.0</v>
       </c>
-      <c r="V7" s="116">
+      <c r="V7" s="120">
+        <v>0.0</v>
+      </c>
+      <c r="W7" s="119"/>
+      <c r="X7" s="119"/>
+      <c r="Y7" s="119"/>
+      <c r="Z7" s="119"/>
+    </row>
+    <row r="8" ht="19.5" customHeight="1">
+      <c r="A8" s="110">
+        <v>4.0</v>
+      </c>
+      <c r="B8" s="114">
+        <v>0.0</v>
+      </c>
+      <c r="C8" s="114">
         <v>150.0</v>
       </c>
-      <c r="W7" s="117"/>
-      <c r="X7" s="117"/>
-      <c r="Y7" s="117"/>
-      <c r="Z7" s="117"/>
-    </row>
-    <row r="8" ht="19.5" customHeight="1">
-      <c r="A8" s="108">
-        <v>4.0</v>
-      </c>
-      <c r="B8" s="112">
-        <v>0.0</v>
-      </c>
-      <c r="C8" s="112">
+      <c r="D8" s="114">
         <v>150.0</v>
       </c>
-      <c r="D8" s="112">
+      <c r="E8" s="114">
         <v>150.0</v>
       </c>
-      <c r="E8" s="112">
+      <c r="F8" s="114">
         <v>150.0</v>
       </c>
-      <c r="F8" s="112">
+      <c r="G8" s="114">
         <v>150.0</v>
       </c>
-      <c r="G8" s="112">
+      <c r="H8" s="114">
         <v>150.0</v>
       </c>
-      <c r="H8" s="112">
+      <c r="I8" s="114">
         <v>150.0</v>
       </c>
-      <c r="I8" s="112">
+      <c r="J8" s="114">
         <v>150.0</v>
       </c>
-      <c r="J8" s="112">
+      <c r="K8" s="114">
         <v>150.0</v>
       </c>
-      <c r="K8" s="112">
+      <c r="L8" s="114">
         <v>150.0</v>
       </c>
-      <c r="L8" s="112">
+      <c r="M8" s="114">
         <v>150.0</v>
       </c>
-      <c r="M8" s="112">
+      <c r="N8" s="115">
         <v>150.0</v>
       </c>
-      <c r="N8" s="113">
+      <c r="O8" s="116">
         <v>150.0</v>
       </c>
-      <c r="O8" s="114">
+      <c r="P8" s="117">
         <v>150.0</v>
       </c>
-      <c r="P8" s="115">
+      <c r="Q8" s="117">
         <v>150.0</v>
       </c>
-      <c r="Q8" s="115">
+      <c r="R8" s="117">
         <v>150.0</v>
       </c>
-      <c r="R8" s="115">
+      <c r="S8" s="117">
         <v>150.0</v>
       </c>
-      <c r="S8" s="115">
+      <c r="T8" s="117">
         <v>150.0</v>
       </c>
-      <c r="T8" s="115">
+      <c r="U8" s="117">
         <v>150.0</v>
       </c>
-      <c r="U8" s="115">
+      <c r="V8" s="118">
         <v>150.0</v>
       </c>
-      <c r="V8" s="116">
-        <v>150.0</v>
-      </c>
-      <c r="W8" s="117"/>
-      <c r="X8" s="117"/>
-      <c r="Y8" s="117"/>
-      <c r="Z8" s="117"/>
+      <c r="W8" s="119"/>
+      <c r="X8" s="119"/>
+      <c r="Y8" s="119"/>
+      <c r="Z8" s="119"/>
     </row>
     <row r="9" ht="15.0" customHeight="1">
-      <c r="A9" s="119"/>
-      <c r="B9" s="120"/>
-      <c r="C9" s="120"/>
-      <c r="D9" s="120"/>
-      <c r="E9" s="120"/>
-      <c r="F9" s="120"/>
-      <c r="G9" s="120"/>
-      <c r="H9" s="120"/>
-      <c r="I9" s="120"/>
-      <c r="J9" s="120"/>
-      <c r="K9" s="120"/>
-      <c r="L9" s="120"/>
-      <c r="M9" s="121"/>
-      <c r="N9" s="119"/>
-      <c r="O9" s="120"/>
-      <c r="P9" s="120"/>
-      <c r="Q9" s="120"/>
-      <c r="R9" s="120"/>
-      <c r="S9" s="120"/>
-      <c r="T9" s="120"/>
-      <c r="U9" s="120"/>
-      <c r="V9" s="120"/>
-      <c r="W9" s="120"/>
-      <c r="X9" s="120"/>
-      <c r="Y9" s="120"/>
-      <c r="Z9" s="121"/>
+      <c r="A9" s="122"/>
+      <c r="B9" s="123"/>
+      <c r="C9" s="123"/>
+      <c r="D9" s="123"/>
+      <c r="E9" s="123"/>
+      <c r="F9" s="123"/>
+      <c r="G9" s="123"/>
+      <c r="H9" s="123"/>
+      <c r="I9" s="123"/>
+      <c r="J9" s="123"/>
+      <c r="K9" s="123"/>
+      <c r="L9" s="123"/>
+      <c r="M9" s="124"/>
+      <c r="N9" s="122"/>
+      <c r="O9" s="123"/>
+      <c r="P9" s="123"/>
+      <c r="Q9" s="123"/>
+      <c r="R9" s="123"/>
+      <c r="S9" s="123"/>
+      <c r="T9" s="123"/>
+      <c r="U9" s="123"/>
+      <c r="V9" s="123"/>
+      <c r="W9" s="123"/>
+      <c r="X9" s="123"/>
+      <c r="Y9" s="123"/>
+      <c r="Z9" s="124"/>
     </row>
     <row r="10" ht="15.0" customHeight="1">
-      <c r="A10" s="105" t="s">
+      <c r="A10" s="107" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="122">
+      <c r="B10" s="125">
         <f t="shared" ref="B10:Z10" si="1">SUM(B5:B8)</f>
         <v>0</v>
       </c>
-      <c r="C10" s="122">
+      <c r="C10" s="125">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="D10" s="122">
+      <c r="D10" s="125">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="E10" s="122">
+      <c r="E10" s="125">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="F10" s="122">
+      <c r="F10" s="125">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="G10" s="122">
+      <c r="G10" s="125">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="H10" s="122">
+      <c r="H10" s="125">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="I10" s="122">
+      <c r="I10" s="125">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="J10" s="122">
+      <c r="J10" s="125">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="K10" s="122">
+      <c r="K10" s="125">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="L10" s="122">
+      <c r="L10" s="125">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="M10" s="122">
+      <c r="M10" s="125">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="N10" s="122">
+      <c r="N10" s="125">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="O10" s="122">
+      <c r="O10" s="125">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="P10" s="122">
+      <c r="P10" s="125">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="Q10" s="122">
+      <c r="Q10" s="125">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="R10" s="122">
+      <c r="R10" s="125">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="S10" s="122">
+      <c r="S10" s="125">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="T10" s="122">
+      <c r="T10" s="125">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="U10" s="122">
+      <c r="U10" s="125">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="V10" s="122">
+      <c r="V10" s="125">
         <f t="shared" si="1"/>
         <v>450</v>
       </c>
-      <c r="W10" s="122">
+      <c r="W10" s="125">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="X10" s="122">
+      <c r="X10" s="125">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y10" s="122">
+      <c r="Y10" s="125">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Z10" s="122">
+      <c r="Z10" s="125">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="1">
-      <c r="A11" s="106"/>
-      <c r="B11" s="106"/>
-      <c r="C11" s="106"/>
-      <c r="D11" s="106"/>
-      <c r="E11" s="106"/>
-      <c r="F11" s="106"/>
-      <c r="G11" s="106"/>
-      <c r="H11" s="106"/>
-      <c r="I11" s="106"/>
-      <c r="J11" s="106"/>
-      <c r="K11" s="106"/>
-      <c r="L11" s="106"/>
-      <c r="M11" s="106"/>
-      <c r="N11" s="106"/>
+      <c r="A11" s="108"/>
+      <c r="B11" s="108"/>
+      <c r="C11" s="108"/>
+      <c r="D11" s="108"/>
+      <c r="E11" s="108"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="108"/>
+      <c r="H11" s="108"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="108"/>
+      <c r="K11" s="108"/>
+      <c r="L11" s="108"/>
+      <c r="M11" s="108"/>
+      <c r="N11" s="108"/>
     </row>
     <row r="12" ht="15.0" customHeight="1">
-      <c r="A12" s="106"/>
-      <c r="B12" s="106"/>
-      <c r="C12" s="106"/>
-      <c r="D12" s="106"/>
-      <c r="E12" s="106"/>
-      <c r="F12" s="106"/>
-      <c r="G12" s="106"/>
-      <c r="H12" s="106"/>
-      <c r="I12" s="106"/>
-      <c r="J12" s="106"/>
-      <c r="K12" s="106"/>
-      <c r="L12" s="106"/>
-      <c r="M12" s="106"/>
-      <c r="N12" s="106"/>
-      <c r="O12" s="123"/>
-      <c r="P12" s="123"/>
-      <c r="Q12" s="123"/>
-      <c r="R12" s="123"/>
-      <c r="S12" s="123"/>
-      <c r="T12" s="123"/>
-      <c r="U12" s="123"/>
-      <c r="V12" s="123"/>
-      <c r="W12" s="123"/>
-      <c r="X12" s="123"/>
-      <c r="Y12" s="123"/>
-      <c r="Z12" s="123"/>
+      <c r="A12" s="108"/>
+      <c r="B12" s="108"/>
+      <c r="C12" s="108"/>
+      <c r="D12" s="108"/>
+      <c r="E12" s="108"/>
+      <c r="F12" s="108"/>
+      <c r="G12" s="108"/>
+      <c r="H12" s="108"/>
+      <c r="I12" s="108"/>
+      <c r="J12" s="108"/>
+      <c r="K12" s="108"/>
+      <c r="L12" s="108"/>
+      <c r="M12" s="108"/>
+      <c r="N12" s="108"/>
+      <c r="O12" s="126"/>
+      <c r="P12" s="126"/>
+      <c r="Q12" s="126"/>
+      <c r="R12" s="126"/>
+      <c r="S12" s="126"/>
+      <c r="T12" s="126"/>
+      <c r="U12" s="126"/>
+      <c r="V12" s="126"/>
+      <c r="W12" s="126"/>
+      <c r="X12" s="126"/>
+      <c r="Y12" s="126"/>
+      <c r="Z12" s="126"/>
     </row>
     <row r="13" ht="15.0" customHeight="1">
-      <c r="A13" s="106"/>
-      <c r="B13" s="106"/>
-      <c r="C13" s="106"/>
-      <c r="D13" s="106"/>
-      <c r="E13" s="106"/>
-      <c r="F13" s="106"/>
-      <c r="G13" s="106"/>
-      <c r="H13" s="106"/>
-      <c r="I13" s="106"/>
-      <c r="J13" s="106"/>
-      <c r="K13" s="106"/>
-      <c r="L13" s="106"/>
-      <c r="M13" s="106"/>
-      <c r="N13" s="106"/>
+      <c r="A13" s="108"/>
+      <c r="B13" s="108"/>
+      <c r="C13" s="108"/>
+      <c r="D13" s="108"/>
+      <c r="E13" s="108"/>
+      <c r="F13" s="108"/>
+      <c r="G13" s="108"/>
+      <c r="H13" s="108"/>
+      <c r="I13" s="108"/>
+      <c r="J13" s="108"/>
+      <c r="K13" s="108"/>
+      <c r="L13" s="108"/>
+      <c r="M13" s="108"/>
+      <c r="N13" s="108"/>
     </row>
     <row r="14" ht="15.0" customHeight="1">
-      <c r="A14" s="106"/>
-      <c r="B14" s="106"/>
-      <c r="C14" s="106"/>
-      <c r="D14" s="106"/>
-      <c r="E14" s="106"/>
-      <c r="F14" s="106"/>
-      <c r="G14" s="106"/>
-      <c r="H14" s="106"/>
-      <c r="I14" s="106"/>
-      <c r="J14" s="106"/>
-      <c r="K14" s="106"/>
-      <c r="L14" s="106"/>
-      <c r="M14" s="106"/>
-      <c r="N14" s="106"/>
+      <c r="A14" s="108"/>
+      <c r="B14" s="108"/>
+      <c r="C14" s="108"/>
+      <c r="D14" s="108"/>
+      <c r="E14" s="108"/>
+      <c r="F14" s="108"/>
+      <c r="G14" s="108"/>
+      <c r="H14" s="108"/>
+      <c r="I14" s="108"/>
+      <c r="J14" s="108"/>
+      <c r="K14" s="108"/>
+      <c r="L14" s="108"/>
+      <c r="M14" s="108"/>
+      <c r="N14" s="108"/>
     </row>
     <row r="15" ht="15.0" customHeight="1">
-      <c r="A15" s="106"/>
-      <c r="B15" s="106"/>
-      <c r="C15" s="106"/>
-      <c r="D15" s="106"/>
-      <c r="E15" s="106"/>
-      <c r="F15" s="106"/>
-      <c r="G15" s="106"/>
-      <c r="H15" s="106"/>
-      <c r="I15" s="106"/>
-      <c r="J15" s="106"/>
-      <c r="K15" s="106"/>
-      <c r="L15" s="106"/>
-      <c r="M15" s="106"/>
-      <c r="N15" s="106"/>
+      <c r="A15" s="108"/>
+      <c r="B15" s="108"/>
+      <c r="C15" s="108"/>
+      <c r="D15" s="108"/>
+      <c r="E15" s="108"/>
+      <c r="F15" s="108"/>
+      <c r="G15" s="108"/>
+      <c r="H15" s="108"/>
+      <c r="I15" s="108"/>
+      <c r="J15" s="108"/>
+      <c r="K15" s="108"/>
+      <c r="L15" s="108"/>
+      <c r="M15" s="108"/>
+      <c r="N15" s="108"/>
     </row>
     <row r="16" ht="15.0" customHeight="1">
-      <c r="A16" s="106"/>
-      <c r="B16" s="106"/>
-      <c r="C16" s="106"/>
-      <c r="D16" s="106"/>
-      <c r="E16" s="106"/>
-      <c r="F16" s="106"/>
-      <c r="G16" s="106"/>
-      <c r="H16" s="106"/>
-      <c r="I16" s="106"/>
-      <c r="J16" s="106"/>
-      <c r="K16" s="106"/>
-      <c r="L16" s="106"/>
-      <c r="M16" s="106"/>
-      <c r="N16" s="106"/>
+      <c r="A16" s="108"/>
+      <c r="B16" s="108"/>
+      <c r="C16" s="108"/>
+      <c r="D16" s="108"/>
+      <c r="E16" s="108"/>
+      <c r="F16" s="108"/>
+      <c r="G16" s="108"/>
+      <c r="H16" s="108"/>
+      <c r="I16" s="108"/>
+      <c r="J16" s="108"/>
+      <c r="K16" s="108"/>
+      <c r="L16" s="108"/>
+      <c r="M16" s="108"/>
+      <c r="N16" s="108"/>
     </row>
     <row r="17" ht="15.0" customHeight="1">
-      <c r="A17" s="106"/>
-      <c r="B17" s="106"/>
-      <c r="C17" s="106"/>
-      <c r="D17" s="106"/>
-      <c r="E17" s="106"/>
-      <c r="F17" s="106"/>
-      <c r="G17" s="106"/>
-      <c r="H17" s="106"/>
-      <c r="I17" s="106"/>
-      <c r="J17" s="106"/>
-      <c r="K17" s="106"/>
-      <c r="L17" s="106"/>
-      <c r="M17" s="106"/>
-      <c r="N17" s="106"/>
+      <c r="A17" s="108"/>
+      <c r="B17" s="108"/>
+      <c r="C17" s="108"/>
+      <c r="D17" s="108"/>
+      <c r="E17" s="108"/>
+      <c r="F17" s="108"/>
+      <c r="G17" s="108"/>
+      <c r="H17" s="108"/>
+      <c r="I17" s="108"/>
+      <c r="J17" s="108"/>
+      <c r="K17" s="108"/>
+      <c r="L17" s="108"/>
+      <c r="M17" s="108"/>
+      <c r="N17" s="108"/>
     </row>
     <row r="18" ht="15.0" customHeight="1">
-      <c r="A18" s="106"/>
-      <c r="B18" s="106"/>
-      <c r="C18" s="106"/>
-      <c r="D18" s="106"/>
-      <c r="E18" s="106"/>
-      <c r="F18" s="106"/>
-      <c r="G18" s="106"/>
-      <c r="H18" s="106"/>
-      <c r="I18" s="106"/>
-      <c r="J18" s="106"/>
-      <c r="K18" s="106"/>
-      <c r="L18" s="106"/>
-      <c r="M18" s="106"/>
-      <c r="N18" s="106"/>
+      <c r="A18" s="108"/>
+      <c r="B18" s="108"/>
+      <c r="C18" s="108"/>
+      <c r="D18" s="108"/>
+      <c r="E18" s="108"/>
+      <c r="F18" s="108"/>
+      <c r="G18" s="108"/>
+      <c r="H18" s="108"/>
+      <c r="I18" s="108"/>
+      <c r="J18" s="108"/>
+      <c r="K18" s="108"/>
+      <c r="L18" s="108"/>
+      <c r="M18" s="108"/>
+      <c r="N18" s="108"/>
     </row>
     <row r="19" ht="15.0" customHeight="1">
-      <c r="A19" s="106"/>
-      <c r="B19" s="106"/>
-      <c r="C19" s="106"/>
-      <c r="D19" s="106"/>
-      <c r="E19" s="106"/>
-      <c r="F19" s="106"/>
-      <c r="G19" s="106"/>
-      <c r="H19" s="106"/>
-      <c r="I19" s="106"/>
-      <c r="J19" s="106"/>
-      <c r="K19" s="106"/>
-      <c r="L19" s="106"/>
-      <c r="M19" s="106"/>
-      <c r="N19" s="106"/>
+      <c r="A19" s="108"/>
+      <c r="B19" s="108"/>
+      <c r="C19" s="108"/>
+      <c r="D19" s="108"/>
+      <c r="E19" s="108"/>
+      <c r="F19" s="108"/>
+      <c r="G19" s="108"/>
+      <c r="H19" s="108"/>
+      <c r="I19" s="108"/>
+      <c r="J19" s="108"/>
+      <c r="K19" s="108"/>
+      <c r="L19" s="108"/>
+      <c r="M19" s="108"/>
+      <c r="N19" s="108"/>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="106"/>
-      <c r="B20" s="106"/>
-      <c r="C20" s="106"/>
-      <c r="D20" s="106"/>
-      <c r="E20" s="106"/>
-      <c r="F20" s="106"/>
-      <c r="G20" s="106"/>
-      <c r="H20" s="106"/>
-      <c r="I20" s="106"/>
-      <c r="J20" s="106"/>
-      <c r="K20" s="106"/>
-      <c r="L20" s="106"/>
-      <c r="M20" s="106"/>
-      <c r="N20" s="106"/>
+      <c r="A20" s="108"/>
+      <c r="B20" s="108"/>
+      <c r="C20" s="108"/>
+      <c r="D20" s="108"/>
+      <c r="E20" s="108"/>
+      <c r="F20" s="108"/>
+      <c r="G20" s="108"/>
+      <c r="H20" s="108"/>
+      <c r="I20" s="108"/>
+      <c r="J20" s="108"/>
+      <c r="K20" s="108"/>
+      <c r="L20" s="108"/>
+      <c r="M20" s="108"/>
+      <c r="N20" s="108"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="106"/>
-      <c r="B21" s="106"/>
-      <c r="C21" s="106"/>
-      <c r="D21" s="106"/>
-      <c r="E21" s="106"/>
-      <c r="F21" s="106"/>
-      <c r="G21" s="106"/>
-      <c r="H21" s="106"/>
-      <c r="I21" s="106"/>
-      <c r="J21" s="106"/>
-      <c r="K21" s="106"/>
-      <c r="L21" s="106"/>
-      <c r="M21" s="106"/>
-      <c r="N21" s="106"/>
+      <c r="A21" s="108"/>
+      <c r="B21" s="108"/>
+      <c r="C21" s="108"/>
+      <c r="D21" s="108"/>
+      <c r="E21" s="108"/>
+      <c r="F21" s="108"/>
+      <c r="G21" s="108"/>
+      <c r="H21" s="108"/>
+      <c r="I21" s="108"/>
+      <c r="J21" s="108"/>
+      <c r="K21" s="108"/>
+      <c r="L21" s="108"/>
+      <c r="M21" s="108"/>
+      <c r="N21" s="108"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="106"/>
-      <c r="B22" s="106"/>
-      <c r="C22" s="106"/>
-      <c r="D22" s="106"/>
-      <c r="E22" s="106"/>
-      <c r="F22" s="106"/>
-      <c r="G22" s="106"/>
-      <c r="H22" s="106"/>
-      <c r="I22" s="106"/>
-      <c r="J22" s="106"/>
-      <c r="K22" s="106"/>
-      <c r="L22" s="106"/>
-      <c r="M22" s="106"/>
-      <c r="N22" s="106"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="108"/>
+      <c r="D22" s="108"/>
+      <c r="E22" s="108"/>
+      <c r="F22" s="108"/>
+      <c r="G22" s="108"/>
+      <c r="H22" s="108"/>
+      <c r="I22" s="108"/>
+      <c r="J22" s="108"/>
+      <c r="K22" s="108"/>
+      <c r="L22" s="108"/>
+      <c r="M22" s="108"/>
+      <c r="N22" s="108"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="106"/>
-      <c r="B23" s="106"/>
-      <c r="C23" s="106"/>
-      <c r="D23" s="106"/>
-      <c r="E23" s="106"/>
-      <c r="F23" s="106"/>
-      <c r="G23" s="106"/>
-      <c r="H23" s="106"/>
-      <c r="I23" s="106"/>
-      <c r="J23" s="106"/>
-      <c r="K23" s="106"/>
-      <c r="L23" s="106"/>
-      <c r="M23" s="106"/>
-      <c r="N23" s="106"/>
+      <c r="A23" s="108"/>
+      <c r="B23" s="108"/>
+      <c r="C23" s="108"/>
+      <c r="D23" s="108"/>
+      <c r="E23" s="108"/>
+      <c r="F23" s="108"/>
+      <c r="G23" s="108"/>
+      <c r="H23" s="108"/>
+      <c r="I23" s="108"/>
+      <c r="J23" s="108"/>
+      <c r="K23" s="108"/>
+      <c r="L23" s="108"/>
+      <c r="M23" s="108"/>
+      <c r="N23" s="108"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="106"/>
-      <c r="B24" s="106"/>
-      <c r="C24" s="106"/>
-      <c r="D24" s="106"/>
-      <c r="E24" s="106"/>
-      <c r="F24" s="106"/>
-      <c r="G24" s="106"/>
-      <c r="H24" s="106"/>
-      <c r="I24" s="106"/>
-      <c r="J24" s="106"/>
-      <c r="K24" s="106"/>
-      <c r="L24" s="106"/>
-      <c r="M24" s="106"/>
-      <c r="N24" s="106"/>
+      <c r="A24" s="108"/>
+      <c r="B24" s="108"/>
+      <c r="C24" s="108"/>
+      <c r="D24" s="108"/>
+      <c r="E24" s="108"/>
+      <c r="F24" s="108"/>
+      <c r="G24" s="108"/>
+      <c r="H24" s="108"/>
+      <c r="I24" s="108"/>
+      <c r="J24" s="108"/>
+      <c r="K24" s="108"/>
+      <c r="L24" s="108"/>
+      <c r="M24" s="108"/>
+      <c r="N24" s="108"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="106"/>
-      <c r="B25" s="106"/>
-      <c r="C25" s="106"/>
-      <c r="D25" s="106"/>
-      <c r="E25" s="106"/>
-      <c r="F25" s="106"/>
-      <c r="G25" s="106"/>
-      <c r="H25" s="106"/>
-      <c r="I25" s="106"/>
-      <c r="J25" s="106"/>
-      <c r="K25" s="106"/>
-      <c r="L25" s="106"/>
-      <c r="M25" s="106"/>
-      <c r="N25" s="106"/>
+      <c r="A25" s="108"/>
+      <c r="B25" s="108"/>
+      <c r="C25" s="108"/>
+      <c r="D25" s="108"/>
+      <c r="E25" s="108"/>
+      <c r="F25" s="108"/>
+      <c r="G25" s="108"/>
+      <c r="H25" s="108"/>
+      <c r="I25" s="108"/>
+      <c r="J25" s="108"/>
+      <c r="K25" s="108"/>
+      <c r="L25" s="108"/>
+      <c r="M25" s="108"/>
+      <c r="N25" s="108"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="106"/>
-      <c r="B26" s="106"/>
-      <c r="C26" s="106"/>
-      <c r="D26" s="106"/>
-      <c r="E26" s="106"/>
-      <c r="F26" s="106"/>
-      <c r="G26" s="106"/>
-      <c r="H26" s="106"/>
-      <c r="I26" s="106"/>
-      <c r="J26" s="106"/>
-      <c r="K26" s="106"/>
-      <c r="L26" s="106"/>
-      <c r="M26" s="106"/>
-      <c r="N26" s="106"/>
+      <c r="A26" s="108"/>
+      <c r="B26" s="108"/>
+      <c r="C26" s="108"/>
+      <c r="D26" s="108"/>
+      <c r="E26" s="108"/>
+      <c r="F26" s="108"/>
+      <c r="G26" s="108"/>
+      <c r="H26" s="108"/>
+      <c r="I26" s="108"/>
+      <c r="J26" s="108"/>
+      <c r="K26" s="108"/>
+      <c r="L26" s="108"/>
+      <c r="M26" s="108"/>
+      <c r="N26" s="108"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="106"/>
-      <c r="B27" s="106"/>
-      <c r="C27" s="106"/>
-      <c r="D27" s="106"/>
-      <c r="E27" s="106"/>
-      <c r="F27" s="106"/>
-      <c r="G27" s="106"/>
-      <c r="H27" s="106"/>
-      <c r="I27" s="106"/>
-      <c r="J27" s="106"/>
-      <c r="K27" s="106"/>
-      <c r="L27" s="106"/>
-      <c r="M27" s="106"/>
-      <c r="N27" s="106"/>
+      <c r="A27" s="108"/>
+      <c r="B27" s="108"/>
+      <c r="C27" s="108"/>
+      <c r="D27" s="108"/>
+      <c r="E27" s="108"/>
+      <c r="F27" s="108"/>
+      <c r="G27" s="108"/>
+      <c r="H27" s="108"/>
+      <c r="I27" s="108"/>
+      <c r="J27" s="108"/>
+      <c r="K27" s="108"/>
+      <c r="L27" s="108"/>
+      <c r="M27" s="108"/>
+      <c r="N27" s="108"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="106"/>
-      <c r="B28" s="106"/>
-      <c r="C28" s="106"/>
-      <c r="D28" s="106"/>
-      <c r="E28" s="106"/>
-      <c r="F28" s="106"/>
-      <c r="G28" s="106"/>
-      <c r="H28" s="106"/>
-      <c r="I28" s="106"/>
-      <c r="J28" s="106"/>
-      <c r="K28" s="106"/>
-      <c r="L28" s="106"/>
-      <c r="M28" s="106"/>
-      <c r="N28" s="106"/>
+      <c r="A28" s="108"/>
+      <c r="B28" s="108"/>
+      <c r="C28" s="108"/>
+      <c r="D28" s="108"/>
+      <c r="E28" s="108"/>
+      <c r="F28" s="108"/>
+      <c r="G28" s="108"/>
+      <c r="H28" s="108"/>
+      <c r="I28" s="108"/>
+      <c r="J28" s="108"/>
+      <c r="K28" s="108"/>
+      <c r="L28" s="108"/>
+      <c r="M28" s="108"/>
+      <c r="N28" s="108"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="106"/>
-      <c r="B29" s="106"/>
-      <c r="C29" s="106"/>
-      <c r="D29" s="106"/>
-      <c r="E29" s="106"/>
-      <c r="F29" s="106"/>
-      <c r="G29" s="106"/>
-      <c r="H29" s="106"/>
-      <c r="I29" s="106"/>
-      <c r="J29" s="106"/>
-      <c r="K29" s="106"/>
-      <c r="L29" s="106"/>
-      <c r="M29" s="106"/>
-      <c r="N29" s="106"/>
+      <c r="A29" s="108"/>
+      <c r="B29" s="108"/>
+      <c r="C29" s="108"/>
+      <c r="D29" s="108"/>
+      <c r="E29" s="108"/>
+      <c r="F29" s="108"/>
+      <c r="G29" s="108"/>
+      <c r="H29" s="108"/>
+      <c r="I29" s="108"/>
+      <c r="J29" s="108"/>
+      <c r="K29" s="108"/>
+      <c r="L29" s="108"/>
+      <c r="M29" s="108"/>
+      <c r="N29" s="108"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="106"/>
-      <c r="B30" s="106"/>
-      <c r="C30" s="106"/>
-      <c r="D30" s="106"/>
-      <c r="E30" s="106"/>
-      <c r="F30" s="106"/>
-      <c r="G30" s="106"/>
-      <c r="H30" s="106"/>
-      <c r="I30" s="106"/>
-      <c r="J30" s="106"/>
-      <c r="K30" s="106"/>
-      <c r="L30" s="106"/>
-      <c r="M30" s="106"/>
-      <c r="N30" s="106"/>
+      <c r="A30" s="108"/>
+      <c r="B30" s="108"/>
+      <c r="C30" s="108"/>
+      <c r="D30" s="108"/>
+      <c r="E30" s="108"/>
+      <c r="F30" s="108"/>
+      <c r="G30" s="108"/>
+      <c r="H30" s="108"/>
+      <c r="I30" s="108"/>
+      <c r="J30" s="108"/>
+      <c r="K30" s="108"/>
+      <c r="L30" s="108"/>
+      <c r="M30" s="108"/>
+      <c r="N30" s="108"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="106"/>
-      <c r="B31" s="106"/>
-      <c r="C31" s="106"/>
-      <c r="D31" s="106"/>
-      <c r="E31" s="106"/>
-      <c r="F31" s="106"/>
-      <c r="G31" s="106"/>
-      <c r="H31" s="106"/>
-      <c r="I31" s="106"/>
-      <c r="J31" s="106"/>
-      <c r="K31" s="106"/>
-      <c r="L31" s="106"/>
-      <c r="M31" s="106"/>
-      <c r="N31" s="106"/>
+      <c r="A31" s="108"/>
+      <c r="B31" s="108"/>
+      <c r="C31" s="108"/>
+      <c r="D31" s="108"/>
+      <c r="E31" s="108"/>
+      <c r="F31" s="108"/>
+      <c r="G31" s="108"/>
+      <c r="H31" s="108"/>
+      <c r="I31" s="108"/>
+      <c r="J31" s="108"/>
+      <c r="K31" s="108"/>
+      <c r="L31" s="108"/>
+      <c r="M31" s="108"/>
+      <c r="N31" s="108"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="106"/>
-      <c r="B32" s="106"/>
-      <c r="C32" s="106"/>
-      <c r="D32" s="106"/>
-      <c r="E32" s="106"/>
-      <c r="F32" s="106"/>
-      <c r="G32" s="106"/>
-      <c r="H32" s="106"/>
-      <c r="I32" s="106"/>
-      <c r="J32" s="106"/>
-      <c r="K32" s="106"/>
-      <c r="L32" s="106"/>
-      <c r="M32" s="106"/>
-      <c r="N32" s="106"/>
+      <c r="A32" s="108"/>
+      <c r="B32" s="108"/>
+      <c r="C32" s="108"/>
+      <c r="D32" s="108"/>
+      <c r="E32" s="108"/>
+      <c r="F32" s="108"/>
+      <c r="G32" s="108"/>
+      <c r="H32" s="108"/>
+      <c r="I32" s="108"/>
+      <c r="J32" s="108"/>
+      <c r="K32" s="108"/>
+      <c r="L32" s="108"/>
+      <c r="M32" s="108"/>
+      <c r="N32" s="108"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="106"/>
-      <c r="B33" s="106"/>
-      <c r="C33" s="106"/>
-      <c r="D33" s="106"/>
-      <c r="E33" s="106"/>
-      <c r="F33" s="106"/>
-      <c r="G33" s="106"/>
-      <c r="H33" s="106"/>
-      <c r="I33" s="106"/>
-      <c r="J33" s="106"/>
-      <c r="K33" s="106"/>
-      <c r="L33" s="106"/>
-      <c r="M33" s="106"/>
-      <c r="N33" s="106"/>
+      <c r="A33" s="108"/>
+      <c r="B33" s="108"/>
+      <c r="C33" s="108"/>
+      <c r="D33" s="108"/>
+      <c r="E33" s="108"/>
+      <c r="F33" s="108"/>
+      <c r="G33" s="108"/>
+      <c r="H33" s="108"/>
+      <c r="I33" s="108"/>
+      <c r="J33" s="108"/>
+      <c r="K33" s="108"/>
+      <c r="L33" s="108"/>
+      <c r="M33" s="108"/>
+      <c r="N33" s="108"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="106"/>
-      <c r="B34" s="106"/>
-      <c r="C34" s="106"/>
-      <c r="D34" s="106"/>
-      <c r="E34" s="106"/>
-      <c r="F34" s="106"/>
-      <c r="G34" s="106"/>
-      <c r="H34" s="106"/>
-      <c r="I34" s="106"/>
-      <c r="J34" s="106"/>
-      <c r="K34" s="106"/>
-      <c r="L34" s="106"/>
-      <c r="M34" s="106"/>
-      <c r="N34" s="106"/>
+      <c r="A34" s="108"/>
+      <c r="B34" s="108"/>
+      <c r="C34" s="108"/>
+      <c r="D34" s="108"/>
+      <c r="E34" s="108"/>
+      <c r="F34" s="108"/>
+      <c r="G34" s="108"/>
+      <c r="H34" s="108"/>
+      <c r="I34" s="108"/>
+      <c r="J34" s="108"/>
+      <c r="K34" s="108"/>
+      <c r="L34" s="108"/>
+      <c r="M34" s="108"/>
+      <c r="N34" s="108"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="106"/>
-      <c r="B35" s="106"/>
-      <c r="C35" s="106"/>
-      <c r="D35" s="106"/>
-      <c r="E35" s="106"/>
-      <c r="F35" s="106"/>
-      <c r="G35" s="106"/>
-      <c r="H35" s="106"/>
-      <c r="I35" s="106"/>
-      <c r="J35" s="106"/>
-      <c r="K35" s="106"/>
-      <c r="L35" s="106"/>
-      <c r="M35" s="106"/>
-      <c r="N35" s="106"/>
+      <c r="A35" s="108"/>
+      <c r="B35" s="108"/>
+      <c r="C35" s="108"/>
+      <c r="D35" s="108"/>
+      <c r="E35" s="108"/>
+      <c r="F35" s="108"/>
+      <c r="G35" s="108"/>
+      <c r="H35" s="108"/>
+      <c r="I35" s="108"/>
+      <c r="J35" s="108"/>
+      <c r="K35" s="108"/>
+      <c r="L35" s="108"/>
+      <c r="M35" s="108"/>
+      <c r="N35" s="108"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="106"/>
-      <c r="B36" s="106"/>
-      <c r="C36" s="106"/>
-      <c r="D36" s="106"/>
-      <c r="E36" s="106"/>
-      <c r="F36" s="106"/>
-      <c r="G36" s="106"/>
-      <c r="H36" s="106"/>
-      <c r="I36" s="106"/>
-      <c r="J36" s="106"/>
-      <c r="K36" s="106"/>
-      <c r="L36" s="106"/>
-      <c r="M36" s="106"/>
-      <c r="N36" s="106"/>
+      <c r="A36" s="108"/>
+      <c r="B36" s="108"/>
+      <c r="C36" s="108"/>
+      <c r="D36" s="108"/>
+      <c r="E36" s="108"/>
+      <c r="F36" s="108"/>
+      <c r="G36" s="108"/>
+      <c r="H36" s="108"/>
+      <c r="I36" s="108"/>
+      <c r="J36" s="108"/>
+      <c r="K36" s="108"/>
+      <c r="L36" s="108"/>
+      <c r="M36" s="108"/>
+      <c r="N36" s="108"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="106"/>
-      <c r="B37" s="106"/>
-      <c r="C37" s="106"/>
-      <c r="D37" s="106"/>
-      <c r="E37" s="106"/>
-      <c r="F37" s="106"/>
-      <c r="G37" s="106"/>
-      <c r="H37" s="106"/>
-      <c r="I37" s="106"/>
-      <c r="J37" s="106"/>
-      <c r="K37" s="106"/>
-      <c r="L37" s="106"/>
-      <c r="M37" s="106"/>
-      <c r="N37" s="106"/>
+      <c r="A37" s="108"/>
+      <c r="B37" s="108"/>
+      <c r="C37" s="108"/>
+      <c r="D37" s="108"/>
+      <c r="E37" s="108"/>
+      <c r="F37" s="108"/>
+      <c r="G37" s="108"/>
+      <c r="H37" s="108"/>
+      <c r="I37" s="108"/>
+      <c r="J37" s="108"/>
+      <c r="K37" s="108"/>
+      <c r="L37" s="108"/>
+      <c r="M37" s="108"/>
+      <c r="N37" s="108"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="106"/>
-      <c r="B38" s="106"/>
-      <c r="C38" s="106"/>
-      <c r="D38" s="106"/>
-      <c r="E38" s="106"/>
-      <c r="F38" s="106"/>
-      <c r="G38" s="106"/>
-      <c r="H38" s="106"/>
-      <c r="I38" s="106"/>
-      <c r="J38" s="106"/>
-      <c r="K38" s="106"/>
-      <c r="L38" s="106"/>
-      <c r="M38" s="106"/>
-      <c r="N38" s="106"/>
+      <c r="A38" s="108"/>
+      <c r="B38" s="108"/>
+      <c r="C38" s="108"/>
+      <c r="D38" s="108"/>
+      <c r="E38" s="108"/>
+      <c r="F38" s="108"/>
+      <c r="G38" s="108"/>
+      <c r="H38" s="108"/>
+      <c r="I38" s="108"/>
+      <c r="J38" s="108"/>
+      <c r="K38" s="108"/>
+      <c r="L38" s="108"/>
+      <c r="M38" s="108"/>
+      <c r="N38" s="108"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="106"/>
-      <c r="B39" s="106"/>
-      <c r="C39" s="106"/>
-      <c r="D39" s="106"/>
-      <c r="E39" s="106"/>
-      <c r="F39" s="106"/>
-      <c r="G39" s="106"/>
-      <c r="H39" s="106"/>
-      <c r="I39" s="106"/>
-      <c r="J39" s="106"/>
-      <c r="K39" s="106"/>
-      <c r="L39" s="106"/>
-      <c r="M39" s="106"/>
-      <c r="N39" s="106"/>
+      <c r="A39" s="108"/>
+      <c r="B39" s="108"/>
+      <c r="C39" s="108"/>
+      <c r="D39" s="108"/>
+      <c r="E39" s="108"/>
+      <c r="F39" s="108"/>
+      <c r="G39" s="108"/>
+      <c r="H39" s="108"/>
+      <c r="I39" s="108"/>
+      <c r="J39" s="108"/>
+      <c r="K39" s="108"/>
+      <c r="L39" s="108"/>
+      <c r="M39" s="108"/>
+      <c r="N39" s="108"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="106"/>
-      <c r="B40" s="106"/>
-      <c r="C40" s="106"/>
-      <c r="D40" s="106"/>
-      <c r="E40" s="106"/>
-      <c r="F40" s="106"/>
-      <c r="G40" s="106"/>
-      <c r="H40" s="106"/>
-      <c r="I40" s="106"/>
-      <c r="J40" s="106"/>
-      <c r="K40" s="106"/>
-      <c r="L40" s="106"/>
-      <c r="M40" s="106"/>
-      <c r="N40" s="106"/>
+      <c r="A40" s="108"/>
+      <c r="B40" s="108"/>
+      <c r="C40" s="108"/>
+      <c r="D40" s="108"/>
+      <c r="E40" s="108"/>
+      <c r="F40" s="108"/>
+      <c r="G40" s="108"/>
+      <c r="H40" s="108"/>
+      <c r="I40" s="108"/>
+      <c r="J40" s="108"/>
+      <c r="K40" s="108"/>
+      <c r="L40" s="108"/>
+      <c r="M40" s="108"/>
+      <c r="N40" s="108"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="106"/>
-      <c r="B41" s="106"/>
-      <c r="C41" s="106"/>
-      <c r="D41" s="106"/>
-      <c r="E41" s="106"/>
-      <c r="F41" s="106"/>
-      <c r="G41" s="106"/>
-      <c r="H41" s="106"/>
-      <c r="I41" s="106"/>
-      <c r="J41" s="106"/>
-      <c r="K41" s="106"/>
-      <c r="L41" s="106"/>
-      <c r="M41" s="106"/>
-      <c r="N41" s="106"/>
+      <c r="A41" s="108"/>
+      <c r="B41" s="108"/>
+      <c r="C41" s="108"/>
+      <c r="D41" s="108"/>
+      <c r="E41" s="108"/>
+      <c r="F41" s="108"/>
+      <c r="G41" s="108"/>
+      <c r="H41" s="108"/>
+      <c r="I41" s="108"/>
+      <c r="J41" s="108"/>
+      <c r="K41" s="108"/>
+      <c r="L41" s="108"/>
+      <c r="M41" s="108"/>
+      <c r="N41" s="108"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="106"/>
-      <c r="B42" s="106"/>
-      <c r="C42" s="106"/>
-      <c r="D42" s="106"/>
-      <c r="E42" s="106"/>
-      <c r="F42" s="106"/>
-      <c r="G42" s="106"/>
-      <c r="H42" s="106"/>
-      <c r="I42" s="106"/>
-      <c r="J42" s="106"/>
-      <c r="K42" s="106"/>
-      <c r="L42" s="106"/>
-      <c r="M42" s="106"/>
-      <c r="N42" s="106"/>
+      <c r="A42" s="108"/>
+      <c r="B42" s="108"/>
+      <c r="C42" s="108"/>
+      <c r="D42" s="108"/>
+      <c r="E42" s="108"/>
+      <c r="F42" s="108"/>
+      <c r="G42" s="108"/>
+      <c r="H42" s="108"/>
+      <c r="I42" s="108"/>
+      <c r="J42" s="108"/>
+      <c r="K42" s="108"/>
+      <c r="L42" s="108"/>
+      <c r="M42" s="108"/>
+      <c r="N42" s="108"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="106"/>
-      <c r="B43" s="106"/>
-      <c r="C43" s="106"/>
-      <c r="D43" s="106"/>
-      <c r="E43" s="106"/>
-      <c r="F43" s="106"/>
-      <c r="G43" s="106"/>
-      <c r="H43" s="106"/>
-      <c r="I43" s="106"/>
-      <c r="J43" s="106"/>
-      <c r="K43" s="106"/>
-      <c r="L43" s="106"/>
-      <c r="M43" s="106"/>
-      <c r="N43" s="106"/>
+      <c r="A43" s="108"/>
+      <c r="B43" s="108"/>
+      <c r="C43" s="108"/>
+      <c r="D43" s="108"/>
+      <c r="E43" s="108"/>
+      <c r="F43" s="108"/>
+      <c r="G43" s="108"/>
+      <c r="H43" s="108"/>
+      <c r="I43" s="108"/>
+      <c r="J43" s="108"/>
+      <c r="K43" s="108"/>
+      <c r="L43" s="108"/>
+      <c r="M43" s="108"/>
+      <c r="N43" s="108"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="106"/>
-      <c r="B44" s="106"/>
-      <c r="C44" s="106"/>
-      <c r="D44" s="106"/>
-      <c r="E44" s="106"/>
-      <c r="F44" s="106"/>
-      <c r="G44" s="106"/>
-      <c r="H44" s="106"/>
-      <c r="I44" s="106"/>
-      <c r="J44" s="106"/>
-      <c r="K44" s="106"/>
-      <c r="L44" s="106"/>
-      <c r="M44" s="106"/>
-      <c r="N44" s="106"/>
+      <c r="A44" s="108"/>
+      <c r="B44" s="108"/>
+      <c r="C44" s="108"/>
+      <c r="D44" s="108"/>
+      <c r="E44" s="108"/>
+      <c r="F44" s="108"/>
+      <c r="G44" s="108"/>
+      <c r="H44" s="108"/>
+      <c r="I44" s="108"/>
+      <c r="J44" s="108"/>
+      <c r="K44" s="108"/>
+      <c r="L44" s="108"/>
+      <c r="M44" s="108"/>
+      <c r="N44" s="108"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="106"/>
-      <c r="B45" s="106"/>
-      <c r="C45" s="106"/>
-      <c r="D45" s="106"/>
-      <c r="E45" s="106"/>
-      <c r="F45" s="106"/>
-      <c r="G45" s="106"/>
-      <c r="H45" s="106"/>
-      <c r="I45" s="106"/>
-      <c r="J45" s="106"/>
-      <c r="K45" s="106"/>
-      <c r="L45" s="106"/>
-      <c r="M45" s="106"/>
-      <c r="N45" s="106"/>
+      <c r="A45" s="108"/>
+      <c r="B45" s="108"/>
+      <c r="C45" s="108"/>
+      <c r="D45" s="108"/>
+      <c r="E45" s="108"/>
+      <c r="F45" s="108"/>
+      <c r="G45" s="108"/>
+      <c r="H45" s="108"/>
+      <c r="I45" s="108"/>
+      <c r="J45" s="108"/>
+      <c r="K45" s="108"/>
+      <c r="L45" s="108"/>
+      <c r="M45" s="108"/>
+      <c r="N45" s="108"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="106"/>
-      <c r="B46" s="106"/>
-      <c r="C46" s="106"/>
-      <c r="D46" s="106"/>
-      <c r="E46" s="106"/>
-      <c r="F46" s="106"/>
-      <c r="G46" s="106"/>
-      <c r="H46" s="106"/>
-      <c r="I46" s="106"/>
-      <c r="J46" s="106"/>
-      <c r="K46" s="106"/>
-      <c r="L46" s="106"/>
-      <c r="M46" s="106"/>
-      <c r="N46" s="106"/>
+      <c r="A46" s="108"/>
+      <c r="B46" s="108"/>
+      <c r="C46" s="108"/>
+      <c r="D46" s="108"/>
+      <c r="E46" s="108"/>
+      <c r="F46" s="108"/>
+      <c r="G46" s="108"/>
+      <c r="H46" s="108"/>
+      <c r="I46" s="108"/>
+      <c r="J46" s="108"/>
+      <c r="K46" s="108"/>
+      <c r="L46" s="108"/>
+      <c r="M46" s="108"/>
+      <c r="N46" s="108"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="106"/>
-      <c r="B47" s="106"/>
-      <c r="C47" s="106"/>
-      <c r="D47" s="106"/>
-      <c r="E47" s="106"/>
-      <c r="F47" s="106"/>
-      <c r="G47" s="106"/>
-      <c r="H47" s="106"/>
-      <c r="I47" s="106"/>
-      <c r="J47" s="106"/>
-      <c r="K47" s="106"/>
-      <c r="L47" s="106"/>
-      <c r="M47" s="106"/>
-      <c r="N47" s="106"/>
+      <c r="A47" s="108"/>
+      <c r="B47" s="108"/>
+      <c r="C47" s="108"/>
+      <c r="D47" s="108"/>
+      <c r="E47" s="108"/>
+      <c r="F47" s="108"/>
+      <c r="G47" s="108"/>
+      <c r="H47" s="108"/>
+      <c r="I47" s="108"/>
+      <c r="J47" s="108"/>
+      <c r="K47" s="108"/>
+      <c r="L47" s="108"/>
+      <c r="M47" s="108"/>
+      <c r="N47" s="108"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="106"/>
-      <c r="B48" s="106"/>
-      <c r="C48" s="106"/>
-      <c r="D48" s="106"/>
-      <c r="E48" s="106"/>
-      <c r="F48" s="106"/>
-      <c r="G48" s="106"/>
-      <c r="H48" s="106"/>
-      <c r="I48" s="106"/>
-      <c r="J48" s="106"/>
-      <c r="K48" s="106"/>
-      <c r="L48" s="106"/>
-      <c r="M48" s="106"/>
-      <c r="N48" s="106"/>
+      <c r="A48" s="108"/>
+      <c r="B48" s="108"/>
+      <c r="C48" s="108"/>
+      <c r="D48" s="108"/>
+      <c r="E48" s="108"/>
+      <c r="F48" s="108"/>
+      <c r="G48" s="108"/>
+      <c r="H48" s="108"/>
+      <c r="I48" s="108"/>
+      <c r="J48" s="108"/>
+      <c r="K48" s="108"/>
+      <c r="L48" s="108"/>
+      <c r="M48" s="108"/>
+      <c r="N48" s="108"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="106"/>
-      <c r="B49" s="106"/>
-      <c r="C49" s="106"/>
-      <c r="D49" s="106"/>
-      <c r="E49" s="106"/>
-      <c r="F49" s="106"/>
-      <c r="G49" s="106"/>
-      <c r="H49" s="106"/>
-      <c r="I49" s="106"/>
-      <c r="J49" s="106"/>
-      <c r="K49" s="106"/>
-      <c r="L49" s="106"/>
-      <c r="M49" s="106"/>
-      <c r="N49" s="106"/>
+      <c r="A49" s="108"/>
+      <c r="B49" s="108"/>
+      <c r="C49" s="108"/>
+      <c r="D49" s="108"/>
+      <c r="E49" s="108"/>
+      <c r="F49" s="108"/>
+      <c r="G49" s="108"/>
+      <c r="H49" s="108"/>
+      <c r="I49" s="108"/>
+      <c r="J49" s="108"/>
+      <c r="K49" s="108"/>
+      <c r="L49" s="108"/>
+      <c r="M49" s="108"/>
+      <c r="N49" s="108"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="106"/>
-      <c r="B50" s="106"/>
-      <c r="C50" s="106"/>
-      <c r="D50" s="106"/>
-      <c r="E50" s="106"/>
-      <c r="F50" s="106"/>
-      <c r="G50" s="106"/>
-      <c r="H50" s="106"/>
-      <c r="I50" s="106"/>
-      <c r="J50" s="106"/>
-      <c r="K50" s="106"/>
-      <c r="L50" s="106"/>
-      <c r="M50" s="106"/>
-      <c r="N50" s="106"/>
+      <c r="A50" s="108"/>
+      <c r="B50" s="108"/>
+      <c r="C50" s="108"/>
+      <c r="D50" s="108"/>
+      <c r="E50" s="108"/>
+      <c r="F50" s="108"/>
+      <c r="G50" s="108"/>
+      <c r="H50" s="108"/>
+      <c r="I50" s="108"/>
+      <c r="J50" s="108"/>
+      <c r="K50" s="108"/>
+      <c r="L50" s="108"/>
+      <c r="M50" s="108"/>
+      <c r="N50" s="108"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="106"/>
-      <c r="B51" s="106"/>
-      <c r="C51" s="106"/>
-      <c r="D51" s="106"/>
-      <c r="E51" s="106"/>
-      <c r="F51" s="106"/>
-      <c r="G51" s="106"/>
-      <c r="H51" s="106"/>
-      <c r="I51" s="106"/>
-      <c r="J51" s="106"/>
-      <c r="K51" s="106"/>
-      <c r="L51" s="106"/>
-      <c r="M51" s="106"/>
-      <c r="N51" s="106"/>
+      <c r="A51" s="108"/>
+      <c r="B51" s="108"/>
+      <c r="C51" s="108"/>
+      <c r="D51" s="108"/>
+      <c r="E51" s="108"/>
+      <c r="F51" s="108"/>
+      <c r="G51" s="108"/>
+      <c r="H51" s="108"/>
+      <c r="I51" s="108"/>
+      <c r="J51" s="108"/>
+      <c r="K51" s="108"/>
+      <c r="L51" s="108"/>
+      <c r="M51" s="108"/>
+      <c r="N51" s="108"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="106"/>
-      <c r="B52" s="106"/>
-      <c r="C52" s="106"/>
-      <c r="D52" s="106"/>
-      <c r="E52" s="106"/>
-      <c r="F52" s="106"/>
-      <c r="G52" s="106"/>
-      <c r="H52" s="106"/>
-      <c r="I52" s="106"/>
-      <c r="J52" s="106"/>
-      <c r="K52" s="106"/>
-      <c r="L52" s="106"/>
-      <c r="M52" s="106"/>
-      <c r="N52" s="106"/>
+      <c r="A52" s="108"/>
+      <c r="B52" s="108"/>
+      <c r="C52" s="108"/>
+      <c r="D52" s="108"/>
+      <c r="E52" s="108"/>
+      <c r="F52" s="108"/>
+      <c r="G52" s="108"/>
+      <c r="H52" s="108"/>
+      <c r="I52" s="108"/>
+      <c r="J52" s="108"/>
+      <c r="K52" s="108"/>
+      <c r="L52" s="108"/>
+      <c r="M52" s="108"/>
+      <c r="N52" s="108"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="106"/>
-      <c r="B53" s="106"/>
-      <c r="C53" s="106"/>
-      <c r="D53" s="106"/>
-      <c r="E53" s="106"/>
-      <c r="F53" s="106"/>
-      <c r="G53" s="106"/>
-      <c r="H53" s="106"/>
-      <c r="I53" s="106"/>
-      <c r="J53" s="106"/>
-      <c r="K53" s="106"/>
-      <c r="L53" s="106"/>
-      <c r="M53" s="106"/>
-      <c r="N53" s="106"/>
+      <c r="A53" s="108"/>
+      <c r="B53" s="108"/>
+      <c r="C53" s="108"/>
+      <c r="D53" s="108"/>
+      <c r="E53" s="108"/>
+      <c r="F53" s="108"/>
+      <c r="G53" s="108"/>
+      <c r="H53" s="108"/>
+      <c r="I53" s="108"/>
+      <c r="J53" s="108"/>
+      <c r="K53" s="108"/>
+      <c r="L53" s="108"/>
+      <c r="M53" s="108"/>
+      <c r="N53" s="108"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="106"/>
-      <c r="B54" s="106"/>
-      <c r="C54" s="106"/>
-      <c r="D54" s="106"/>
-      <c r="E54" s="106"/>
-      <c r="F54" s="106"/>
-      <c r="G54" s="106"/>
-      <c r="H54" s="106"/>
-      <c r="I54" s="106"/>
-      <c r="J54" s="106"/>
-      <c r="K54" s="106"/>
-      <c r="L54" s="106"/>
-      <c r="M54" s="106"/>
-      <c r="N54" s="106"/>
+      <c r="A54" s="108"/>
+      <c r="B54" s="108"/>
+      <c r="C54" s="108"/>
+      <c r="D54" s="108"/>
+      <c r="E54" s="108"/>
+      <c r="F54" s="108"/>
+      <c r="G54" s="108"/>
+      <c r="H54" s="108"/>
+      <c r="I54" s="108"/>
+      <c r="J54" s="108"/>
+      <c r="K54" s="108"/>
+      <c r="L54" s="108"/>
+      <c r="M54" s="108"/>
+      <c r="N54" s="108"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="106"/>
-      <c r="B55" s="106"/>
-      <c r="C55" s="106"/>
-      <c r="D55" s="106"/>
-      <c r="E55" s="106"/>
-      <c r="F55" s="106"/>
-      <c r="G55" s="106"/>
-      <c r="H55" s="106"/>
-      <c r="I55" s="106"/>
-      <c r="J55" s="106"/>
-      <c r="K55" s="106"/>
-      <c r="L55" s="106"/>
-      <c r="M55" s="106"/>
-      <c r="N55" s="106"/>
+      <c r="A55" s="108"/>
+      <c r="B55" s="108"/>
+      <c r="C55" s="108"/>
+      <c r="D55" s="108"/>
+      <c r="E55" s="108"/>
+      <c r="F55" s="108"/>
+      <c r="G55" s="108"/>
+      <c r="H55" s="108"/>
+      <c r="I55" s="108"/>
+      <c r="J55" s="108"/>
+      <c r="K55" s="108"/>
+      <c r="L55" s="108"/>
+      <c r="M55" s="108"/>
+      <c r="N55" s="108"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="106"/>
-      <c r="B56" s="106"/>
-      <c r="C56" s="106"/>
-      <c r="D56" s="106"/>
-      <c r="E56" s="106"/>
-      <c r="F56" s="106"/>
-      <c r="G56" s="106"/>
-      <c r="H56" s="106"/>
-      <c r="I56" s="106"/>
-      <c r="J56" s="106"/>
-      <c r="K56" s="106"/>
-      <c r="L56" s="106"/>
-      <c r="M56" s="106"/>
-      <c r="N56" s="106"/>
+      <c r="A56" s="108"/>
+      <c r="B56" s="108"/>
+      <c r="C56" s="108"/>
+      <c r="D56" s="108"/>
+      <c r="E56" s="108"/>
+      <c r="F56" s="108"/>
+      <c r="G56" s="108"/>
+      <c r="H56" s="108"/>
+      <c r="I56" s="108"/>
+      <c r="J56" s="108"/>
+      <c r="K56" s="108"/>
+      <c r="L56" s="108"/>
+      <c r="M56" s="108"/>
+      <c r="N56" s="108"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="106"/>
-      <c r="B57" s="106"/>
-      <c r="C57" s="106"/>
-      <c r="D57" s="106"/>
-      <c r="E57" s="106"/>
-      <c r="F57" s="106"/>
-      <c r="G57" s="106"/>
-      <c r="H57" s="106"/>
-      <c r="I57" s="106"/>
-      <c r="J57" s="106"/>
-      <c r="K57" s="106"/>
-      <c r="L57" s="106"/>
-      <c r="M57" s="106"/>
-      <c r="N57" s="106"/>
+      <c r="A57" s="108"/>
+      <c r="B57" s="108"/>
+      <c r="C57" s="108"/>
+      <c r="D57" s="108"/>
+      <c r="E57" s="108"/>
+      <c r="F57" s="108"/>
+      <c r="G57" s="108"/>
+      <c r="H57" s="108"/>
+      <c r="I57" s="108"/>
+      <c r="J57" s="108"/>
+      <c r="K57" s="108"/>
+      <c r="L57" s="108"/>
+      <c r="M57" s="108"/>
+      <c r="N57" s="108"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="106"/>
-      <c r="B58" s="106"/>
-      <c r="C58" s="106"/>
-      <c r="D58" s="106"/>
-      <c r="E58" s="106"/>
-      <c r="F58" s="106"/>
-      <c r="G58" s="106"/>
-      <c r="H58" s="106"/>
-      <c r="I58" s="106"/>
-      <c r="J58" s="106"/>
-      <c r="K58" s="106"/>
-      <c r="L58" s="106"/>
-      <c r="M58" s="106"/>
-      <c r="N58" s="106"/>
+      <c r="A58" s="108"/>
+      <c r="B58" s="108"/>
+      <c r="C58" s="108"/>
+      <c r="D58" s="108"/>
+      <c r="E58" s="108"/>
+      <c r="F58" s="108"/>
+      <c r="G58" s="108"/>
+      <c r="H58" s="108"/>
+      <c r="I58" s="108"/>
+      <c r="J58" s="108"/>
+      <c r="K58" s="108"/>
+      <c r="L58" s="108"/>
+      <c r="M58" s="108"/>
+      <c r="N58" s="108"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="106"/>
-      <c r="B59" s="106"/>
-      <c r="C59" s="106"/>
-      <c r="D59" s="106"/>
-      <c r="E59" s="106"/>
-      <c r="F59" s="106"/>
-      <c r="G59" s="106"/>
-      <c r="H59" s="106"/>
-      <c r="I59" s="106"/>
-      <c r="J59" s="106"/>
-      <c r="K59" s="106"/>
-      <c r="L59" s="106"/>
-      <c r="M59" s="106"/>
-      <c r="N59" s="106"/>
+      <c r="A59" s="108"/>
+      <c r="B59" s="108"/>
+      <c r="C59" s="108"/>
+      <c r="D59" s="108"/>
+      <c r="E59" s="108"/>
+      <c r="F59" s="108"/>
+      <c r="G59" s="108"/>
+      <c r="H59" s="108"/>
+      <c r="I59" s="108"/>
+      <c r="J59" s="108"/>
+      <c r="K59" s="108"/>
+      <c r="L59" s="108"/>
+      <c r="M59" s="108"/>
+      <c r="N59" s="108"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="106"/>
-      <c r="B60" s="106"/>
-      <c r="C60" s="106"/>
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="106"/>
-      <c r="G60" s="106"/>
-      <c r="H60" s="106"/>
-      <c r="I60" s="106"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="106"/>
-      <c r="L60" s="106"/>
-      <c r="M60" s="106"/>
-      <c r="N60" s="106"/>
+      <c r="A60" s="108"/>
+      <c r="B60" s="108"/>
+      <c r="C60" s="108"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="108"/>
+      <c r="L60" s="108"/>
+      <c r="M60" s="108"/>
+      <c r="N60" s="108"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="106"/>
-      <c r="B61" s="106"/>
-      <c r="C61" s="106"/>
-      <c r="D61" s="106"/>
-      <c r="E61" s="106"/>
-      <c r="F61" s="106"/>
-      <c r="G61" s="106"/>
-      <c r="H61" s="106"/>
-      <c r="I61" s="106"/>
-      <c r="J61" s="106"/>
-      <c r="K61" s="106"/>
-      <c r="L61" s="106"/>
-      <c r="M61" s="106"/>
-      <c r="N61" s="106"/>
+      <c r="A61" s="108"/>
+      <c r="B61" s="108"/>
+      <c r="C61" s="108"/>
+      <c r="D61" s="108"/>
+      <c r="E61" s="108"/>
+      <c r="F61" s="108"/>
+      <c r="G61" s="108"/>
+      <c r="H61" s="108"/>
+      <c r="I61" s="108"/>
+      <c r="J61" s="108"/>
+      <c r="K61" s="108"/>
+      <c r="L61" s="108"/>
+      <c r="M61" s="108"/>
+      <c r="N61" s="108"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="106"/>
-      <c r="B62" s="106"/>
-      <c r="C62" s="106"/>
-      <c r="D62" s="106"/>
-      <c r="E62" s="106"/>
-      <c r="F62" s="106"/>
-      <c r="G62" s="106"/>
-      <c r="H62" s="106"/>
-      <c r="I62" s="106"/>
-      <c r="J62" s="106"/>
-      <c r="K62" s="106"/>
-      <c r="L62" s="106"/>
-      <c r="M62" s="106"/>
-      <c r="N62" s="106"/>
+      <c r="A62" s="108"/>
+      <c r="B62" s="108"/>
+      <c r="C62" s="108"/>
+      <c r="D62" s="108"/>
+      <c r="E62" s="108"/>
+      <c r="F62" s="108"/>
+      <c r="G62" s="108"/>
+      <c r="H62" s="108"/>
+      <c r="I62" s="108"/>
+      <c r="J62" s="108"/>
+      <c r="K62" s="108"/>
+      <c r="L62" s="108"/>
+      <c r="M62" s="108"/>
+      <c r="N62" s="108"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="106"/>
-      <c r="B63" s="106"/>
-      <c r="C63" s="106"/>
-      <c r="D63" s="106"/>
-      <c r="E63" s="106"/>
-      <c r="F63" s="106"/>
-      <c r="G63" s="106"/>
-      <c r="H63" s="106"/>
-      <c r="I63" s="106"/>
-      <c r="J63" s="106"/>
-      <c r="K63" s="106"/>
-      <c r="L63" s="106"/>
-      <c r="M63" s="106"/>
-      <c r="N63" s="106"/>
+      <c r="A63" s="108"/>
+      <c r="B63" s="108"/>
+      <c r="C63" s="108"/>
+      <c r="D63" s="108"/>
+      <c r="E63" s="108"/>
+      <c r="F63" s="108"/>
+      <c r="G63" s="108"/>
+      <c r="H63" s="108"/>
+      <c r="I63" s="108"/>
+      <c r="J63" s="108"/>
+      <c r="K63" s="108"/>
+      <c r="L63" s="108"/>
+      <c r="M63" s="108"/>
+      <c r="N63" s="108"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="106"/>
-      <c r="B64" s="106"/>
-      <c r="C64" s="106"/>
-      <c r="D64" s="106"/>
-      <c r="E64" s="106"/>
-      <c r="F64" s="106"/>
-      <c r="G64" s="106"/>
-      <c r="H64" s="106"/>
-      <c r="I64" s="106"/>
-      <c r="J64" s="106"/>
-      <c r="K64" s="106"/>
-      <c r="L64" s="106"/>
-      <c r="M64" s="106"/>
-      <c r="N64" s="106"/>
+      <c r="A64" s="108"/>
+      <c r="B64" s="108"/>
+      <c r="C64" s="108"/>
+      <c r="D64" s="108"/>
+      <c r="E64" s="108"/>
+      <c r="F64" s="108"/>
+      <c r="G64" s="108"/>
+      <c r="H64" s="108"/>
+      <c r="I64" s="108"/>
+      <c r="J64" s="108"/>
+      <c r="K64" s="108"/>
+      <c r="L64" s="108"/>
+      <c r="M64" s="108"/>
+      <c r="N64" s="108"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="106"/>
-      <c r="B65" s="106"/>
-      <c r="C65" s="106"/>
-      <c r="D65" s="106"/>
-      <c r="E65" s="106"/>
-      <c r="F65" s="106"/>
-      <c r="G65" s="106"/>
-      <c r="H65" s="106"/>
-      <c r="I65" s="106"/>
-      <c r="J65" s="106"/>
-      <c r="K65" s="106"/>
-      <c r="L65" s="106"/>
-      <c r="M65" s="106"/>
-      <c r="N65" s="106"/>
+      <c r="A65" s="108"/>
+      <c r="B65" s="108"/>
+      <c r="C65" s="108"/>
+      <c r="D65" s="108"/>
+      <c r="E65" s="108"/>
+      <c r="F65" s="108"/>
+      <c r="G65" s="108"/>
+      <c r="H65" s="108"/>
+      <c r="I65" s="108"/>
+      <c r="J65" s="108"/>
+      <c r="K65" s="108"/>
+      <c r="L65" s="108"/>
+      <c r="M65" s="108"/>
+      <c r="N65" s="108"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="106"/>
-      <c r="B66" s="106"/>
-      <c r="C66" s="106"/>
-      <c r="D66" s="106"/>
-      <c r="E66" s="106"/>
-      <c r="F66" s="106"/>
-      <c r="G66" s="106"/>
-      <c r="H66" s="106"/>
-      <c r="I66" s="106"/>
-      <c r="J66" s="106"/>
-      <c r="K66" s="106"/>
-      <c r="L66" s="106"/>
-      <c r="M66" s="106"/>
-      <c r="N66" s="106"/>
+      <c r="A66" s="108"/>
+      <c r="B66" s="108"/>
+      <c r="C66" s="108"/>
+      <c r="D66" s="108"/>
+      <c r="E66" s="108"/>
+      <c r="F66" s="108"/>
+      <c r="G66" s="108"/>
+      <c r="H66" s="108"/>
+      <c r="I66" s="108"/>
+      <c r="J66" s="108"/>
+      <c r="K66" s="108"/>
+      <c r="L66" s="108"/>
+      <c r="M66" s="108"/>
+      <c r="N66" s="108"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="106"/>
-      <c r="B67" s="106"/>
-      <c r="C67" s="106"/>
-      <c r="D67" s="106"/>
-      <c r="E67" s="106"/>
-      <c r="F67" s="106"/>
-      <c r="G67" s="106"/>
-      <c r="H67" s="106"/>
-      <c r="I67" s="106"/>
-      <c r="J67" s="106"/>
-      <c r="K67" s="106"/>
-      <c r="L67" s="106"/>
-      <c r="M67" s="106"/>
-      <c r="N67" s="106"/>
+      <c r="A67" s="108"/>
+      <c r="B67" s="108"/>
+      <c r="C67" s="108"/>
+      <c r="D67" s="108"/>
+      <c r="E67" s="108"/>
+      <c r="F67" s="108"/>
+      <c r="G67" s="108"/>
+      <c r="H67" s="108"/>
+      <c r="I67" s="108"/>
+      <c r="J67" s="108"/>
+      <c r="K67" s="108"/>
+      <c r="L67" s="108"/>
+      <c r="M67" s="108"/>
+      <c r="N67" s="108"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="106"/>
-      <c r="B68" s="106"/>
-      <c r="C68" s="106"/>
-      <c r="D68" s="106"/>
-      <c r="E68" s="106"/>
-      <c r="F68" s="106"/>
-      <c r="G68" s="106"/>
-      <c r="H68" s="106"/>
-      <c r="I68" s="106"/>
-      <c r="J68" s="106"/>
-      <c r="K68" s="106"/>
-      <c r="L68" s="106"/>
-      <c r="M68" s="106"/>
-      <c r="N68" s="106"/>
+      <c r="A68" s="108"/>
+      <c r="B68" s="108"/>
+      <c r="C68" s="108"/>
+      <c r="D68" s="108"/>
+      <c r="E68" s="108"/>
+      <c r="F68" s="108"/>
+      <c r="G68" s="108"/>
+      <c r="H68" s="108"/>
+      <c r="I68" s="108"/>
+      <c r="J68" s="108"/>
+      <c r="K68" s="108"/>
+      <c r="L68" s="108"/>
+      <c r="M68" s="108"/>
+      <c r="N68" s="108"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="106"/>
-      <c r="B69" s="106"/>
-      <c r="C69" s="106"/>
-      <c r="D69" s="106"/>
-      <c r="E69" s="106"/>
-      <c r="F69" s="106"/>
-      <c r="G69" s="106"/>
-      <c r="H69" s="106"/>
-      <c r="I69" s="106"/>
-      <c r="J69" s="106"/>
-      <c r="K69" s="106"/>
-      <c r="L69" s="106"/>
-      <c r="M69" s="106"/>
-      <c r="N69" s="106"/>
+      <c r="A69" s="108"/>
+      <c r="B69" s="108"/>
+      <c r="C69" s="108"/>
+      <c r="D69" s="108"/>
+      <c r="E69" s="108"/>
+      <c r="F69" s="108"/>
+      <c r="G69" s="108"/>
+      <c r="H69" s="108"/>
+      <c r="I69" s="108"/>
+      <c r="J69" s="108"/>
+      <c r="K69" s="108"/>
+      <c r="L69" s="108"/>
+      <c r="M69" s="108"/>
+      <c r="N69" s="108"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="106"/>
-      <c r="B70" s="106"/>
-      <c r="C70" s="106"/>
-      <c r="D70" s="106"/>
-      <c r="E70" s="106"/>
-      <c r="F70" s="106"/>
-      <c r="G70" s="106"/>
-      <c r="H70" s="106"/>
-      <c r="I70" s="106"/>
-      <c r="J70" s="106"/>
-      <c r="K70" s="106"/>
-      <c r="L70" s="106"/>
-      <c r="M70" s="106"/>
-      <c r="N70" s="106"/>
+      <c r="A70" s="108"/>
+      <c r="B70" s="108"/>
+      <c r="C70" s="108"/>
+      <c r="D70" s="108"/>
+      <c r="E70" s="108"/>
+      <c r="F70" s="108"/>
+      <c r="G70" s="108"/>
+      <c r="H70" s="108"/>
+      <c r="I70" s="108"/>
+      <c r="J70" s="108"/>
+      <c r="K70" s="108"/>
+      <c r="L70" s="108"/>
+      <c r="M70" s="108"/>
+      <c r="N70" s="108"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="106"/>
-      <c r="B71" s="106"/>
-      <c r="C71" s="106"/>
-      <c r="D71" s="106"/>
-      <c r="E71" s="106"/>
-      <c r="F71" s="106"/>
-      <c r="G71" s="106"/>
-      <c r="H71" s="106"/>
-      <c r="I71" s="106"/>
-      <c r="J71" s="106"/>
-      <c r="K71" s="106"/>
-      <c r="L71" s="106"/>
-      <c r="M71" s="106"/>
-      <c r="N71" s="106"/>
+      <c r="A71" s="108"/>
+      <c r="B71" s="108"/>
+      <c r="C71" s="108"/>
+      <c r="D71" s="108"/>
+      <c r="E71" s="108"/>
+      <c r="F71" s="108"/>
+      <c r="G71" s="108"/>
+      <c r="H71" s="108"/>
+      <c r="I71" s="108"/>
+      <c r="J71" s="108"/>
+      <c r="K71" s="108"/>
+      <c r="L71" s="108"/>
+      <c r="M71" s="108"/>
+      <c r="N71" s="108"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="106"/>
-      <c r="B72" s="106"/>
-      <c r="C72" s="106"/>
-      <c r="D72" s="106"/>
-      <c r="E72" s="106"/>
-      <c r="F72" s="106"/>
-      <c r="G72" s="106"/>
-      <c r="H72" s="106"/>
-      <c r="I72" s="106"/>
-      <c r="J72" s="106"/>
-      <c r="K72" s="106"/>
-      <c r="L72" s="106"/>
-      <c r="M72" s="106"/>
-      <c r="N72" s="106"/>
+      <c r="A72" s="108"/>
+      <c r="B72" s="108"/>
+      <c r="C72" s="108"/>
+      <c r="D72" s="108"/>
+      <c r="E72" s="108"/>
+      <c r="F72" s="108"/>
+      <c r="G72" s="108"/>
+      <c r="H72" s="108"/>
+      <c r="I72" s="108"/>
+      <c r="J72" s="108"/>
+      <c r="K72" s="108"/>
+      <c r="L72" s="108"/>
+      <c r="M72" s="108"/>
+      <c r="N72" s="108"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="106"/>
-      <c r="B73" s="106"/>
-      <c r="C73" s="106"/>
-      <c r="D73" s="106"/>
-      <c r="E73" s="106"/>
-      <c r="F73" s="106"/>
-      <c r="G73" s="106"/>
-      <c r="H73" s="106"/>
-      <c r="I73" s="106"/>
-      <c r="J73" s="106"/>
-      <c r="K73" s="106"/>
-      <c r="L73" s="106"/>
-      <c r="M73" s="106"/>
-      <c r="N73" s="106"/>
+      <c r="A73" s="108"/>
+      <c r="B73" s="108"/>
+      <c r="C73" s="108"/>
+      <c r="D73" s="108"/>
+      <c r="E73" s="108"/>
+      <c r="F73" s="108"/>
+      <c r="G73" s="108"/>
+      <c r="H73" s="108"/>
+      <c r="I73" s="108"/>
+      <c r="J73" s="108"/>
+      <c r="K73" s="108"/>
+      <c r="L73" s="108"/>
+      <c r="M73" s="108"/>
+      <c r="N73" s="108"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="106"/>
-      <c r="B74" s="106"/>
-      <c r="C74" s="106"/>
-      <c r="D74" s="106"/>
-      <c r="E74" s="106"/>
-      <c r="F74" s="106"/>
-      <c r="G74" s="106"/>
-      <c r="H74" s="106"/>
-      <c r="I74" s="106"/>
-      <c r="J74" s="106"/>
-      <c r="K74" s="106"/>
-      <c r="L74" s="106"/>
-      <c r="M74" s="106"/>
-      <c r="N74" s="106"/>
+      <c r="A74" s="108"/>
+      <c r="B74" s="108"/>
+      <c r="C74" s="108"/>
+      <c r="D74" s="108"/>
+      <c r="E74" s="108"/>
+      <c r="F74" s="108"/>
+      <c r="G74" s="108"/>
+      <c r="H74" s="108"/>
+      <c r="I74" s="108"/>
+      <c r="J74" s="108"/>
+      <c r="K74" s="108"/>
+      <c r="L74" s="108"/>
+      <c r="M74" s="108"/>
+      <c r="N74" s="108"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="106"/>
-      <c r="B75" s="106"/>
-      <c r="C75" s="106"/>
-      <c r="D75" s="106"/>
-      <c r="E75" s="106"/>
-      <c r="F75" s="106"/>
-      <c r="G75" s="106"/>
-      <c r="H75" s="106"/>
-      <c r="I75" s="106"/>
-      <c r="J75" s="106"/>
-      <c r="K75" s="106"/>
-      <c r="L75" s="106"/>
-      <c r="M75" s="106"/>
-      <c r="N75" s="106"/>
+      <c r="A75" s="108"/>
+      <c r="B75" s="108"/>
+      <c r="C75" s="108"/>
+      <c r="D75" s="108"/>
+      <c r="E75" s="108"/>
+      <c r="F75" s="108"/>
+      <c r="G75" s="108"/>
+      <c r="H75" s="108"/>
+      <c r="I75" s="108"/>
+      <c r="J75" s="108"/>
+      <c r="K75" s="108"/>
+      <c r="L75" s="108"/>
+      <c r="M75" s="108"/>
+      <c r="N75" s="108"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="106"/>
-      <c r="B76" s="106"/>
-      <c r="C76" s="106"/>
-      <c r="D76" s="106"/>
-      <c r="E76" s="106"/>
-      <c r="F76" s="106"/>
-      <c r="G76" s="106"/>
-      <c r="H76" s="106"/>
-      <c r="I76" s="106"/>
-      <c r="J76" s="106"/>
-      <c r="K76" s="106"/>
-      <c r="L76" s="106"/>
-      <c r="M76" s="106"/>
-      <c r="N76" s="106"/>
+      <c r="A76" s="108"/>
+      <c r="B76" s="108"/>
+      <c r="C76" s="108"/>
+      <c r="D76" s="108"/>
+      <c r="E76" s="108"/>
+      <c r="F76" s="108"/>
+      <c r="G76" s="108"/>
+      <c r="H76" s="108"/>
+      <c r="I76" s="108"/>
+      <c r="J76" s="108"/>
+      <c r="K76" s="108"/>
+      <c r="L76" s="108"/>
+      <c r="M76" s="108"/>
+      <c r="N76" s="108"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="106"/>
-      <c r="B77" s="106"/>
-      <c r="C77" s="106"/>
-      <c r="D77" s="106"/>
-      <c r="E77" s="106"/>
-      <c r="F77" s="106"/>
-      <c r="G77" s="106"/>
-      <c r="H77" s="106"/>
-      <c r="I77" s="106"/>
-      <c r="J77" s="106"/>
-      <c r="K77" s="106"/>
-      <c r="L77" s="106"/>
-      <c r="M77" s="106"/>
-      <c r="N77" s="106"/>
+      <c r="A77" s="108"/>
+      <c r="B77" s="108"/>
+      <c r="C77" s="108"/>
+      <c r="D77" s="108"/>
+      <c r="E77" s="108"/>
+      <c r="F77" s="108"/>
+      <c r="G77" s="108"/>
+      <c r="H77" s="108"/>
+      <c r="I77" s="108"/>
+      <c r="J77" s="108"/>
+      <c r="K77" s="108"/>
+      <c r="L77" s="108"/>
+      <c r="M77" s="108"/>
+      <c r="N77" s="108"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="106"/>
-      <c r="B78" s="106"/>
-      <c r="C78" s="106"/>
-      <c r="D78" s="106"/>
-      <c r="E78" s="106"/>
-      <c r="F78" s="106"/>
-      <c r="G78" s="106"/>
-      <c r="H78" s="106"/>
-      <c r="I78" s="106"/>
-      <c r="J78" s="106"/>
-      <c r="K78" s="106"/>
-      <c r="L78" s="106"/>
-      <c r="M78" s="106"/>
-      <c r="N78" s="106"/>
+      <c r="A78" s="108"/>
+      <c r="B78" s="108"/>
+      <c r="C78" s="108"/>
+      <c r="D78" s="108"/>
+      <c r="E78" s="108"/>
+      <c r="F78" s="108"/>
+      <c r="G78" s="108"/>
+      <c r="H78" s="108"/>
+      <c r="I78" s="108"/>
+      <c r="J78" s="108"/>
+      <c r="K78" s="108"/>
+      <c r="L78" s="108"/>
+      <c r="M78" s="108"/>
+      <c r="N78" s="108"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="106"/>
-      <c r="B79" s="106"/>
-      <c r="C79" s="106"/>
-      <c r="D79" s="106"/>
-      <c r="E79" s="106"/>
-      <c r="F79" s="106"/>
-      <c r="G79" s="106"/>
-      <c r="H79" s="106"/>
-      <c r="I79" s="106"/>
-      <c r="J79" s="106"/>
-      <c r="K79" s="106"/>
-      <c r="L79" s="106"/>
-      <c r="M79" s="106"/>
-      <c r="N79" s="106"/>
+      <c r="A79" s="108"/>
+      <c r="B79" s="108"/>
+      <c r="C79" s="108"/>
+      <c r="D79" s="108"/>
+      <c r="E79" s="108"/>
+      <c r="F79" s="108"/>
+      <c r="G79" s="108"/>
+      <c r="H79" s="108"/>
+      <c r="I79" s="108"/>
+      <c r="J79" s="108"/>
+      <c r="K79" s="108"/>
+      <c r="L79" s="108"/>
+      <c r="M79" s="108"/>
+      <c r="N79" s="108"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="106"/>
-      <c r="B80" s="106"/>
-      <c r="C80" s="106"/>
-      <c r="D80" s="106"/>
-      <c r="E80" s="106"/>
-      <c r="F80" s="106"/>
-      <c r="G80" s="106"/>
-      <c r="H80" s="106"/>
-      <c r="I80" s="106"/>
-      <c r="J80" s="106"/>
-      <c r="K80" s="106"/>
-      <c r="L80" s="106"/>
-      <c r="M80" s="106"/>
-      <c r="N80" s="106"/>
+      <c r="A80" s="108"/>
+      <c r="B80" s="108"/>
+      <c r="C80" s="108"/>
+      <c r="D80" s="108"/>
+      <c r="E80" s="108"/>
+      <c r="F80" s="108"/>
+      <c r="G80" s="108"/>
+      <c r="H80" s="108"/>
+      <c r="I80" s="108"/>
+      <c r="J80" s="108"/>
+      <c r="K80" s="108"/>
+      <c r="L80" s="108"/>
+      <c r="M80" s="108"/>
+      <c r="N80" s="108"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="106"/>
-      <c r="B81" s="106"/>
-      <c r="C81" s="106"/>
-      <c r="D81" s="106"/>
-      <c r="E81" s="106"/>
-      <c r="F81" s="106"/>
-      <c r="G81" s="106"/>
-      <c r="H81" s="106"/>
-      <c r="I81" s="106"/>
-      <c r="J81" s="106"/>
-      <c r="K81" s="106"/>
-      <c r="L81" s="106"/>
-      <c r="M81" s="106"/>
-      <c r="N81" s="106"/>
+      <c r="A81" s="108"/>
+      <c r="B81" s="108"/>
+      <c r="C81" s="108"/>
+      <c r="D81" s="108"/>
+      <c r="E81" s="108"/>
+      <c r="F81" s="108"/>
+      <c r="G81" s="108"/>
+      <c r="H81" s="108"/>
+      <c r="I81" s="108"/>
+      <c r="J81" s="108"/>
+      <c r="K81" s="108"/>
+      <c r="L81" s="108"/>
+      <c r="M81" s="108"/>
+      <c r="N81" s="108"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="106"/>
-      <c r="B82" s="106"/>
-      <c r="C82" s="106"/>
-      <c r="D82" s="106"/>
-      <c r="E82" s="106"/>
-      <c r="F82" s="106"/>
-      <c r="G82" s="106"/>
-      <c r="H82" s="106"/>
-      <c r="I82" s="106"/>
-      <c r="J82" s="106"/>
-      <c r="K82" s="106"/>
-      <c r="L82" s="106"/>
-      <c r="M82" s="106"/>
-      <c r="N82" s="106"/>
+      <c r="A82" s="108"/>
+      <c r="B82" s="108"/>
+      <c r="C82" s="108"/>
+      <c r="D82" s="108"/>
+      <c r="E82" s="108"/>
+      <c r="F82" s="108"/>
+      <c r="G82" s="108"/>
+      <c r="H82" s="108"/>
+      <c r="I82" s="108"/>
+      <c r="J82" s="108"/>
+      <c r="K82" s="108"/>
+      <c r="L82" s="108"/>
+      <c r="M82" s="108"/>
+      <c r="N82" s="108"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="106"/>
-      <c r="B83" s="106"/>
-      <c r="C83" s="106"/>
-      <c r="D83" s="106"/>
-      <c r="E83" s="106"/>
-      <c r="F83" s="106"/>
-      <c r="G83" s="106"/>
-      <c r="H83" s="106"/>
-      <c r="I83" s="106"/>
-      <c r="J83" s="106"/>
-      <c r="K83" s="106"/>
-      <c r="L83" s="106"/>
-      <c r="M83" s="106"/>
-      <c r="N83" s="106"/>
+      <c r="A83" s="108"/>
+      <c r="B83" s="108"/>
+      <c r="C83" s="108"/>
+      <c r="D83" s="108"/>
+      <c r="E83" s="108"/>
+      <c r="F83" s="108"/>
+      <c r="G83" s="108"/>
+      <c r="H83" s="108"/>
+      <c r="I83" s="108"/>
+      <c r="J83" s="108"/>
+      <c r="K83" s="108"/>
+      <c r="L83" s="108"/>
+      <c r="M83" s="108"/>
+      <c r="N83" s="108"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="106"/>
-      <c r="B84" s="106"/>
-      <c r="C84" s="106"/>
-      <c r="D84" s="106"/>
-      <c r="E84" s="106"/>
-      <c r="F84" s="106"/>
-      <c r="G84" s="106"/>
-      <c r="H84" s="106"/>
-      <c r="I84" s="106"/>
-      <c r="J84" s="106"/>
-      <c r="K84" s="106"/>
-      <c r="L84" s="106"/>
-      <c r="M84" s="106"/>
-      <c r="N84" s="106"/>
+      <c r="A84" s="108"/>
+      <c r="B84" s="108"/>
+      <c r="C84" s="108"/>
+      <c r="D84" s="108"/>
+      <c r="E84" s="108"/>
+      <c r="F84" s="108"/>
+      <c r="G84" s="108"/>
+      <c r="H84" s="108"/>
+      <c r="I84" s="108"/>
+      <c r="J84" s="108"/>
+      <c r="K84" s="108"/>
+      <c r="L84" s="108"/>
+      <c r="M84" s="108"/>
+      <c r="N84" s="108"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="106"/>
-      <c r="B85" s="106"/>
-      <c r="C85" s="106"/>
-      <c r="D85" s="106"/>
-      <c r="E85" s="106"/>
-      <c r="F85" s="106"/>
-      <c r="G85" s="106"/>
-      <c r="H85" s="106"/>
-      <c r="I85" s="106"/>
-      <c r="J85" s="106"/>
-      <c r="K85" s="106"/>
-      <c r="L85" s="106"/>
-      <c r="M85" s="106"/>
-      <c r="N85" s="106"/>
+      <c r="A85" s="108"/>
+      <c r="B85" s="108"/>
+      <c r="C85" s="108"/>
+      <c r="D85" s="108"/>
+      <c r="E85" s="108"/>
+      <c r="F85" s="108"/>
+      <c r="G85" s="108"/>
+      <c r="H85" s="108"/>
+      <c r="I85" s="108"/>
+      <c r="J85" s="108"/>
+      <c r="K85" s="108"/>
+      <c r="L85" s="108"/>
+      <c r="M85" s="108"/>
+      <c r="N85" s="108"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="106"/>
-      <c r="B86" s="106"/>
-      <c r="C86" s="106"/>
-      <c r="D86" s="106"/>
-      <c r="E86" s="106"/>
-      <c r="F86" s="106"/>
-      <c r="G86" s="106"/>
-      <c r="H86" s="106"/>
-      <c r="I86" s="106"/>
-      <c r="J86" s="106"/>
-      <c r="K86" s="106"/>
-      <c r="L86" s="106"/>
-      <c r="M86" s="106"/>
-      <c r="N86" s="106"/>
+      <c r="A86" s="108"/>
+      <c r="B86" s="108"/>
+      <c r="C86" s="108"/>
+      <c r="D86" s="108"/>
+      <c r="E86" s="108"/>
+      <c r="F86" s="108"/>
+      <c r="G86" s="108"/>
+      <c r="H86" s="108"/>
+      <c r="I86" s="108"/>
+      <c r="J86" s="108"/>
+      <c r="K86" s="108"/>
+      <c r="L86" s="108"/>
+      <c r="M86" s="108"/>
+      <c r="N86" s="108"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="106"/>
-      <c r="B87" s="106"/>
-      <c r="C87" s="106"/>
-      <c r="D87" s="106"/>
-      <c r="E87" s="106"/>
-      <c r="F87" s="106"/>
-      <c r="G87" s="106"/>
-      <c r="H87" s="106"/>
-      <c r="I87" s="106"/>
-      <c r="J87" s="106"/>
-      <c r="K87" s="106"/>
-      <c r="L87" s="106"/>
-      <c r="M87" s="106"/>
-      <c r="N87" s="106"/>
+      <c r="A87" s="108"/>
+      <c r="B87" s="108"/>
+      <c r="C87" s="108"/>
+      <c r="D87" s="108"/>
+      <c r="E87" s="108"/>
+      <c r="F87" s="108"/>
+      <c r="G87" s="108"/>
+      <c r="H87" s="108"/>
+      <c r="I87" s="108"/>
+      <c r="J87" s="108"/>
+      <c r="K87" s="108"/>
+      <c r="L87" s="108"/>
+      <c r="M87" s="108"/>
+      <c r="N87" s="108"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="106"/>
-      <c r="B88" s="106"/>
-      <c r="C88" s="106"/>
-      <c r="D88" s="106"/>
-      <c r="E88" s="106"/>
-      <c r="F88" s="106"/>
-      <c r="G88" s="106"/>
-      <c r="H88" s="106"/>
-      <c r="I88" s="106"/>
-      <c r="J88" s="106"/>
-      <c r="K88" s="106"/>
-      <c r="L88" s="106"/>
-      <c r="M88" s="106"/>
-      <c r="N88" s="106"/>
+      <c r="A88" s="108"/>
+      <c r="B88" s="108"/>
+      <c r="C88" s="108"/>
+      <c r="D88" s="108"/>
+      <c r="E88" s="108"/>
+      <c r="F88" s="108"/>
+      <c r="G88" s="108"/>
+      <c r="H88" s="108"/>
+      <c r="I88" s="108"/>
+      <c r="J88" s="108"/>
+      <c r="K88" s="108"/>
+      <c r="L88" s="108"/>
+      <c r="M88" s="108"/>
+      <c r="N88" s="108"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="106"/>
-      <c r="B89" s="106"/>
-      <c r="C89" s="106"/>
-      <c r="D89" s="106"/>
-      <c r="E89" s="106"/>
-      <c r="F89" s="106"/>
-      <c r="G89" s="106"/>
-      <c r="H89" s="106"/>
-      <c r="I89" s="106"/>
-      <c r="J89" s="106"/>
-      <c r="K89" s="106"/>
-      <c r="L89" s="106"/>
-      <c r="M89" s="106"/>
-      <c r="N89" s="106"/>
+      <c r="A89" s="108"/>
+      <c r="B89" s="108"/>
+      <c r="C89" s="108"/>
+      <c r="D89" s="108"/>
+      <c r="E89" s="108"/>
+      <c r="F89" s="108"/>
+      <c r="G89" s="108"/>
+      <c r="H89" s="108"/>
+      <c r="I89" s="108"/>
+      <c r="J89" s="108"/>
+      <c r="K89" s="108"/>
+      <c r="L89" s="108"/>
+      <c r="M89" s="108"/>
+      <c r="N89" s="108"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="106"/>
-      <c r="B90" s="106"/>
-      <c r="C90" s="106"/>
-      <c r="D90" s="106"/>
-      <c r="E90" s="106"/>
-      <c r="F90" s="106"/>
-      <c r="G90" s="106"/>
-      <c r="H90" s="106"/>
-      <c r="I90" s="106"/>
-      <c r="J90" s="106"/>
-      <c r="K90" s="106"/>
-      <c r="L90" s="106"/>
-      <c r="M90" s="106"/>
-      <c r="N90" s="106"/>
+      <c r="A90" s="108"/>
+      <c r="B90" s="108"/>
+      <c r="C90" s="108"/>
+      <c r="D90" s="108"/>
+      <c r="E90" s="108"/>
+      <c r="F90" s="108"/>
+      <c r="G90" s="108"/>
+      <c r="H90" s="108"/>
+      <c r="I90" s="108"/>
+      <c r="J90" s="108"/>
+      <c r="K90" s="108"/>
+      <c r="L90" s="108"/>
+      <c r="M90" s="108"/>
+      <c r="N90" s="108"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="106"/>
-      <c r="B91" s="106"/>
-      <c r="C91" s="106"/>
-      <c r="D91" s="106"/>
-      <c r="E91" s="106"/>
-      <c r="F91" s="106"/>
-      <c r="G91" s="106"/>
-      <c r="H91" s="106"/>
-      <c r="I91" s="106"/>
-      <c r="J91" s="106"/>
-      <c r="K91" s="106"/>
-      <c r="L91" s="106"/>
-      <c r="M91" s="106"/>
-      <c r="N91" s="106"/>
+      <c r="A91" s="108"/>
+      <c r="B91" s="108"/>
+      <c r="C91" s="108"/>
+      <c r="D91" s="108"/>
+      <c r="E91" s="108"/>
+      <c r="F91" s="108"/>
+      <c r="G91" s="108"/>
+      <c r="H91" s="108"/>
+      <c r="I91" s="108"/>
+      <c r="J91" s="108"/>
+      <c r="K91" s="108"/>
+      <c r="L91" s="108"/>
+      <c r="M91" s="108"/>
+      <c r="N91" s="108"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="106"/>
-      <c r="B92" s="106"/>
-      <c r="C92" s="106"/>
-      <c r="D92" s="106"/>
-      <c r="E92" s="106"/>
-      <c r="F92" s="106"/>
-      <c r="G92" s="106"/>
-      <c r="H92" s="106"/>
-      <c r="I92" s="106"/>
-      <c r="J92" s="106"/>
-      <c r="K92" s="106"/>
-      <c r="L92" s="106"/>
-      <c r="M92" s="106"/>
-      <c r="N92" s="106"/>
+      <c r="A92" s="108"/>
+      <c r="B92" s="108"/>
+      <c r="C92" s="108"/>
+      <c r="D92" s="108"/>
+      <c r="E92" s="108"/>
+      <c r="F92" s="108"/>
+      <c r="G92" s="108"/>
+      <c r="H92" s="108"/>
+      <c r="I92" s="108"/>
+      <c r="J92" s="108"/>
+      <c r="K92" s="108"/>
+      <c r="L92" s="108"/>
+      <c r="M92" s="108"/>
+      <c r="N92" s="108"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="106"/>
-      <c r="B93" s="106"/>
-      <c r="C93" s="106"/>
-      <c r="D93" s="106"/>
-      <c r="E93" s="106"/>
-      <c r="F93" s="106"/>
-      <c r="G93" s="106"/>
-      <c r="H93" s="106"/>
-      <c r="I93" s="106"/>
-      <c r="J93" s="106"/>
-      <c r="K93" s="106"/>
-      <c r="L93" s="106"/>
-      <c r="M93" s="106"/>
-      <c r="N93" s="106"/>
+      <c r="A93" s="108"/>
+      <c r="B93" s="108"/>
+      <c r="C93" s="108"/>
+      <c r="D93" s="108"/>
+      <c r="E93" s="108"/>
+      <c r="F93" s="108"/>
+      <c r="G93" s="108"/>
+      <c r="H93" s="108"/>
+      <c r="I93" s="108"/>
+      <c r="J93" s="108"/>
+      <c r="K93" s="108"/>
+      <c r="L93" s="108"/>
+      <c r="M93" s="108"/>
+      <c r="N93" s="108"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="106"/>
-      <c r="B94" s="106"/>
-      <c r="C94" s="106"/>
-      <c r="D94" s="106"/>
-      <c r="E94" s="106"/>
-      <c r="F94" s="106"/>
-      <c r="G94" s="106"/>
-      <c r="H94" s="106"/>
-      <c r="I94" s="106"/>
-      <c r="J94" s="106"/>
-      <c r="K94" s="106"/>
-      <c r="L94" s="106"/>
-      <c r="M94" s="106"/>
-      <c r="N94" s="106"/>
+      <c r="A94" s="108"/>
+      <c r="B94" s="108"/>
+      <c r="C94" s="108"/>
+      <c r="D94" s="108"/>
+      <c r="E94" s="108"/>
+      <c r="F94" s="108"/>
+      <c r="G94" s="108"/>
+      <c r="H94" s="108"/>
+      <c r="I94" s="108"/>
+      <c r="J94" s="108"/>
+      <c r="K94" s="108"/>
+      <c r="L94" s="108"/>
+      <c r="M94" s="108"/>
+      <c r="N94" s="108"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="106"/>
-      <c r="B95" s="106"/>
-      <c r="C95" s="106"/>
-      <c r="D95" s="106"/>
-      <c r="E95" s="106"/>
-      <c r="F95" s="106"/>
-      <c r="G95" s="106"/>
-      <c r="H95" s="106"/>
-      <c r="I95" s="106"/>
-      <c r="J95" s="106"/>
-      <c r="K95" s="106"/>
-      <c r="L95" s="106"/>
-      <c r="M95" s="106"/>
-      <c r="N95" s="106"/>
+      <c r="A95" s="108"/>
+      <c r="B95" s="108"/>
+      <c r="C95" s="108"/>
+      <c r="D95" s="108"/>
+      <c r="E95" s="108"/>
+      <c r="F95" s="108"/>
+      <c r="G95" s="108"/>
+      <c r="H95" s="108"/>
+      <c r="I95" s="108"/>
+      <c r="J95" s="108"/>
+      <c r="K95" s="108"/>
+      <c r="L95" s="108"/>
+      <c r="M95" s="108"/>
+      <c r="N95" s="108"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="106"/>
-      <c r="B96" s="106"/>
-      <c r="C96" s="106"/>
-      <c r="D96" s="106"/>
-      <c r="E96" s="106"/>
-      <c r="F96" s="106"/>
-      <c r="G96" s="106"/>
-      <c r="H96" s="106"/>
-      <c r="I96" s="106"/>
-      <c r="J96" s="106"/>
-      <c r="K96" s="106"/>
-      <c r="L96" s="106"/>
-      <c r="M96" s="106"/>
-      <c r="N96" s="106"/>
+      <c r="A96" s="108"/>
+      <c r="B96" s="108"/>
+      <c r="C96" s="108"/>
+      <c r="D96" s="108"/>
+      <c r="E96" s="108"/>
+      <c r="F96" s="108"/>
+      <c r="G96" s="108"/>
+      <c r="H96" s="108"/>
+      <c r="I96" s="108"/>
+      <c r="J96" s="108"/>
+      <c r="K96" s="108"/>
+      <c r="L96" s="108"/>
+      <c r="M96" s="108"/>
+      <c r="N96" s="108"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="106"/>
-      <c r="B97" s="106"/>
-      <c r="C97" s="106"/>
-      <c r="D97" s="106"/>
-      <c r="E97" s="106"/>
-      <c r="F97" s="106"/>
-      <c r="G97" s="106"/>
-      <c r="H97" s="106"/>
-      <c r="I97" s="106"/>
-      <c r="J97" s="106"/>
-      <c r="K97" s="106"/>
-      <c r="L97" s="106"/>
-      <c r="M97" s="106"/>
-      <c r="N97" s="106"/>
+      <c r="A97" s="108"/>
+      <c r="B97" s="108"/>
+      <c r="C97" s="108"/>
+      <c r="D97" s="108"/>
+      <c r="E97" s="108"/>
+      <c r="F97" s="108"/>
+      <c r="G97" s="108"/>
+      <c r="H97" s="108"/>
+      <c r="I97" s="108"/>
+      <c r="J97" s="108"/>
+      <c r="K97" s="108"/>
+      <c r="L97" s="108"/>
+      <c r="M97" s="108"/>
+      <c r="N97" s="108"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="106"/>
-      <c r="B98" s="106"/>
-      <c r="C98" s="106"/>
-      <c r="D98" s="106"/>
-      <c r="E98" s="106"/>
-      <c r="F98" s="106"/>
-      <c r="G98" s="106"/>
-      <c r="H98" s="106"/>
-      <c r="I98" s="106"/>
-      <c r="J98" s="106"/>
-      <c r="K98" s="106"/>
-      <c r="L98" s="106"/>
-      <c r="M98" s="106"/>
-      <c r="N98" s="106"/>
+      <c r="A98" s="108"/>
+      <c r="B98" s="108"/>
+      <c r="C98" s="108"/>
+      <c r="D98" s="108"/>
+      <c r="E98" s="108"/>
+      <c r="F98" s="108"/>
+      <c r="G98" s="108"/>
+      <c r="H98" s="108"/>
+      <c r="I98" s="108"/>
+      <c r="J98" s="108"/>
+      <c r="K98" s="108"/>
+      <c r="L98" s="108"/>
+      <c r="M98" s="108"/>
+      <c r="N98" s="108"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="106"/>
-      <c r="B99" s="106"/>
-      <c r="C99" s="106"/>
-      <c r="D99" s="106"/>
-      <c r="E99" s="106"/>
-      <c r="F99" s="106"/>
-      <c r="G99" s="106"/>
-      <c r="H99" s="106"/>
-      <c r="I99" s="106"/>
-      <c r="J99" s="106"/>
-      <c r="K99" s="106"/>
-      <c r="L99" s="106"/>
-      <c r="M99" s="106"/>
-      <c r="N99" s="106"/>
+      <c r="A99" s="108"/>
+      <c r="B99" s="108"/>
+      <c r="C99" s="108"/>
+      <c r="D99" s="108"/>
+      <c r="E99" s="108"/>
+      <c r="F99" s="108"/>
+      <c r="G99" s="108"/>
+      <c r="H99" s="108"/>
+      <c r="I99" s="108"/>
+      <c r="J99" s="108"/>
+      <c r="K99" s="108"/>
+      <c r="L99" s="108"/>
+      <c r="M99" s="108"/>
+      <c r="N99" s="108"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="106"/>
-      <c r="B100" s="106"/>
-      <c r="C100" s="106"/>
-      <c r="D100" s="106"/>
-      <c r="E100" s="106"/>
-      <c r="F100" s="106"/>
-      <c r="G100" s="106"/>
-      <c r="H100" s="106"/>
-      <c r="I100" s="106"/>
-      <c r="J100" s="106"/>
-      <c r="K100" s="106"/>
-      <c r="L100" s="106"/>
-      <c r="M100" s="106"/>
-      <c r="N100" s="106"/>
+      <c r="A100" s="108"/>
+      <c r="B100" s="108"/>
+      <c r="C100" s="108"/>
+      <c r="D100" s="108"/>
+      <c r="E100" s="108"/>
+      <c r="F100" s="108"/>
+      <c r="G100" s="108"/>
+      <c r="H100" s="108"/>
+      <c r="I100" s="108"/>
+      <c r="J100" s="108"/>
+      <c r="K100" s="108"/>
+      <c r="L100" s="108"/>
+      <c r="M100" s="108"/>
+      <c r="N100" s="108"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="106"/>
-      <c r="B101" s="106"/>
-      <c r="C101" s="106"/>
-      <c r="D101" s="106"/>
-      <c r="E101" s="106"/>
-      <c r="F101" s="106"/>
-      <c r="G101" s="106"/>
-      <c r="H101" s="106"/>
-      <c r="I101" s="106"/>
-      <c r="J101" s="106"/>
-      <c r="K101" s="106"/>
-      <c r="L101" s="106"/>
-      <c r="M101" s="106"/>
-      <c r="N101" s="106"/>
+      <c r="A101" s="108"/>
+      <c r="B101" s="108"/>
+      <c r="C101" s="108"/>
+      <c r="D101" s="108"/>
+      <c r="E101" s="108"/>
+      <c r="F101" s="108"/>
+      <c r="G101" s="108"/>
+      <c r="H101" s="108"/>
+      <c r="I101" s="108"/>
+      <c r="J101" s="108"/>
+      <c r="K101" s="108"/>
+      <c r="L101" s="108"/>
+      <c r="M101" s="108"/>
+      <c r="N101" s="108"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="106"/>
-      <c r="B102" s="106"/>
-      <c r="C102" s="106"/>
-      <c r="D102" s="106"/>
-      <c r="E102" s="106"/>
-      <c r="F102" s="106"/>
-      <c r="G102" s="106"/>
-      <c r="H102" s="106"/>
-      <c r="I102" s="106"/>
-      <c r="J102" s="106"/>
-      <c r="K102" s="106"/>
-      <c r="L102" s="106"/>
-      <c r="M102" s="106"/>
-      <c r="N102" s="106"/>
+      <c r="A102" s="108"/>
+      <c r="B102" s="108"/>
+      <c r="C102" s="108"/>
+      <c r="D102" s="108"/>
+      <c r="E102" s="108"/>
+      <c r="F102" s="108"/>
+      <c r="G102" s="108"/>
+      <c r="H102" s="108"/>
+      <c r="I102" s="108"/>
+      <c r="J102" s="108"/>
+      <c r="K102" s="108"/>
+      <c r="L102" s="108"/>
+      <c r="M102" s="108"/>
+      <c r="N102" s="108"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="106"/>
-      <c r="B103" s="106"/>
-      <c r="C103" s="106"/>
-      <c r="D103" s="106"/>
-      <c r="E103" s="106"/>
-      <c r="F103" s="106"/>
-      <c r="G103" s="106"/>
-      <c r="H103" s="106"/>
-      <c r="I103" s="106"/>
-      <c r="J103" s="106"/>
-      <c r="K103" s="106"/>
-      <c r="L103" s="106"/>
-      <c r="M103" s="106"/>
-      <c r="N103" s="106"/>
+      <c r="A103" s="108"/>
+      <c r="B103" s="108"/>
+      <c r="C103" s="108"/>
+      <c r="D103" s="108"/>
+      <c r="E103" s="108"/>
+      <c r="F103" s="108"/>
+      <c r="G103" s="108"/>
+      <c r="H103" s="108"/>
+      <c r="I103" s="108"/>
+      <c r="J103" s="108"/>
+      <c r="K103" s="108"/>
+      <c r="L103" s="108"/>
+      <c r="M103" s="108"/>
+      <c r="N103" s="108"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="106"/>
-      <c r="B104" s="106"/>
-      <c r="C104" s="106"/>
-      <c r="D104" s="106"/>
-      <c r="E104" s="106"/>
-      <c r="F104" s="106"/>
-      <c r="G104" s="106"/>
-      <c r="H104" s="106"/>
-      <c r="I104" s="106"/>
-      <c r="J104" s="106"/>
-      <c r="K104" s="106"/>
-      <c r="L104" s="106"/>
-      <c r="M104" s="106"/>
-      <c r="N104" s="106"/>
+      <c r="A104" s="108"/>
+      <c r="B104" s="108"/>
+      <c r="C104" s="108"/>
+      <c r="D104" s="108"/>
+      <c r="E104" s="108"/>
+      <c r="F104" s="108"/>
+      <c r="G104" s="108"/>
+      <c r="H104" s="108"/>
+      <c r="I104" s="108"/>
+      <c r="J104" s="108"/>
+      <c r="K104" s="108"/>
+      <c r="L104" s="108"/>
+      <c r="M104" s="108"/>
+      <c r="N104" s="108"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="106"/>
-      <c r="B105" s="106"/>
-      <c r="C105" s="106"/>
-      <c r="D105" s="106"/>
-      <c r="E105" s="106"/>
-      <c r="F105" s="106"/>
-      <c r="G105" s="106"/>
-      <c r="H105" s="106"/>
-      <c r="I105" s="106"/>
-      <c r="J105" s="106"/>
-      <c r="K105" s="106"/>
-      <c r="L105" s="106"/>
-      <c r="M105" s="106"/>
-      <c r="N105" s="106"/>
+      <c r="A105" s="108"/>
+      <c r="B105" s="108"/>
+      <c r="C105" s="108"/>
+      <c r="D105" s="108"/>
+      <c r="E105" s="108"/>
+      <c r="F105" s="108"/>
+      <c r="G105" s="108"/>
+      <c r="H105" s="108"/>
+      <c r="I105" s="108"/>
+      <c r="J105" s="108"/>
+      <c r="K105" s="108"/>
+      <c r="L105" s="108"/>
+      <c r="M105" s="108"/>
+      <c r="N105" s="108"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="106"/>
-      <c r="B106" s="106"/>
-      <c r="C106" s="106"/>
-      <c r="D106" s="106"/>
-      <c r="E106" s="106"/>
-      <c r="F106" s="106"/>
-      <c r="G106" s="106"/>
-      <c r="H106" s="106"/>
-      <c r="I106" s="106"/>
-      <c r="J106" s="106"/>
-      <c r="K106" s="106"/>
-      <c r="L106" s="106"/>
-      <c r="M106" s="106"/>
-      <c r="N106" s="106"/>
+      <c r="A106" s="108"/>
+      <c r="B106" s="108"/>
+      <c r="C106" s="108"/>
+      <c r="D106" s="108"/>
+      <c r="E106" s="108"/>
+      <c r="F106" s="108"/>
+      <c r="G106" s="108"/>
+      <c r="H106" s="108"/>
+      <c r="I106" s="108"/>
+      <c r="J106" s="108"/>
+      <c r="K106" s="108"/>
+      <c r="L106" s="108"/>
+      <c r="M106" s="108"/>
+      <c r="N106" s="108"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="106"/>
-      <c r="B107" s="106"/>
-      <c r="C107" s="106"/>
-      <c r="D107" s="106"/>
-      <c r="E107" s="106"/>
-      <c r="F107" s="106"/>
-      <c r="G107" s="106"/>
-      <c r="H107" s="106"/>
-      <c r="I107" s="106"/>
-      <c r="J107" s="106"/>
-      <c r="K107" s="106"/>
-      <c r="L107" s="106"/>
-      <c r="M107" s="106"/>
-      <c r="N107" s="106"/>
+      <c r="A107" s="108"/>
+      <c r="B107" s="108"/>
+      <c r="C107" s="108"/>
+      <c r="D107" s="108"/>
+      <c r="E107" s="108"/>
+      <c r="F107" s="108"/>
+      <c r="G107" s="108"/>
+      <c r="H107" s="108"/>
+      <c r="I107" s="108"/>
+      <c r="J107" s="108"/>
+      <c r="K107" s="108"/>
+      <c r="L107" s="108"/>
+      <c r="M107" s="108"/>
+      <c r="N107" s="108"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="106"/>
-      <c r="B108" s="106"/>
-      <c r="C108" s="106"/>
-      <c r="D108" s="106"/>
-      <c r="E108" s="106"/>
-      <c r="F108" s="106"/>
-      <c r="G108" s="106"/>
-      <c r="H108" s="106"/>
-      <c r="I108" s="106"/>
-      <c r="J108" s="106"/>
-      <c r="K108" s="106"/>
-      <c r="L108" s="106"/>
-      <c r="M108" s="106"/>
-      <c r="N108" s="106"/>
+      <c r="A108" s="108"/>
+      <c r="B108" s="108"/>
+      <c r="C108" s="108"/>
+      <c r="D108" s="108"/>
+      <c r="E108" s="108"/>
+      <c r="F108" s="108"/>
+      <c r="G108" s="108"/>
+      <c r="H108" s="108"/>
+      <c r="I108" s="108"/>
+      <c r="J108" s="108"/>
+      <c r="K108" s="108"/>
+      <c r="L108" s="108"/>
+      <c r="M108" s="108"/>
+      <c r="N108" s="108"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="106"/>
-      <c r="B109" s="106"/>
-      <c r="C109" s="106"/>
-      <c r="D109" s="106"/>
-      <c r="E109" s="106"/>
-      <c r="F109" s="106"/>
-      <c r="G109" s="106"/>
-      <c r="H109" s="106"/>
-      <c r="I109" s="106"/>
-      <c r="J109" s="106"/>
-      <c r="K109" s="106"/>
-      <c r="L109" s="106"/>
-      <c r="M109" s="106"/>
-      <c r="N109" s="106"/>
+      <c r="A109" s="108"/>
+      <c r="B109" s="108"/>
+      <c r="C109" s="108"/>
+      <c r="D109" s="108"/>
+      <c r="E109" s="108"/>
+      <c r="F109" s="108"/>
+      <c r="G109" s="108"/>
+      <c r="H109" s="108"/>
+      <c r="I109" s="108"/>
+      <c r="J109" s="108"/>
+      <c r="K109" s="108"/>
+      <c r="L109" s="108"/>
+      <c r="M109" s="108"/>
+      <c r="N109" s="108"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="106"/>
-      <c r="B110" s="106"/>
-      <c r="C110" s="106"/>
-      <c r="D110" s="106"/>
-      <c r="E110" s="106"/>
-      <c r="F110" s="106"/>
-      <c r="G110" s="106"/>
-      <c r="H110" s="106"/>
-      <c r="I110" s="106"/>
-      <c r="J110" s="106"/>
-      <c r="K110" s="106"/>
-      <c r="L110" s="106"/>
-      <c r="M110" s="106"/>
-      <c r="N110" s="106"/>
+      <c r="A110" s="108"/>
+      <c r="B110" s="108"/>
+      <c r="C110" s="108"/>
+      <c r="D110" s="108"/>
+      <c r="E110" s="108"/>
+      <c r="F110" s="108"/>
+      <c r="G110" s="108"/>
+      <c r="H110" s="108"/>
+      <c r="I110" s="108"/>
+      <c r="J110" s="108"/>
+      <c r="K110" s="108"/>
+      <c r="L110" s="108"/>
+      <c r="M110" s="108"/>
+      <c r="N110" s="108"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="106"/>
-      <c r="B111" s="106"/>
-      <c r="C111" s="106"/>
-      <c r="D111" s="106"/>
-      <c r="E111" s="106"/>
-      <c r="F111" s="106"/>
-      <c r="G111" s="106"/>
-      <c r="H111" s="106"/>
-      <c r="I111" s="106"/>
-      <c r="J111" s="106"/>
-      <c r="K111" s="106"/>
-      <c r="L111" s="106"/>
-      <c r="M111" s="106"/>
-      <c r="N111" s="106"/>
+      <c r="A111" s="108"/>
+      <c r="B111" s="108"/>
+      <c r="C111" s="108"/>
+      <c r="D111" s="108"/>
+      <c r="E111" s="108"/>
+      <c r="F111" s="108"/>
+      <c r="G111" s="108"/>
+      <c r="H111" s="108"/>
+      <c r="I111" s="108"/>
+      <c r="J111" s="108"/>
+      <c r="K111" s="108"/>
+      <c r="L111" s="108"/>
+      <c r="M111" s="108"/>
+      <c r="N111" s="108"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="106"/>
-      <c r="B112" s="106"/>
-      <c r="C112" s="106"/>
-      <c r="D112" s="106"/>
-      <c r="E112" s="106"/>
-      <c r="F112" s="106"/>
-      <c r="G112" s="106"/>
-      <c r="H112" s="106"/>
-      <c r="I112" s="106"/>
-      <c r="J112" s="106"/>
-      <c r="K112" s="106"/>
-      <c r="L112" s="106"/>
-      <c r="M112" s="106"/>
-      <c r="N112" s="106"/>
+      <c r="A112" s="108"/>
+      <c r="B112" s="108"/>
+      <c r="C112" s="108"/>
+      <c r="D112" s="108"/>
+      <c r="E112" s="108"/>
+      <c r="F112" s="108"/>
+      <c r="G112" s="108"/>
+      <c r="H112" s="108"/>
+      <c r="I112" s="108"/>
+      <c r="J112" s="108"/>
+      <c r="K112" s="108"/>
+      <c r="L112" s="108"/>
+      <c r="M112" s="108"/>
+      <c r="N112" s="108"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="106"/>
-      <c r="B113" s="106"/>
-      <c r="C113" s="106"/>
-      <c r="D113" s="106"/>
-      <c r="E113" s="106"/>
-      <c r="F113" s="106"/>
-      <c r="G113" s="106"/>
-      <c r="H113" s="106"/>
-      <c r="I113" s="106"/>
-      <c r="J113" s="106"/>
-      <c r="K113" s="106"/>
-      <c r="L113" s="106"/>
-      <c r="M113" s="106"/>
-      <c r="N113" s="106"/>
+      <c r="A113" s="108"/>
+      <c r="B113" s="108"/>
+      <c r="C113" s="108"/>
+      <c r="D113" s="108"/>
+      <c r="E113" s="108"/>
+      <c r="F113" s="108"/>
+      <c r="G113" s="108"/>
+      <c r="H113" s="108"/>
+      <c r="I113" s="108"/>
+      <c r="J113" s="108"/>
+      <c r="K113" s="108"/>
+      <c r="L113" s="108"/>
+      <c r="M113" s="108"/>
+      <c r="N113" s="108"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="106"/>
-      <c r="B114" s="106"/>
-      <c r="C114" s="106"/>
-      <c r="D114" s="106"/>
-      <c r="E114" s="106"/>
-      <c r="F114" s="106"/>
-      <c r="G114" s="106"/>
-      <c r="H114" s="106"/>
-      <c r="I114" s="106"/>
-      <c r="J114" s="106"/>
-      <c r="K114" s="106"/>
-      <c r="L114" s="106"/>
-      <c r="M114" s="106"/>
-      <c r="N114" s="106"/>
+      <c r="A114" s="108"/>
+      <c r="B114" s="108"/>
+      <c r="C114" s="108"/>
+      <c r="D114" s="108"/>
+      <c r="E114" s="108"/>
+      <c r="F114" s="108"/>
+      <c r="G114" s="108"/>
+      <c r="H114" s="108"/>
+      <c r="I114" s="108"/>
+      <c r="J114" s="108"/>
+      <c r="K114" s="108"/>
+      <c r="L114" s="108"/>
+      <c r="M114" s="108"/>
+      <c r="N114" s="108"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="106"/>
-      <c r="B115" s="106"/>
-      <c r="C115" s="106"/>
-      <c r="D115" s="106"/>
-      <c r="E115" s="106"/>
-      <c r="F115" s="106"/>
-      <c r="G115" s="106"/>
-      <c r="H115" s="106"/>
-      <c r="I115" s="106"/>
-      <c r="J115" s="106"/>
-      <c r="K115" s="106"/>
-      <c r="L115" s="106"/>
-      <c r="M115" s="106"/>
-      <c r="N115" s="106"/>
+      <c r="A115" s="108"/>
+      <c r="B115" s="108"/>
+      <c r="C115" s="108"/>
+      <c r="D115" s="108"/>
+      <c r="E115" s="108"/>
+      <c r="F115" s="108"/>
+      <c r="G115" s="108"/>
+      <c r="H115" s="108"/>
+      <c r="I115" s="108"/>
+      <c r="J115" s="108"/>
+      <c r="K115" s="108"/>
+      <c r="L115" s="108"/>
+      <c r="M115" s="108"/>
+      <c r="N115" s="108"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="106"/>
-      <c r="B116" s="106"/>
-      <c r="C116" s="106"/>
-      <c r="D116" s="106"/>
-      <c r="E116" s="106"/>
-      <c r="F116" s="106"/>
-      <c r="G116" s="106"/>
-      <c r="H116" s="106"/>
-      <c r="I116" s="106"/>
-      <c r="J116" s="106"/>
-      <c r="K116" s="106"/>
-      <c r="L116" s="106"/>
-      <c r="M116" s="106"/>
-      <c r="N116" s="106"/>
+      <c r="A116" s="108"/>
+      <c r="B116" s="108"/>
+      <c r="C116" s="108"/>
+      <c r="D116" s="108"/>
+      <c r="E116" s="108"/>
+      <c r="F116" s="108"/>
+      <c r="G116" s="108"/>
+      <c r="H116" s="108"/>
+      <c r="I116" s="108"/>
+      <c r="J116" s="108"/>
+      <c r="K116" s="108"/>
+      <c r="L116" s="108"/>
+      <c r="M116" s="108"/>
+      <c r="N116" s="108"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="106"/>
-      <c r="B117" s="106"/>
-      <c r="C117" s="106"/>
-      <c r="D117" s="106"/>
-      <c r="E117" s="106"/>
-      <c r="F117" s="106"/>
-      <c r="G117" s="106"/>
-      <c r="H117" s="106"/>
-      <c r="I117" s="106"/>
-      <c r="J117" s="106"/>
-      <c r="K117" s="106"/>
-      <c r="L117" s="106"/>
-      <c r="M117" s="106"/>
-      <c r="N117" s="106"/>
+      <c r="A117" s="108"/>
+      <c r="B117" s="108"/>
+      <c r="C117" s="108"/>
+      <c r="D117" s="108"/>
+      <c r="E117" s="108"/>
+      <c r="F117" s="108"/>
+      <c r="G117" s="108"/>
+      <c r="H117" s="108"/>
+      <c r="I117" s="108"/>
+      <c r="J117" s="108"/>
+      <c r="K117" s="108"/>
+      <c r="L117" s="108"/>
+      <c r="M117" s="108"/>
+      <c r="N117" s="108"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="106"/>
-      <c r="B118" s="106"/>
-      <c r="C118" s="106"/>
-      <c r="D118" s="106"/>
-      <c r="E118" s="106"/>
-      <c r="F118" s="106"/>
-      <c r="G118" s="106"/>
-      <c r="H118" s="106"/>
-      <c r="I118" s="106"/>
-      <c r="J118" s="106"/>
-      <c r="K118" s="106"/>
-      <c r="L118" s="106"/>
-      <c r="M118" s="106"/>
-      <c r="N118" s="106"/>
+      <c r="A118" s="108"/>
+      <c r="B118" s="108"/>
+      <c r="C118" s="108"/>
+      <c r="D118" s="108"/>
+      <c r="E118" s="108"/>
+      <c r="F118" s="108"/>
+      <c r="G118" s="108"/>
+      <c r="H118" s="108"/>
+      <c r="I118" s="108"/>
+      <c r="J118" s="108"/>
+      <c r="K118" s="108"/>
+      <c r="L118" s="108"/>
+      <c r="M118" s="108"/>
+      <c r="N118" s="108"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="106"/>
-      <c r="B119" s="106"/>
-      <c r="C119" s="106"/>
-      <c r="D119" s="106"/>
-      <c r="E119" s="106"/>
-      <c r="F119" s="106"/>
-      <c r="G119" s="106"/>
-      <c r="H119" s="106"/>
-      <c r="I119" s="106"/>
-      <c r="J119" s="106"/>
-      <c r="K119" s="106"/>
-      <c r="L119" s="106"/>
-      <c r="M119" s="106"/>
-      <c r="N119" s="106"/>
+      <c r="A119" s="108"/>
+      <c r="B119" s="108"/>
+      <c r="C119" s="108"/>
+      <c r="D119" s="108"/>
+      <c r="E119" s="108"/>
+      <c r="F119" s="108"/>
+      <c r="G119" s="108"/>
+      <c r="H119" s="108"/>
+      <c r="I119" s="108"/>
+      <c r="J119" s="108"/>
+      <c r="K119" s="108"/>
+      <c r="L119" s="108"/>
+      <c r="M119" s="108"/>
+      <c r="N119" s="108"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="106"/>
-      <c r="B120" s="106"/>
-      <c r="C120" s="106"/>
-      <c r="D120" s="106"/>
-      <c r="E120" s="106"/>
-      <c r="F120" s="106"/>
-      <c r="G120" s="106"/>
-      <c r="H120" s="106"/>
-      <c r="I120" s="106"/>
-      <c r="J120" s="106"/>
-      <c r="K120" s="106"/>
-      <c r="L120" s="106"/>
-      <c r="M120" s="106"/>
-      <c r="N120" s="106"/>
+      <c r="A120" s="108"/>
+      <c r="B120" s="108"/>
+      <c r="C120" s="108"/>
+      <c r="D120" s="108"/>
+      <c r="E120" s="108"/>
+      <c r="F120" s="108"/>
+      <c r="G120" s="108"/>
+      <c r="H120" s="108"/>
+      <c r="I120" s="108"/>
+      <c r="J120" s="108"/>
+      <c r="K120" s="108"/>
+      <c r="L120" s="108"/>
+      <c r="M120" s="108"/>
+      <c r="N120" s="108"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="106"/>
-      <c r="B121" s="106"/>
-      <c r="C121" s="106"/>
-      <c r="D121" s="106"/>
-      <c r="E121" s="106"/>
-      <c r="F121" s="106"/>
-      <c r="G121" s="106"/>
-      <c r="H121" s="106"/>
-      <c r="I121" s="106"/>
-      <c r="J121" s="106"/>
-      <c r="K121" s="106"/>
-      <c r="L121" s="106"/>
-      <c r="M121" s="106"/>
-      <c r="N121" s="106"/>
+      <c r="A121" s="108"/>
+      <c r="B121" s="108"/>
+      <c r="C121" s="108"/>
+      <c r="D121" s="108"/>
+      <c r="E121" s="108"/>
+      <c r="F121" s="108"/>
+      <c r="G121" s="108"/>
+      <c r="H121" s="108"/>
+      <c r="I121" s="108"/>
+      <c r="J121" s="108"/>
+      <c r="K121" s="108"/>
+      <c r="L121" s="108"/>
+      <c r="M121" s="108"/>
+      <c r="N121" s="108"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="106"/>
-      <c r="B122" s="106"/>
-      <c r="C122" s="106"/>
-      <c r="D122" s="106"/>
-      <c r="E122" s="106"/>
-      <c r="F122" s="106"/>
-      <c r="G122" s="106"/>
-      <c r="H122" s="106"/>
-      <c r="I122" s="106"/>
-      <c r="J122" s="106"/>
-      <c r="K122" s="106"/>
-      <c r="L122" s="106"/>
-      <c r="M122" s="106"/>
-      <c r="N122" s="106"/>
+      <c r="A122" s="108"/>
+      <c r="B122" s="108"/>
+      <c r="C122" s="108"/>
+      <c r="D122" s="108"/>
+      <c r="E122" s="108"/>
+      <c r="F122" s="108"/>
+      <c r="G122" s="108"/>
+      <c r="H122" s="108"/>
+      <c r="I122" s="108"/>
+      <c r="J122" s="108"/>
+      <c r="K122" s="108"/>
+      <c r="L122" s="108"/>
+      <c r="M122" s="108"/>
+      <c r="N122" s="108"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="106"/>
-      <c r="B123" s="106"/>
-      <c r="C123" s="106"/>
-      <c r="D123" s="106"/>
-      <c r="E123" s="106"/>
-      <c r="F123" s="106"/>
-      <c r="G123" s="106"/>
-      <c r="H123" s="106"/>
-      <c r="I123" s="106"/>
-      <c r="J123" s="106"/>
-      <c r="K123" s="106"/>
-      <c r="L123" s="106"/>
-      <c r="M123" s="106"/>
-      <c r="N123" s="106"/>
+      <c r="A123" s="108"/>
+      <c r="B123" s="108"/>
+      <c r="C123" s="108"/>
+      <c r="D123" s="108"/>
+      <c r="E123" s="108"/>
+      <c r="F123" s="108"/>
+      <c r="G123" s="108"/>
+      <c r="H123" s="108"/>
+      <c r="I123" s="108"/>
+      <c r="J123" s="108"/>
+      <c r="K123" s="108"/>
+      <c r="L123" s="108"/>
+      <c r="M123" s="108"/>
+      <c r="N123" s="108"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="106"/>
-      <c r="B124" s="106"/>
-      <c r="C124" s="106"/>
-      <c r="D124" s="106"/>
-      <c r="E124" s="106"/>
-      <c r="F124" s="106"/>
-      <c r="G124" s="106"/>
-      <c r="H124" s="106"/>
-      <c r="I124" s="106"/>
-      <c r="J124" s="106"/>
-      <c r="K124" s="106"/>
-      <c r="L124" s="106"/>
-      <c r="M124" s="106"/>
-      <c r="N124" s="106"/>
+      <c r="A124" s="108"/>
+      <c r="B124" s="108"/>
+      <c r="C124" s="108"/>
+      <c r="D124" s="108"/>
+      <c r="E124" s="108"/>
+      <c r="F124" s="108"/>
+      <c r="G124" s="108"/>
+      <c r="H124" s="108"/>
+      <c r="I124" s="108"/>
+      <c r="J124" s="108"/>
+      <c r="K124" s="108"/>
+      <c r="L124" s="108"/>
+      <c r="M124" s="108"/>
+      <c r="N124" s="108"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="106"/>
-      <c r="B125" s="106"/>
-      <c r="C125" s="106"/>
-      <c r="D125" s="106"/>
-      <c r="E125" s="106"/>
-      <c r="F125" s="106"/>
-      <c r="G125" s="106"/>
-      <c r="H125" s="106"/>
-      <c r="I125" s="106"/>
-      <c r="J125" s="106"/>
-      <c r="K125" s="106"/>
-      <c r="L125" s="106"/>
-      <c r="M125" s="106"/>
-      <c r="N125" s="106"/>
+      <c r="A125" s="108"/>
+      <c r="B125" s="108"/>
+      <c r="C125" s="108"/>
+      <c r="D125" s="108"/>
+      <c r="E125" s="108"/>
+      <c r="F125" s="108"/>
+      <c r="G125" s="108"/>
+      <c r="H125" s="108"/>
+      <c r="I125" s="108"/>
+      <c r="J125" s="108"/>
+      <c r="K125" s="108"/>
+      <c r="L125" s="108"/>
+      <c r="M125" s="108"/>
+      <c r="N125" s="108"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="106"/>
-      <c r="B126" s="106"/>
-      <c r="C126" s="106"/>
-      <c r="D126" s="106"/>
-      <c r="E126" s="106"/>
-      <c r="F126" s="106"/>
-      <c r="G126" s="106"/>
-      <c r="H126" s="106"/>
-      <c r="I126" s="106"/>
-      <c r="J126" s="106"/>
-      <c r="K126" s="106"/>
-      <c r="L126" s="106"/>
-      <c r="M126" s="106"/>
-      <c r="N126" s="106"/>
+      <c r="A126" s="108"/>
+      <c r="B126" s="108"/>
+      <c r="C126" s="108"/>
+      <c r="D126" s="108"/>
+      <c r="E126" s="108"/>
+      <c r="F126" s="108"/>
+      <c r="G126" s="108"/>
+      <c r="H126" s="108"/>
+      <c r="I126" s="108"/>
+      <c r="J126" s="108"/>
+      <c r="K126" s="108"/>
+      <c r="L126" s="108"/>
+      <c r="M126" s="108"/>
+      <c r="N126" s="108"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="106"/>
-      <c r="B127" s="106"/>
-      <c r="C127" s="106"/>
-      <c r="D127" s="106"/>
-      <c r="E127" s="106"/>
-      <c r="F127" s="106"/>
-      <c r="G127" s="106"/>
-      <c r="H127" s="106"/>
-      <c r="I127" s="106"/>
-      <c r="J127" s="106"/>
-      <c r="K127" s="106"/>
-      <c r="L127" s="106"/>
-      <c r="M127" s="106"/>
-      <c r="N127" s="106"/>
+      <c r="A127" s="108"/>
+      <c r="B127" s="108"/>
+      <c r="C127" s="108"/>
+      <c r="D127" s="108"/>
+      <c r="E127" s="108"/>
+      <c r="F127" s="108"/>
+      <c r="G127" s="108"/>
+      <c r="H127" s="108"/>
+      <c r="I127" s="108"/>
+      <c r="J127" s="108"/>
+      <c r="K127" s="108"/>
+      <c r="L127" s="108"/>
+      <c r="M127" s="108"/>
+      <c r="N127" s="108"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="106"/>
-      <c r="B128" s="106"/>
-      <c r="C128" s="106"/>
-      <c r="D128" s="106"/>
-      <c r="E128" s="106"/>
-      <c r="F128" s="106"/>
-      <c r="G128" s="106"/>
-      <c r="H128" s="106"/>
-      <c r="I128" s="106"/>
-      <c r="J128" s="106"/>
-      <c r="K128" s="106"/>
-      <c r="L128" s="106"/>
-      <c r="M128" s="106"/>
-      <c r="N128" s="106"/>
+      <c r="A128" s="108"/>
+      <c r="B128" s="108"/>
+      <c r="C128" s="108"/>
+      <c r="D128" s="108"/>
+      <c r="E128" s="108"/>
+      <c r="F128" s="108"/>
+      <c r="G128" s="108"/>
+      <c r="H128" s="108"/>
+      <c r="I128" s="108"/>
+      <c r="J128" s="108"/>
+      <c r="K128" s="108"/>
+      <c r="L128" s="108"/>
+      <c r="M128" s="108"/>
+      <c r="N128" s="108"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="106"/>
-      <c r="B129" s="106"/>
-      <c r="C129" s="106"/>
-      <c r="D129" s="106"/>
-      <c r="E129" s="106"/>
-      <c r="F129" s="106"/>
-      <c r="G129" s="106"/>
-      <c r="H129" s="106"/>
-      <c r="I129" s="106"/>
-      <c r="J129" s="106"/>
-      <c r="K129" s="106"/>
-      <c r="L129" s="106"/>
-      <c r="M129" s="106"/>
-      <c r="N129" s="106"/>
+      <c r="A129" s="108"/>
+      <c r="B129" s="108"/>
+      <c r="C129" s="108"/>
+      <c r="D129" s="108"/>
+      <c r="E129" s="108"/>
+      <c r="F129" s="108"/>
+      <c r="G129" s="108"/>
+      <c r="H129" s="108"/>
+      <c r="I129" s="108"/>
+      <c r="J129" s="108"/>
+      <c r="K129" s="108"/>
+      <c r="L129" s="108"/>
+      <c r="M129" s="108"/>
+      <c r="N129" s="108"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="106"/>
-      <c r="B130" s="106"/>
-      <c r="C130" s="106"/>
-      <c r="D130" s="106"/>
-      <c r="E130" s="106"/>
-      <c r="F130" s="106"/>
-      <c r="G130" s="106"/>
-      <c r="H130" s="106"/>
-      <c r="I130" s="106"/>
-      <c r="J130" s="106"/>
-      <c r="K130" s="106"/>
-      <c r="L130" s="106"/>
-      <c r="M130" s="106"/>
-      <c r="N130" s="106"/>
+      <c r="A130" s="108"/>
+      <c r="B130" s="108"/>
+      <c r="C130" s="108"/>
+      <c r="D130" s="108"/>
+      <c r="E130" s="108"/>
+      <c r="F130" s="108"/>
+      <c r="G130" s="108"/>
+      <c r="H130" s="108"/>
+      <c r="I130" s="108"/>
+      <c r="J130" s="108"/>
+      <c r="K130" s="108"/>
+      <c r="L130" s="108"/>
+      <c r="M130" s="108"/>
+      <c r="N130" s="108"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="106"/>
-      <c r="B131" s="106"/>
-      <c r="C131" s="106"/>
-      <c r="D131" s="106"/>
-      <c r="E131" s="106"/>
-      <c r="F131" s="106"/>
-      <c r="G131" s="106"/>
-      <c r="H131" s="106"/>
-      <c r="I131" s="106"/>
-      <c r="J131" s="106"/>
-      <c r="K131" s="106"/>
-      <c r="L131" s="106"/>
-      <c r="M131" s="106"/>
-      <c r="N131" s="106"/>
+      <c r="A131" s="108"/>
+      <c r="B131" s="108"/>
+      <c r="C131" s="108"/>
+      <c r="D131" s="108"/>
+      <c r="E131" s="108"/>
+      <c r="F131" s="108"/>
+      <c r="G131" s="108"/>
+      <c r="H131" s="108"/>
+      <c r="I131" s="108"/>
+      <c r="J131" s="108"/>
+      <c r="K131" s="108"/>
+      <c r="L131" s="108"/>
+      <c r="M131" s="108"/>
+      <c r="N131" s="108"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="106"/>
-      <c r="B132" s="106"/>
-      <c r="C132" s="106"/>
-      <c r="D132" s="106"/>
-      <c r="E132" s="106"/>
-      <c r="F132" s="106"/>
-      <c r="G132" s="106"/>
-      <c r="H132" s="106"/>
-      <c r="I132" s="106"/>
-      <c r="J132" s="106"/>
-      <c r="K132" s="106"/>
-      <c r="L132" s="106"/>
-      <c r="M132" s="106"/>
-      <c r="N132" s="106"/>
+      <c r="A132" s="108"/>
+      <c r="B132" s="108"/>
+      <c r="C132" s="108"/>
+      <c r="D132" s="108"/>
+      <c r="E132" s="108"/>
+      <c r="F132" s="108"/>
+      <c r="G132" s="108"/>
+      <c r="H132" s="108"/>
+      <c r="I132" s="108"/>
+      <c r="J132" s="108"/>
+      <c r="K132" s="108"/>
+      <c r="L132" s="108"/>
+      <c r="M132" s="108"/>
+      <c r="N132" s="108"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="106"/>
-      <c r="B133" s="106"/>
-      <c r="C133" s="106"/>
-      <c r="D133" s="106"/>
-      <c r="E133" s="106"/>
-      <c r="F133" s="106"/>
-      <c r="G133" s="106"/>
-      <c r="H133" s="106"/>
-      <c r="I133" s="106"/>
-      <c r="J133" s="106"/>
-      <c r="K133" s="106"/>
-      <c r="L133" s="106"/>
-      <c r="M133" s="106"/>
-      <c r="N133" s="106"/>
+      <c r="A133" s="108"/>
+      <c r="B133" s="108"/>
+      <c r="C133" s="108"/>
+      <c r="D133" s="108"/>
+      <c r="E133" s="108"/>
+      <c r="F133" s="108"/>
+      <c r="G133" s="108"/>
+      <c r="H133" s="108"/>
+      <c r="I133" s="108"/>
+      <c r="J133" s="108"/>
+      <c r="K133" s="108"/>
+      <c r="L133" s="108"/>
+      <c r="M133" s="108"/>
+      <c r="N133" s="108"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="106"/>
-      <c r="B134" s="106"/>
-      <c r="C134" s="106"/>
-      <c r="D134" s="106"/>
-      <c r="E134" s="106"/>
-      <c r="F134" s="106"/>
-      <c r="G134" s="106"/>
-      <c r="H134" s="106"/>
-      <c r="I134" s="106"/>
-      <c r="J134" s="106"/>
-      <c r="K134" s="106"/>
-      <c r="L134" s="106"/>
-      <c r="M134" s="106"/>
-      <c r="N134" s="106"/>
+      <c r="A134" s="108"/>
+      <c r="B134" s="108"/>
+      <c r="C134" s="108"/>
+      <c r="D134" s="108"/>
+      <c r="E134" s="108"/>
+      <c r="F134" s="108"/>
+      <c r="G134" s="108"/>
+      <c r="H134" s="108"/>
+      <c r="I134" s="108"/>
+      <c r="J134" s="108"/>
+      <c r="K134" s="108"/>
+      <c r="L134" s="108"/>
+      <c r="M134" s="108"/>
+      <c r="N134" s="108"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="106"/>
-      <c r="B135" s="106"/>
-      <c r="C135" s="106"/>
-      <c r="D135" s="106"/>
-      <c r="E135" s="106"/>
-      <c r="F135" s="106"/>
-      <c r="G135" s="106"/>
-      <c r="H135" s="106"/>
-      <c r="I135" s="106"/>
-      <c r="J135" s="106"/>
-      <c r="K135" s="106"/>
-      <c r="L135" s="106"/>
-      <c r="M135" s="106"/>
-      <c r="N135" s="106"/>
+      <c r="A135" s="108"/>
+      <c r="B135" s="108"/>
+      <c r="C135" s="108"/>
+      <c r="D135" s="108"/>
+      <c r="E135" s="108"/>
+      <c r="F135" s="108"/>
+      <c r="G135" s="108"/>
+      <c r="H135" s="108"/>
+      <c r="I135" s="108"/>
+      <c r="J135" s="108"/>
+      <c r="K135" s="108"/>
+      <c r="L135" s="108"/>
+      <c r="M135" s="108"/>
+      <c r="N135" s="108"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="106"/>
-      <c r="B136" s="106"/>
-      <c r="C136" s="106"/>
-      <c r="D136" s="106"/>
-      <c r="E136" s="106"/>
-      <c r="F136" s="106"/>
-      <c r="G136" s="106"/>
-      <c r="H136" s="106"/>
-      <c r="I136" s="106"/>
-      <c r="J136" s="106"/>
-      <c r="K136" s="106"/>
-      <c r="L136" s="106"/>
-      <c r="M136" s="106"/>
-      <c r="N136" s="106"/>
+      <c r="A136" s="108"/>
+      <c r="B136" s="108"/>
+      <c r="C136" s="108"/>
+      <c r="D136" s="108"/>
+      <c r="E136" s="108"/>
+      <c r="F136" s="108"/>
+      <c r="G136" s="108"/>
+      <c r="H136" s="108"/>
+      <c r="I136" s="108"/>
+      <c r="J136" s="108"/>
+      <c r="K136" s="108"/>
+      <c r="L136" s="108"/>
+      <c r="M136" s="108"/>
+      <c r="N136" s="108"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="106"/>
-      <c r="B137" s="106"/>
-      <c r="C137" s="106"/>
-      <c r="D137" s="106"/>
-      <c r="E137" s="106"/>
-      <c r="F137" s="106"/>
-      <c r="G137" s="106"/>
-      <c r="H137" s="106"/>
-      <c r="I137" s="106"/>
-      <c r="J137" s="106"/>
-      <c r="K137" s="106"/>
-      <c r="L137" s="106"/>
-      <c r="M137" s="106"/>
-      <c r="N137" s="106"/>
+      <c r="A137" s="108"/>
+      <c r="B137" s="108"/>
+      <c r="C137" s="108"/>
+      <c r="D137" s="108"/>
+      <c r="E137" s="108"/>
+      <c r="F137" s="108"/>
+      <c r="G137" s="108"/>
+      <c r="H137" s="108"/>
+      <c r="I137" s="108"/>
+      <c r="J137" s="108"/>
+      <c r="K137" s="108"/>
+      <c r="L137" s="108"/>
+      <c r="M137" s="108"/>
+      <c r="N137" s="108"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="106"/>
-      <c r="B138" s="106"/>
-      <c r="C138" s="106"/>
-      <c r="D138" s="106"/>
-      <c r="E138" s="106"/>
-      <c r="F138" s="106"/>
-      <c r="G138" s="106"/>
-      <c r="H138" s="106"/>
-      <c r="I138" s="106"/>
-      <c r="J138" s="106"/>
-      <c r="K138" s="106"/>
-      <c r="L138" s="106"/>
-      <c r="M138" s="106"/>
-      <c r="N138" s="106"/>
+      <c r="A138" s="108"/>
+      <c r="B138" s="108"/>
+      <c r="C138" s="108"/>
+      <c r="D138" s="108"/>
+      <c r="E138" s="108"/>
+      <c r="F138" s="108"/>
+      <c r="G138" s="108"/>
+      <c r="H138" s="108"/>
+      <c r="I138" s="108"/>
+      <c r="J138" s="108"/>
+      <c r="K138" s="108"/>
+      <c r="L138" s="108"/>
+      <c r="M138" s="108"/>
+      <c r="N138" s="108"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="106"/>
-      <c r="B139" s="106"/>
-      <c r="C139" s="106"/>
-      <c r="D139" s="106"/>
-      <c r="E139" s="106"/>
-      <c r="F139" s="106"/>
-      <c r="G139" s="106"/>
-      <c r="H139" s="106"/>
-      <c r="I139" s="106"/>
-      <c r="J139" s="106"/>
-      <c r="K139" s="106"/>
-      <c r="L139" s="106"/>
-      <c r="M139" s="106"/>
-      <c r="N139" s="106"/>
+      <c r="A139" s="108"/>
+      <c r="B139" s="108"/>
+      <c r="C139" s="108"/>
+      <c r="D139" s="108"/>
+      <c r="E139" s="108"/>
+      <c r="F139" s="108"/>
+      <c r="G139" s="108"/>
+      <c r="H139" s="108"/>
+      <c r="I139" s="108"/>
+      <c r="J139" s="108"/>
+      <c r="K139" s="108"/>
+      <c r="L139" s="108"/>
+      <c r="M139" s="108"/>
+      <c r="N139" s="108"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="106"/>
-      <c r="B140" s="106"/>
-      <c r="C140" s="106"/>
-      <c r="D140" s="106"/>
-      <c r="E140" s="106"/>
-      <c r="F140" s="106"/>
-      <c r="G140" s="106"/>
-      <c r="H140" s="106"/>
-      <c r="I140" s="106"/>
-      <c r="J140" s="106"/>
-      <c r="K140" s="106"/>
-      <c r="L140" s="106"/>
-      <c r="M140" s="106"/>
-      <c r="N140" s="106"/>
+      <c r="A140" s="108"/>
+      <c r="B140" s="108"/>
+      <c r="C140" s="108"/>
+      <c r="D140" s="108"/>
+      <c r="E140" s="108"/>
+      <c r="F140" s="108"/>
+      <c r="G140" s="108"/>
+      <c r="H140" s="108"/>
+      <c r="I140" s="108"/>
+      <c r="J140" s="108"/>
+      <c r="K140" s="108"/>
+      <c r="L140" s="108"/>
+      <c r="M140" s="108"/>
+      <c r="N140" s="108"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="106"/>
-      <c r="B141" s="106"/>
-      <c r="C141" s="106"/>
-      <c r="D141" s="106"/>
-      <c r="E141" s="106"/>
-      <c r="F141" s="106"/>
-      <c r="G141" s="106"/>
-      <c r="H141" s="106"/>
-      <c r="I141" s="106"/>
-      <c r="J141" s="106"/>
-      <c r="K141" s="106"/>
-      <c r="L141" s="106"/>
-      <c r="M141" s="106"/>
-      <c r="N141" s="106"/>
+      <c r="A141" s="108"/>
+      <c r="B141" s="108"/>
+      <c r="C141" s="108"/>
+      <c r="D141" s="108"/>
+      <c r="E141" s="108"/>
+      <c r="F141" s="108"/>
+      <c r="G141" s="108"/>
+      <c r="H141" s="108"/>
+      <c r="I141" s="108"/>
+      <c r="J141" s="108"/>
+      <c r="K141" s="108"/>
+      <c r="L141" s="108"/>
+      <c r="M141" s="108"/>
+      <c r="N141" s="108"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="106"/>
-      <c r="B142" s="106"/>
-      <c r="C142" s="106"/>
-      <c r="D142" s="106"/>
-      <c r="E142" s="106"/>
-      <c r="F142" s="106"/>
-      <c r="G142" s="106"/>
-      <c r="H142" s="106"/>
-      <c r="I142" s="106"/>
-      <c r="J142" s="106"/>
-      <c r="K142" s="106"/>
-      <c r="L142" s="106"/>
-      <c r="M142" s="106"/>
-      <c r="N142" s="106"/>
+      <c r="A142" s="108"/>
+      <c r="B142" s="108"/>
+      <c r="C142" s="108"/>
+      <c r="D142" s="108"/>
+      <c r="E142" s="108"/>
+      <c r="F142" s="108"/>
+      <c r="G142" s="108"/>
+      <c r="H142" s="108"/>
+      <c r="I142" s="108"/>
+      <c r="J142" s="108"/>
+      <c r="K142" s="108"/>
+      <c r="L142" s="108"/>
+      <c r="M142" s="108"/>
+      <c r="N142" s="108"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="106"/>
-      <c r="B143" s="106"/>
-      <c r="C143" s="106"/>
-      <c r="D143" s="106"/>
-      <c r="E143" s="106"/>
-      <c r="F143" s="106"/>
-      <c r="G143" s="106"/>
-      <c r="H143" s="106"/>
-      <c r="I143" s="106"/>
-      <c r="J143" s="106"/>
-      <c r="K143" s="106"/>
-      <c r="L143" s="106"/>
-      <c r="M143" s="106"/>
-      <c r="N143" s="106"/>
+      <c r="A143" s="108"/>
+      <c r="B143" s="108"/>
+      <c r="C143" s="108"/>
+      <c r="D143" s="108"/>
+      <c r="E143" s="108"/>
+      <c r="F143" s="108"/>
+      <c r="G143" s="108"/>
+      <c r="H143" s="108"/>
+      <c r="I143" s="108"/>
+      <c r="J143" s="108"/>
+      <c r="K143" s="108"/>
+      <c r="L143" s="108"/>
+      <c r="M143" s="108"/>
+      <c r="N143" s="108"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="106"/>
-      <c r="B144" s="106"/>
-      <c r="C144" s="106"/>
-      <c r="D144" s="106"/>
-      <c r="E144" s="106"/>
-      <c r="F144" s="106"/>
-      <c r="G144" s="106"/>
-      <c r="H144" s="106"/>
-      <c r="I144" s="106"/>
-      <c r="J144" s="106"/>
-      <c r="K144" s="106"/>
-      <c r="L144" s="106"/>
-      <c r="M144" s="106"/>
-      <c r="N144" s="106"/>
+      <c r="A144" s="108"/>
+      <c r="B144" s="108"/>
+      <c r="C144" s="108"/>
+      <c r="D144" s="108"/>
+      <c r="E144" s="108"/>
+      <c r="F144" s="108"/>
+      <c r="G144" s="108"/>
+      <c r="H144" s="108"/>
+      <c r="I144" s="108"/>
+      <c r="J144" s="108"/>
+      <c r="K144" s="108"/>
+      <c r="L144" s="108"/>
+      <c r="M144" s="108"/>
+      <c r="N144" s="108"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="106"/>
-      <c r="B145" s="106"/>
-      <c r="C145" s="106"/>
-      <c r="D145" s="106"/>
-      <c r="E145" s="106"/>
-      <c r="F145" s="106"/>
-      <c r="G145" s="106"/>
-      <c r="H145" s="106"/>
-      <c r="I145" s="106"/>
-      <c r="J145" s="106"/>
-      <c r="K145" s="106"/>
-      <c r="L145" s="106"/>
-      <c r="M145" s="106"/>
-      <c r="N145" s="106"/>
+      <c r="A145" s="108"/>
+      <c r="B145" s="108"/>
+      <c r="C145" s="108"/>
+      <c r="D145" s="108"/>
+      <c r="E145" s="108"/>
+      <c r="F145" s="108"/>
+      <c r="G145" s="108"/>
+      <c r="H145" s="108"/>
+      <c r="I145" s="108"/>
+      <c r="J145" s="108"/>
+      <c r="K145" s="108"/>
+      <c r="L145" s="108"/>
+      <c r="M145" s="108"/>
+      <c r="N145" s="108"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="106"/>
-      <c r="B146" s="106"/>
-      <c r="C146" s="106"/>
-      <c r="D146" s="106"/>
-      <c r="E146" s="106"/>
-      <c r="F146" s="106"/>
-      <c r="G146" s="106"/>
-      <c r="H146" s="106"/>
-      <c r="I146" s="106"/>
-      <c r="J146" s="106"/>
-      <c r="K146" s="106"/>
-      <c r="L146" s="106"/>
-      <c r="M146" s="106"/>
-      <c r="N146" s="106"/>
+      <c r="A146" s="108"/>
+      <c r="B146" s="108"/>
+      <c r="C146" s="108"/>
+      <c r="D146" s="108"/>
+      <c r="E146" s="108"/>
+      <c r="F146" s="108"/>
+      <c r="G146" s="108"/>
+      <c r="H146" s="108"/>
+      <c r="I146" s="108"/>
+      <c r="J146" s="108"/>
+      <c r="K146" s="108"/>
+      <c r="L146" s="108"/>
+      <c r="M146" s="108"/>
+      <c r="N146" s="108"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="106"/>
-      <c r="B147" s="106"/>
-      <c r="C147" s="106"/>
-      <c r="D147" s="106"/>
-      <c r="E147" s="106"/>
-      <c r="F147" s="106"/>
-      <c r="G147" s="106"/>
-      <c r="H147" s="106"/>
-      <c r="I147" s="106"/>
-      <c r="J147" s="106"/>
-      <c r="K147" s="106"/>
-      <c r="L147" s="106"/>
-      <c r="M147" s="106"/>
-      <c r="N147" s="106"/>
+      <c r="A147" s="108"/>
+      <c r="B147" s="108"/>
+      <c r="C147" s="108"/>
+      <c r="D147" s="108"/>
+      <c r="E147" s="108"/>
+      <c r="F147" s="108"/>
+      <c r="G147" s="108"/>
+      <c r="H147" s="108"/>
+      <c r="I147" s="108"/>
+      <c r="J147" s="108"/>
+      <c r="K147" s="108"/>
+      <c r="L147" s="108"/>
+      <c r="M147" s="108"/>
+      <c r="N147" s="108"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="106"/>
-      <c r="B148" s="106"/>
-      <c r="C148" s="106"/>
-      <c r="D148" s="106"/>
-      <c r="E148" s="106"/>
-      <c r="F148" s="106"/>
-      <c r="G148" s="106"/>
-      <c r="H148" s="106"/>
-      <c r="I148" s="106"/>
-      <c r="J148" s="106"/>
-      <c r="K148" s="106"/>
-      <c r="L148" s="106"/>
-      <c r="M148" s="106"/>
-      <c r="N148" s="106"/>
+      <c r="A148" s="108"/>
+      <c r="B148" s="108"/>
+      <c r="C148" s="108"/>
+      <c r="D148" s="108"/>
+      <c r="E148" s="108"/>
+      <c r="F148" s="108"/>
+      <c r="G148" s="108"/>
+      <c r="H148" s="108"/>
+      <c r="I148" s="108"/>
+      <c r="J148" s="108"/>
+      <c r="K148" s="108"/>
+      <c r="L148" s="108"/>
+      <c r="M148" s="108"/>
+      <c r="N148" s="108"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="106"/>
-      <c r="B149" s="106"/>
-      <c r="C149" s="106"/>
-      <c r="D149" s="106"/>
-      <c r="E149" s="106"/>
-      <c r="F149" s="106"/>
-      <c r="G149" s="106"/>
-      <c r="H149" s="106"/>
-      <c r="I149" s="106"/>
-      <c r="J149" s="106"/>
-      <c r="K149" s="106"/>
-      <c r="L149" s="106"/>
-      <c r="M149" s="106"/>
-      <c r="N149" s="106"/>
+      <c r="A149" s="108"/>
+      <c r="B149" s="108"/>
+      <c r="C149" s="108"/>
+      <c r="D149" s="108"/>
+      <c r="E149" s="108"/>
+      <c r="F149" s="108"/>
+      <c r="G149" s="108"/>
+      <c r="H149" s="108"/>
+      <c r="I149" s="108"/>
+      <c r="J149" s="108"/>
+      <c r="K149" s="108"/>
+      <c r="L149" s="108"/>
+      <c r="M149" s="108"/>
+      <c r="N149" s="108"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="106"/>
-      <c r="B150" s="106"/>
-      <c r="C150" s="106"/>
-      <c r="D150" s="106"/>
-      <c r="E150" s="106"/>
-      <c r="F150" s="106"/>
-      <c r="G150" s="106"/>
-      <c r="H150" s="106"/>
-      <c r="I150" s="106"/>
-      <c r="J150" s="106"/>
-      <c r="K150" s="106"/>
-      <c r="L150" s="106"/>
-      <c r="M150" s="106"/>
-      <c r="N150" s="106"/>
+      <c r="A150" s="108"/>
+      <c r="B150" s="108"/>
+      <c r="C150" s="108"/>
+      <c r="D150" s="108"/>
+      <c r="E150" s="108"/>
+      <c r="F150" s="108"/>
+      <c r="G150" s="108"/>
+      <c r="H150" s="108"/>
+      <c r="I150" s="108"/>
+      <c r="J150" s="108"/>
+      <c r="K150" s="108"/>
+      <c r="L150" s="108"/>
+      <c r="M150" s="108"/>
+      <c r="N150" s="108"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="106"/>
-      <c r="B151" s="106"/>
-      <c r="C151" s="106"/>
-      <c r="D151" s="106"/>
-      <c r="E151" s="106"/>
-      <c r="F151" s="106"/>
-      <c r="G151" s="106"/>
-      <c r="H151" s="106"/>
-      <c r="I151" s="106"/>
-      <c r="J151" s="106"/>
-      <c r="K151" s="106"/>
-      <c r="L151" s="106"/>
-      <c r="M151" s="106"/>
-      <c r="N151" s="106"/>
+      <c r="A151" s="108"/>
+      <c r="B151" s="108"/>
+      <c r="C151" s="108"/>
+      <c r="D151" s="108"/>
+      <c r="E151" s="108"/>
+      <c r="F151" s="108"/>
+      <c r="G151" s="108"/>
+      <c r="H151" s="108"/>
+      <c r="I151" s="108"/>
+      <c r="J151" s="108"/>
+      <c r="K151" s="108"/>
+      <c r="L151" s="108"/>
+      <c r="M151" s="108"/>
+      <c r="N151" s="108"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="106"/>
-      <c r="B152" s="106"/>
-      <c r="C152" s="106"/>
-      <c r="D152" s="106"/>
-      <c r="E152" s="106"/>
-      <c r="F152" s="106"/>
-      <c r="G152" s="106"/>
-      <c r="H152" s="106"/>
-      <c r="I152" s="106"/>
-      <c r="J152" s="106"/>
-      <c r="K152" s="106"/>
-      <c r="L152" s="106"/>
-      <c r="M152" s="106"/>
-      <c r="N152" s="106"/>
+      <c r="A152" s="108"/>
+      <c r="B152" s="108"/>
+      <c r="C152" s="108"/>
+      <c r="D152" s="108"/>
+      <c r="E152" s="108"/>
+      <c r="F152" s="108"/>
+      <c r="G152" s="108"/>
+      <c r="H152" s="108"/>
+      <c r="I152" s="108"/>
+      <c r="J152" s="108"/>
+      <c r="K152" s="108"/>
+      <c r="L152" s="108"/>
+      <c r="M152" s="108"/>
+      <c r="N152" s="108"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="106"/>
-      <c r="B153" s="106"/>
-      <c r="C153" s="106"/>
-      <c r="D153" s="106"/>
-      <c r="E153" s="106"/>
-      <c r="F153" s="106"/>
-      <c r="G153" s="106"/>
-      <c r="H153" s="106"/>
-      <c r="I153" s="106"/>
-      <c r="J153" s="106"/>
-      <c r="K153" s="106"/>
-      <c r="L153" s="106"/>
-      <c r="M153" s="106"/>
-      <c r="N153" s="106"/>
+      <c r="A153" s="108"/>
+      <c r="B153" s="108"/>
+      <c r="C153" s="108"/>
+      <c r="D153" s="108"/>
+      <c r="E153" s="108"/>
+      <c r="F153" s="108"/>
+      <c r="G153" s="108"/>
+      <c r="H153" s="108"/>
+      <c r="I153" s="108"/>
+      <c r="J153" s="108"/>
+      <c r="K153" s="108"/>
+      <c r="L153" s="108"/>
+      <c r="M153" s="108"/>
+      <c r="N153" s="108"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="106"/>
-      <c r="B154" s="106"/>
-      <c r="C154" s="106"/>
-      <c r="D154" s="106"/>
-      <c r="E154" s="106"/>
-      <c r="F154" s="106"/>
-      <c r="G154" s="106"/>
-      <c r="H154" s="106"/>
-      <c r="I154" s="106"/>
-      <c r="J154" s="106"/>
-      <c r="K154" s="106"/>
-      <c r="L154" s="106"/>
-      <c r="M154" s="106"/>
-      <c r="N154" s="106"/>
+      <c r="A154" s="108"/>
+      <c r="B154" s="108"/>
+      <c r="C154" s="108"/>
+      <c r="D154" s="108"/>
+      <c r="E154" s="108"/>
+      <c r="F154" s="108"/>
+      <c r="G154" s="108"/>
+      <c r="H154" s="108"/>
+      <c r="I154" s="108"/>
+      <c r="J154" s="108"/>
+      <c r="K154" s="108"/>
+      <c r="L154" s="108"/>
+      <c r="M154" s="108"/>
+      <c r="N154" s="108"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="106"/>
-      <c r="B155" s="106"/>
-      <c r="C155" s="106"/>
-      <c r="D155" s="106"/>
-      <c r="E155" s="106"/>
-      <c r="F155" s="106"/>
-      <c r="G155" s="106"/>
-      <c r="H155" s="106"/>
-      <c r="I155" s="106"/>
-      <c r="J155" s="106"/>
-      <c r="K155" s="106"/>
-      <c r="L155" s="106"/>
-      <c r="M155" s="106"/>
-      <c r="N155" s="106"/>
+      <c r="A155" s="108"/>
+      <c r="B155" s="108"/>
+      <c r="C155" s="108"/>
+      <c r="D155" s="108"/>
+      <c r="E155" s="108"/>
+      <c r="F155" s="108"/>
+      <c r="G155" s="108"/>
+      <c r="H155" s="108"/>
+      <c r="I155" s="108"/>
+      <c r="J155" s="108"/>
+      <c r="K155" s="108"/>
+      <c r="L155" s="108"/>
+      <c r="M155" s="108"/>
+      <c r="N155" s="108"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="106"/>
-      <c r="B156" s="106"/>
-      <c r="C156" s="106"/>
-      <c r="D156" s="106"/>
-      <c r="E156" s="106"/>
-      <c r="F156" s="106"/>
-      <c r="G156" s="106"/>
-      <c r="H156" s="106"/>
-      <c r="I156" s="106"/>
-      <c r="J156" s="106"/>
-      <c r="K156" s="106"/>
-      <c r="L156" s="106"/>
-      <c r="M156" s="106"/>
-      <c r="N156" s="106"/>
+      <c r="A156" s="108"/>
+      <c r="B156" s="108"/>
+      <c r="C156" s="108"/>
+      <c r="D156" s="108"/>
+      <c r="E156" s="108"/>
+      <c r="F156" s="108"/>
+      <c r="G156" s="108"/>
+      <c r="H156" s="108"/>
+      <c r="I156" s="108"/>
+      <c r="J156" s="108"/>
+      <c r="K156" s="108"/>
+      <c r="L156" s="108"/>
+      <c r="M156" s="108"/>
+      <c r="N156" s="108"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="106"/>
-      <c r="B157" s="106"/>
-      <c r="C157" s="106"/>
-      <c r="D157" s="106"/>
-      <c r="E157" s="106"/>
-      <c r="F157" s="106"/>
-      <c r="G157" s="106"/>
-      <c r="H157" s="106"/>
-      <c r="I157" s="106"/>
-      <c r="J157" s="106"/>
-      <c r="K157" s="106"/>
-      <c r="L157" s="106"/>
-      <c r="M157" s="106"/>
-      <c r="N157" s="106"/>
+      <c r="A157" s="108"/>
+      <c r="B157" s="108"/>
+      <c r="C157" s="108"/>
+      <c r="D157" s="108"/>
+      <c r="E157" s="108"/>
+      <c r="F157" s="108"/>
+      <c r="G157" s="108"/>
+      <c r="H157" s="108"/>
+      <c r="I157" s="108"/>
+      <c r="J157" s="108"/>
+      <c r="K157" s="108"/>
+      <c r="L157" s="108"/>
+      <c r="M157" s="108"/>
+      <c r="N157" s="108"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="106"/>
-      <c r="B158" s="106"/>
-      <c r="C158" s="106"/>
-      <c r="D158" s="106"/>
-      <c r="E158" s="106"/>
-      <c r="F158" s="106"/>
-      <c r="G158" s="106"/>
-      <c r="H158" s="106"/>
-      <c r="I158" s="106"/>
-      <c r="J158" s="106"/>
-      <c r="K158" s="106"/>
-      <c r="L158" s="106"/>
-      <c r="M158" s="106"/>
-      <c r="N158" s="106"/>
+      <c r="A158" s="108"/>
+      <c r="B158" s="108"/>
+      <c r="C158" s="108"/>
+      <c r="D158" s="108"/>
+      <c r="E158" s="108"/>
+      <c r="F158" s="108"/>
+      <c r="G158" s="108"/>
+      <c r="H158" s="108"/>
+      <c r="I158" s="108"/>
+      <c r="J158" s="108"/>
+      <c r="K158" s="108"/>
+      <c r="L158" s="108"/>
+      <c r="M158" s="108"/>
+      <c r="N158" s="108"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="106"/>
-      <c r="B159" s="106"/>
-      <c r="C159" s="106"/>
-      <c r="D159" s="106"/>
-      <c r="E159" s="106"/>
-      <c r="F159" s="106"/>
-      <c r="G159" s="106"/>
-      <c r="H159" s="106"/>
-      <c r="I159" s="106"/>
-      <c r="J159" s="106"/>
-      <c r="K159" s="106"/>
-      <c r="L159" s="106"/>
-      <c r="M159" s="106"/>
-      <c r="N159" s="106"/>
+      <c r="A159" s="108"/>
+      <c r="B159" s="108"/>
+      <c r="C159" s="108"/>
+      <c r="D159" s="108"/>
+      <c r="E159" s="108"/>
+      <c r="F159" s="108"/>
+      <c r="G159" s="108"/>
+      <c r="H159" s="108"/>
+      <c r="I159" s="108"/>
+      <c r="J159" s="108"/>
+      <c r="K159" s="108"/>
+      <c r="L159" s="108"/>
+      <c r="M159" s="108"/>
+      <c r="N159" s="108"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="106"/>
-      <c r="B160" s="106"/>
-      <c r="C160" s="106"/>
-      <c r="D160" s="106"/>
-      <c r="E160" s="106"/>
-      <c r="F160" s="106"/>
-      <c r="G160" s="106"/>
-      <c r="H160" s="106"/>
-      <c r="I160" s="106"/>
-      <c r="J160" s="106"/>
-      <c r="K160" s="106"/>
-      <c r="L160" s="106"/>
-      <c r="M160" s="106"/>
-      <c r="N160" s="106"/>
+      <c r="A160" s="108"/>
+      <c r="B160" s="108"/>
+      <c r="C160" s="108"/>
+      <c r="D160" s="108"/>
+      <c r="E160" s="108"/>
+      <c r="F160" s="108"/>
+      <c r="G160" s="108"/>
+      <c r="H160" s="108"/>
+      <c r="I160" s="108"/>
+      <c r="J160" s="108"/>
+      <c r="K160" s="108"/>
+      <c r="L160" s="108"/>
+      <c r="M160" s="108"/>
+      <c r="N160" s="108"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="106"/>
-      <c r="B161" s="106"/>
-      <c r="C161" s="106"/>
-      <c r="D161" s="106"/>
-      <c r="E161" s="106"/>
-      <c r="F161" s="106"/>
-      <c r="G161" s="106"/>
-      <c r="H161" s="106"/>
-      <c r="I161" s="106"/>
-      <c r="J161" s="106"/>
-      <c r="K161" s="106"/>
-      <c r="L161" s="106"/>
-      <c r="M161" s="106"/>
-      <c r="N161" s="106"/>
+      <c r="A161" s="108"/>
+      <c r="B161" s="108"/>
+      <c r="C161" s="108"/>
+      <c r="D161" s="108"/>
+      <c r="E161" s="108"/>
+      <c r="F161" s="108"/>
+      <c r="G161" s="108"/>
+      <c r="H161" s="108"/>
+      <c r="I161" s="108"/>
+      <c r="J161" s="108"/>
+      <c r="K161" s="108"/>
+      <c r="L161" s="108"/>
+      <c r="M161" s="108"/>
+      <c r="N161" s="108"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="106"/>
-      <c r="B162" s="106"/>
-      <c r="C162" s="106"/>
-      <c r="D162" s="106"/>
-      <c r="E162" s="106"/>
-      <c r="F162" s="106"/>
-      <c r="G162" s="106"/>
-      <c r="H162" s="106"/>
-      <c r="I162" s="106"/>
-      <c r="J162" s="106"/>
-      <c r="K162" s="106"/>
-      <c r="L162" s="106"/>
-      <c r="M162" s="106"/>
-      <c r="N162" s="106"/>
+      <c r="A162" s="108"/>
+      <c r="B162" s="108"/>
+      <c r="C162" s="108"/>
+      <c r="D162" s="108"/>
+      <c r="E162" s="108"/>
+      <c r="F162" s="108"/>
+      <c r="G162" s="108"/>
+      <c r="H162" s="108"/>
+      <c r="I162" s="108"/>
+      <c r="J162" s="108"/>
+      <c r="K162" s="108"/>
+      <c r="L162" s="108"/>
+      <c r="M162" s="108"/>
+      <c r="N162" s="108"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="106"/>
-      <c r="B163" s="106"/>
-      <c r="C163" s="106"/>
-      <c r="D163" s="106"/>
-      <c r="E163" s="106"/>
-      <c r="F163" s="106"/>
-      <c r="G163" s="106"/>
-      <c r="H163" s="106"/>
-      <c r="I163" s="106"/>
-      <c r="J163" s="106"/>
-      <c r="K163" s="106"/>
-      <c r="L163" s="106"/>
-      <c r="M163" s="106"/>
-      <c r="N163" s="106"/>
+      <c r="A163" s="108"/>
+      <c r="B163" s="108"/>
+      <c r="C163" s="108"/>
+      <c r="D163" s="108"/>
+      <c r="E163" s="108"/>
+      <c r="F163" s="108"/>
+      <c r="G163" s="108"/>
+      <c r="H163" s="108"/>
+      <c r="I163" s="108"/>
+      <c r="J163" s="108"/>
+      <c r="K163" s="108"/>
+      <c r="L163" s="108"/>
+      <c r="M163" s="108"/>
+      <c r="N163" s="108"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="106"/>
-      <c r="B164" s="106"/>
-      <c r="C164" s="106"/>
-      <c r="D164" s="106"/>
-      <c r="E164" s="106"/>
-      <c r="F164" s="106"/>
-      <c r="G164" s="106"/>
-      <c r="H164" s="106"/>
-      <c r="I164" s="106"/>
-      <c r="J164" s="106"/>
-      <c r="K164" s="106"/>
-      <c r="L164" s="106"/>
-      <c r="M164" s="106"/>
-      <c r="N164" s="106"/>
+      <c r="A164" s="108"/>
+      <c r="B164" s="108"/>
+      <c r="C164" s="108"/>
+      <c r="D164" s="108"/>
+      <c r="E164" s="108"/>
+      <c r="F164" s="108"/>
+      <c r="G164" s="108"/>
+      <c r="H164" s="108"/>
+      <c r="I164" s="108"/>
+      <c r="J164" s="108"/>
+      <c r="K164" s="108"/>
+      <c r="L164" s="108"/>
+      <c r="M164" s="108"/>
+      <c r="N164" s="108"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="106"/>
-      <c r="B165" s="106"/>
-      <c r="C165" s="106"/>
-      <c r="D165" s="106"/>
-      <c r="E165" s="106"/>
-      <c r="F165" s="106"/>
-      <c r="G165" s="106"/>
-      <c r="H165" s="106"/>
-      <c r="I165" s="106"/>
-      <c r="J165" s="106"/>
-      <c r="K165" s="106"/>
-      <c r="L165" s="106"/>
-      <c r="M165" s="106"/>
-      <c r="N165" s="106"/>
+      <c r="A165" s="108"/>
+      <c r="B165" s="108"/>
+      <c r="C165" s="108"/>
+      <c r="D165" s="108"/>
+      <c r="E165" s="108"/>
+      <c r="F165" s="108"/>
+      <c r="G165" s="108"/>
+      <c r="H165" s="108"/>
+      <c r="I165" s="108"/>
+      <c r="J165" s="108"/>
+      <c r="K165" s="108"/>
+      <c r="L165" s="108"/>
+      <c r="M165" s="108"/>
+      <c r="N165" s="108"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="106"/>
-      <c r="B166" s="106"/>
-      <c r="C166" s="106"/>
-      <c r="D166" s="106"/>
-      <c r="E166" s="106"/>
-      <c r="F166" s="106"/>
-      <c r="G166" s="106"/>
-      <c r="H166" s="106"/>
-      <c r="I166" s="106"/>
-      <c r="J166" s="106"/>
-      <c r="K166" s="106"/>
-      <c r="L166" s="106"/>
-      <c r="M166" s="106"/>
-      <c r="N166" s="106"/>
+      <c r="A166" s="108"/>
+      <c r="B166" s="108"/>
+      <c r="C166" s="108"/>
+      <c r="D166" s="108"/>
+      <c r="E166" s="108"/>
+      <c r="F166" s="108"/>
+      <c r="G166" s="108"/>
+      <c r="H166" s="108"/>
+      <c r="I166" s="108"/>
+      <c r="J166" s="108"/>
+      <c r="K166" s="108"/>
+      <c r="L166" s="108"/>
+      <c r="M166" s="108"/>
+      <c r="N166" s="108"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="106"/>
-      <c r="B167" s="106"/>
-      <c r="C167" s="106"/>
-      <c r="D167" s="106"/>
-      <c r="E167" s="106"/>
-      <c r="F167" s="106"/>
-      <c r="G167" s="106"/>
-      <c r="H167" s="106"/>
-      <c r="I167" s="106"/>
-      <c r="J167" s="106"/>
-      <c r="K167" s="106"/>
-      <c r="L167" s="106"/>
-      <c r="M167" s="106"/>
-      <c r="N167" s="106"/>
+      <c r="A167" s="108"/>
+      <c r="B167" s="108"/>
+      <c r="C167" s="108"/>
+      <c r="D167" s="108"/>
+      <c r="E167" s="108"/>
+      <c r="F167" s="108"/>
+      <c r="G167" s="108"/>
+      <c r="H167" s="108"/>
+      <c r="I167" s="108"/>
+      <c r="J167" s="108"/>
+      <c r="K167" s="108"/>
+      <c r="L167" s="108"/>
+      <c r="M167" s="108"/>
+      <c r="N167" s="108"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="106"/>
-      <c r="B168" s="106"/>
-      <c r="C168" s="106"/>
-      <c r="D168" s="106"/>
-      <c r="E168" s="106"/>
-      <c r="F168" s="106"/>
-      <c r="G168" s="106"/>
-      <c r="H168" s="106"/>
-      <c r="I168" s="106"/>
-      <c r="J168" s="106"/>
-      <c r="K168" s="106"/>
-      <c r="L168" s="106"/>
-      <c r="M168" s="106"/>
-      <c r="N168" s="106"/>
+      <c r="A168" s="108"/>
+      <c r="B168" s="108"/>
+      <c r="C168" s="108"/>
+      <c r="D168" s="108"/>
+      <c r="E168" s="108"/>
+      <c r="F168" s="108"/>
+      <c r="G168" s="108"/>
+      <c r="H168" s="108"/>
+      <c r="I168" s="108"/>
+      <c r="J168" s="108"/>
+      <c r="K168" s="108"/>
+      <c r="L168" s="108"/>
+      <c r="M168" s="108"/>
+      <c r="N168" s="108"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="106"/>
-      <c r="B169" s="106"/>
-      <c r="C169" s="106"/>
-      <c r="D169" s="106"/>
-      <c r="E169" s="106"/>
-      <c r="F169" s="106"/>
-      <c r="G169" s="106"/>
-      <c r="H169" s="106"/>
-      <c r="I169" s="106"/>
-      <c r="J169" s="106"/>
-      <c r="K169" s="106"/>
-      <c r="L169" s="106"/>
-      <c r="M169" s="106"/>
-      <c r="N169" s="106"/>
+      <c r="A169" s="108"/>
+      <c r="B169" s="108"/>
+      <c r="C169" s="108"/>
+      <c r="D169" s="108"/>
+      <c r="E169" s="108"/>
+      <c r="F169" s="108"/>
+      <c r="G169" s="108"/>
+      <c r="H169" s="108"/>
+      <c r="I169" s="108"/>
+      <c r="J169" s="108"/>
+      <c r="K169" s="108"/>
+      <c r="L169" s="108"/>
+      <c r="M169" s="108"/>
+      <c r="N169" s="108"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="106"/>
-      <c r="B170" s="106"/>
-      <c r="C170" s="106"/>
-      <c r="D170" s="106"/>
-      <c r="E170" s="106"/>
-      <c r="F170" s="106"/>
-      <c r="G170" s="106"/>
-      <c r="H170" s="106"/>
-      <c r="I170" s="106"/>
-      <c r="J170" s="106"/>
-      <c r="K170" s="106"/>
-      <c r="L170" s="106"/>
-      <c r="M170" s="106"/>
-      <c r="N170" s="106"/>
+      <c r="A170" s="108"/>
+      <c r="B170" s="108"/>
+      <c r="C170" s="108"/>
+      <c r="D170" s="108"/>
+      <c r="E170" s="108"/>
+      <c r="F170" s="108"/>
+      <c r="G170" s="108"/>
+      <c r="H170" s="108"/>
+      <c r="I170" s="108"/>
+      <c r="J170" s="108"/>
+      <c r="K170" s="108"/>
+      <c r="L170" s="108"/>
+      <c r="M170" s="108"/>
+      <c r="N170" s="108"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="106"/>
-      <c r="B171" s="106"/>
-      <c r="C171" s="106"/>
-      <c r="D171" s="106"/>
-      <c r="E171" s="106"/>
-      <c r="F171" s="106"/>
-      <c r="G171" s="106"/>
-      <c r="H171" s="106"/>
-      <c r="I171" s="106"/>
-      <c r="J171" s="106"/>
-      <c r="K171" s="106"/>
-      <c r="L171" s="106"/>
-      <c r="M171" s="106"/>
-      <c r="N171" s="106"/>
+      <c r="A171" s="108"/>
+      <c r="B171" s="108"/>
+      <c r="C171" s="108"/>
+      <c r="D171" s="108"/>
+      <c r="E171" s="108"/>
+      <c r="F171" s="108"/>
+      <c r="G171" s="108"/>
+      <c r="H171" s="108"/>
+      <c r="I171" s="108"/>
+      <c r="J171" s="108"/>
+      <c r="K171" s="108"/>
+      <c r="L171" s="108"/>
+      <c r="M171" s="108"/>
+      <c r="N171" s="108"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="106"/>
-      <c r="B172" s="106"/>
-      <c r="C172" s="106"/>
-      <c r="D172" s="106"/>
-      <c r="E172" s="106"/>
-      <c r="F172" s="106"/>
-      <c r="G172" s="106"/>
-      <c r="H172" s="106"/>
-      <c r="I172" s="106"/>
-      <c r="J172" s="106"/>
-      <c r="K172" s="106"/>
-      <c r="L172" s="106"/>
-      <c r="M172" s="106"/>
-      <c r="N172" s="106"/>
+      <c r="A172" s="108"/>
+      <c r="B172" s="108"/>
+      <c r="C172" s="108"/>
+      <c r="D172" s="108"/>
+      <c r="E172" s="108"/>
+      <c r="F172" s="108"/>
+      <c r="G172" s="108"/>
+      <c r="H172" s="108"/>
+      <c r="I172" s="108"/>
+      <c r="J172" s="108"/>
+      <c r="K172" s="108"/>
+      <c r="L172" s="108"/>
+      <c r="M172" s="108"/>
+      <c r="N172" s="108"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="106"/>
-      <c r="B173" s="106"/>
-      <c r="C173" s="106"/>
-      <c r="D173" s="106"/>
-      <c r="E173" s="106"/>
-      <c r="F173" s="106"/>
-      <c r="G173" s="106"/>
-      <c r="H173" s="106"/>
-      <c r="I173" s="106"/>
-      <c r="J173" s="106"/>
-      <c r="K173" s="106"/>
-      <c r="L173" s="106"/>
-      <c r="M173" s="106"/>
-      <c r="N173" s="106"/>
+      <c r="A173" s="108"/>
+      <c r="B173" s="108"/>
+      <c r="C173" s="108"/>
+      <c r="D173" s="108"/>
+      <c r="E173" s="108"/>
+      <c r="F173" s="108"/>
+      <c r="G173" s="108"/>
+      <c r="H173" s="108"/>
+      <c r="I173" s="108"/>
+      <c r="J173" s="108"/>
+      <c r="K173" s="108"/>
+      <c r="L173" s="108"/>
+      <c r="M173" s="108"/>
+      <c r="N173" s="108"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="106"/>
-      <c r="B174" s="106"/>
-      <c r="C174" s="106"/>
-      <c r="D174" s="106"/>
-      <c r="E174" s="106"/>
-      <c r="F174" s="106"/>
-      <c r="G174" s="106"/>
-      <c r="H174" s="106"/>
-      <c r="I174" s="106"/>
-      <c r="J174" s="106"/>
-      <c r="K174" s="106"/>
-      <c r="L174" s="106"/>
-      <c r="M174" s="106"/>
-      <c r="N174" s="106"/>
+      <c r="A174" s="108"/>
+      <c r="B174" s="108"/>
+      <c r="C174" s="108"/>
+      <c r="D174" s="108"/>
+      <c r="E174" s="108"/>
+      <c r="F174" s="108"/>
+      <c r="G174" s="108"/>
+      <c r="H174" s="108"/>
+      <c r="I174" s="108"/>
+      <c r="J174" s="108"/>
+      <c r="K174" s="108"/>
+      <c r="L174" s="108"/>
+      <c r="M174" s="108"/>
+      <c r="N174" s="108"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="106"/>
-      <c r="B175" s="106"/>
-      <c r="C175" s="106"/>
-      <c r="D175" s="106"/>
-      <c r="E175" s="106"/>
-      <c r="F175" s="106"/>
-      <c r="G175" s="106"/>
-      <c r="H175" s="106"/>
-      <c r="I175" s="106"/>
-      <c r="J175" s="106"/>
-      <c r="K175" s="106"/>
-      <c r="L175" s="106"/>
-      <c r="M175" s="106"/>
-      <c r="N175" s="106"/>
+      <c r="A175" s="108"/>
+      <c r="B175" s="108"/>
+      <c r="C175" s="108"/>
+      <c r="D175" s="108"/>
+      <c r="E175" s="108"/>
+      <c r="F175" s="108"/>
+      <c r="G175" s="108"/>
+      <c r="H175" s="108"/>
+      <c r="I175" s="108"/>
+      <c r="J175" s="108"/>
+      <c r="K175" s="108"/>
+      <c r="L175" s="108"/>
+      <c r="M175" s="108"/>
+      <c r="N175" s="108"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="106"/>
-      <c r="B176" s="106"/>
-      <c r="C176" s="106"/>
-      <c r="D176" s="106"/>
-      <c r="E176" s="106"/>
-      <c r="F176" s="106"/>
-      <c r="G176" s="106"/>
-      <c r="H176" s="106"/>
-      <c r="I176" s="106"/>
-      <c r="J176" s="106"/>
-      <c r="K176" s="106"/>
-      <c r="L176" s="106"/>
-      <c r="M176" s="106"/>
-      <c r="N176" s="106"/>
+      <c r="A176" s="108"/>
+      <c r="B176" s="108"/>
+      <c r="C176" s="108"/>
+      <c r="D176" s="108"/>
+      <c r="E176" s="108"/>
+      <c r="F176" s="108"/>
+      <c r="G176" s="108"/>
+      <c r="H176" s="108"/>
+      <c r="I176" s="108"/>
+      <c r="J176" s="108"/>
+      <c r="K176" s="108"/>
+      <c r="L176" s="108"/>
+      <c r="M176" s="108"/>
+      <c r="N176" s="108"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="106"/>
-      <c r="B177" s="106"/>
-      <c r="C177" s="106"/>
-      <c r="D177" s="106"/>
-      <c r="E177" s="106"/>
-      <c r="F177" s="106"/>
-      <c r="G177" s="106"/>
-      <c r="H177" s="106"/>
-      <c r="I177" s="106"/>
-      <c r="J177" s="106"/>
-      <c r="K177" s="106"/>
-      <c r="L177" s="106"/>
-      <c r="M177" s="106"/>
-      <c r="N177" s="106"/>
+      <c r="A177" s="108"/>
+      <c r="B177" s="108"/>
+      <c r="C177" s="108"/>
+      <c r="D177" s="108"/>
+      <c r="E177" s="108"/>
+      <c r="F177" s="108"/>
+      <c r="G177" s="108"/>
+      <c r="H177" s="108"/>
+      <c r="I177" s="108"/>
+      <c r="J177" s="108"/>
+      <c r="K177" s="108"/>
+      <c r="L177" s="108"/>
+      <c r="M177" s="108"/>
+      <c r="N177" s="108"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="A178" s="106"/>
-      <c r="B178" s="106"/>
-      <c r="C178" s="106"/>
-      <c r="D178" s="106"/>
-      <c r="E178" s="106"/>
-      <c r="F178" s="106"/>
-      <c r="G178" s="106"/>
-      <c r="H178" s="106"/>
-      <c r="I178" s="106"/>
-      <c r="J178" s="106"/>
-      <c r="K178" s="106"/>
-      <c r="L178" s="106"/>
-      <c r="M178" s="106"/>
-      <c r="N178" s="106"/>
+      <c r="A178" s="108"/>
+      <c r="B178" s="108"/>
+      <c r="C178" s="108"/>
+      <c r="D178" s="108"/>
+      <c r="E178" s="108"/>
+      <c r="F178" s="108"/>
+      <c r="G178" s="108"/>
+      <c r="H178" s="108"/>
+      <c r="I178" s="108"/>
+      <c r="J178" s="108"/>
+      <c r="K178" s="108"/>
+      <c r="L178" s="108"/>
+      <c r="M178" s="108"/>
+      <c r="N178" s="108"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="A179" s="106"/>
-      <c r="B179" s="106"/>
-      <c r="C179" s="106"/>
-      <c r="D179" s="106"/>
-      <c r="E179" s="106"/>
-      <c r="F179" s="106"/>
-      <c r="G179" s="106"/>
-      <c r="H179" s="106"/>
-      <c r="I179" s="106"/>
-      <c r="J179" s="106"/>
-      <c r="K179" s="106"/>
-      <c r="L179" s="106"/>
-      <c r="M179" s="106"/>
-      <c r="N179" s="106"/>
+      <c r="A179" s="108"/>
+      <c r="B179" s="108"/>
+      <c r="C179" s="108"/>
+      <c r="D179" s="108"/>
+      <c r="E179" s="108"/>
+      <c r="F179" s="108"/>
+      <c r="G179" s="108"/>
+      <c r="H179" s="108"/>
+      <c r="I179" s="108"/>
+      <c r="J179" s="108"/>
+      <c r="K179" s="108"/>
+      <c r="L179" s="108"/>
+      <c r="M179" s="108"/>
+      <c r="N179" s="108"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="A180" s="106"/>
-      <c r="B180" s="106"/>
-      <c r="C180" s="106"/>
-      <c r="D180" s="106"/>
-      <c r="E180" s="106"/>
-      <c r="F180" s="106"/>
-      <c r="G180" s="106"/>
-      <c r="H180" s="106"/>
-      <c r="I180" s="106"/>
-      <c r="J180" s="106"/>
-      <c r="K180" s="106"/>
-      <c r="L180" s="106"/>
-      <c r="M180" s="106"/>
-      <c r="N180" s="106"/>
+      <c r="A180" s="108"/>
+      <c r="B180" s="108"/>
+      <c r="C180" s="108"/>
+      <c r="D180" s="108"/>
+      <c r="E180" s="108"/>
+      <c r="F180" s="108"/>
+      <c r="G180" s="108"/>
+      <c r="H180" s="108"/>
+      <c r="I180" s="108"/>
+      <c r="J180" s="108"/>
+      <c r="K180" s="108"/>
+      <c r="L180" s="108"/>
+      <c r="M180" s="108"/>
+      <c r="N180" s="108"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="A181" s="106"/>
-      <c r="B181" s="106"/>
-      <c r="C181" s="106"/>
-      <c r="D181" s="106"/>
-      <c r="E181" s="106"/>
-      <c r="F181" s="106"/>
-      <c r="G181" s="106"/>
-      <c r="H181" s="106"/>
-      <c r="I181" s="106"/>
-      <c r="J181" s="106"/>
-      <c r="K181" s="106"/>
-      <c r="L181" s="106"/>
-      <c r="M181" s="106"/>
-      <c r="N181" s="106"/>
+      <c r="A181" s="108"/>
+      <c r="B181" s="108"/>
+      <c r="C181" s="108"/>
+      <c r="D181" s="108"/>
+      <c r="E181" s="108"/>
+      <c r="F181" s="108"/>
+      <c r="G181" s="108"/>
+      <c r="H181" s="108"/>
+      <c r="I181" s="108"/>
+      <c r="J181" s="108"/>
+      <c r="K181" s="108"/>
+      <c r="L181" s="108"/>
+      <c r="M181" s="108"/>
+      <c r="N181" s="108"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="A182" s="106"/>
-      <c r="B182" s="106"/>
-      <c r="C182" s="106"/>
-      <c r="D182" s="106"/>
-      <c r="E182" s="106"/>
-      <c r="F182" s="106"/>
-      <c r="G182" s="106"/>
-      <c r="H182" s="106"/>
-      <c r="I182" s="106"/>
-      <c r="J182" s="106"/>
-      <c r="K182" s="106"/>
-      <c r="L182" s="106"/>
-      <c r="M182" s="106"/>
-      <c r="N182" s="106"/>
+      <c r="A182" s="108"/>
+      <c r="B182" s="108"/>
+      <c r="C182" s="108"/>
+      <c r="D182" s="108"/>
+      <c r="E182" s="108"/>
+      <c r="F182" s="108"/>
+      <c r="G182" s="108"/>
+      <c r="H182" s="108"/>
+      <c r="I182" s="108"/>
+      <c r="J182" s="108"/>
+      <c r="K182" s="108"/>
+      <c r="L182" s="108"/>
+      <c r="M182" s="108"/>
+      <c r="N182" s="108"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="A183" s="106"/>
-      <c r="B183" s="106"/>
-      <c r="C183" s="106"/>
-      <c r="D183" s="106"/>
-      <c r="E183" s="106"/>
-      <c r="F183" s="106"/>
-      <c r="G183" s="106"/>
-      <c r="H183" s="106"/>
-      <c r="I183" s="106"/>
-      <c r="J183" s="106"/>
-      <c r="K183" s="106"/>
-      <c r="L183" s="106"/>
-      <c r="M183" s="106"/>
-      <c r="N183" s="106"/>
+      <c r="A183" s="108"/>
+      <c r="B183" s="108"/>
+      <c r="C183" s="108"/>
+      <c r="D183" s="108"/>
+      <c r="E183" s="108"/>
+      <c r="F183" s="108"/>
+      <c r="G183" s="108"/>
+      <c r="H183" s="108"/>
+      <c r="I183" s="108"/>
+      <c r="J183" s="108"/>
+      <c r="K183" s="108"/>
+      <c r="L183" s="108"/>
+      <c r="M183" s="108"/>
+      <c r="N183" s="108"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="A184" s="106"/>
-      <c r="B184" s="106"/>
-      <c r="C184" s="106"/>
-      <c r="D184" s="106"/>
-      <c r="E184" s="106"/>
-      <c r="F184" s="106"/>
-      <c r="G184" s="106"/>
-      <c r="H184" s="106"/>
-      <c r="I184" s="106"/>
-      <c r="J184" s="106"/>
-      <c r="K184" s="106"/>
-      <c r="L184" s="106"/>
-      <c r="M184" s="106"/>
-      <c r="N184" s="106"/>
+      <c r="A184" s="108"/>
+      <c r="B184" s="108"/>
+      <c r="C184" s="108"/>
+      <c r="D184" s="108"/>
+      <c r="E184" s="108"/>
+      <c r="F184" s="108"/>
+      <c r="G184" s="108"/>
+      <c r="H184" s="108"/>
+      <c r="I184" s="108"/>
+      <c r="J184" s="108"/>
+      <c r="K184" s="108"/>
+      <c r="L184" s="108"/>
+      <c r="M184" s="108"/>
+      <c r="N184" s="108"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="A185" s="106"/>
-      <c r="B185" s="106"/>
-      <c r="C185" s="106"/>
-      <c r="D185" s="106"/>
-      <c r="E185" s="106"/>
-      <c r="F185" s="106"/>
-      <c r="G185" s="106"/>
-      <c r="H185" s="106"/>
-      <c r="I185" s="106"/>
-      <c r="J185" s="106"/>
-      <c r="K185" s="106"/>
-      <c r="L185" s="106"/>
-      <c r="M185" s="106"/>
-      <c r="N185" s="106"/>
+      <c r="A185" s="108"/>
+      <c r="B185" s="108"/>
+      <c r="C185" s="108"/>
+      <c r="D185" s="108"/>
+      <c r="E185" s="108"/>
+      <c r="F185" s="108"/>
+      <c r="G185" s="108"/>
+      <c r="H185" s="108"/>
+      <c r="I185" s="108"/>
+      <c r="J185" s="108"/>
+      <c r="K185" s="108"/>
+      <c r="L185" s="108"/>
+      <c r="M185" s="108"/>
+      <c r="N185" s="108"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="A186" s="106"/>
-      <c r="B186" s="106"/>
-      <c r="C186" s="106"/>
-      <c r="D186" s="106"/>
-      <c r="E186" s="106"/>
-      <c r="F186" s="106"/>
-      <c r="G186" s="106"/>
-      <c r="H186" s="106"/>
-      <c r="I186" s="106"/>
-      <c r="J186" s="106"/>
-      <c r="K186" s="106"/>
-      <c r="L186" s="106"/>
-      <c r="M186" s="106"/>
-      <c r="N186" s="106"/>
+      <c r="A186" s="108"/>
+      <c r="B186" s="108"/>
+      <c r="C186" s="108"/>
+      <c r="D186" s="108"/>
+      <c r="E186" s="108"/>
+      <c r="F186" s="108"/>
+      <c r="G186" s="108"/>
+      <c r="H186" s="108"/>
+      <c r="I186" s="108"/>
+      <c r="J186" s="108"/>
+      <c r="K186" s="108"/>
+      <c r="L186" s="108"/>
+      <c r="M186" s="108"/>
+      <c r="N186" s="108"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="A187" s="106"/>
-      <c r="B187" s="106"/>
-      <c r="C187" s="106"/>
-      <c r="D187" s="106"/>
-      <c r="E187" s="106"/>
-      <c r="F187" s="106"/>
-      <c r="G187" s="106"/>
-      <c r="H187" s="106"/>
-      <c r="I187" s="106"/>
-      <c r="J187" s="106"/>
-      <c r="K187" s="106"/>
-      <c r="L187" s="106"/>
-      <c r="M187" s="106"/>
-      <c r="N187" s="106"/>
+      <c r="A187" s="108"/>
+      <c r="B187" s="108"/>
+      <c r="C187" s="108"/>
+      <c r="D187" s="108"/>
+      <c r="E187" s="108"/>
+      <c r="F187" s="108"/>
+      <c r="G187" s="108"/>
+      <c r="H187" s="108"/>
+      <c r="I187" s="108"/>
+      <c r="J187" s="108"/>
+      <c r="K187" s="108"/>
+      <c r="L187" s="108"/>
+      <c r="M187" s="108"/>
+      <c r="N187" s="108"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="A188" s="106"/>
-      <c r="B188" s="106"/>
-      <c r="C188" s="106"/>
-      <c r="D188" s="106"/>
-      <c r="E188" s="106"/>
-      <c r="F188" s="106"/>
-      <c r="G188" s="106"/>
-      <c r="H188" s="106"/>
-      <c r="I188" s="106"/>
-      <c r="J188" s="106"/>
-      <c r="K188" s="106"/>
-      <c r="L188" s="106"/>
-      <c r="M188" s="106"/>
-      <c r="N188" s="106"/>
+      <c r="A188" s="108"/>
+      <c r="B188" s="108"/>
+      <c r="C188" s="108"/>
+      <c r="D188" s="108"/>
+      <c r="E188" s="108"/>
+      <c r="F188" s="108"/>
+      <c r="G188" s="108"/>
+      <c r="H188" s="108"/>
+      <c r="I188" s="108"/>
+      <c r="J188" s="108"/>
+      <c r="K188" s="108"/>
+      <c r="L188" s="108"/>
+      <c r="M188" s="108"/>
+      <c r="N188" s="108"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="A189" s="106"/>
-      <c r="B189" s="106"/>
-      <c r="C189" s="106"/>
-      <c r="D189" s="106"/>
-      <c r="E189" s="106"/>
-      <c r="F189" s="106"/>
-      <c r="G189" s="106"/>
-      <c r="H189" s="106"/>
-      <c r="I189" s="106"/>
-      <c r="J189" s="106"/>
-      <c r="K189" s="106"/>
-      <c r="L189" s="106"/>
-      <c r="M189" s="106"/>
-      <c r="N189" s="106"/>
+      <c r="A189" s="108"/>
+      <c r="B189" s="108"/>
+      <c r="C189" s="108"/>
+      <c r="D189" s="108"/>
+      <c r="E189" s="108"/>
+      <c r="F189" s="108"/>
+      <c r="G189" s="108"/>
+      <c r="H189" s="108"/>
+      <c r="I189" s="108"/>
+      <c r="J189" s="108"/>
+      <c r="K189" s="108"/>
+      <c r="L189" s="108"/>
+      <c r="M189" s="108"/>
+      <c r="N189" s="108"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="A190" s="106"/>
-      <c r="B190" s="106"/>
-      <c r="C190" s="106"/>
-      <c r="D190" s="106"/>
-      <c r="E190" s="106"/>
-      <c r="F190" s="106"/>
-      <c r="G190" s="106"/>
-      <c r="H190" s="106"/>
-      <c r="I190" s="106"/>
-      <c r="J190" s="106"/>
-      <c r="K190" s="106"/>
-      <c r="L190" s="106"/>
-      <c r="M190" s="106"/>
-      <c r="N190" s="106"/>
+      <c r="A190" s="108"/>
+      <c r="B190" s="108"/>
+      <c r="C190" s="108"/>
+      <c r="D190" s="108"/>
+      <c r="E190" s="108"/>
+      <c r="F190" s="108"/>
+      <c r="G190" s="108"/>
+      <c r="H190" s="108"/>
+      <c r="I190" s="108"/>
+      <c r="J190" s="108"/>
+      <c r="K190" s="108"/>
+      <c r="L190" s="108"/>
+      <c r="M190" s="108"/>
+      <c r="N190" s="108"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="A191" s="106"/>
-      <c r="B191" s="106"/>
-      <c r="C191" s="106"/>
-      <c r="D191" s="106"/>
-      <c r="E191" s="106"/>
-      <c r="F191" s="106"/>
-      <c r="G191" s="106"/>
-      <c r="H191" s="106"/>
-      <c r="I191" s="106"/>
-      <c r="J191" s="106"/>
-      <c r="K191" s="106"/>
-      <c r="L191" s="106"/>
-      <c r="M191" s="106"/>
-      <c r="N191" s="106"/>
+      <c r="A191" s="108"/>
+      <c r="B191" s="108"/>
+      <c r="C191" s="108"/>
+      <c r="D191" s="108"/>
+      <c r="E191" s="108"/>
+      <c r="F191" s="108"/>
+      <c r="G191" s="108"/>
+      <c r="H191" s="108"/>
+      <c r="I191" s="108"/>
+      <c r="J191" s="108"/>
+      <c r="K191" s="108"/>
+      <c r="L191" s="108"/>
+      <c r="M191" s="108"/>
+      <c r="N191" s="108"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="A192" s="106"/>
-      <c r="B192" s="106"/>
-      <c r="C192" s="106"/>
-      <c r="D192" s="106"/>
-      <c r="E192" s="106"/>
-      <c r="F192" s="106"/>
-      <c r="G192" s="106"/>
-      <c r="H192" s="106"/>
-      <c r="I192" s="106"/>
-      <c r="J192" s="106"/>
-      <c r="K192" s="106"/>
-      <c r="L192" s="106"/>
-      <c r="M192" s="106"/>
-      <c r="N192" s="106"/>
+      <c r="A192" s="108"/>
+      <c r="B192" s="108"/>
+      <c r="C192" s="108"/>
+      <c r="D192" s="108"/>
+      <c r="E192" s="108"/>
+      <c r="F192" s="108"/>
+      <c r="G192" s="108"/>
+      <c r="H192" s="108"/>
+      <c r="I192" s="108"/>
+      <c r="J192" s="108"/>
+      <c r="K192" s="108"/>
+      <c r="L192" s="108"/>
+      <c r="M192" s="108"/>
+      <c r="N192" s="108"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="A193" s="106"/>
-      <c r="B193" s="106"/>
-      <c r="C193" s="106"/>
-      <c r="D193" s="106"/>
-      <c r="E193" s="106"/>
-      <c r="F193" s="106"/>
-      <c r="G193" s="106"/>
-      <c r="H193" s="106"/>
-      <c r="I193" s="106"/>
-      <c r="J193" s="106"/>
-      <c r="K193" s="106"/>
-      <c r="L193" s="106"/>
-      <c r="M193" s="106"/>
-      <c r="N193" s="106"/>
+      <c r="A193" s="108"/>
+      <c r="B193" s="108"/>
+      <c r="C193" s="108"/>
+      <c r="D193" s="108"/>
+      <c r="E193" s="108"/>
+      <c r="F193" s="108"/>
+      <c r="G193" s="108"/>
+      <c r="H193" s="108"/>
+      <c r="I193" s="108"/>
+      <c r="J193" s="108"/>
+      <c r="K193" s="108"/>
+      <c r="L193" s="108"/>
+      <c r="M193" s="108"/>
+      <c r="N193" s="108"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="106"/>
-      <c r="B194" s="106"/>
-      <c r="C194" s="106"/>
-      <c r="D194" s="106"/>
-      <c r="E194" s="106"/>
-      <c r="F194" s="106"/>
-      <c r="G194" s="106"/>
-      <c r="H194" s="106"/>
-      <c r="I194" s="106"/>
-      <c r="J194" s="106"/>
-      <c r="K194" s="106"/>
-      <c r="L194" s="106"/>
-      <c r="M194" s="106"/>
-      <c r="N194" s="106"/>
+      <c r="A194" s="108"/>
+      <c r="B194" s="108"/>
+      <c r="C194" s="108"/>
+      <c r="D194" s="108"/>
+      <c r="E194" s="108"/>
+      <c r="F194" s="108"/>
+      <c r="G194" s="108"/>
+      <c r="H194" s="108"/>
+      <c r="I194" s="108"/>
+      <c r="J194" s="108"/>
+      <c r="K194" s="108"/>
+      <c r="L194" s="108"/>
+      <c r="M194" s="108"/>
+      <c r="N194" s="108"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="A195" s="106"/>
-      <c r="B195" s="106"/>
-      <c r="C195" s="106"/>
-      <c r="D195" s="106"/>
-      <c r="E195" s="106"/>
-      <c r="F195" s="106"/>
-      <c r="G195" s="106"/>
-      <c r="H195" s="106"/>
-      <c r="I195" s="106"/>
-      <c r="J195" s="106"/>
-      <c r="K195" s="106"/>
-      <c r="L195" s="106"/>
-      <c r="M195" s="106"/>
-      <c r="N195" s="106"/>
+      <c r="A195" s="108"/>
+      <c r="B195" s="108"/>
+      <c r="C195" s="108"/>
+      <c r="D195" s="108"/>
+      <c r="E195" s="108"/>
+      <c r="F195" s="108"/>
+      <c r="G195" s="108"/>
+      <c r="H195" s="108"/>
+      <c r="I195" s="108"/>
+      <c r="J195" s="108"/>
+      <c r="K195" s="108"/>
+      <c r="L195" s="108"/>
+      <c r="M195" s="108"/>
+      <c r="N195" s="108"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="A196" s="106"/>
-      <c r="B196" s="106"/>
-      <c r="C196" s="106"/>
-      <c r="D196" s="106"/>
-      <c r="E196" s="106"/>
-      <c r="F196" s="106"/>
-      <c r="G196" s="106"/>
-      <c r="H196" s="106"/>
-      <c r="I196" s="106"/>
-      <c r="J196" s="106"/>
-      <c r="K196" s="106"/>
-      <c r="L196" s="106"/>
-      <c r="M196" s="106"/>
-      <c r="N196" s="106"/>
+      <c r="A196" s="108"/>
+      <c r="B196" s="108"/>
+      <c r="C196" s="108"/>
+      <c r="D196" s="108"/>
+      <c r="E196" s="108"/>
+      <c r="F196" s="108"/>
+      <c r="G196" s="108"/>
+      <c r="H196" s="108"/>
+      <c r="I196" s="108"/>
+      <c r="J196" s="108"/>
+      <c r="K196" s="108"/>
+      <c r="L196" s="108"/>
+      <c r="M196" s="108"/>
+      <c r="N196" s="108"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="A197" s="106"/>
-      <c r="B197" s="106"/>
-      <c r="C197" s="106"/>
-      <c r="D197" s="106"/>
-      <c r="E197" s="106"/>
-      <c r="F197" s="106"/>
-      <c r="G197" s="106"/>
-      <c r="H197" s="106"/>
-      <c r="I197" s="106"/>
-      <c r="J197" s="106"/>
-      <c r="K197" s="106"/>
-      <c r="L197" s="106"/>
-      <c r="M197" s="106"/>
-      <c r="N197" s="106"/>
+      <c r="A197" s="108"/>
+      <c r="B197" s="108"/>
+      <c r="C197" s="108"/>
+      <c r="D197" s="108"/>
+      <c r="E197" s="108"/>
+      <c r="F197" s="108"/>
+      <c r="G197" s="108"/>
+      <c r="H197" s="108"/>
+      <c r="I197" s="108"/>
+      <c r="J197" s="108"/>
+      <c r="K197" s="108"/>
+      <c r="L197" s="108"/>
+      <c r="M197" s="108"/>
+      <c r="N197" s="108"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="A198" s="106"/>
-      <c r="B198" s="106"/>
-      <c r="C198" s="106"/>
-      <c r="D198" s="106"/>
-      <c r="E198" s="106"/>
-      <c r="F198" s="106"/>
-      <c r="G198" s="106"/>
-      <c r="H198" s="106"/>
-      <c r="I198" s="106"/>
-      <c r="J198" s="106"/>
-      <c r="K198" s="106"/>
-      <c r="L198" s="106"/>
-      <c r="M198" s="106"/>
-      <c r="N198" s="106"/>
+      <c r="A198" s="108"/>
+      <c r="B198" s="108"/>
+      <c r="C198" s="108"/>
+      <c r="D198" s="108"/>
+      <c r="E198" s="108"/>
+      <c r="F198" s="108"/>
+      <c r="G198" s="108"/>
+      <c r="H198" s="108"/>
+      <c r="I198" s="108"/>
+      <c r="J198" s="108"/>
+      <c r="K198" s="108"/>
+      <c r="L198" s="108"/>
+      <c r="M198" s="108"/>
+      <c r="N198" s="108"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="A199" s="106"/>
-      <c r="B199" s="106"/>
-      <c r="C199" s="106"/>
-      <c r="D199" s="106"/>
-      <c r="E199" s="106"/>
-      <c r="F199" s="106"/>
-      <c r="G199" s="106"/>
-      <c r="H199" s="106"/>
-      <c r="I199" s="106"/>
-      <c r="J199" s="106"/>
-      <c r="K199" s="106"/>
-      <c r="L199" s="106"/>
-      <c r="M199" s="106"/>
-      <c r="N199" s="106"/>
+      <c r="A199" s="108"/>
+      <c r="B199" s="108"/>
+      <c r="C199" s="108"/>
+      <c r="D199" s="108"/>
+      <c r="E199" s="108"/>
+      <c r="F199" s="108"/>
+      <c r="G199" s="108"/>
+      <c r="H199" s="108"/>
+      <c r="I199" s="108"/>
+      <c r="J199" s="108"/>
+      <c r="K199" s="108"/>
+      <c r="L199" s="108"/>
+      <c r="M199" s="108"/>
+      <c r="N199" s="108"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="A200" s="106"/>
-      <c r="B200" s="106"/>
-      <c r="C200" s="106"/>
-      <c r="D200" s="106"/>
-      <c r="E200" s="106"/>
-      <c r="F200" s="106"/>
-      <c r="G200" s="106"/>
-      <c r="H200" s="106"/>
-      <c r="I200" s="106"/>
-      <c r="J200" s="106"/>
-      <c r="K200" s="106"/>
-      <c r="L200" s="106"/>
-      <c r="M200" s="106"/>
-      <c r="N200" s="106"/>
+      <c r="A200" s="108"/>
+      <c r="B200" s="108"/>
+      <c r="C200" s="108"/>
+      <c r="D200" s="108"/>
+      <c r="E200" s="108"/>
+      <c r="F200" s="108"/>
+      <c r="G200" s="108"/>
+      <c r="H200" s="108"/>
+      <c r="I200" s="108"/>
+      <c r="J200" s="108"/>
+      <c r="K200" s="108"/>
+      <c r="L200" s="108"/>
+      <c r="M200" s="108"/>
+      <c r="N200" s="108"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="A201" s="106"/>
-      <c r="B201" s="106"/>
-      <c r="C201" s="106"/>
-      <c r="D201" s="106"/>
-      <c r="E201" s="106"/>
-      <c r="F201" s="106"/>
-      <c r="G201" s="106"/>
-      <c r="H201" s="106"/>
-      <c r="I201" s="106"/>
-      <c r="J201" s="106"/>
-      <c r="K201" s="106"/>
-      <c r="L201" s="106"/>
-      <c r="M201" s="106"/>
-      <c r="N201" s="106"/>
+      <c r="A201" s="108"/>
+      <c r="B201" s="108"/>
+      <c r="C201" s="108"/>
+      <c r="D201" s="108"/>
+      <c r="E201" s="108"/>
+      <c r="F201" s="108"/>
+      <c r="G201" s="108"/>
+      <c r="H201" s="108"/>
+      <c r="I201" s="108"/>
+      <c r="J201" s="108"/>
+      <c r="K201" s="108"/>
+      <c r="L201" s="108"/>
+      <c r="M201" s="108"/>
+      <c r="N201" s="108"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="A202" s="106"/>
-      <c r="B202" s="106"/>
-      <c r="C202" s="106"/>
-      <c r="D202" s="106"/>
-      <c r="E202" s="106"/>
-      <c r="F202" s="106"/>
-      <c r="G202" s="106"/>
-      <c r="H202" s="106"/>
-      <c r="I202" s="106"/>
-      <c r="J202" s="106"/>
-      <c r="K202" s="106"/>
-      <c r="L202" s="106"/>
-      <c r="M202" s="106"/>
-      <c r="N202" s="106"/>
+      <c r="A202" s="108"/>
+      <c r="B202" s="108"/>
+      <c r="C202" s="108"/>
+      <c r="D202" s="108"/>
+      <c r="E202" s="108"/>
+      <c r="F202" s="108"/>
+      <c r="G202" s="108"/>
+      <c r="H202" s="108"/>
+      <c r="I202" s="108"/>
+      <c r="J202" s="108"/>
+      <c r="K202" s="108"/>
+      <c r="L202" s="108"/>
+      <c r="M202" s="108"/>
+      <c r="N202" s="108"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="A203" s="106"/>
-      <c r="B203" s="106"/>
-      <c r="C203" s="106"/>
-      <c r="D203" s="106"/>
-      <c r="E203" s="106"/>
-      <c r="F203" s="106"/>
-      <c r="G203" s="106"/>
-      <c r="H203" s="106"/>
-      <c r="I203" s="106"/>
-      <c r="J203" s="106"/>
-      <c r="K203" s="106"/>
-      <c r="L203" s="106"/>
-      <c r="M203" s="106"/>
-      <c r="N203" s="106"/>
+      <c r="A203" s="108"/>
+      <c r="B203" s="108"/>
+      <c r="C203" s="108"/>
+      <c r="D203" s="108"/>
+      <c r="E203" s="108"/>
+      <c r="F203" s="108"/>
+      <c r="G203" s="108"/>
+      <c r="H203" s="108"/>
+      <c r="I203" s="108"/>
+      <c r="J203" s="108"/>
+      <c r="K203" s="108"/>
+      <c r="L203" s="108"/>
+      <c r="M203" s="108"/>
+      <c r="N203" s="108"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="A204" s="106"/>
-      <c r="B204" s="106"/>
-      <c r="C204" s="106"/>
-      <c r="D204" s="106"/>
-      <c r="E204" s="106"/>
-      <c r="F204" s="106"/>
-      <c r="G204" s="106"/>
-      <c r="H204" s="106"/>
-      <c r="I204" s="106"/>
-      <c r="J204" s="106"/>
-      <c r="K204" s="106"/>
-      <c r="L204" s="106"/>
-      <c r="M204" s="106"/>
-      <c r="N204" s="106"/>
+      <c r="A204" s="108"/>
+      <c r="B204" s="108"/>
+      <c r="C204" s="108"/>
+      <c r="D204" s="108"/>
+      <c r="E204" s="108"/>
+      <c r="F204" s="108"/>
+      <c r="G204" s="108"/>
+      <c r="H204" s="108"/>
+      <c r="I204" s="108"/>
+      <c r="J204" s="108"/>
+      <c r="K204" s="108"/>
+      <c r="L204" s="108"/>
+      <c r="M204" s="108"/>
+      <c r="N204" s="108"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="A205" s="106"/>
-      <c r="B205" s="106"/>
-      <c r="C205" s="106"/>
-      <c r="D205" s="106"/>
-      <c r="E205" s="106"/>
-      <c r="F205" s="106"/>
-      <c r="G205" s="106"/>
-      <c r="H205" s="106"/>
-      <c r="I205" s="106"/>
-      <c r="J205" s="106"/>
-      <c r="K205" s="106"/>
-      <c r="L205" s="106"/>
-      <c r="M205" s="106"/>
-      <c r="N205" s="106"/>
+      <c r="A205" s="108"/>
+      <c r="B205" s="108"/>
+      <c r="C205" s="108"/>
+      <c r="D205" s="108"/>
+      <c r="E205" s="108"/>
+      <c r="F205" s="108"/>
+      <c r="G205" s="108"/>
+      <c r="H205" s="108"/>
+      <c r="I205" s="108"/>
+      <c r="J205" s="108"/>
+      <c r="K205" s="108"/>
+      <c r="L205" s="108"/>
+      <c r="M205" s="108"/>
+      <c r="N205" s="108"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="A206" s="106"/>
-      <c r="B206" s="106"/>
-      <c r="C206" s="106"/>
-      <c r="D206" s="106"/>
-      <c r="E206" s="106"/>
-      <c r="F206" s="106"/>
-      <c r="G206" s="106"/>
-      <c r="H206" s="106"/>
-      <c r="I206" s="106"/>
-      <c r="J206" s="106"/>
-      <c r="K206" s="106"/>
-      <c r="L206" s="106"/>
-      <c r="M206" s="106"/>
-      <c r="N206" s="106"/>
+      <c r="A206" s="108"/>
+      <c r="B206" s="108"/>
+      <c r="C206" s="108"/>
+      <c r="D206" s="108"/>
+      <c r="E206" s="108"/>
+      <c r="F206" s="108"/>
+      <c r="G206" s="108"/>
+      <c r="H206" s="108"/>
+      <c r="I206" s="108"/>
+      <c r="J206" s="108"/>
+      <c r="K206" s="108"/>
+      <c r="L206" s="108"/>
+      <c r="M206" s="108"/>
+      <c r="N206" s="108"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="A207" s="106"/>
-      <c r="B207" s="106"/>
-      <c r="C207" s="106"/>
-      <c r="D207" s="106"/>
-      <c r="E207" s="106"/>
-      <c r="F207" s="106"/>
-      <c r="G207" s="106"/>
-      <c r="H207" s="106"/>
-      <c r="I207" s="106"/>
-      <c r="J207" s="106"/>
-      <c r="K207" s="106"/>
-      <c r="L207" s="106"/>
-      <c r="M207" s="106"/>
-      <c r="N207" s="106"/>
+      <c r="A207" s="108"/>
+      <c r="B207" s="108"/>
+      <c r="C207" s="108"/>
+      <c r="D207" s="108"/>
+      <c r="E207" s="108"/>
+      <c r="F207" s="108"/>
+      <c r="G207" s="108"/>
+      <c r="H207" s="108"/>
+      <c r="I207" s="108"/>
+      <c r="J207" s="108"/>
+      <c r="K207" s="108"/>
+      <c r="L207" s="108"/>
+      <c r="M207" s="108"/>
+      <c r="N207" s="108"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="A208" s="106"/>
-      <c r="B208" s="106"/>
-      <c r="C208" s="106"/>
-      <c r="D208" s="106"/>
-      <c r="E208" s="106"/>
-      <c r="F208" s="106"/>
-      <c r="G208" s="106"/>
-      <c r="H208" s="106"/>
-      <c r="I208" s="106"/>
-      <c r="J208" s="106"/>
-      <c r="K208" s="106"/>
-      <c r="L208" s="106"/>
-      <c r="M208" s="106"/>
-      <c r="N208" s="106"/>
+      <c r="A208" s="108"/>
+      <c r="B208" s="108"/>
+      <c r="C208" s="108"/>
+      <c r="D208" s="108"/>
+      <c r="E208" s="108"/>
+      <c r="F208" s="108"/>
+      <c r="G208" s="108"/>
+      <c r="H208" s="108"/>
+      <c r="I208" s="108"/>
+      <c r="J208" s="108"/>
+      <c r="K208" s="108"/>
+      <c r="L208" s="108"/>
+      <c r="M208" s="108"/>
+      <c r="N208" s="108"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="A209" s="106"/>
-      <c r="B209" s="106"/>
-      <c r="C209" s="106"/>
-      <c r="D209" s="106"/>
-      <c r="E209" s="106"/>
-      <c r="F209" s="106"/>
-      <c r="G209" s="106"/>
-      <c r="H209" s="106"/>
-      <c r="I209" s="106"/>
-      <c r="J209" s="106"/>
-      <c r="K209" s="106"/>
-      <c r="L209" s="106"/>
-      <c r="M209" s="106"/>
-      <c r="N209" s="106"/>
+      <c r="A209" s="108"/>
+      <c r="B209" s="108"/>
+      <c r="C209" s="108"/>
+      <c r="D209" s="108"/>
+      <c r="E209" s="108"/>
+      <c r="F209" s="108"/>
+      <c r="G209" s="108"/>
+      <c r="H209" s="108"/>
+      <c r="I209" s="108"/>
+      <c r="J209" s="108"/>
+      <c r="K209" s="108"/>
+      <c r="L209" s="108"/>
+      <c r="M209" s="108"/>
+      <c r="N209" s="108"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="A210" s="106"/>
-      <c r="B210" s="106"/>
-      <c r="C210" s="106"/>
-      <c r="D210" s="106"/>
-      <c r="E210" s="106"/>
-      <c r="F210" s="106"/>
-      <c r="G210" s="106"/>
-      <c r="H210" s="106"/>
-      <c r="I210" s="106"/>
-      <c r="J210" s="106"/>
-      <c r="K210" s="106"/>
-      <c r="L210" s="106"/>
-      <c r="M210" s="106"/>
-      <c r="N210" s="106"/>
+      <c r="A210" s="108"/>
+      <c r="B210" s="108"/>
+      <c r="C210" s="108"/>
+      <c r="D210" s="108"/>
+      <c r="E210" s="108"/>
+      <c r="F210" s="108"/>
+      <c r="G210" s="108"/>
+      <c r="H210" s="108"/>
+      <c r="I210" s="108"/>
+      <c r="J210" s="108"/>
+      <c r="K210" s="108"/>
+      <c r="L210" s="108"/>
+      <c r="M210" s="108"/>
+      <c r="N210" s="108"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="A211" s="106"/>
-      <c r="B211" s="106"/>
-      <c r="C211" s="106"/>
-      <c r="D211" s="106"/>
-      <c r="E211" s="106"/>
-      <c r="F211" s="106"/>
-      <c r="G211" s="106"/>
-      <c r="H211" s="106"/>
-      <c r="I211" s="106"/>
-      <c r="J211" s="106"/>
-      <c r="K211" s="106"/>
-      <c r="L211" s="106"/>
-      <c r="M211" s="106"/>
-      <c r="N211" s="106"/>
+      <c r="A211" s="108"/>
+      <c r="B211" s="108"/>
+      <c r="C211" s="108"/>
+      <c r="D211" s="108"/>
+      <c r="E211" s="108"/>
+      <c r="F211" s="108"/>
+      <c r="G211" s="108"/>
+      <c r="H211" s="108"/>
+      <c r="I211" s="108"/>
+      <c r="J211" s="108"/>
+      <c r="K211" s="108"/>
+      <c r="L211" s="108"/>
+      <c r="M211" s="108"/>
+      <c r="N211" s="108"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="A212" s="106"/>
-      <c r="B212" s="106"/>
-      <c r="C212" s="106"/>
-      <c r="D212" s="106"/>
-      <c r="E212" s="106"/>
-      <c r="F212" s="106"/>
-      <c r="G212" s="106"/>
-      <c r="H212" s="106"/>
-      <c r="I212" s="106"/>
-      <c r="J212" s="106"/>
-      <c r="K212" s="106"/>
-      <c r="L212" s="106"/>
-      <c r="M212" s="106"/>
-      <c r="N212" s="106"/>
+      <c r="A212" s="108"/>
+      <c r="B212" s="108"/>
+      <c r="C212" s="108"/>
+      <c r="D212" s="108"/>
+      <c r="E212" s="108"/>
+      <c r="F212" s="108"/>
+      <c r="G212" s="108"/>
+      <c r="H212" s="108"/>
+      <c r="I212" s="108"/>
+      <c r="J212" s="108"/>
+      <c r="K212" s="108"/>
+      <c r="L212" s="108"/>
+      <c r="M212" s="108"/>
+      <c r="N212" s="108"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="A213" s="106"/>
-      <c r="B213" s="106"/>
-      <c r="C213" s="106"/>
-      <c r="D213" s="106"/>
-      <c r="E213" s="106"/>
-      <c r="F213" s="106"/>
-      <c r="G213" s="106"/>
-      <c r="H213" s="106"/>
-      <c r="I213" s="106"/>
-      <c r="J213" s="106"/>
-      <c r="K213" s="106"/>
-      <c r="L213" s="106"/>
-      <c r="M213" s="106"/>
-      <c r="N213" s="106"/>
+      <c r="A213" s="108"/>
+      <c r="B213" s="108"/>
+      <c r="C213" s="108"/>
+      <c r="D213" s="108"/>
+      <c r="E213" s="108"/>
+      <c r="F213" s="108"/>
+      <c r="G213" s="108"/>
+      <c r="H213" s="108"/>
+      <c r="I213" s="108"/>
+      <c r="J213" s="108"/>
+      <c r="K213" s="108"/>
+      <c r="L213" s="108"/>
+      <c r="M213" s="108"/>
+      <c r="N213" s="108"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="A214" s="106"/>
-      <c r="B214" s="106"/>
-      <c r="C214" s="106"/>
-      <c r="D214" s="106"/>
-      <c r="E214" s="106"/>
-      <c r="F214" s="106"/>
-      <c r="G214" s="106"/>
-      <c r="H214" s="106"/>
-      <c r="I214" s="106"/>
-      <c r="J214" s="106"/>
-      <c r="K214" s="106"/>
-      <c r="L214" s="106"/>
-      <c r="M214" s="106"/>
-      <c r="N214" s="106"/>
+      <c r="A214" s="108"/>
+      <c r="B214" s="108"/>
+      <c r="C214" s="108"/>
+      <c r="D214" s="108"/>
+      <c r="E214" s="108"/>
+      <c r="F214" s="108"/>
+      <c r="G214" s="108"/>
+      <c r="H214" s="108"/>
+      <c r="I214" s="108"/>
+      <c r="J214" s="108"/>
+      <c r="K214" s="108"/>
+      <c r="L214" s="108"/>
+      <c r="M214" s="108"/>
+      <c r="N214" s="108"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="A215" s="106"/>
-      <c r="B215" s="106"/>
-      <c r="C215" s="106"/>
-      <c r="D215" s="106"/>
-      <c r="E215" s="106"/>
-      <c r="F215" s="106"/>
-      <c r="G215" s="106"/>
-      <c r="H215" s="106"/>
-      <c r="I215" s="106"/>
-      <c r="J215" s="106"/>
-      <c r="K215" s="106"/>
-      <c r="L215" s="106"/>
-      <c r="M215" s="106"/>
-      <c r="N215" s="106"/>
+      <c r="A215" s="108"/>
+      <c r="B215" s="108"/>
+      <c r="C215" s="108"/>
+      <c r="D215" s="108"/>
+      <c r="E215" s="108"/>
+      <c r="F215" s="108"/>
+      <c r="G215" s="108"/>
+      <c r="H215" s="108"/>
+      <c r="I215" s="108"/>
+      <c r="J215" s="108"/>
+      <c r="K215" s="108"/>
+      <c r="L215" s="108"/>
+      <c r="M215" s="108"/>
+      <c r="N215" s="108"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
-      <c r="A216" s="106"/>
-      <c r="B216" s="106"/>
-      <c r="C216" s="106"/>
-      <c r="D216" s="106"/>
-      <c r="E216" s="106"/>
-      <c r="F216" s="106"/>
-      <c r="G216" s="106"/>
-      <c r="H216" s="106"/>
-      <c r="I216" s="106"/>
-      <c r="J216" s="106"/>
-      <c r="K216" s="106"/>
-      <c r="L216" s="106"/>
-      <c r="M216" s="106"/>
-      <c r="N216" s="106"/>
+      <c r="A216" s="108"/>
+      <c r="B216" s="108"/>
+      <c r="C216" s="108"/>
+      <c r="D216" s="108"/>
+      <c r="E216" s="108"/>
+      <c r="F216" s="108"/>
+      <c r="G216" s="108"/>
+      <c r="H216" s="108"/>
+      <c r="I216" s="108"/>
+      <c r="J216" s="108"/>
+      <c r="K216" s="108"/>
+      <c r="L216" s="108"/>
+      <c r="M216" s="108"/>
+      <c r="N216" s="108"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
-      <c r="A217" s="106"/>
-      <c r="B217" s="106"/>
-      <c r="C217" s="106"/>
-      <c r="D217" s="106"/>
-      <c r="E217" s="106"/>
-      <c r="F217" s="106"/>
-      <c r="G217" s="106"/>
-      <c r="H217" s="106"/>
-      <c r="I217" s="106"/>
-      <c r="J217" s="106"/>
-      <c r="K217" s="106"/>
-      <c r="L217" s="106"/>
-      <c r="M217" s="106"/>
-      <c r="N217" s="106"/>
+      <c r="A217" s="108"/>
+      <c r="B217" s="108"/>
+      <c r="C217" s="108"/>
+      <c r="D217" s="108"/>
+      <c r="E217" s="108"/>
+      <c r="F217" s="108"/>
+      <c r="G217" s="108"/>
+      <c r="H217" s="108"/>
+      <c r="I217" s="108"/>
+      <c r="J217" s="108"/>
+      <c r="K217" s="108"/>
+      <c r="L217" s="108"/>
+      <c r="M217" s="108"/>
+      <c r="N217" s="108"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="A218" s="106"/>
-      <c r="B218" s="106"/>
-      <c r="C218" s="106"/>
-      <c r="D218" s="106"/>
-      <c r="E218" s="106"/>
-      <c r="F218" s="106"/>
-      <c r="G218" s="106"/>
-      <c r="H218" s="106"/>
-      <c r="I218" s="106"/>
-      <c r="J218" s="106"/>
-      <c r="K218" s="106"/>
-      <c r="L218" s="106"/>
-      <c r="M218" s="106"/>
-      <c r="N218" s="106"/>
+      <c r="A218" s="108"/>
+      <c r="B218" s="108"/>
+      <c r="C218" s="108"/>
+      <c r="D218" s="108"/>
+      <c r="E218" s="108"/>
+      <c r="F218" s="108"/>
+      <c r="G218" s="108"/>
+      <c r="H218" s="108"/>
+      <c r="I218" s="108"/>
+      <c r="J218" s="108"/>
+      <c r="K218" s="108"/>
+      <c r="L218" s="108"/>
+      <c r="M218" s="108"/>
+      <c r="N218" s="108"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
-      <c r="A219" s="106"/>
-      <c r="B219" s="106"/>
-      <c r="C219" s="106"/>
-      <c r="D219" s="106"/>
-      <c r="E219" s="106"/>
-      <c r="F219" s="106"/>
-      <c r="G219" s="106"/>
-      <c r="H219" s="106"/>
-      <c r="I219" s="106"/>
-      <c r="J219" s="106"/>
-      <c r="K219" s="106"/>
-      <c r="L219" s="106"/>
-      <c r="M219" s="106"/>
-      <c r="N219" s="106"/>
+      <c r="A219" s="108"/>
+      <c r="B219" s="108"/>
+      <c r="C219" s="108"/>
+      <c r="D219" s="108"/>
+      <c r="E219" s="108"/>
+      <c r="F219" s="108"/>
+      <c r="G219" s="108"/>
+      <c r="H219" s="108"/>
+      <c r="I219" s="108"/>
+      <c r="J219" s="108"/>
+      <c r="K219" s="108"/>
+      <c r="L219" s="108"/>
+      <c r="M219" s="108"/>
+      <c r="N219" s="108"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="A220" s="106"/>
-      <c r="B220" s="106"/>
-      <c r="C220" s="106"/>
-      <c r="D220" s="106"/>
-      <c r="E220" s="106"/>
-      <c r="F220" s="106"/>
-      <c r="G220" s="106"/>
-      <c r="H220" s="106"/>
-      <c r="I220" s="106"/>
-      <c r="J220" s="106"/>
-      <c r="K220" s="106"/>
-      <c r="L220" s="106"/>
-      <c r="M220" s="106"/>
-      <c r="N220" s="106"/>
+      <c r="A220" s="108"/>
+      <c r="B220" s="108"/>
+      <c r="C220" s="108"/>
+      <c r="D220" s="108"/>
+      <c r="E220" s="108"/>
+      <c r="F220" s="108"/>
+      <c r="G220" s="108"/>
+      <c r="H220" s="108"/>
+      <c r="I220" s="108"/>
+      <c r="J220" s="108"/>
+      <c r="K220" s="108"/>
+      <c r="L220" s="108"/>
+      <c r="M220" s="108"/>
+      <c r="N220" s="108"/>
     </row>
     <row r="221" ht="15.75" customHeight="1"/>
     <row r="222" ht="15.75" customHeight="1"/>
@@ -11825,138 +11850,138 @@
   </cols>
   <sheetData>
     <row r="1" ht="26.25" customHeight="1">
-      <c r="B1" s="124" t="s">
+      <c r="B1" s="127" t="s">
         <v>48</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="4"/>
-      <c r="G1" s="125"/>
+      <c r="G1" s="128"/>
     </row>
     <row r="2">
-      <c r="A2" s="126" t="s">
+      <c r="A2" s="129" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="127" t="s">
+      <c r="B2" s="130" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="126" t="s">
+      <c r="C2" s="129" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="126" t="s">
+      <c r="D2" s="129" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="126" t="s">
+      <c r="E2" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F2" s="127" t="s">
+      <c r="F2" s="130" t="s">
         <v>54</v>
       </c>
-      <c r="G2" s="128"/>
+      <c r="G2" s="131"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="129"/>
-      <c r="B3" s="130"/>
-      <c r="C3" s="131"/>
-      <c r="D3" s="131"/>
-      <c r="E3" s="131"/>
-      <c r="F3" s="132"/>
-      <c r="G3" s="133"/>
+      <c r="A3" s="132"/>
+      <c r="B3" s="133"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="134"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="136"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="134" t="s">
+      <c r="A4" s="137" t="s">
         <v>55</v>
       </c>
       <c r="B4" s="67"/>
       <c r="C4" s="67"/>
       <c r="D4" s="67"/>
       <c r="E4" s="67"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="136"/>
+      <c r="F4" s="138"/>
+      <c r="G4" s="139"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="137" t="s">
         <v>56</v>
       </c>
       <c r="B5" s="67"/>
       <c r="C5" s="67"/>
       <c r="D5" s="67"/>
       <c r="E5" s="67"/>
-      <c r="F5" s="135"/>
-      <c r="G5" s="136"/>
+      <c r="F5" s="138"/>
+      <c r="G5" s="139"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="134" t="s">
+      <c r="A6" s="137" t="s">
         <v>57</v>
       </c>
       <c r="B6" s="67"/>
       <c r="C6" s="67"/>
       <c r="D6" s="67"/>
       <c r="E6" s="67"/>
-      <c r="F6" s="135"/>
-      <c r="G6" s="136"/>
+      <c r="F6" s="138"/>
+      <c r="G6" s="139"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="134" t="s">
+      <c r="A7" s="137" t="s">
         <v>58</v>
       </c>
       <c r="B7" s="67"/>
       <c r="C7" s="67"/>
       <c r="D7" s="67"/>
       <c r="E7" s="67"/>
-      <c r="F7" s="135"/>
-      <c r="G7" s="136"/>
+      <c r="F7" s="138"/>
+      <c r="G7" s="139"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="134" t="s">
+      <c r="A8" s="137" t="s">
         <v>59</v>
       </c>
       <c r="B8" s="67"/>
       <c r="C8" s="67"/>
       <c r="D8" s="67"/>
       <c r="E8" s="67"/>
-      <c r="F8" s="135"/>
-      <c r="G8" s="136"/>
+      <c r="F8" s="138"/>
+      <c r="G8" s="139"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="134" t="s">
+      <c r="A9" s="137" t="s">
         <v>60</v>
       </c>
       <c r="B9" s="67"/>
       <c r="C9" s="67"/>
       <c r="D9" s="67"/>
       <c r="E9" s="67"/>
-      <c r="F9" s="135"/>
-      <c r="G9" s="136"/>
+      <c r="F9" s="138"/>
+      <c r="G9" s="139"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="134" t="s">
+      <c r="A10" s="137" t="s">
         <v>61</v>
       </c>
       <c r="B10" s="67"/>
       <c r="C10" s="67"/>
       <c r="D10" s="67"/>
       <c r="E10" s="67"/>
-      <c r="F10" s="135"/>
-      <c r="G10" s="136"/>
+      <c r="F10" s="138"/>
+      <c r="G10" s="139"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="134" t="s">
+      <c r="A11" s="137" t="s">
         <v>62</v>
       </c>
       <c r="B11" s="67"/>
       <c r="C11" s="67"/>
       <c r="D11" s="67"/>
       <c r="E11" s="67"/>
-      <c r="F11" s="135"/>
-      <c r="G11" s="136"/>
+      <c r="F11" s="138"/>
+      <c r="G11" s="139"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="134" t="s">
+      <c r="A12" s="137" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="137">
+      <c r="B12" s="140">
         <v>45366.0</v>
       </c>
       <c r="C12" s="75"/>
@@ -11964,14 +11989,14 @@
         <v>64</v>
       </c>
       <c r="E12" s="75"/>
-      <c r="F12" s="138">
+      <c r="F12" s="141">
         <v>100.0</v>
       </c>
-      <c r="G12" s="136"/>
+      <c r="G12" s="139"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="134"/>
-      <c r="B13" s="137">
+      <c r="A13" s="137"/>
+      <c r="B13" s="140">
         <v>45387.0</v>
       </c>
       <c r="C13" s="75"/>
@@ -11979,31 +12004,31 @@
         <v>64</v>
       </c>
       <c r="E13" s="75"/>
-      <c r="F13" s="138"/>
-      <c r="G13" s="136"/>
-      <c r="H13" s="123"/>
-      <c r="I13" s="123"/>
-      <c r="J13" s="123"/>
-      <c r="K13" s="123"/>
-      <c r="L13" s="123"/>
-      <c r="M13" s="123"/>
-      <c r="N13" s="123"/>
-      <c r="O13" s="123"/>
-      <c r="P13" s="123"/>
-      <c r="Q13" s="123"/>
-      <c r="R13" s="123"/>
-      <c r="S13" s="123"/>
-      <c r="T13" s="123"/>
-      <c r="U13" s="123"/>
-      <c r="V13" s="123"/>
-      <c r="W13" s="123"/>
-      <c r="X13" s="123"/>
-      <c r="Y13" s="123"/>
-      <c r="Z13" s="123"/>
+      <c r="F13" s="141"/>
+      <c r="G13" s="139"/>
+      <c r="H13" s="126"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="126"/>
+      <c r="K13" s="126"/>
+      <c r="L13" s="126"/>
+      <c r="M13" s="126"/>
+      <c r="N13" s="126"/>
+      <c r="O13" s="126"/>
+      <c r="P13" s="126"/>
+      <c r="Q13" s="126"/>
+      <c r="R13" s="126"/>
+      <c r="S13" s="126"/>
+      <c r="T13" s="126"/>
+      <c r="U13" s="126"/>
+      <c r="V13" s="126"/>
+      <c r="W13" s="126"/>
+      <c r="X13" s="126"/>
+      <c r="Y13" s="126"/>
+      <c r="Z13" s="126"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="134"/>
-      <c r="B14" s="137">
+      <c r="A14" s="137"/>
+      <c r="B14" s="140">
         <v>45415.0</v>
       </c>
       <c r="C14" s="75"/>
@@ -12011,31 +12036,31 @@
         <v>65</v>
       </c>
       <c r="E14" s="75"/>
-      <c r="F14" s="138"/>
-      <c r="G14" s="136"/>
-      <c r="H14" s="123"/>
-      <c r="I14" s="123"/>
-      <c r="J14" s="123"/>
-      <c r="K14" s="123"/>
-      <c r="L14" s="123"/>
-      <c r="M14" s="123"/>
-      <c r="N14" s="123"/>
-      <c r="O14" s="123"/>
-      <c r="P14" s="123"/>
-      <c r="Q14" s="123"/>
-      <c r="R14" s="123"/>
-      <c r="S14" s="123"/>
-      <c r="T14" s="123"/>
-      <c r="U14" s="123"/>
-      <c r="V14" s="123"/>
-      <c r="W14" s="123"/>
-      <c r="X14" s="123"/>
-      <c r="Y14" s="123"/>
-      <c r="Z14" s="123"/>
+      <c r="F14" s="141"/>
+      <c r="G14" s="139"/>
+      <c r="H14" s="126"/>
+      <c r="I14" s="126"/>
+      <c r="J14" s="126"/>
+      <c r="K14" s="126"/>
+      <c r="L14" s="126"/>
+      <c r="M14" s="126"/>
+      <c r="N14" s="126"/>
+      <c r="O14" s="126"/>
+      <c r="P14" s="126"/>
+      <c r="Q14" s="126"/>
+      <c r="R14" s="126"/>
+      <c r="S14" s="126"/>
+      <c r="T14" s="126"/>
+      <c r="U14" s="126"/>
+      <c r="V14" s="126"/>
+      <c r="W14" s="126"/>
+      <c r="X14" s="126"/>
+      <c r="Y14" s="126"/>
+      <c r="Z14" s="126"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="134"/>
-      <c r="B15" s="137">
+      <c r="A15" s="137"/>
+      <c r="B15" s="140">
         <v>45450.0</v>
       </c>
       <c r="C15" s="75"/>
@@ -12043,194 +12068,194 @@
         <v>64</v>
       </c>
       <c r="E15" s="75"/>
-      <c r="F15" s="138"/>
-      <c r="G15" s="136"/>
-      <c r="H15" s="123"/>
-      <c r="I15" s="123"/>
-      <c r="J15" s="123"/>
-      <c r="K15" s="123"/>
-      <c r="L15" s="123"/>
-      <c r="M15" s="123"/>
-      <c r="N15" s="123"/>
-      <c r="O15" s="123"/>
-      <c r="P15" s="123"/>
-      <c r="Q15" s="123"/>
-      <c r="R15" s="123"/>
-      <c r="S15" s="123"/>
-      <c r="T15" s="123"/>
-      <c r="U15" s="123"/>
-      <c r="V15" s="123"/>
-      <c r="W15" s="123"/>
-      <c r="X15" s="123"/>
-      <c r="Y15" s="123"/>
-      <c r="Z15" s="123"/>
+      <c r="F15" s="141"/>
+      <c r="G15" s="139"/>
+      <c r="H15" s="126"/>
+      <c r="I15" s="126"/>
+      <c r="J15" s="126"/>
+      <c r="K15" s="126"/>
+      <c r="L15" s="126"/>
+      <c r="M15" s="126"/>
+      <c r="N15" s="126"/>
+      <c r="O15" s="126"/>
+      <c r="P15" s="126"/>
+      <c r="Q15" s="126"/>
+      <c r="R15" s="126"/>
+      <c r="S15" s="126"/>
+      <c r="T15" s="126"/>
+      <c r="U15" s="126"/>
+      <c r="V15" s="126"/>
+      <c r="W15" s="126"/>
+      <c r="X15" s="126"/>
+      <c r="Y15" s="126"/>
+      <c r="Z15" s="126"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="134"/>
-      <c r="B16" s="137"/>
+      <c r="A16" s="137"/>
+      <c r="B16" s="140"/>
       <c r="C16" s="75"/>
       <c r="D16" s="75"/>
       <c r="E16" s="75"/>
-      <c r="F16" s="138"/>
-      <c r="G16" s="136"/>
-      <c r="H16" s="123"/>
-      <c r="I16" s="123"/>
-      <c r="J16" s="123"/>
-      <c r="K16" s="123"/>
-      <c r="L16" s="123"/>
-      <c r="M16" s="123"/>
-      <c r="N16" s="123"/>
-      <c r="O16" s="123"/>
-      <c r="P16" s="123"/>
-      <c r="Q16" s="123"/>
-      <c r="R16" s="123"/>
-      <c r="S16" s="123"/>
-      <c r="T16" s="123"/>
-      <c r="U16" s="123"/>
-      <c r="V16" s="123"/>
-      <c r="W16" s="123"/>
-      <c r="X16" s="123"/>
-      <c r="Y16" s="123"/>
-      <c r="Z16" s="123"/>
+      <c r="F16" s="141"/>
+      <c r="G16" s="139"/>
+      <c r="H16" s="126"/>
+      <c r="I16" s="126"/>
+      <c r="J16" s="126"/>
+      <c r="K16" s="126"/>
+      <c r="L16" s="126"/>
+      <c r="M16" s="126"/>
+      <c r="N16" s="126"/>
+      <c r="O16" s="126"/>
+      <c r="P16" s="126"/>
+      <c r="Q16" s="126"/>
+      <c r="R16" s="126"/>
+      <c r="S16" s="126"/>
+      <c r="T16" s="126"/>
+      <c r="U16" s="126"/>
+      <c r="V16" s="126"/>
+      <c r="W16" s="126"/>
+      <c r="X16" s="126"/>
+      <c r="Y16" s="126"/>
+      <c r="Z16" s="126"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="134"/>
-      <c r="B17" s="137"/>
+      <c r="A17" s="137"/>
+      <c r="B17" s="140"/>
       <c r="C17" s="75"/>
       <c r="D17" s="75"/>
       <c r="E17" s="75"/>
-      <c r="F17" s="138"/>
-      <c r="G17" s="136"/>
-      <c r="H17" s="123"/>
-      <c r="I17" s="123"/>
-      <c r="J17" s="123"/>
-      <c r="K17" s="123"/>
-      <c r="L17" s="123"/>
-      <c r="M17" s="123"/>
-      <c r="N17" s="123"/>
-      <c r="O17" s="123"/>
-      <c r="P17" s="123"/>
-      <c r="Q17" s="123"/>
-      <c r="R17" s="123"/>
-      <c r="S17" s="123"/>
-      <c r="T17" s="123"/>
-      <c r="U17" s="123"/>
-      <c r="V17" s="123"/>
-      <c r="W17" s="123"/>
-      <c r="X17" s="123"/>
-      <c r="Y17" s="123"/>
-      <c r="Z17" s="123"/>
+      <c r="F17" s="141"/>
+      <c r="G17" s="139"/>
+      <c r="H17" s="126"/>
+      <c r="I17" s="126"/>
+      <c r="J17" s="126"/>
+      <c r="K17" s="126"/>
+      <c r="L17" s="126"/>
+      <c r="M17" s="126"/>
+      <c r="N17" s="126"/>
+      <c r="O17" s="126"/>
+      <c r="P17" s="126"/>
+      <c r="Q17" s="126"/>
+      <c r="R17" s="126"/>
+      <c r="S17" s="126"/>
+      <c r="T17" s="126"/>
+      <c r="U17" s="126"/>
+      <c r="V17" s="126"/>
+      <c r="W17" s="126"/>
+      <c r="X17" s="126"/>
+      <c r="Y17" s="126"/>
+      <c r="Z17" s="126"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="139" t="s">
+      <c r="A18" s="142" t="s">
         <v>66</v>
       </c>
-      <c r="B18" s="140"/>
-      <c r="C18" s="140"/>
-      <c r="D18" s="140"/>
-      <c r="E18" s="140"/>
-      <c r="F18" s="138"/>
-      <c r="G18" s="141"/>
+      <c r="B18" s="143"/>
+      <c r="C18" s="143"/>
+      <c r="D18" s="143"/>
+      <c r="E18" s="143"/>
+      <c r="F18" s="141"/>
+      <c r="G18" s="144"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="134" t="s">
+      <c r="A19" s="137" t="s">
         <v>67</v>
       </c>
       <c r="B19" s="75"/>
       <c r="C19" s="75"/>
       <c r="D19" s="75"/>
       <c r="E19" s="75"/>
-      <c r="F19" s="138"/>
-      <c r="G19" s="136"/>
+      <c r="F19" s="141"/>
+      <c r="G19" s="139"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="139" t="s">
+      <c r="A20" s="142" t="s">
         <v>68</v>
       </c>
-      <c r="B20" s="140"/>
-      <c r="C20" s="140"/>
-      <c r="D20" s="140"/>
-      <c r="E20" s="140"/>
-      <c r="F20" s="138"/>
-      <c r="G20" s="136"/>
+      <c r="B20" s="143"/>
+      <c r="C20" s="143"/>
+      <c r="D20" s="143"/>
+      <c r="E20" s="143"/>
+      <c r="F20" s="141"/>
+      <c r="G20" s="139"/>
     </row>
     <row r="21" ht="27.0" customHeight="1">
-      <c r="A21" s="142" t="s">
+      <c r="A21" s="145" t="s">
         <v>69</v>
       </c>
-      <c r="B21" s="140"/>
-      <c r="C21" s="140"/>
-      <c r="D21" s="140"/>
-      <c r="E21" s="140"/>
-      <c r="F21" s="138"/>
-      <c r="G21" s="136"/>
+      <c r="B21" s="143"/>
+      <c r="C21" s="143"/>
+      <c r="D21" s="143"/>
+      <c r="E21" s="143"/>
+      <c r="F21" s="141"/>
+      <c r="G21" s="139"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="134" t="s">
+      <c r="A22" s="137" t="s">
         <v>70</v>
       </c>
       <c r="B22" s="75"/>
       <c r="C22" s="75"/>
       <c r="D22" s="75"/>
       <c r="E22" s="75"/>
-      <c r="F22" s="138"/>
-      <c r="G22" s="136"/>
+      <c r="F22" s="141"/>
+      <c r="G22" s="139"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="139" t="s">
+      <c r="A23" s="142" t="s">
         <v>71</v>
       </c>
-      <c r="B23" s="140"/>
-      <c r="C23" s="140"/>
-      <c r="D23" s="140"/>
-      <c r="E23" s="140"/>
-      <c r="F23" s="138"/>
-      <c r="G23" s="136"/>
+      <c r="B23" s="143"/>
+      <c r="C23" s="143"/>
+      <c r="D23" s="143"/>
+      <c r="E23" s="143"/>
+      <c r="F23" s="141"/>
+      <c r="G23" s="139"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="143" t="s">
+      <c r="A24" s="146" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="144"/>
-      <c r="C24" s="144"/>
-      <c r="D24" s="144"/>
-      <c r="E24" s="144"/>
-      <c r="F24" s="138"/>
-      <c r="G24" s="136"/>
+      <c r="B24" s="147"/>
+      <c r="C24" s="147"/>
+      <c r="D24" s="147"/>
+      <c r="E24" s="147"/>
+      <c r="F24" s="141"/>
+      <c r="G24" s="139"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="145" t="s">
+      <c r="A25" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="B25" s="146"/>
-      <c r="C25" s="140"/>
-      <c r="D25" s="140"/>
-      <c r="E25" s="140"/>
-      <c r="F25" s="138"/>
-      <c r="G25" s="136"/>
+      <c r="B25" s="149"/>
+      <c r="C25" s="143"/>
+      <c r="D25" s="143"/>
+      <c r="E25" s="143"/>
+      <c r="F25" s="141"/>
+      <c r="G25" s="139"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="147"/>
-      <c r="B26" s="148"/>
-      <c r="C26" s="148"/>
-      <c r="D26" s="148"/>
-      <c r="E26" s="148"/>
-      <c r="F26" s="138"/>
-      <c r="G26" s="136"/>
+      <c r="A26" s="150"/>
+      <c r="B26" s="151"/>
+      <c r="C26" s="151"/>
+      <c r="D26" s="151"/>
+      <c r="E26" s="151"/>
+      <c r="F26" s="141"/>
+      <c r="G26" s="139"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="B27" s="149"/>
-      <c r="C27" s="149"/>
-      <c r="D27" s="149"/>
-      <c r="E27" s="149"/>
-      <c r="F27" s="149"/>
+      <c r="B27" s="152"/>
+      <c r="C27" s="152"/>
+      <c r="D27" s="152"/>
+      <c r="E27" s="152"/>
+      <c r="F27" s="152"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="B28" s="149"/>
-      <c r="C28" s="149"/>
-      <c r="D28" s="149"/>
-      <c r="E28" s="149"/>
-      <c r="F28" s="149"/>
+      <c r="B28" s="152"/>
+      <c r="C28" s="152"/>
+      <c r="D28" s="152"/>
+      <c r="E28" s="152"/>
+      <c r="F28" s="152"/>
     </row>
     <row r="29" ht="15.75" customHeight="1"/>
     <row r="30" ht="15.75" customHeight="1"/>

--- a/planilhas/Contabilidade Condominio.xlsx
+++ b/planilhas/Contabilidade Condominio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Condominio\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B06688-1002-4BBB-8C34-82858E9F7873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4426E17-E78F-400C-A6D2-7F1376FE38F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CAPA Explicações" sheetId="1" r:id="rId1"/>
@@ -1594,9 +1594,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1635,22 +1650,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1898,68 +1898,68 @@
   <sheetData>
     <row r="1" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
-      <c r="B1" s="126" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="128"/>
+      <c r="B1" s="131" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="132"/>
+      <c r="K1" s="132"/>
+      <c r="L1" s="133"/>
       <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" s="129" t="s">
+      <c r="B2" s="134" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="127"/>
-      <c r="K2" s="127"/>
-      <c r="L2" s="128"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="132"/>
+      <c r="H2" s="132"/>
+      <c r="I2" s="132"/>
+      <c r="J2" s="132"/>
+      <c r="K2" s="132"/>
+      <c r="L2" s="133"/>
       <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
-      <c r="B3" s="130" t="s">
+      <c r="B3" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="131"/>
-      <c r="D3" s="131"/>
-      <c r="E3" s="131"/>
-      <c r="F3" s="131"/>
-      <c r="G3" s="131"/>
-      <c r="H3" s="131"/>
-      <c r="I3" s="131"/>
-      <c r="J3" s="131"/>
-      <c r="K3" s="131"/>
-      <c r="L3" s="132"/>
+      <c r="C3" s="136"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="136"/>
+      <c r="I3" s="136"/>
+      <c r="J3" s="136"/>
+      <c r="K3" s="136"/>
+      <c r="L3" s="137"/>
       <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3"/>
-      <c r="B4" s="133"/>
-      <c r="C4" s="134"/>
-      <c r="D4" s="134"/>
-      <c r="E4" s="134"/>
-      <c r="F4" s="134"/>
-      <c r="G4" s="134"/>
-      <c r="H4" s="134"/>
-      <c r="I4" s="134"/>
-      <c r="J4" s="134"/>
-      <c r="K4" s="134"/>
-      <c r="L4" s="135"/>
+      <c r="B4" s="138"/>
+      <c r="C4" s="139"/>
+      <c r="D4" s="139"/>
+      <c r="E4" s="139"/>
+      <c r="F4" s="139"/>
+      <c r="G4" s="139"/>
+      <c r="H4" s="139"/>
+      <c r="I4" s="139"/>
+      <c r="J4" s="139"/>
+      <c r="K4" s="139"/>
+      <c r="L4" s="140"/>
       <c r="M4" s="3"/>
     </row>
     <row r="5" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -1967,26 +1967,26 @@
       <c r="B5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="136" t="s">
+      <c r="C5" s="141" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="137"/>
-      <c r="E5" s="137"/>
-      <c r="F5" s="137"/>
-      <c r="G5" s="137"/>
-      <c r="H5" s="137"/>
-      <c r="I5" s="137"/>
-      <c r="J5" s="137"/>
-      <c r="K5" s="137"/>
-      <c r="L5" s="138"/>
+      <c r="D5" s="142"/>
+      <c r="E5" s="142"/>
+      <c r="F5" s="142"/>
+      <c r="G5" s="142"/>
+      <c r="H5" s="142"/>
+      <c r="I5" s="142"/>
+      <c r="J5" s="142"/>
+      <c r="K5" s="142"/>
+      <c r="L5" s="143"/>
       <c r="M5" s="4"/>
     </row>
     <row r="6" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6"/>
-      <c r="B6" s="139" t="s">
+      <c r="B6" s="144" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="121" t="s">
+      <c r="C6" s="127" t="s">
         <v>6</v>
       </c>
       <c r="D6" s="122"/>
@@ -1997,12 +1997,12 @@
       <c r="I6" s="122"/>
       <c r="J6" s="122"/>
       <c r="K6" s="122"/>
-      <c r="L6" s="123"/>
+      <c r="L6" s="128"/>
       <c r="M6" s="6"/>
     </row>
     <row r="7" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6"/>
-      <c r="B7" s="140"/>
+      <c r="B7" s="145"/>
       <c r="C7" s="122"/>
       <c r="D7" s="122"/>
       <c r="E7" s="122"/>
@@ -2012,15 +2012,15 @@
       <c r="I7" s="122"/>
       <c r="J7" s="122"/>
       <c r="K7" s="122"/>
-      <c r="L7" s="123"/>
+      <c r="L7" s="128"/>
       <c r="M7" s="6"/>
     </row>
     <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6"/>
-      <c r="B8" s="139" t="s">
+      <c r="B8" s="144" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="121" t="s">
+      <c r="C8" s="127" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="122"/>
@@ -2031,12 +2031,12 @@
       <c r="I8" s="122"/>
       <c r="J8" s="122"/>
       <c r="K8" s="122"/>
-      <c r="L8" s="123"/>
+      <c r="L8" s="128"/>
       <c r="M8" s="6"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6"/>
-      <c r="B9" s="140"/>
+      <c r="B9" s="145"/>
       <c r="C9" s="122"/>
       <c r="D9" s="122"/>
       <c r="E9" s="122"/>
@@ -2046,15 +2046,15 @@
       <c r="I9" s="122"/>
       <c r="J9" s="122"/>
       <c r="K9" s="122"/>
-      <c r="L9" s="123"/>
+      <c r="L9" s="128"/>
       <c r="M9" s="6"/>
     </row>
     <row r="10" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6"/>
-      <c r="B10" s="139" t="s">
+      <c r="B10" s="144" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="121" t="s">
+      <c r="C10" s="127" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="122"/>
@@ -2065,12 +2065,12 @@
       <c r="I10" s="122"/>
       <c r="J10" s="122"/>
       <c r="K10" s="122"/>
-      <c r="L10" s="123"/>
+      <c r="L10" s="128"/>
       <c r="M10" s="6"/>
     </row>
     <row r="11" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6"/>
-      <c r="B11" s="140"/>
+      <c r="B11" s="145"/>
       <c r="C11" s="122"/>
       <c r="D11" s="122"/>
       <c r="E11" s="122"/>
@@ -2080,15 +2080,15 @@
       <c r="I11" s="122"/>
       <c r="J11" s="122"/>
       <c r="K11" s="122"/>
-      <c r="L11" s="123"/>
+      <c r="L11" s="128"/>
       <c r="M11" s="6"/>
     </row>
     <row r="12" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6"/>
-      <c r="B12" s="139" t="s">
+      <c r="B12" s="144" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="121" t="s">
+      <c r="C12" s="127" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="122"/>
@@ -2099,12 +2099,12 @@
       <c r="I12" s="122"/>
       <c r="J12" s="122"/>
       <c r="K12" s="122"/>
-      <c r="L12" s="123"/>
+      <c r="L12" s="128"/>
       <c r="M12" s="6"/>
     </row>
     <row r="13" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
-      <c r="B13" s="140"/>
+      <c r="B13" s="145"/>
       <c r="C13" s="122"/>
       <c r="D13" s="122"/>
       <c r="E13" s="122"/>
@@ -2114,15 +2114,15 @@
       <c r="I13" s="122"/>
       <c r="J13" s="122"/>
       <c r="K13" s="122"/>
-      <c r="L13" s="123"/>
+      <c r="L13" s="128"/>
       <c r="M13" s="6"/>
     </row>
     <row r="14" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6"/>
-      <c r="B14" s="139" t="s">
+      <c r="B14" s="144" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="121" t="s">
+      <c r="C14" s="127" t="s">
         <v>14</v>
       </c>
       <c r="D14" s="122"/>
@@ -2133,12 +2133,12 @@
       <c r="I14" s="122"/>
       <c r="J14" s="122"/>
       <c r="K14" s="122"/>
-      <c r="L14" s="123"/>
+      <c r="L14" s="128"/>
       <c r="M14" s="6"/>
     </row>
     <row r="15" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6"/>
-      <c r="B15" s="140"/>
+      <c r="B15" s="145"/>
       <c r="C15" s="122"/>
       <c r="D15" s="122"/>
       <c r="E15" s="122"/>
@@ -2148,15 +2148,15 @@
       <c r="I15" s="122"/>
       <c r="J15" s="122"/>
       <c r="K15" s="122"/>
-      <c r="L15" s="123"/>
+      <c r="L15" s="128"/>
       <c r="M15" s="6"/>
     </row>
     <row r="16" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6"/>
-      <c r="B16" s="139" t="s">
+      <c r="B16" s="144" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="121" t="s">
+      <c r="C16" s="127" t="s">
         <v>16</v>
       </c>
       <c r="D16" s="122"/>
@@ -2167,22 +2167,22 @@
       <c r="I16" s="122"/>
       <c r="J16" s="122"/>
       <c r="K16" s="122"/>
-      <c r="L16" s="123"/>
+      <c r="L16" s="128"/>
       <c r="M16" s="6"/>
     </row>
     <row r="17" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6"/>
-      <c r="B17" s="141"/>
-      <c r="C17" s="124"/>
-      <c r="D17" s="124"/>
-      <c r="E17" s="124"/>
-      <c r="F17" s="124"/>
-      <c r="G17" s="124"/>
-      <c r="H17" s="124"/>
-      <c r="I17" s="124"/>
-      <c r="J17" s="124"/>
-      <c r="K17" s="124"/>
-      <c r="L17" s="125"/>
+      <c r="B17" s="146"/>
+      <c r="C17" s="129"/>
+      <c r="D17" s="129"/>
+      <c r="E17" s="129"/>
+      <c r="F17" s="129"/>
+      <c r="G17" s="129"/>
+      <c r="H17" s="129"/>
+      <c r="I17" s="129"/>
+      <c r="J17" s="129"/>
+      <c r="K17" s="129"/>
+      <c r="L17" s="130"/>
       <c r="M17" s="6"/>
     </row>
     <row r="18" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3240,12 +3240,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="142"/>
-      <c r="B1" s="143" t="s">
+      <c r="A1" s="147"/>
+      <c r="B1" s="148" t="s">
         <v>17</v>
       </c>
       <c r="C1" s="122"/>
-      <c r="D1" s="144" t="s">
+      <c r="D1" s="149" t="s">
         <v>18</v>
       </c>
       <c r="E1" s="122"/>
@@ -3260,11 +3260,11 @@
     </row>
     <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="122"/>
-      <c r="B2" s="143" t="s">
+      <c r="B2" s="148" t="s">
         <v>19</v>
       </c>
       <c r="C2" s="122"/>
-      <c r="D2" s="145" t="s">
+      <c r="D2" s="125" t="s">
         <v>20</v>
       </c>
       <c r="E2" s="122"/>
@@ -3283,12 +3283,12 @@
     </row>
     <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="122"/>
-      <c r="B3" s="143"/>
+      <c r="B3" s="148"/>
       <c r="C3" s="122"/>
-      <c r="D3" s="146"/>
+      <c r="D3" s="150"/>
       <c r="E3" s="122"/>
       <c r="F3" s="14"/>
-      <c r="G3" s="146"/>
+      <c r="G3" s="150"/>
       <c r="H3" s="122"/>
       <c r="I3" s="15"/>
       <c r="J3" s="16"/>
@@ -5304,12 +5304,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="147"/>
-      <c r="B1" s="148" t="s">
+      <c r="A1" s="121"/>
+      <c r="B1" s="123" t="s">
         <v>17</v>
       </c>
       <c r="C1" s="122"/>
-      <c r="D1" s="149" t="s">
+      <c r="D1" s="124" t="s">
         <v>18</v>
       </c>
       <c r="E1" s="122"/>
@@ -5324,11 +5324,11 @@
     </row>
     <row r="2" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="122"/>
-      <c r="B2" s="148" t="s">
+      <c r="B2" s="123" t="s">
         <v>19</v>
       </c>
       <c r="C2" s="122"/>
-      <c r="D2" s="145" t="s">
+      <c r="D2" s="125" t="s">
         <v>20</v>
       </c>
       <c r="E2" s="122"/>
@@ -5347,12 +5347,12 @@
     </row>
     <row r="3" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="122"/>
-      <c r="B3" s="148"/>
+      <c r="B3" s="123"/>
       <c r="C3" s="122"/>
-      <c r="D3" s="150"/>
+      <c r="D3" s="126"/>
       <c r="E3" s="122"/>
       <c r="F3" s="47"/>
-      <c r="G3" s="150"/>
+      <c r="G3" s="126"/>
       <c r="H3" s="122"/>
       <c r="I3" s="48"/>
       <c r="J3" s="49"/>
@@ -7578,13 +7578,13 @@
     <col min="14" max="26" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="147"/>
-      <c r="B1" s="148" t="s">
+    <row r="1" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="121"/>
+      <c r="B1" s="123" t="s">
         <v>17</v>
       </c>
       <c r="C1" s="122"/>
-      <c r="D1" s="149" t="s">
+      <c r="D1" s="124" t="s">
         <v>18</v>
       </c>
       <c r="E1" s="122"/>
@@ -7597,13 +7597,13 @@
       <c r="L1" s="46"/>
       <c r="M1" s="46"/>
     </row>
-    <row r="2" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="122"/>
-      <c r="B2" s="148" t="s">
+      <c r="B2" s="123" t="s">
         <v>19</v>
       </c>
       <c r="C2" s="122"/>
-      <c r="D2" s="145" t="s">
+      <c r="D2" s="125" t="s">
         <v>20</v>
       </c>
       <c r="E2" s="122"/>
@@ -7620,14 +7620,14 @@
       <c r="L2" s="49"/>
       <c r="M2" s="49"/>
     </row>
-    <row r="3" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="122"/>
-      <c r="B3" s="148"/>
+      <c r="B3" s="123"/>
       <c r="C3" s="122"/>
-      <c r="D3" s="150"/>
+      <c r="D3" s="126"/>
       <c r="E3" s="122"/>
       <c r="F3" s="47"/>
-      <c r="G3" s="150"/>
+      <c r="G3" s="126"/>
       <c r="H3" s="122"/>
       <c r="I3" s="48"/>
       <c r="J3" s="49"/>
@@ -7635,7 +7635,7 @@
       <c r="L3" s="49"/>
       <c r="M3" s="49"/>
     </row>
-    <row r="4" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="122"/>
       <c r="B4" s="51"/>
       <c r="C4" s="52"/>
@@ -7650,7 +7650,7 @@
       <c r="L4" s="53"/>
       <c r="M4" s="53"/>
     </row>
-    <row r="5" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="54" t="s">
         <v>22</v>
       </c>
@@ -7703,7 +7703,7 @@
         <v>Dezembro/2026</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="56" t="s">
         <v>23</v>
       </c>
@@ -7715,7 +7715,10 @@
         <f>C33</f>
         <v>2733.21</v>
       </c>
-      <c r="D6" s="57"/>
+      <c r="D6" s="57">
+        <f>D33</f>
+        <v>2794.29</v>
+      </c>
       <c r="E6" s="57"/>
       <c r="F6" s="57"/>
       <c r="G6" s="57"/>
@@ -7726,7 +7729,7 @@
       <c r="L6" s="57"/>
       <c r="M6" s="57"/>
     </row>
-    <row r="7" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="51"/>
       <c r="B7" s="58"/>
       <c r="C7" s="58"/>
@@ -7741,7 +7744,7 @@
       <c r="L7" s="58"/>
       <c r="M7" s="59"/>
     </row>
-    <row r="8" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="60" t="s">
         <v>24</v>
       </c>
@@ -7755,7 +7758,7 @@
       </c>
       <c r="D8" s="61">
         <f t="shared" ref="D8:E8" si="0">D9+D10</f>
-        <v>0</v>
+        <v>656.21</v>
       </c>
       <c r="E8" s="61">
         <f t="shared" si="0"/>
@@ -7794,7 +7797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="62" t="s">
         <v>25</v>
       </c>
@@ -7808,7 +7811,7 @@
       </c>
       <c r="D9" s="63">
         <f>TaxaCondominio!AB10</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E9" s="63">
         <f>TaxaCondominio!AC10</f>
@@ -7847,7 +7850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="62" t="s">
         <v>26</v>
       </c>
@@ -7857,7 +7860,9 @@
       <c r="C10" s="65">
         <v>27.74</v>
       </c>
-      <c r="D10" s="65"/>
+      <c r="D10" s="65">
+        <v>56.21</v>
+      </c>
       <c r="E10" s="65"/>
       <c r="F10" s="66"/>
       <c r="G10" s="66"/>
@@ -7868,7 +7873,7 @@
       <c r="L10" s="65"/>
       <c r="M10" s="65"/>
     </row>
-    <row r="11" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="51"/>
       <c r="B11" s="58"/>
       <c r="C11" s="58"/>
@@ -7883,7 +7888,7 @@
       <c r="L11" s="58"/>
       <c r="M11" s="59"/>
     </row>
-    <row r="12" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="51"/>
       <c r="B12" s="58"/>
       <c r="C12" s="58"/>
@@ -7898,7 +7903,7 @@
       <c r="L12" s="58"/>
       <c r="M12" s="59"/>
     </row>
-    <row r="13" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="67" t="s">
         <v>27</v>
       </c>
@@ -7950,8 +7955,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P13" s="118"/>
+    </row>
+    <row r="14" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="62" t="s">
         <v>28</v>
       </c>
@@ -7992,7 +7998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="62" t="s">
         <v>74</v>
       </c>
@@ -8033,7 +8039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="51"/>
       <c r="B16" s="58"/>
       <c r="C16" s="58"/>
@@ -8062,7 +8068,7 @@
       </c>
       <c r="D17" s="68">
         <f t="shared" ref="D17:M17" si="4">SUM(D18:D21)</f>
-        <v>0</v>
+        <v>145.13</v>
       </c>
       <c r="E17" s="68">
         <f t="shared" si="4"/>
@@ -8112,7 +8118,7 @@
         <v>81.25</v>
       </c>
       <c r="D18" s="70">
-        <v>0</v>
+        <v>81.239999999999995</v>
       </c>
       <c r="E18" s="70">
         <v>0</v>
@@ -8153,7 +8159,7 @@
         <v>69.989999999999995</v>
       </c>
       <c r="D19" s="70">
-        <v>0</v>
+        <v>63.89</v>
       </c>
       <c r="E19" s="70">
         <v>0</v>
@@ -8253,7 +8259,7 @@
       </c>
       <c r="D22" s="68">
         <f t="shared" si="5"/>
-        <v>150</v>
+        <v>450</v>
       </c>
       <c r="E22" s="68">
         <f t="shared" si="5"/>
@@ -8303,7 +8309,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="69">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E23" s="69">
         <v>0</v>
@@ -8460,7 +8466,8 @@
         <v>3234.45</v>
       </c>
       <c r="D28" s="70">
-        <v>0</v>
+        <f>C33+D8</f>
+        <v>3389.42</v>
       </c>
       <c r="E28" s="70">
         <v>0</v>
@@ -8504,7 +8511,7 @@
       </c>
       <c r="D29" s="70">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>56.21</v>
       </c>
       <c r="E29" s="70">
         <f t="shared" si="6"/>
@@ -8556,7 +8563,7 @@
       </c>
       <c r="D30" s="70">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>145.13</v>
       </c>
       <c r="E30" s="70">
         <f t="shared" si="8"/>
@@ -8609,7 +8616,7 @@
       </c>
       <c r="D31" s="70">
         <f t="shared" si="9"/>
-        <v>150</v>
+        <v>450</v>
       </c>
       <c r="E31" s="70">
         <f t="shared" si="9"/>
@@ -8716,7 +8723,7 @@
       </c>
       <c r="D33" s="73">
         <f t="shared" si="11"/>
-        <v>-150</v>
+        <v>2794.29</v>
       </c>
       <c r="E33" s="73">
         <f t="shared" si="11"/>
@@ -8810,7 +8817,9 @@
       <c r="D36" s="118"/>
       <c r="I36" s="118"/>
     </row>
-    <row r="37" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N37" s="118"/>
+    </row>
     <row r="38" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E38" s="118"/>
     </row>
@@ -9893,6 +9902,7 @@
       <c r="Y3" s="82"/>
       <c r="Z3" s="82"/>
       <c r="AA3" s="82"/>
+      <c r="AB3" s="82"/>
     </row>
     <row r="4" spans="1:39" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="78" t="s">
@@ -9988,6 +9998,9 @@
       <c r="AA4" s="84">
         <v>46054</v>
       </c>
+      <c r="AB4" s="84">
+        <v>46082</v>
+      </c>
     </row>
     <row r="5" spans="1:39" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="81">
@@ -10071,6 +10084,9 @@
       <c r="AA5" s="120">
         <v>150</v>
       </c>
+      <c r="AB5" s="120">
+        <v>150</v>
+      </c>
     </row>
     <row r="6" spans="1:39" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="81">
@@ -10154,6 +10170,9 @@
       <c r="AA6" s="89">
         <v>150</v>
       </c>
+      <c r="AB6" s="89">
+        <v>150</v>
+      </c>
     </row>
     <row r="7" spans="1:39" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="81">
@@ -10237,6 +10256,9 @@
       <c r="AA7" s="89">
         <v>150</v>
       </c>
+      <c r="AB7" s="89">
+        <v>150</v>
+      </c>
     </row>
     <row r="8" spans="1:39" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="81">
@@ -10318,6 +10340,9 @@
         <v>150</v>
       </c>
       <c r="AA8" s="89">
+        <v>150</v>
+      </c>
+      <c r="AB8" s="89">
         <v>150</v>
       </c>
     </row>
@@ -10467,7 +10492,11 @@
         <v>600</v>
       </c>
       <c r="AA10" s="91">
-        <f t="shared" ref="AA10" si="1">SUM(AA5:AA8)</f>
+        <f t="shared" ref="AA10:AB10" si="1">SUM(AA5:AA8)</f>
+        <v>600</v>
+      </c>
+      <c r="AB10" s="91">
+        <f t="shared" si="1"/>
         <v>600</v>
       </c>
     </row>
@@ -14658,10 +14687,10 @@
       <c r="B1" s="155" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="128"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="133"/>
       <c r="G1" s="93"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">

--- a/planilhas/Contabilidade Condominio.xlsx
+++ b/planilhas/Contabilidade Condominio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Condominio\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4426E17-E78F-400C-A6D2-7F1376FE38F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4964A83-0902-4BBA-B6A4-F88C01389AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7719,7 +7719,10 @@
         <f>D33</f>
         <v>2794.29</v>
       </c>
-      <c r="E6" s="57"/>
+      <c r="E6" s="57">
+        <f>E33</f>
+        <v>3124.3500000000004</v>
+      </c>
       <c r="F6" s="57"/>
       <c r="G6" s="57"/>
       <c r="H6" s="57"/>
@@ -7762,7 +7765,7 @@
       </c>
       <c r="E8" s="61">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>624.97</v>
       </c>
       <c r="F8" s="61">
         <f t="shared" ref="F8:M8" si="1">SUM(F9:F11)</f>
@@ -7815,7 +7818,7 @@
       </c>
       <c r="E9" s="63">
         <f>TaxaCondominio!AC10</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F9" s="63">
         <f>TaxaCondominio!AD10</f>
@@ -7863,7 +7866,9 @@
       <c r="D10" s="65">
         <v>56.21</v>
       </c>
-      <c r="E10" s="65"/>
+      <c r="E10" s="65">
+        <v>24.97</v>
+      </c>
       <c r="F10" s="66"/>
       <c r="G10" s="66"/>
       <c r="H10" s="65"/>
@@ -8072,7 +8077,7 @@
       </c>
       <c r="E17" s="68">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>144.91</v>
       </c>
       <c r="F17" s="68">
         <f t="shared" si="4"/>
@@ -8121,7 +8126,7 @@
         <v>81.239999999999995</v>
       </c>
       <c r="E18" s="70">
-        <v>0</v>
+        <v>81.239999999999995</v>
       </c>
       <c r="F18" s="70">
         <v>0</v>
@@ -8162,7 +8167,7 @@
         <v>63.89</v>
       </c>
       <c r="E19" s="70">
-        <v>0</v>
+        <v>63.67</v>
       </c>
       <c r="F19" s="70">
         <v>0</v>
@@ -8470,7 +8475,8 @@
         <v>3389.42</v>
       </c>
       <c r="E28" s="70">
-        <v>0</v>
+        <f>D33+E8</f>
+        <v>3419.26</v>
       </c>
       <c r="F28" s="70">
         <v>0</v>
@@ -8515,7 +8521,7 @@
       </c>
       <c r="E29" s="70">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>24.97</v>
       </c>
       <c r="F29" s="70">
         <f>F13</f>
@@ -8567,7 +8573,7 @@
       </c>
       <c r="E30" s="70">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>144.91</v>
       </c>
       <c r="F30" s="70">
         <f t="shared" si="8"/>
@@ -8727,7 +8733,7 @@
       </c>
       <c r="E33" s="73">
         <f t="shared" si="11"/>
-        <v>-150</v>
+        <v>3124.3500000000004</v>
       </c>
       <c r="F33" s="73">
         <f t="shared" si="11"/>
@@ -8821,7 +8827,7 @@
       <c r="N37" s="118"/>
     </row>
     <row r="38" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E38" s="118"/>
+      <c r="E38" s="116"/>
     </row>
     <row r="39" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F39" s="118"/>
@@ -9903,6 +9909,7 @@
       <c r="Z3" s="82"/>
       <c r="AA3" s="82"/>
       <c r="AB3" s="82"/>
+      <c r="AC3" s="82"/>
     </row>
     <row r="4" spans="1:39" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="78" t="s">
@@ -10001,6 +10008,9 @@
       <c r="AB4" s="84">
         <v>46082</v>
       </c>
+      <c r="AC4" s="84">
+        <v>46113</v>
+      </c>
     </row>
     <row r="5" spans="1:39" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="81">
@@ -10087,6 +10097,9 @@
       <c r="AB5" s="120">
         <v>150</v>
       </c>
+      <c r="AC5" s="120">
+        <v>150</v>
+      </c>
     </row>
     <row r="6" spans="1:39" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="81">
@@ -10173,6 +10186,9 @@
       <c r="AB6" s="89">
         <v>150</v>
       </c>
+      <c r="AC6" s="89">
+        <v>150</v>
+      </c>
     </row>
     <row r="7" spans="1:39" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="81">
@@ -10259,6 +10275,9 @@
       <c r="AB7" s="89">
         <v>150</v>
       </c>
+      <c r="AC7" s="89">
+        <v>150</v>
+      </c>
     </row>
     <row r="8" spans="1:39" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="81">
@@ -10343,6 +10362,9 @@
         <v>150</v>
       </c>
       <c r="AB8" s="89">
+        <v>150</v>
+      </c>
+      <c r="AC8" s="89">
         <v>150</v>
       </c>
     </row>
@@ -10497,6 +10519,10 @@
       </c>
       <c r="AB10" s="91">
         <f t="shared" si="1"/>
+        <v>600</v>
+      </c>
+      <c r="AC10" s="91">
+        <f t="shared" ref="AC10" si="2">SUM(AC5:AC8)</f>
         <v>600</v>
       </c>
     </row>

--- a/planilhas/Contabilidade Condominio.xlsx
+++ b/planilhas/Contabilidade Condominio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Condominio\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4964A83-0902-4BBA-B6A4-F88C01389AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64267CF7-3CCC-46BF-B07D-2CDF22BC1374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CAPA Explicações" sheetId="1" r:id="rId1"/>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="F8" s="61">
         <f t="shared" ref="F8:M8" si="1">SUM(F9:F11)</f>
-        <v>0</v>
+        <v>635.12</v>
       </c>
       <c r="G8" s="61">
         <f t="shared" si="1"/>
@@ -7822,7 +7822,7 @@
       </c>
       <c r="F9" s="63">
         <f>TaxaCondominio!AD10</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G9" s="63">
         <f>TaxaCondominio!AE10</f>
@@ -7869,7 +7869,9 @@
       <c r="E10" s="65">
         <v>24.97</v>
       </c>
-      <c r="F10" s="66"/>
+      <c r="F10" s="66">
+        <v>35.119999999999997</v>
+      </c>
       <c r="G10" s="66"/>
       <c r="H10" s="65"/>
       <c r="I10" s="65"/>
@@ -8081,7 +8083,7 @@
       </c>
       <c r="F17" s="68">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>976.31</v>
       </c>
       <c r="G17" s="68">
         <f t="shared" si="4"/>
@@ -8129,7 +8131,7 @@
         <v>81.239999999999995</v>
       </c>
       <c r="F18" s="70">
-        <v>0</v>
+        <v>81.239999999999995</v>
       </c>
       <c r="G18" s="70">
         <v>0</v>
@@ -8170,7 +8172,7 @@
         <v>63.67</v>
       </c>
       <c r="F19" s="70">
-        <v>0</v>
+        <v>64.680000000000007</v>
       </c>
       <c r="G19" s="70">
         <v>0</v>
@@ -8211,7 +8213,8 @@
         <v>0</v>
       </c>
       <c r="F20" s="69">
-        <v>0</v>
+        <f>150 + 150 + 399 + 131.39</f>
+        <v>830.39</v>
       </c>
       <c r="G20" s="69">
         <v>0</v>
@@ -8479,7 +8482,8 @@
         <v>3419.26</v>
       </c>
       <c r="F28" s="70">
-        <v>0</v>
+        <f>E33+F8</f>
+        <v>3759.4700000000003</v>
       </c>
       <c r="G28" s="70">
         <v>0</v>
@@ -8577,7 +8581,7 @@
       </c>
       <c r="F30" s="70">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>976.31</v>
       </c>
       <c r="G30" s="70">
         <f t="shared" si="8"/>
@@ -8737,7 +8741,7 @@
       </c>
       <c r="F33" s="73">
         <f t="shared" si="11"/>
-        <v>-150</v>
+        <v>2633.1600000000003</v>
       </c>
       <c r="G33" s="73">
         <f t="shared" si="11"/>
@@ -9910,6 +9914,7 @@
       <c r="AA3" s="82"/>
       <c r="AB3" s="82"/>
       <c r="AC3" s="82"/>
+      <c r="AD3" s="82"/>
     </row>
     <row r="4" spans="1:39" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="78" t="s">
@@ -10011,6 +10016,9 @@
       <c r="AC4" s="84">
         <v>46113</v>
       </c>
+      <c r="AD4" s="84">
+        <v>46143</v>
+      </c>
     </row>
     <row r="5" spans="1:39" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="81">
@@ -10100,6 +10108,9 @@
       <c r="AC5" s="120">
         <v>150</v>
       </c>
+      <c r="AD5" s="120">
+        <v>150</v>
+      </c>
     </row>
     <row r="6" spans="1:39" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="81">
@@ -10189,6 +10200,9 @@
       <c r="AC6" s="89">
         <v>150</v>
       </c>
+      <c r="AD6" s="89">
+        <v>150</v>
+      </c>
     </row>
     <row r="7" spans="1:39" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="81">
@@ -10278,6 +10292,9 @@
       <c r="AC7" s="89">
         <v>150</v>
       </c>
+      <c r="AD7" s="89">
+        <v>150</v>
+      </c>
     </row>
     <row r="8" spans="1:39" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="81">
@@ -10365,6 +10382,9 @@
         <v>150</v>
       </c>
       <c r="AC8" s="89">
+        <v>150</v>
+      </c>
+      <c r="AD8" s="89">
         <v>150</v>
       </c>
     </row>
@@ -10522,7 +10542,11 @@
         <v>600</v>
       </c>
       <c r="AC10" s="91">
-        <f t="shared" ref="AC10" si="2">SUM(AC5:AC8)</f>
+        <f t="shared" ref="AC10:AD10" si="2">SUM(AC5:AC8)</f>
+        <v>600</v>
+      </c>
+      <c r="AD10" s="91">
+        <f t="shared" si="2"/>
         <v>600</v>
       </c>
     </row>

--- a/planilhas/Contabilidade Condominio.xlsx
+++ b/planilhas/Contabilidade Condominio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Condominio\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64267CF7-3CCC-46BF-B07D-2CDF22BC1374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{128587C1-0DAE-4330-BFA4-73CDCAE7FDFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7723,7 +7723,10 @@
         <f>E33</f>
         <v>3124.3500000000004</v>
       </c>
-      <c r="F6" s="57"/>
+      <c r="F6" s="57">
+        <f>F33</f>
+        <v>2633.1600000000003</v>
+      </c>
       <c r="G6" s="57"/>
       <c r="H6" s="57"/>
       <c r="I6" s="57"/>

--- a/planilhas/Contabilidade Condominio.xlsx
+++ b/planilhas/Contabilidade Condominio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Condominio\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{128587C1-0DAE-4330-BFA4-73CDCAE7FDFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{880521C3-95E8-4E5B-8CCB-B874B3E7CF60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CAPA Explicações" sheetId="1" r:id="rId1"/>
@@ -1253,7 +1253,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1593,6 +1593,7 @@
     <xf numFmtId="2" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="8" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1898,68 +1899,68 @@
   <sheetData>
     <row r="1" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
-      <c r="B1" s="131" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
-      <c r="K1" s="132"/>
-      <c r="L1" s="133"/>
+      <c r="B1" s="132" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="133"/>
+      <c r="H1" s="133"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="133"/>
+      <c r="K1" s="133"/>
+      <c r="L1" s="134"/>
       <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" s="134" t="s">
+      <c r="B2" s="135" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="132"/>
-      <c r="D2" s="132"/>
-      <c r="E2" s="132"/>
-      <c r="F2" s="132"/>
-      <c r="G2" s="132"/>
-      <c r="H2" s="132"/>
-      <c r="I2" s="132"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="132"/>
-      <c r="L2" s="133"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
+      <c r="I2" s="133"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="134"/>
       <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
-      <c r="B3" s="135" t="s">
+      <c r="B3" s="136" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="136"/>
-      <c r="D3" s="136"/>
-      <c r="E3" s="136"/>
-      <c r="F3" s="136"/>
-      <c r="G3" s="136"/>
-      <c r="H3" s="136"/>
-      <c r="I3" s="136"/>
-      <c r="J3" s="136"/>
-      <c r="K3" s="136"/>
-      <c r="L3" s="137"/>
+      <c r="C3" s="137"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="137"/>
+      <c r="F3" s="137"/>
+      <c r="G3" s="137"/>
+      <c r="H3" s="137"/>
+      <c r="I3" s="137"/>
+      <c r="J3" s="137"/>
+      <c r="K3" s="137"/>
+      <c r="L3" s="138"/>
       <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3"/>
-      <c r="B4" s="138"/>
-      <c r="C4" s="139"/>
-      <c r="D4" s="139"/>
-      <c r="E4" s="139"/>
-      <c r="F4" s="139"/>
-      <c r="G4" s="139"/>
-      <c r="H4" s="139"/>
-      <c r="I4" s="139"/>
-      <c r="J4" s="139"/>
-      <c r="K4" s="139"/>
-      <c r="L4" s="140"/>
+      <c r="B4" s="139"/>
+      <c r="C4" s="140"/>
+      <c r="D4" s="140"/>
+      <c r="E4" s="140"/>
+      <c r="F4" s="140"/>
+      <c r="G4" s="140"/>
+      <c r="H4" s="140"/>
+      <c r="I4" s="140"/>
+      <c r="J4" s="140"/>
+      <c r="K4" s="140"/>
+      <c r="L4" s="141"/>
       <c r="M4" s="3"/>
     </row>
     <row r="5" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -1967,222 +1968,222 @@
       <c r="B5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="141" t="s">
+      <c r="C5" s="142" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="142"/>
-      <c r="E5" s="142"/>
-      <c r="F5" s="142"/>
-      <c r="G5" s="142"/>
-      <c r="H5" s="142"/>
-      <c r="I5" s="142"/>
-      <c r="J5" s="142"/>
-      <c r="K5" s="142"/>
-      <c r="L5" s="143"/>
+      <c r="D5" s="143"/>
+      <c r="E5" s="143"/>
+      <c r="F5" s="143"/>
+      <c r="G5" s="143"/>
+      <c r="H5" s="143"/>
+      <c r="I5" s="143"/>
+      <c r="J5" s="143"/>
+      <c r="K5" s="143"/>
+      <c r="L5" s="144"/>
       <c r="M5" s="4"/>
     </row>
     <row r="6" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6"/>
-      <c r="B6" s="144" t="s">
+      <c r="B6" s="145" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="127" t="s">
+      <c r="C6" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="122"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="122"/>
-      <c r="J6" s="122"/>
-      <c r="K6" s="122"/>
-      <c r="L6" s="128"/>
+      <c r="D6" s="123"/>
+      <c r="E6" s="123"/>
+      <c r="F6" s="123"/>
+      <c r="G6" s="123"/>
+      <c r="H6" s="123"/>
+      <c r="I6" s="123"/>
+      <c r="J6" s="123"/>
+      <c r="K6" s="123"/>
+      <c r="L6" s="129"/>
       <c r="M6" s="6"/>
     </row>
     <row r="7" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6"/>
-      <c r="B7" s="145"/>
-      <c r="C7" s="122"/>
-      <c r="D7" s="122"/>
-      <c r="E7" s="122"/>
-      <c r="F7" s="122"/>
-      <c r="G7" s="122"/>
-      <c r="H7" s="122"/>
-      <c r="I7" s="122"/>
-      <c r="J7" s="122"/>
-      <c r="K7" s="122"/>
-      <c r="L7" s="128"/>
+      <c r="B7" s="146"/>
+      <c r="C7" s="123"/>
+      <c r="D7" s="123"/>
+      <c r="E7" s="123"/>
+      <c r="F7" s="123"/>
+      <c r="G7" s="123"/>
+      <c r="H7" s="123"/>
+      <c r="I7" s="123"/>
+      <c r="J7" s="123"/>
+      <c r="K7" s="123"/>
+      <c r="L7" s="129"/>
       <c r="M7" s="6"/>
     </row>
     <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6"/>
-      <c r="B8" s="144" t="s">
+      <c r="B8" s="145" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="127" t="s">
+      <c r="C8" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="122"/>
-      <c r="E8" s="122"/>
-      <c r="F8" s="122"/>
-      <c r="G8" s="122"/>
-      <c r="H8" s="122"/>
-      <c r="I8" s="122"/>
-      <c r="J8" s="122"/>
-      <c r="K8" s="122"/>
-      <c r="L8" s="128"/>
+      <c r="D8" s="123"/>
+      <c r="E8" s="123"/>
+      <c r="F8" s="123"/>
+      <c r="G8" s="123"/>
+      <c r="H8" s="123"/>
+      <c r="I8" s="123"/>
+      <c r="J8" s="123"/>
+      <c r="K8" s="123"/>
+      <c r="L8" s="129"/>
       <c r="M8" s="6"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6"/>
-      <c r="B9" s="145"/>
-      <c r="C9" s="122"/>
-      <c r="D9" s="122"/>
-      <c r="E9" s="122"/>
-      <c r="F9" s="122"/>
-      <c r="G9" s="122"/>
-      <c r="H9" s="122"/>
-      <c r="I9" s="122"/>
-      <c r="J9" s="122"/>
-      <c r="K9" s="122"/>
-      <c r="L9" s="128"/>
+      <c r="B9" s="146"/>
+      <c r="C9" s="123"/>
+      <c r="D9" s="123"/>
+      <c r="E9" s="123"/>
+      <c r="F9" s="123"/>
+      <c r="G9" s="123"/>
+      <c r="H9" s="123"/>
+      <c r="I9" s="123"/>
+      <c r="J9" s="123"/>
+      <c r="K9" s="123"/>
+      <c r="L9" s="129"/>
       <c r="M9" s="6"/>
     </row>
     <row r="10" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6"/>
-      <c r="B10" s="144" t="s">
+      <c r="B10" s="145" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="127" t="s">
+      <c r="C10" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="122"/>
-      <c r="E10" s="122"/>
-      <c r="F10" s="122"/>
-      <c r="G10" s="122"/>
-      <c r="H10" s="122"/>
-      <c r="I10" s="122"/>
-      <c r="J10" s="122"/>
-      <c r="K10" s="122"/>
-      <c r="L10" s="128"/>
+      <c r="D10" s="123"/>
+      <c r="E10" s="123"/>
+      <c r="F10" s="123"/>
+      <c r="G10" s="123"/>
+      <c r="H10" s="123"/>
+      <c r="I10" s="123"/>
+      <c r="J10" s="123"/>
+      <c r="K10" s="123"/>
+      <c r="L10" s="129"/>
       <c r="M10" s="6"/>
     </row>
     <row r="11" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6"/>
-      <c r="B11" s="145"/>
-      <c r="C11" s="122"/>
-      <c r="D11" s="122"/>
-      <c r="E11" s="122"/>
-      <c r="F11" s="122"/>
-      <c r="G11" s="122"/>
-      <c r="H11" s="122"/>
-      <c r="I11" s="122"/>
-      <c r="J11" s="122"/>
-      <c r="K11" s="122"/>
-      <c r="L11" s="128"/>
+      <c r="B11" s="146"/>
+      <c r="C11" s="123"/>
+      <c r="D11" s="123"/>
+      <c r="E11" s="123"/>
+      <c r="F11" s="123"/>
+      <c r="G11" s="123"/>
+      <c r="H11" s="123"/>
+      <c r="I11" s="123"/>
+      <c r="J11" s="123"/>
+      <c r="K11" s="123"/>
+      <c r="L11" s="129"/>
       <c r="M11" s="6"/>
     </row>
     <row r="12" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6"/>
-      <c r="B12" s="144" t="s">
+      <c r="B12" s="145" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="127" t="s">
+      <c r="C12" s="128" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="122"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="122"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="122"/>
-      <c r="J12" s="122"/>
-      <c r="K12" s="122"/>
-      <c r="L12" s="128"/>
+      <c r="D12" s="123"/>
+      <c r="E12" s="123"/>
+      <c r="F12" s="123"/>
+      <c r="G12" s="123"/>
+      <c r="H12" s="123"/>
+      <c r="I12" s="123"/>
+      <c r="J12" s="123"/>
+      <c r="K12" s="123"/>
+      <c r="L12" s="129"/>
       <c r="M12" s="6"/>
     </row>
     <row r="13" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
-      <c r="B13" s="145"/>
-      <c r="C13" s="122"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="122"/>
-      <c r="F13" s="122"/>
-      <c r="G13" s="122"/>
-      <c r="H13" s="122"/>
-      <c r="I13" s="122"/>
-      <c r="J13" s="122"/>
-      <c r="K13" s="122"/>
-      <c r="L13" s="128"/>
+      <c r="B13" s="146"/>
+      <c r="C13" s="123"/>
+      <c r="D13" s="123"/>
+      <c r="E13" s="123"/>
+      <c r="F13" s="123"/>
+      <c r="G13" s="123"/>
+      <c r="H13" s="123"/>
+      <c r="I13" s="123"/>
+      <c r="J13" s="123"/>
+      <c r="K13" s="123"/>
+      <c r="L13" s="129"/>
       <c r="M13" s="6"/>
     </row>
     <row r="14" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6"/>
-      <c r="B14" s="144" t="s">
+      <c r="B14" s="145" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="127" t="s">
+      <c r="C14" s="128" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="122"/>
-      <c r="E14" s="122"/>
-      <c r="F14" s="122"/>
-      <c r="G14" s="122"/>
-      <c r="H14" s="122"/>
-      <c r="I14" s="122"/>
-      <c r="J14" s="122"/>
-      <c r="K14" s="122"/>
-      <c r="L14" s="128"/>
+      <c r="D14" s="123"/>
+      <c r="E14" s="123"/>
+      <c r="F14" s="123"/>
+      <c r="G14" s="123"/>
+      <c r="H14" s="123"/>
+      <c r="I14" s="123"/>
+      <c r="J14" s="123"/>
+      <c r="K14" s="123"/>
+      <c r="L14" s="129"/>
       <c r="M14" s="6"/>
     </row>
     <row r="15" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6"/>
-      <c r="B15" s="145"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="122"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="122"/>
-      <c r="H15" s="122"/>
-      <c r="I15" s="122"/>
-      <c r="J15" s="122"/>
-      <c r="K15" s="122"/>
-      <c r="L15" s="128"/>
+      <c r="B15" s="146"/>
+      <c r="C15" s="123"/>
+      <c r="D15" s="123"/>
+      <c r="E15" s="123"/>
+      <c r="F15" s="123"/>
+      <c r="G15" s="123"/>
+      <c r="H15" s="123"/>
+      <c r="I15" s="123"/>
+      <c r="J15" s="123"/>
+      <c r="K15" s="123"/>
+      <c r="L15" s="129"/>
       <c r="M15" s="6"/>
     </row>
     <row r="16" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6"/>
-      <c r="B16" s="144" t="s">
+      <c r="B16" s="145" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="127" t="s">
+      <c r="C16" s="128" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="122"/>
-      <c r="J16" s="122"/>
-      <c r="K16" s="122"/>
-      <c r="L16" s="128"/>
+      <c r="D16" s="123"/>
+      <c r="E16" s="123"/>
+      <c r="F16" s="123"/>
+      <c r="G16" s="123"/>
+      <c r="H16" s="123"/>
+      <c r="I16" s="123"/>
+      <c r="J16" s="123"/>
+      <c r="K16" s="123"/>
+      <c r="L16" s="129"/>
       <c r="M16" s="6"/>
     </row>
     <row r="17" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6"/>
-      <c r="B17" s="146"/>
-      <c r="C17" s="129"/>
-      <c r="D17" s="129"/>
-      <c r="E17" s="129"/>
-      <c r="F17" s="129"/>
-      <c r="G17" s="129"/>
-      <c r="H17" s="129"/>
-      <c r="I17" s="129"/>
-      <c r="J17" s="129"/>
-      <c r="K17" s="129"/>
-      <c r="L17" s="130"/>
+      <c r="B17" s="147"/>
+      <c r="C17" s="130"/>
+      <c r="D17" s="130"/>
+      <c r="E17" s="130"/>
+      <c r="F17" s="130"/>
+      <c r="G17" s="130"/>
+      <c r="H17" s="130"/>
+      <c r="I17" s="130"/>
+      <c r="J17" s="130"/>
+      <c r="K17" s="130"/>
+      <c r="L17" s="131"/>
       <c r="M17" s="6"/>
     </row>
     <row r="18" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3240,18 +3241,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="147"/>
-      <c r="B1" s="148" t="s">
+      <c r="A1" s="148"/>
+      <c r="B1" s="149" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="122"/>
-      <c r="D1" s="149" t="s">
+      <c r="C1" s="123"/>
+      <c r="D1" s="150" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
+      <c r="H1" s="123"/>
       <c r="I1" s="12"/>
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
@@ -3259,16 +3260,16 @@
       <c r="M1" s="13"/>
     </row>
     <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="122"/>
-      <c r="B2" s="148" t="s">
+      <c r="A2" s="123"/>
+      <c r="B2" s="149" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="122"/>
-      <c r="D2" s="125" t="s">
+      <c r="C2" s="123"/>
+      <c r="D2" s="126" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="122"/>
-      <c r="F2" s="122"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="123"/>
       <c r="G2" s="14" t="s">
         <v>21</v>
       </c>
@@ -3282,14 +3283,14 @@
       <c r="M2" s="16"/>
     </row>
     <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="122"/>
-      <c r="B3" s="148"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="150"/>
-      <c r="E3" s="122"/>
+      <c r="A3" s="123"/>
+      <c r="B3" s="149"/>
+      <c r="C3" s="123"/>
+      <c r="D3" s="151"/>
+      <c r="E3" s="123"/>
       <c r="F3" s="14"/>
-      <c r="G3" s="150"/>
-      <c r="H3" s="122"/>
+      <c r="G3" s="151"/>
+      <c r="H3" s="123"/>
       <c r="I3" s="15"/>
       <c r="J3" s="16"/>
       <c r="K3" s="16"/>
@@ -3297,7 +3298,7 @@
       <c r="M3" s="16"/>
     </row>
     <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="122"/>
+      <c r="A4" s="123"/>
       <c r="B4" s="17"/>
       <c r="C4" s="18"/>
       <c r="D4" s="18"/>
@@ -5304,18 +5305,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="121"/>
-      <c r="B1" s="123" t="s">
+      <c r="A1" s="122"/>
+      <c r="B1" s="124" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="122"/>
-      <c r="D1" s="124" t="s">
+      <c r="C1" s="123"/>
+      <c r="D1" s="125" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
+      <c r="H1" s="123"/>
       <c r="I1" s="45"/>
       <c r="J1" s="46"/>
       <c r="K1" s="46"/>
@@ -5323,16 +5324,16 @@
       <c r="M1" s="46"/>
     </row>
     <row r="2" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="122"/>
-      <c r="B2" s="123" t="s">
+      <c r="A2" s="123"/>
+      <c r="B2" s="124" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="122"/>
-      <c r="D2" s="125" t="s">
+      <c r="C2" s="123"/>
+      <c r="D2" s="126" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="122"/>
-      <c r="F2" s="122"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="123"/>
       <c r="G2" s="47" t="s">
         <v>21</v>
       </c>
@@ -5346,14 +5347,14 @@
       <c r="M2" s="49"/>
     </row>
     <row r="3" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="122"/>
-      <c r="B3" s="123"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="126"/>
-      <c r="E3" s="122"/>
+      <c r="A3" s="123"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="123"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="123"/>
       <c r="F3" s="47"/>
-      <c r="G3" s="126"/>
-      <c r="H3" s="122"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="123"/>
       <c r="I3" s="48"/>
       <c r="J3" s="49"/>
       <c r="K3" s="49"/>
@@ -5361,7 +5362,7 @@
       <c r="M3" s="49"/>
     </row>
     <row r="4" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="122"/>
+      <c r="A4" s="123"/>
       <c r="B4" s="51"/>
       <c r="C4" s="52"/>
       <c r="D4" s="52"/>
@@ -7579,18 +7580,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="121"/>
-      <c r="B1" s="123" t="s">
+      <c r="A1" s="122"/>
+      <c r="B1" s="124" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="122"/>
-      <c r="D1" s="124" t="s">
+      <c r="C1" s="123"/>
+      <c r="D1" s="125" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
+      <c r="H1" s="123"/>
       <c r="I1" s="45"/>
       <c r="J1" s="46"/>
       <c r="K1" s="46"/>
@@ -7598,16 +7599,16 @@
       <c r="M1" s="46"/>
     </row>
     <row r="2" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="122"/>
-      <c r="B2" s="123" t="s">
+      <c r="A2" s="123"/>
+      <c r="B2" s="124" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="122"/>
-      <c r="D2" s="125" t="s">
+      <c r="C2" s="123"/>
+      <c r="D2" s="126" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="122"/>
-      <c r="F2" s="122"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="123"/>
       <c r="G2" s="47" t="s">
         <v>21</v>
       </c>
@@ -7621,14 +7622,14 @@
       <c r="M2" s="49"/>
     </row>
     <row r="3" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="122"/>
-      <c r="B3" s="123"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="126"/>
-      <c r="E3" s="122"/>
+      <c r="A3" s="123"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="123"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="123"/>
       <c r="F3" s="47"/>
-      <c r="G3" s="126"/>
-      <c r="H3" s="122"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="123"/>
       <c r="I3" s="48"/>
       <c r="J3" s="49"/>
       <c r="K3" s="49"/>
@@ -7636,7 +7637,7 @@
       <c r="M3" s="49"/>
     </row>
     <row r="4" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="122"/>
+      <c r="A4" s="123"/>
       <c r="B4" s="51"/>
       <c r="C4" s="52"/>
       <c r="D4" s="52"/>
@@ -7763,43 +7764,43 @@
         <v>600</v>
       </c>
       <c r="D8" s="61">
-        <f t="shared" ref="D8:E8" si="0">D9+D10</f>
+        <f>D9+D10</f>
         <v>656.21</v>
       </c>
       <c r="E8" s="61">
+        <f>E9+E10</f>
+        <v>624.97</v>
+      </c>
+      <c r="F8" s="61">
+        <f t="shared" ref="F8:M8" si="0">SUM(F9:F11)</f>
+        <v>635.12</v>
+      </c>
+      <c r="G8" s="61">
         <f t="shared" si="0"/>
-        <v>624.97</v>
-      </c>
-      <c r="F8" s="61">
-        <f t="shared" ref="F8:M8" si="1">SUM(F9:F11)</f>
-        <v>635.12</v>
-      </c>
-      <c r="G8" s="61">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>605.55999999999995</v>
       </c>
       <c r="H8" s="61">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I8" s="61">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J8" s="61">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K8" s="61">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L8" s="61">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M8" s="61">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -7829,7 +7830,7 @@
       </c>
       <c r="G9" s="63">
         <f>TaxaCondominio!AE10</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H9" s="63">
         <f>TaxaCondominio!AF10</f>
@@ -7875,7 +7876,9 @@
       <c r="F10" s="66">
         <v>35.119999999999997</v>
       </c>
-      <c r="G10" s="66"/>
+      <c r="G10" s="66">
+        <v>5.56</v>
+      </c>
       <c r="H10" s="65"/>
       <c r="I10" s="65"/>
       <c r="J10" s="65"/>
@@ -7918,51 +7921,51 @@
         <v>27</v>
       </c>
       <c r="B13" s="68">
-        <f t="shared" ref="B13:M13" si="2">SUM(B14:B16)</f>
+        <f t="shared" ref="B13:M13" si="1">SUM(B14:B16)</f>
         <v>0</v>
       </c>
       <c r="C13" s="68">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D13" s="68">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E13" s="68">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F13" s="68">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G13" s="68">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H13" s="68">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I13" s="68">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J13" s="68">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K13" s="68">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L13" s="68">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M13" s="68">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P13" s="118"/>
@@ -8069,51 +8072,51 @@
         <v>29</v>
       </c>
       <c r="B17" s="68">
-        <f t="shared" ref="B17:C17" si="3">B18+B19+B20</f>
+        <f t="shared" ref="B17:C17" si="2">B18+B19+B20</f>
         <v>345.65</v>
       </c>
       <c r="C17" s="68">
+        <f t="shared" si="2"/>
+        <v>351.24</v>
+      </c>
+      <c r="D17" s="68">
+        <f t="shared" ref="D17:M17" si="3">SUM(D18:D21)</f>
+        <v>145.13</v>
+      </c>
+      <c r="E17" s="68">
         <f t="shared" si="3"/>
-        <v>351.24</v>
-      </c>
-      <c r="D17" s="68">
-        <f t="shared" ref="D17:M17" si="4">SUM(D18:D21)</f>
-        <v>145.13</v>
-      </c>
-      <c r="E17" s="68">
-        <f t="shared" si="4"/>
         <v>144.91</v>
       </c>
       <c r="F17" s="68">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>976.31</v>
       </c>
       <c r="G17" s="68">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>445.96</v>
       </c>
       <c r="H17" s="68">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I17" s="68">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J17" s="68">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K17" s="68">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L17" s="68">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M17" s="68">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -8137,7 +8140,7 @@
         <v>81.239999999999995</v>
       </c>
       <c r="G18" s="70">
-        <v>0</v>
+        <v>81.239999999999995</v>
       </c>
       <c r="H18" s="70">
         <v>0</v>
@@ -8178,7 +8181,7 @@
         <v>64.680000000000007</v>
       </c>
       <c r="G19" s="70">
-        <v>0</v>
+        <v>64.72</v>
       </c>
       <c r="H19" s="70">
         <v>0</v>
@@ -8220,7 +8223,7 @@
         <v>830.39</v>
       </c>
       <c r="G20" s="69">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H20" s="69">
         <v>0</v>
@@ -8265,47 +8268,47 @@
         <v>1000</v>
       </c>
       <c r="C22" s="68">
-        <f t="shared" ref="C22:M22" si="5">SUM(C23:C26)</f>
+        <f t="shared" ref="C22:M22" si="4">SUM(C23:C26)</f>
         <v>150</v>
       </c>
       <c r="D22" s="68">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>450</v>
       </c>
       <c r="E22" s="68">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>150</v>
       </c>
       <c r="F22" s="68">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>150</v>
       </c>
       <c r="G22" s="68">
-        <f t="shared" si="5"/>
-        <v>150</v>
+        <f t="shared" si="4"/>
+        <v>2353.2399999999998</v>
       </c>
       <c r="H22" s="68">
-        <f t="shared" si="5"/>
-        <v>150</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="I22" s="68">
-        <f t="shared" si="5"/>
-        <v>150</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="J22" s="68">
-        <f t="shared" si="5"/>
-        <v>150</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="K22" s="68">
-        <f t="shared" si="5"/>
-        <v>150</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="L22" s="68">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M22" s="68">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -8329,7 +8332,8 @@
         <v>0</v>
       </c>
       <c r="G23" s="69">
-        <v>0</v>
+        <f xml:space="preserve"> 1500 + 673.24</f>
+        <v>2173.2399999999998</v>
       </c>
       <c r="H23" s="69">
         <v>0</v>
@@ -8370,7 +8374,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="70">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H24" s="70">
         <v>0</v>
@@ -8411,20 +8415,12 @@
         <v>150</v>
       </c>
       <c r="G25" s="70">
-        <v>150</v>
-      </c>
-      <c r="H25" s="70">
-        <v>150</v>
-      </c>
-      <c r="I25" s="70">
-        <v>150</v>
-      </c>
-      <c r="J25" s="70">
-        <v>150</v>
-      </c>
-      <c r="K25" s="70">
-        <v>150</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="70"/>
+      <c r="K25" s="70"/>
       <c r="L25" s="70">
         <v>0</v>
       </c>
@@ -8473,26 +8469,28 @@
         <v>3980.1</v>
       </c>
       <c r="C28" s="70">
-        <f>B33+C8</f>
+        <f t="shared" ref="C28:H28" si="5">B33+C8</f>
         <v>3234.45</v>
       </c>
       <c r="D28" s="70">
-        <f>C33+D8</f>
+        <f t="shared" si="5"/>
         <v>3389.42</v>
       </c>
       <c r="E28" s="70">
-        <f>D33+E8</f>
+        <f t="shared" si="5"/>
         <v>3419.26</v>
       </c>
       <c r="F28" s="70">
-        <f>E33+F8</f>
+        <f t="shared" si="5"/>
         <v>3759.4700000000003</v>
       </c>
       <c r="G28" s="70">
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>3238.7200000000003</v>
       </c>
       <c r="H28" s="70">
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>439.52000000000044</v>
       </c>
       <c r="I28" s="70">
         <v>0</v>
@@ -8515,7 +8513,7 @@
         <v>38</v>
       </c>
       <c r="B29" s="70">
-        <f t="shared" ref="B29:E29" si="6">B10</f>
+        <f t="shared" ref="B29:F29" si="6">B10</f>
         <v>36.1</v>
       </c>
       <c r="C29" s="70">
@@ -8531,11 +8529,12 @@
         <v>24.97</v>
       </c>
       <c r="F29" s="70">
-        <f>F13</f>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>35.119999999999997</v>
       </c>
       <c r="G29" s="70">
-        <v>0</v>
+        <f>G10</f>
+        <v>5.56</v>
       </c>
       <c r="H29" s="70">
         <f>H10</f>
@@ -8588,7 +8587,7 @@
       </c>
       <c r="G30" s="70">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>445.96</v>
       </c>
       <c r="H30" s="70">
         <f t="shared" si="8"/>
@@ -8641,23 +8640,23 @@
       </c>
       <c r="G31" s="70">
         <f t="shared" si="9"/>
-        <v>150</v>
+        <v>2353.2399999999998</v>
       </c>
       <c r="H31" s="70">
         <f t="shared" si="9"/>
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="I31" s="70">
         <f t="shared" si="9"/>
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="J31" s="70">
         <f t="shared" si="9"/>
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="K31" s="70">
         <f t="shared" si="9"/>
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="L31" s="70">
         <f t="shared" si="9"/>
@@ -8748,23 +8747,23 @@
       </c>
       <c r="G33" s="73">
         <f t="shared" si="11"/>
-        <v>-150</v>
+        <v>439.52000000000044</v>
       </c>
       <c r="H33" s="73">
         <f t="shared" si="11"/>
-        <v>-150</v>
+        <v>439.52000000000044</v>
       </c>
       <c r="I33" s="73">
         <f t="shared" si="11"/>
-        <v>-150</v>
+        <v>0</v>
       </c>
       <c r="J33" s="70">
         <f>J28-J30-J31</f>
-        <v>-150</v>
+        <v>0</v>
       </c>
       <c r="K33" s="70">
         <f t="shared" ref="K33" si="12">K28+K29-K30-K31</f>
-        <v>-150</v>
+        <v>0</v>
       </c>
       <c r="L33" s="117">
         <f>L28+L29-L30-L31-L32</f>
@@ -8789,7 +8788,7 @@
         <v>-1350</v>
       </c>
       <c r="D35" s="119">
-        <f t="shared" ref="D35:L35" si="13">C35+150</f>
+        <f t="shared" ref="D35:F35" si="13">C35+150</f>
         <v>-1200</v>
       </c>
       <c r="E35" s="119">
@@ -8800,30 +8799,12 @@
         <f t="shared" si="13"/>
         <v>-900</v>
       </c>
-      <c r="G35" s="119">
-        <f t="shared" si="13"/>
-        <v>-750</v>
-      </c>
-      <c r="H35" s="119">
-        <f t="shared" si="13"/>
-        <v>-600</v>
-      </c>
-      <c r="I35" s="119">
-        <f t="shared" si="13"/>
-        <v>-450</v>
-      </c>
-      <c r="J35" s="119">
-        <f t="shared" si="13"/>
-        <v>-300</v>
-      </c>
-      <c r="K35" s="119">
-        <f t="shared" si="13"/>
-        <v>-150</v>
-      </c>
-      <c r="L35" s="119">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
+      <c r="G35" s="121"/>
+      <c r="H35" s="119"/>
+      <c r="I35" s="119"/>
+      <c r="J35" s="119"/>
+      <c r="K35" s="119"/>
+      <c r="L35" s="119"/>
       <c r="M35" s="119"/>
     </row>
     <row r="36" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9850,21 +9831,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="152" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
+      <c r="H1" s="123"/>
+      <c r="I1" s="123"/>
+      <c r="J1" s="123"/>
+      <c r="K1" s="123"/>
+      <c r="L1" s="123"/>
+      <c r="M1" s="123"/>
       <c r="N1" s="79"/>
     </row>
     <row r="2" spans="1:39" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -10022,6 +10003,9 @@
       <c r="AD4" s="84">
         <v>46143</v>
       </c>
+      <c r="AE4" s="84">
+        <v>46174</v>
+      </c>
     </row>
     <row r="5" spans="1:39" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="81">
@@ -10114,6 +10098,9 @@
       <c r="AD5" s="120">
         <v>150</v>
       </c>
+      <c r="AE5" s="120">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:39" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="81">
@@ -10206,6 +10193,9 @@
       <c r="AD6" s="89">
         <v>150</v>
       </c>
+      <c r="AE6" s="89">
+        <v>200</v>
+      </c>
     </row>
     <row r="7" spans="1:39" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="81">
@@ -10298,6 +10288,9 @@
       <c r="AD7" s="89">
         <v>150</v>
       </c>
+      <c r="AE7" s="89">
+        <v>200</v>
+      </c>
     </row>
     <row r="8" spans="1:39" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="81">
@@ -10390,47 +10383,50 @@
       <c r="AD8" s="89">
         <v>150</v>
       </c>
+      <c r="AE8" s="89">
+        <v>200</v>
+      </c>
     </row>
     <row r="9" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="152"/>
-      <c r="B9" s="153"/>
-      <c r="C9" s="153"/>
-      <c r="D9" s="153"/>
-      <c r="E9" s="153"/>
-      <c r="F9" s="153"/>
-      <c r="G9" s="153"/>
-      <c r="H9" s="153"/>
-      <c r="I9" s="153"/>
-      <c r="J9" s="153"/>
-      <c r="K9" s="153"/>
-      <c r="L9" s="153"/>
-      <c r="M9" s="154"/>
-      <c r="N9" s="152"/>
-      <c r="O9" s="153"/>
-      <c r="P9" s="153"/>
-      <c r="Q9" s="153"/>
-      <c r="R9" s="153"/>
-      <c r="S9" s="153"/>
-      <c r="T9" s="153"/>
-      <c r="U9" s="153"/>
-      <c r="V9" s="153"/>
-      <c r="W9" s="153"/>
-      <c r="X9" s="153"/>
-      <c r="Y9" s="153"/>
-      <c r="Z9" s="154"/>
-      <c r="AA9" s="152"/>
-      <c r="AB9" s="153"/>
-      <c r="AC9" s="153"/>
-      <c r="AD9" s="153"/>
-      <c r="AE9" s="153"/>
-      <c r="AF9" s="153"/>
-      <c r="AG9" s="153"/>
-      <c r="AH9" s="153"/>
-      <c r="AI9" s="153"/>
-      <c r="AJ9" s="153"/>
-      <c r="AK9" s="153"/>
-      <c r="AL9" s="153"/>
-      <c r="AM9" s="154"/>
+      <c r="A9" s="153"/>
+      <c r="B9" s="154"/>
+      <c r="C9" s="154"/>
+      <c r="D9" s="154"/>
+      <c r="E9" s="154"/>
+      <c r="F9" s="154"/>
+      <c r="G9" s="154"/>
+      <c r="H9" s="154"/>
+      <c r="I9" s="154"/>
+      <c r="J9" s="154"/>
+      <c r="K9" s="154"/>
+      <c r="L9" s="154"/>
+      <c r="M9" s="155"/>
+      <c r="N9" s="153"/>
+      <c r="O9" s="154"/>
+      <c r="P9" s="154"/>
+      <c r="Q9" s="154"/>
+      <c r="R9" s="154"/>
+      <c r="S9" s="154"/>
+      <c r="T9" s="154"/>
+      <c r="U9" s="154"/>
+      <c r="V9" s="154"/>
+      <c r="W9" s="154"/>
+      <c r="X9" s="154"/>
+      <c r="Y9" s="154"/>
+      <c r="Z9" s="155"/>
+      <c r="AA9" s="153"/>
+      <c r="AB9" s="154"/>
+      <c r="AC9" s="154"/>
+      <c r="AD9" s="154"/>
+      <c r="AE9" s="154"/>
+      <c r="AF9" s="154"/>
+      <c r="AG9" s="154"/>
+      <c r="AH9" s="154"/>
+      <c r="AI9" s="154"/>
+      <c r="AJ9" s="154"/>
+      <c r="AK9" s="154"/>
+      <c r="AL9" s="154"/>
+      <c r="AM9" s="155"/>
     </row>
     <row r="10" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="78" t="s">
@@ -10545,10 +10541,14 @@
         <v>600</v>
       </c>
       <c r="AC10" s="91">
-        <f t="shared" ref="AC10:AD10" si="2">SUM(AC5:AC8)</f>
+        <f t="shared" ref="AC10:AE10" si="2">SUM(AC5:AC8)</f>
         <v>600</v>
       </c>
       <c r="AD10" s="91">
+        <f t="shared" si="2"/>
+        <v>600</v>
+      </c>
+      <c r="AE10" s="91">
         <f t="shared" si="2"/>
         <v>600</v>
       </c>
@@ -14737,13 +14737,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="155" t="s">
+      <c r="B1" s="156" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="134"/>
       <c r="G1" s="93"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
@@ -14769,11 +14769,11 @@
     </row>
     <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="97"/>
-      <c r="B3" s="156"/>
-      <c r="C3" s="157"/>
-      <c r="D3" s="157"/>
-      <c r="E3" s="157"/>
-      <c r="F3" s="158"/>
+      <c r="B3" s="157"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="158"/>
+      <c r="F3" s="159"/>
       <c r="G3" s="98"/>
     </row>
     <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">

--- a/planilhas/Contabilidade Condominio.xlsx
+++ b/planilhas/Contabilidade Condominio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Condominio\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{880521C3-95E8-4E5B-8CCB-B874B3E7CF60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C898D4EC-DDF8-41B8-8514-16B96BFB837A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -381,7 +381,7 @@
     <numFmt numFmtId="165" formatCode="&quot;R$&quot;#,##0.00;[Red]&quot;R$&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="33" x14ac:knownFonts="1">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -568,6 +568,13 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF006411"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1253,7 +1260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1670,6 +1677,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="33" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7728,7 +7738,10 @@
         <f>F33</f>
         <v>2633.1600000000003</v>
       </c>
-      <c r="G6" s="57"/>
+      <c r="G6" s="160">
+        <f>G33</f>
+        <v>439.52000000000044</v>
+      </c>
       <c r="H6" s="57"/>
       <c r="I6" s="57"/>
       <c r="J6" s="57"/>

--- a/planilhas/Contabilidade Condominio.xlsx
+++ b/planilhas/Contabilidade Condominio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Condominio\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C898D4EC-DDF8-41B8-8514-16B96BFB837A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED525A7-35D2-4EBD-B098-23A6C00310EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -138,8 +138,26 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={629604FD-A46D-4353-9480-10C9E82C566F}</author>
+  </authors>
+  <commentList>
+    <comment ref="G35" authorId="0" shapeId="0" xr:uid="{629604FD-A46D-4353-9480-10C9E82C566F}">
+      <text>
+        <t>[Comentário encadeado]
+Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
+Comentário:
+    Definido em convenção do condominio que o valor do material perdido seria repassado como custos a ser coberto pelo AP01, o valor total dos materiais ficou em R$4.521,24, revertendo o crédito positivo de R$ 900,00 para R$ 3621,24. Taxa de Condominio não recolhida R$ 200,00</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="81">
   <si>
     <t>Facilite ainda mais o seu trabalho</t>
   </si>
@@ -368,6 +386,21 @@
   <si>
     <t>Despesas Fixas</t>
   </si>
+  <si>
+    <t>Creditos / Debitos AP</t>
+  </si>
+  <si>
+    <t>AP01</t>
+  </si>
+  <si>
+    <t>AP02</t>
+  </si>
+  <si>
+    <t>AP03</t>
+  </si>
+  <si>
+    <t>AP04</t>
+  </si>
 </sst>
 </file>
 
@@ -381,7 +414,7 @@
     <numFmt numFmtId="165" formatCode="&quot;R$&quot;#,##0.00;[Red]&quot;R$&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="35" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -577,6 +610,11 @@
       <color rgb="FF006411"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="15">
@@ -1260,7 +1298,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="161">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1601,6 +1639,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="8" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="33" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1677,14 +1730,28 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="33" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1695,6 +1762,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="David Melo" id="{94384591-832C-4E54-BCC6-025FEE2D32A2}" userId="bba1af4b17a61bc8" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1893,6 +1966,14 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="G35" dT="2026-06-18T12:37:56.77" personId="{94384591-832C-4E54-BCC6-025FEE2D32A2}" id="{629604FD-A46D-4353-9480-10C9E82C566F}">
+    <text>Definido em convenção do condominio que o valor do material perdido seria repassado como custos a ser coberto pelo AP01, o valor total dos materiais ficou em R$4.521,24, revertendo o crédito positivo de R$ 900,00 para R$ 3621,24. Taxa de Condominio não recolhida R$ 200,00</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
@@ -1909,68 +1990,68 @@
   <sheetData>
     <row r="1" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
-      <c r="B1" s="132" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="134"/>
+      <c r="B1" s="137" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="138"/>
+      <c r="I1" s="138"/>
+      <c r="J1" s="138"/>
+      <c r="K1" s="138"/>
+      <c r="L1" s="139"/>
       <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" s="135" t="s">
+      <c r="B2" s="140" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="133"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="133"/>
-      <c r="F2" s="133"/>
-      <c r="G2" s="133"/>
-      <c r="H2" s="133"/>
-      <c r="I2" s="133"/>
-      <c r="J2" s="133"/>
-      <c r="K2" s="133"/>
-      <c r="L2" s="134"/>
+      <c r="C2" s="138"/>
+      <c r="D2" s="138"/>
+      <c r="E2" s="138"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="138"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="139"/>
       <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
-      <c r="B3" s="136" t="s">
+      <c r="B3" s="141" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="137"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="137"/>
-      <c r="F3" s="137"/>
-      <c r="G3" s="137"/>
-      <c r="H3" s="137"/>
-      <c r="I3" s="137"/>
-      <c r="J3" s="137"/>
-      <c r="K3" s="137"/>
-      <c r="L3" s="138"/>
+      <c r="C3" s="142"/>
+      <c r="D3" s="142"/>
+      <c r="E3" s="142"/>
+      <c r="F3" s="142"/>
+      <c r="G3" s="142"/>
+      <c r="H3" s="142"/>
+      <c r="I3" s="142"/>
+      <c r="J3" s="142"/>
+      <c r="K3" s="142"/>
+      <c r="L3" s="143"/>
       <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3"/>
-      <c r="B4" s="139"/>
-      <c r="C4" s="140"/>
-      <c r="D4" s="140"/>
-      <c r="E4" s="140"/>
-      <c r="F4" s="140"/>
-      <c r="G4" s="140"/>
-      <c r="H4" s="140"/>
-      <c r="I4" s="140"/>
-      <c r="J4" s="140"/>
-      <c r="K4" s="140"/>
-      <c r="L4" s="141"/>
+      <c r="B4" s="144"/>
+      <c r="C4" s="145"/>
+      <c r="D4" s="145"/>
+      <c r="E4" s="145"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="145"/>
+      <c r="J4" s="145"/>
+      <c r="K4" s="145"/>
+      <c r="L4" s="146"/>
       <c r="M4" s="3"/>
     </row>
     <row r="5" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.2">
@@ -1978,222 +2059,222 @@
       <c r="B5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="142" t="s">
+      <c r="C5" s="147" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="143"/>
-      <c r="E5" s="143"/>
-      <c r="F5" s="143"/>
-      <c r="G5" s="143"/>
-      <c r="H5" s="143"/>
-      <c r="I5" s="143"/>
-      <c r="J5" s="143"/>
-      <c r="K5" s="143"/>
-      <c r="L5" s="144"/>
+      <c r="D5" s="148"/>
+      <c r="E5" s="148"/>
+      <c r="F5" s="148"/>
+      <c r="G5" s="148"/>
+      <c r="H5" s="148"/>
+      <c r="I5" s="148"/>
+      <c r="J5" s="148"/>
+      <c r="K5" s="148"/>
+      <c r="L5" s="149"/>
       <c r="M5" s="4"/>
     </row>
     <row r="6" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6"/>
-      <c r="B6" s="145" t="s">
+      <c r="B6" s="150" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="128" t="s">
+      <c r="C6" s="133" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="123"/>
-      <c r="E6" s="123"/>
-      <c r="F6" s="123"/>
-      <c r="G6" s="123"/>
-      <c r="H6" s="123"/>
-      <c r="I6" s="123"/>
-      <c r="J6" s="123"/>
-      <c r="K6" s="123"/>
-      <c r="L6" s="129"/>
+      <c r="D6" s="128"/>
+      <c r="E6" s="128"/>
+      <c r="F6" s="128"/>
+      <c r="G6" s="128"/>
+      <c r="H6" s="128"/>
+      <c r="I6" s="128"/>
+      <c r="J6" s="128"/>
+      <c r="K6" s="128"/>
+      <c r="L6" s="134"/>
       <c r="M6" s="6"/>
     </row>
     <row r="7" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6"/>
-      <c r="B7" s="146"/>
-      <c r="C7" s="123"/>
-      <c r="D7" s="123"/>
-      <c r="E7" s="123"/>
-      <c r="F7" s="123"/>
-      <c r="G7" s="123"/>
-      <c r="H7" s="123"/>
-      <c r="I7" s="123"/>
-      <c r="J7" s="123"/>
-      <c r="K7" s="123"/>
-      <c r="L7" s="129"/>
+      <c r="B7" s="151"/>
+      <c r="C7" s="128"/>
+      <c r="D7" s="128"/>
+      <c r="E7" s="128"/>
+      <c r="F7" s="128"/>
+      <c r="G7" s="128"/>
+      <c r="H7" s="128"/>
+      <c r="I7" s="128"/>
+      <c r="J7" s="128"/>
+      <c r="K7" s="128"/>
+      <c r="L7" s="134"/>
       <c r="M7" s="6"/>
     </row>
     <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6"/>
-      <c r="B8" s="145" t="s">
+      <c r="B8" s="150" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="128" t="s">
+      <c r="C8" s="133" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="123"/>
-      <c r="E8" s="123"/>
-      <c r="F8" s="123"/>
-      <c r="G8" s="123"/>
-      <c r="H8" s="123"/>
-      <c r="I8" s="123"/>
-      <c r="J8" s="123"/>
-      <c r="K8" s="123"/>
-      <c r="L8" s="129"/>
+      <c r="D8" s="128"/>
+      <c r="E8" s="128"/>
+      <c r="F8" s="128"/>
+      <c r="G8" s="128"/>
+      <c r="H8" s="128"/>
+      <c r="I8" s="128"/>
+      <c r="J8" s="128"/>
+      <c r="K8" s="128"/>
+      <c r="L8" s="134"/>
       <c r="M8" s="6"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6"/>
-      <c r="B9" s="146"/>
-      <c r="C9" s="123"/>
-      <c r="D9" s="123"/>
-      <c r="E9" s="123"/>
-      <c r="F9" s="123"/>
-      <c r="G9" s="123"/>
-      <c r="H9" s="123"/>
-      <c r="I9" s="123"/>
-      <c r="J9" s="123"/>
-      <c r="K9" s="123"/>
-      <c r="L9" s="129"/>
+      <c r="B9" s="151"/>
+      <c r="C9" s="128"/>
+      <c r="D9" s="128"/>
+      <c r="E9" s="128"/>
+      <c r="F9" s="128"/>
+      <c r="G9" s="128"/>
+      <c r="H9" s="128"/>
+      <c r="I9" s="128"/>
+      <c r="J9" s="128"/>
+      <c r="K9" s="128"/>
+      <c r="L9" s="134"/>
       <c r="M9" s="6"/>
     </row>
     <row r="10" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6"/>
-      <c r="B10" s="145" t="s">
+      <c r="B10" s="150" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="128" t="s">
+      <c r="C10" s="133" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="123"/>
-      <c r="E10" s="123"/>
-      <c r="F10" s="123"/>
-      <c r="G10" s="123"/>
-      <c r="H10" s="123"/>
-      <c r="I10" s="123"/>
-      <c r="J10" s="123"/>
-      <c r="K10" s="123"/>
-      <c r="L10" s="129"/>
+      <c r="D10" s="128"/>
+      <c r="E10" s="128"/>
+      <c r="F10" s="128"/>
+      <c r="G10" s="128"/>
+      <c r="H10" s="128"/>
+      <c r="I10" s="128"/>
+      <c r="J10" s="128"/>
+      <c r="K10" s="128"/>
+      <c r="L10" s="134"/>
       <c r="M10" s="6"/>
     </row>
     <row r="11" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6"/>
-      <c r="B11" s="146"/>
-      <c r="C11" s="123"/>
-      <c r="D11" s="123"/>
-      <c r="E11" s="123"/>
-      <c r="F11" s="123"/>
-      <c r="G11" s="123"/>
-      <c r="H11" s="123"/>
-      <c r="I11" s="123"/>
-      <c r="J11" s="123"/>
-      <c r="K11" s="123"/>
-      <c r="L11" s="129"/>
+      <c r="B11" s="151"/>
+      <c r="C11" s="128"/>
+      <c r="D11" s="128"/>
+      <c r="E11" s="128"/>
+      <c r="F11" s="128"/>
+      <c r="G11" s="128"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="128"/>
+      <c r="J11" s="128"/>
+      <c r="K11" s="128"/>
+      <c r="L11" s="134"/>
       <c r="M11" s="6"/>
     </row>
     <row r="12" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6"/>
-      <c r="B12" s="145" t="s">
+      <c r="B12" s="150" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="128" t="s">
+      <c r="C12" s="133" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="123"/>
-      <c r="E12" s="123"/>
-      <c r="F12" s="123"/>
-      <c r="G12" s="123"/>
-      <c r="H12" s="123"/>
-      <c r="I12" s="123"/>
-      <c r="J12" s="123"/>
-      <c r="K12" s="123"/>
-      <c r="L12" s="129"/>
+      <c r="D12" s="128"/>
+      <c r="E12" s="128"/>
+      <c r="F12" s="128"/>
+      <c r="G12" s="128"/>
+      <c r="H12" s="128"/>
+      <c r="I12" s="128"/>
+      <c r="J12" s="128"/>
+      <c r="K12" s="128"/>
+      <c r="L12" s="134"/>
       <c r="M12" s="6"/>
     </row>
     <row r="13" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
-      <c r="B13" s="146"/>
-      <c r="C13" s="123"/>
-      <c r="D13" s="123"/>
-      <c r="E13" s="123"/>
-      <c r="F13" s="123"/>
-      <c r="G13" s="123"/>
-      <c r="H13" s="123"/>
-      <c r="I13" s="123"/>
-      <c r="J13" s="123"/>
-      <c r="K13" s="123"/>
-      <c r="L13" s="129"/>
+      <c r="B13" s="151"/>
+      <c r="C13" s="128"/>
+      <c r="D13" s="128"/>
+      <c r="E13" s="128"/>
+      <c r="F13" s="128"/>
+      <c r="G13" s="128"/>
+      <c r="H13" s="128"/>
+      <c r="I13" s="128"/>
+      <c r="J13" s="128"/>
+      <c r="K13" s="128"/>
+      <c r="L13" s="134"/>
       <c r="M13" s="6"/>
     </row>
     <row r="14" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6"/>
-      <c r="B14" s="145" t="s">
+      <c r="B14" s="150" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="128" t="s">
+      <c r="C14" s="133" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="123"/>
-      <c r="E14" s="123"/>
-      <c r="F14" s="123"/>
-      <c r="G14" s="123"/>
-      <c r="H14" s="123"/>
-      <c r="I14" s="123"/>
-      <c r="J14" s="123"/>
-      <c r="K14" s="123"/>
-      <c r="L14" s="129"/>
+      <c r="D14" s="128"/>
+      <c r="E14" s="128"/>
+      <c r="F14" s="128"/>
+      <c r="G14" s="128"/>
+      <c r="H14" s="128"/>
+      <c r="I14" s="128"/>
+      <c r="J14" s="128"/>
+      <c r="K14" s="128"/>
+      <c r="L14" s="134"/>
       <c r="M14" s="6"/>
     </row>
     <row r="15" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6"/>
-      <c r="B15" s="146"/>
-      <c r="C15" s="123"/>
-      <c r="D15" s="123"/>
-      <c r="E15" s="123"/>
-      <c r="F15" s="123"/>
-      <c r="G15" s="123"/>
-      <c r="H15" s="123"/>
-      <c r="I15" s="123"/>
-      <c r="J15" s="123"/>
-      <c r="K15" s="123"/>
-      <c r="L15" s="129"/>
+      <c r="B15" s="151"/>
+      <c r="C15" s="128"/>
+      <c r="D15" s="128"/>
+      <c r="E15" s="128"/>
+      <c r="F15" s="128"/>
+      <c r="G15" s="128"/>
+      <c r="H15" s="128"/>
+      <c r="I15" s="128"/>
+      <c r="J15" s="128"/>
+      <c r="K15" s="128"/>
+      <c r="L15" s="134"/>
       <c r="M15" s="6"/>
     </row>
     <row r="16" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6"/>
-      <c r="B16" s="145" t="s">
+      <c r="B16" s="150" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="128" t="s">
+      <c r="C16" s="133" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="123"/>
-      <c r="E16" s="123"/>
-      <c r="F16" s="123"/>
-      <c r="G16" s="123"/>
-      <c r="H16" s="123"/>
-      <c r="I16" s="123"/>
-      <c r="J16" s="123"/>
-      <c r="K16" s="123"/>
-      <c r="L16" s="129"/>
+      <c r="D16" s="128"/>
+      <c r="E16" s="128"/>
+      <c r="F16" s="128"/>
+      <c r="G16" s="128"/>
+      <c r="H16" s="128"/>
+      <c r="I16" s="128"/>
+      <c r="J16" s="128"/>
+      <c r="K16" s="128"/>
+      <c r="L16" s="134"/>
       <c r="M16" s="6"/>
     </row>
     <row r="17" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6"/>
-      <c r="B17" s="147"/>
-      <c r="C17" s="130"/>
-      <c r="D17" s="130"/>
-      <c r="E17" s="130"/>
-      <c r="F17" s="130"/>
-      <c r="G17" s="130"/>
-      <c r="H17" s="130"/>
-      <c r="I17" s="130"/>
-      <c r="J17" s="130"/>
-      <c r="K17" s="130"/>
-      <c r="L17" s="131"/>
+      <c r="B17" s="152"/>
+      <c r="C17" s="135"/>
+      <c r="D17" s="135"/>
+      <c r="E17" s="135"/>
+      <c r="F17" s="135"/>
+      <c r="G17" s="135"/>
+      <c r="H17" s="135"/>
+      <c r="I17" s="135"/>
+      <c r="J17" s="135"/>
+      <c r="K17" s="135"/>
+      <c r="L17" s="136"/>
       <c r="M17" s="6"/>
     </row>
     <row r="18" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3251,18 +3332,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="148"/>
-      <c r="B1" s="149" t="s">
+      <c r="A1" s="153"/>
+      <c r="B1" s="154" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="123"/>
-      <c r="D1" s="150" t="s">
+      <c r="C1" s="128"/>
+      <c r="D1" s="155" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="123"/>
-      <c r="F1" s="123"/>
-      <c r="G1" s="123"/>
-      <c r="H1" s="123"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
       <c r="I1" s="12"/>
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
@@ -3270,16 +3351,16 @@
       <c r="M1" s="13"/>
     </row>
     <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="123"/>
-      <c r="B2" s="149" t="s">
+      <c r="A2" s="128"/>
+      <c r="B2" s="154" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="123"/>
-      <c r="D2" s="126" t="s">
+      <c r="C2" s="128"/>
+      <c r="D2" s="131" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
       <c r="G2" s="14" t="s">
         <v>21</v>
       </c>
@@ -3293,14 +3374,14 @@
       <c r="M2" s="16"/>
     </row>
     <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="123"/>
-      <c r="B3" s="149"/>
-      <c r="C3" s="123"/>
-      <c r="D3" s="151"/>
-      <c r="E3" s="123"/>
+      <c r="A3" s="128"/>
+      <c r="B3" s="154"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="156"/>
+      <c r="E3" s="128"/>
       <c r="F3" s="14"/>
-      <c r="G3" s="151"/>
-      <c r="H3" s="123"/>
+      <c r="G3" s="156"/>
+      <c r="H3" s="128"/>
       <c r="I3" s="15"/>
       <c r="J3" s="16"/>
       <c r="K3" s="16"/>
@@ -3308,7 +3389,7 @@
       <c r="M3" s="16"/>
     </row>
     <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="123"/>
+      <c r="A4" s="128"/>
       <c r="B4" s="17"/>
       <c r="C4" s="18"/>
       <c r="D4" s="18"/>
@@ -5315,18 +5396,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="122"/>
-      <c r="B1" s="124" t="s">
+      <c r="A1" s="127"/>
+      <c r="B1" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="123"/>
-      <c r="D1" s="125" t="s">
+      <c r="C1" s="128"/>
+      <c r="D1" s="130" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="123"/>
-      <c r="F1" s="123"/>
-      <c r="G1" s="123"/>
-      <c r="H1" s="123"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
       <c r="I1" s="45"/>
       <c r="J1" s="46"/>
       <c r="K1" s="46"/>
@@ -5334,16 +5415,16 @@
       <c r="M1" s="46"/>
     </row>
     <row r="2" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="123"/>
-      <c r="B2" s="124" t="s">
+      <c r="A2" s="128"/>
+      <c r="B2" s="129" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="123"/>
-      <c r="D2" s="126" t="s">
+      <c r="C2" s="128"/>
+      <c r="D2" s="131" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
       <c r="G2" s="47" t="s">
         <v>21</v>
       </c>
@@ -5357,14 +5438,14 @@
       <c r="M2" s="49"/>
     </row>
     <row r="3" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="123"/>
-      <c r="B3" s="124"/>
-      <c r="C3" s="123"/>
-      <c r="D3" s="127"/>
-      <c r="E3" s="123"/>
+      <c r="A3" s="128"/>
+      <c r="B3" s="129"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="132"/>
+      <c r="E3" s="128"/>
       <c r="F3" s="47"/>
-      <c r="G3" s="127"/>
-      <c r="H3" s="123"/>
+      <c r="G3" s="132"/>
+      <c r="H3" s="128"/>
       <c r="I3" s="48"/>
       <c r="J3" s="49"/>
       <c r="K3" s="49"/>
@@ -5372,7 +5453,7 @@
       <c r="M3" s="49"/>
     </row>
     <row r="4" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="123"/>
+      <c r="A4" s="128"/>
       <c r="B4" s="51"/>
       <c r="C4" s="52"/>
       <c r="D4" s="52"/>
@@ -7571,11 +7652,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBBAE314-5C93-4389-B302-08B220D7C7FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBBAE314-5C93-4389-B302-08B220D7C7FD}">
   <sheetPr>
     <tabColor rgb="FF7EBC0A"/>
   </sheetPr>
-  <dimension ref="A1:P1002"/>
+  <dimension ref="A1:U1005"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
@@ -7586,39 +7667,42 @@
     <col min="7" max="7" width="12.7109375" customWidth="1"/>
     <col min="8" max="9" width="12.42578125" customWidth="1"/>
     <col min="10" max="13" width="14.7109375" customWidth="1"/>
-    <col min="14" max="26" width="8.5703125" customWidth="1"/>
+    <col min="14" max="15" width="8.5703125" customWidth="1"/>
+    <col min="16" max="16" width="17.7109375" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" customWidth="1"/>
+    <col min="18" max="26" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="122"/>
-      <c r="B1" s="124" t="s">
+    <row r="1" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="127"/>
+      <c r="B1" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="123"/>
-      <c r="D1" s="125" t="s">
+      <c r="C1" s="128"/>
+      <c r="D1" s="130" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="123"/>
-      <c r="F1" s="123"/>
-      <c r="G1" s="123"/>
-      <c r="H1" s="123"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
       <c r="I1" s="45"/>
       <c r="J1" s="46"/>
       <c r="K1" s="46"/>
       <c r="L1" s="46"/>
       <c r="M1" s="46"/>
     </row>
-    <row r="2" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="123"/>
-      <c r="B2" s="124" t="s">
+    <row r="2" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="128"/>
+      <c r="B2" s="129" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="123"/>
-      <c r="D2" s="126" t="s">
+      <c r="C2" s="128"/>
+      <c r="D2" s="131" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
       <c r="G2" s="47" t="s">
         <v>21</v>
       </c>
@@ -7631,23 +7715,23 @@
       <c r="L2" s="49"/>
       <c r="M2" s="49"/>
     </row>
-    <row r="3" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="123"/>
-      <c r="B3" s="124"/>
-      <c r="C3" s="123"/>
-      <c r="D3" s="127"/>
-      <c r="E3" s="123"/>
+    <row r="3" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="128"/>
+      <c r="B3" s="129"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="132"/>
+      <c r="E3" s="128"/>
       <c r="F3" s="47"/>
-      <c r="G3" s="127"/>
-      <c r="H3" s="123"/>
+      <c r="G3" s="132"/>
+      <c r="H3" s="128"/>
       <c r="I3" s="48"/>
       <c r="J3" s="49"/>
       <c r="K3" s="49"/>
       <c r="L3" s="49"/>
       <c r="M3" s="49"/>
     </row>
-    <row r="4" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="123"/>
+    <row r="4" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="128"/>
       <c r="B4" s="51"/>
       <c r="C4" s="52"/>
       <c r="D4" s="52"/>
@@ -7661,7 +7745,7 @@
       <c r="L4" s="53"/>
       <c r="M4" s="53"/>
     </row>
-    <row r="5" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="54" t="s">
         <v>22</v>
       </c>
@@ -7713,34 +7797,40 @@
         <f>CONCATENATE("Dezembro/",$H$2)</f>
         <v>Dezembro/2026</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P5" s="74"/>
+      <c r="Q5" s="119"/>
+      <c r="R5" s="119"/>
+      <c r="S5" s="119"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="119"/>
+    </row>
+    <row r="6" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="56" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="57">
-        <f>'Fluxo de caixa 2025'!M33+B8-B17-B22</f>
+        <f>'Fluxo de caixa 2025'!M33+B8-B16-B21</f>
         <v>2634.45</v>
       </c>
       <c r="C6" s="57">
-        <f>C33</f>
+        <f>C32</f>
         <v>2733.21</v>
       </c>
       <c r="D6" s="57">
-        <f>D33</f>
+        <f>D32</f>
         <v>2794.29</v>
       </c>
       <c r="E6" s="57">
-        <f>E33</f>
+        <f>E32</f>
         <v>3124.3500000000004</v>
       </c>
       <c r="F6" s="57">
-        <f>F33</f>
+        <f>F32</f>
         <v>2633.1600000000003</v>
       </c>
-      <c r="G6" s="160">
-        <f>G33</f>
-        <v>439.52000000000044</v>
+      <c r="G6" s="122">
+        <f>G32</f>
+        <v>442.07000000000062</v>
       </c>
       <c r="H6" s="57"/>
       <c r="I6" s="57"/>
@@ -7749,7 +7839,7 @@
       <c r="L6" s="57"/>
       <c r="M6" s="57"/>
     </row>
-    <row r="7" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="51"/>
       <c r="B7" s="58"/>
       <c r="C7" s="58"/>
@@ -7764,7 +7854,7 @@
       <c r="L7" s="58"/>
       <c r="M7" s="59"/>
     </row>
-    <row r="8" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="60" t="s">
         <v>24</v>
       </c>
@@ -7790,7 +7880,7 @@
       </c>
       <c r="G8" s="61">
         <f t="shared" si="0"/>
-        <v>605.55999999999995</v>
+        <v>608.11</v>
       </c>
       <c r="H8" s="61">
         <f t="shared" si="0"/>
@@ -7817,7 +7907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="62" t="s">
         <v>25</v>
       </c>
@@ -7870,7 +7960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="62" t="s">
         <v>26</v>
       </c>
@@ -7890,7 +7980,7 @@
         <v>35.119999999999997</v>
       </c>
       <c r="G10" s="66">
-        <v>5.56</v>
+        <v>8.11</v>
       </c>
       <c r="H10" s="65"/>
       <c r="I10" s="65"/>
@@ -7899,7 +7989,7 @@
       <c r="L10" s="65"/>
       <c r="M10" s="65"/>
     </row>
-    <row r="11" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="51"/>
       <c r="B11" s="58"/>
       <c r="C11" s="58"/>
@@ -7914,78 +8004,104 @@
       <c r="L11" s="58"/>
       <c r="M11" s="59"/>
     </row>
-    <row r="12" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="51"/>
-      <c r="B12" s="58"/>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="58"/>
-      <c r="J12" s="58"/>
-      <c r="K12" s="58"/>
-      <c r="L12" s="58"/>
-      <c r="M12" s="59"/>
-    </row>
-    <row r="13" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="67" t="s">
+    <row r="12" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="68">
-        <f t="shared" ref="B13:M13" si="1">SUM(B14:B16)</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="68">
+      <c r="B12" s="68">
+        <f t="shared" ref="B12:M12" si="1">SUM(B13:B15)</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="68">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D13" s="68">
+      <c r="D12" s="68">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E13" s="68">
+      <c r="E12" s="68">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F13" s="68">
+      <c r="F12" s="68">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G13" s="68">
+      <c r="G12" s="68">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H13" s="68">
+      <c r="H12" s="68">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I13" s="68">
+      <c r="I12" s="68">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J13" s="68">
+      <c r="J12" s="68">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K13" s="68">
+      <c r="K12" s="68">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L13" s="68">
+      <c r="L12" s="68">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M13" s="68">
+      <c r="M12" s="68">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P13" s="118"/>
-    </row>
-    <row r="14" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P12" s="118"/>
+    </row>
+    <row r="13" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="62" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="69">
+        <v>0</v>
+      </c>
+      <c r="C13" s="69">
+        <v>0</v>
+      </c>
+      <c r="D13" s="69">
+        <v>0</v>
+      </c>
+      <c r="E13" s="69">
+        <v>0</v>
+      </c>
+      <c r="F13" s="69">
+        <v>0</v>
+      </c>
+      <c r="G13" s="69">
+        <v>0</v>
+      </c>
+      <c r="H13" s="69">
+        <v>0</v>
+      </c>
+      <c r="I13" s="69">
+        <v>0</v>
+      </c>
+      <c r="J13" s="69">
+        <v>0</v>
+      </c>
+      <c r="K13" s="69">
+        <v>0</v>
+      </c>
+      <c r="L13" s="69">
+        <v>0</v>
+      </c>
+      <c r="M13" s="69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="62" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="B14" s="69">
         <v>0</v>
@@ -8024,136 +8140,136 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="62" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" s="69">
-        <v>0</v>
-      </c>
-      <c r="C15" s="69">
-        <v>0</v>
-      </c>
-      <c r="D15" s="69">
-        <v>0</v>
-      </c>
-      <c r="E15" s="69">
-        <v>0</v>
-      </c>
-      <c r="F15" s="69">
-        <v>0</v>
-      </c>
-      <c r="G15" s="69">
-        <v>0</v>
-      </c>
-      <c r="H15" s="69">
-        <v>0</v>
-      </c>
-      <c r="I15" s="69">
-        <v>0</v>
-      </c>
-      <c r="J15" s="69">
-        <v>0</v>
-      </c>
-      <c r="K15" s="69">
-        <v>0</v>
-      </c>
-      <c r="L15" s="69">
-        <v>0</v>
-      </c>
-      <c r="M15" s="69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="51"/>
-      <c r="B16" s="58"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="58"/>
-      <c r="I16" s="58"/>
-      <c r="J16" s="58"/>
-      <c r="K16" s="58"/>
-      <c r="L16" s="58"/>
-      <c r="M16" s="59"/>
-    </row>
-    <row r="17" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="67" t="s">
+    <row r="15" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="51"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="58"/>
+      <c r="I15" s="58"/>
+      <c r="J15" s="58"/>
+      <c r="K15" s="58"/>
+      <c r="L15" s="58"/>
+      <c r="M15" s="59"/>
+    </row>
+    <row r="16" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="68">
-        <f t="shared" ref="B17:C17" si="2">B18+B19+B20</f>
+      <c r="B16" s="68">
+        <f t="shared" ref="B16:C16" si="2">B17+B18+B19</f>
         <v>345.65</v>
       </c>
-      <c r="C17" s="68">
+      <c r="C16" s="68">
         <f t="shared" si="2"/>
         <v>351.24</v>
       </c>
-      <c r="D17" s="68">
-        <f t="shared" ref="D17:M17" si="3">SUM(D18:D21)</f>
+      <c r="D16" s="68">
+        <f t="shared" ref="D16:M16" si="3">SUM(D17:D20)</f>
         <v>145.13</v>
       </c>
-      <c r="E17" s="68">
+      <c r="E16" s="68">
         <f t="shared" si="3"/>
         <v>144.91</v>
       </c>
-      <c r="F17" s="68">
+      <c r="F16" s="68">
         <f t="shared" si="3"/>
         <v>976.31</v>
       </c>
-      <c r="G17" s="68">
+      <c r="G16" s="68">
         <f t="shared" si="3"/>
         <v>445.96</v>
       </c>
-      <c r="H17" s="68">
+      <c r="H16" s="68">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I17" s="68">
+      <c r="I16" s="68">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="68">
+      <c r="J16" s="68">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K17" s="68">
+      <c r="K16" s="68">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L17" s="68">
+      <c r="L16" s="68">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M17" s="68">
+      <c r="M16" s="68">
         <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="62" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="70">
+        <v>80.22</v>
+      </c>
+      <c r="C17" s="70">
+        <v>81.25</v>
+      </c>
+      <c r="D17" s="70">
+        <v>81.239999999999995</v>
+      </c>
+      <c r="E17" s="70">
+        <v>81.239999999999995</v>
+      </c>
+      <c r="F17" s="70">
+        <v>81.239999999999995</v>
+      </c>
+      <c r="G17" s="70">
+        <v>81.239999999999995</v>
+      </c>
+      <c r="H17" s="70">
+        <v>0</v>
+      </c>
+      <c r="I17" s="70">
+        <v>0</v>
+      </c>
+      <c r="J17" s="70">
+        <v>0</v>
+      </c>
+      <c r="K17" s="70">
+        <v>0</v>
+      </c>
+      <c r="L17" s="70">
+        <v>0</v>
+      </c>
+      <c r="M17" s="70">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="62" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B18" s="70">
-        <v>80.22</v>
+        <v>65.430000000000007</v>
       </c>
       <c r="C18" s="70">
-        <v>81.25</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="D18" s="70">
-        <v>81.239999999999995</v>
+        <v>63.89</v>
       </c>
       <c r="E18" s="70">
-        <v>81.239999999999995</v>
+        <v>63.67</v>
       </c>
       <c r="F18" s="70">
-        <v>81.239999999999995</v>
+        <v>64.680000000000007</v>
       </c>
       <c r="G18" s="70">
-        <v>81.239999999999995</v>
+        <v>64.72</v>
       </c>
       <c r="H18" s="70">
         <v>0</v>
@@ -8176,231 +8292,223 @@
     </row>
     <row r="19" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="62" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" s="70">
-        <v>65.430000000000007</v>
-      </c>
-      <c r="C19" s="70">
-        <v>69.989999999999995</v>
-      </c>
-      <c r="D19" s="70">
-        <v>63.89</v>
-      </c>
-      <c r="E19" s="70">
-        <v>63.67</v>
-      </c>
-      <c r="F19" s="70">
-        <v>64.680000000000007</v>
-      </c>
-      <c r="G19" s="70">
-        <v>64.72</v>
-      </c>
-      <c r="H19" s="70">
-        <v>0</v>
-      </c>
-      <c r="I19" s="70">
-        <v>0</v>
-      </c>
-      <c r="J19" s="70">
-        <v>0</v>
-      </c>
-      <c r="K19" s="70">
-        <v>0</v>
-      </c>
-      <c r="L19" s="70">
-        <v>0</v>
-      </c>
-      <c r="M19" s="70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="69">
+      <c r="B19" s="69">
         <v>200</v>
       </c>
-      <c r="C20" s="69">
+      <c r="C19" s="69">
         <v>200</v>
       </c>
-      <c r="D20" s="69">
-        <v>0</v>
-      </c>
-      <c r="E20" s="69">
-        <v>0</v>
-      </c>
-      <c r="F20" s="69">
+      <c r="D19" s="69">
+        <v>0</v>
+      </c>
+      <c r="E19" s="69">
+        <v>0</v>
+      </c>
+      <c r="F19" s="69">
         <f>150 + 150 + 399 + 131.39</f>
         <v>830.39</v>
       </c>
-      <c r="G20" s="69">
+      <c r="G19" s="69">
         <v>300</v>
       </c>
-      <c r="H20" s="69">
-        <v>0</v>
-      </c>
-      <c r="I20" s="69">
-        <v>0</v>
-      </c>
-      <c r="J20" s="69">
-        <v>0</v>
-      </c>
-      <c r="K20" s="69">
-        <v>0</v>
-      </c>
-      <c r="L20" s="69">
-        <v>0</v>
-      </c>
-      <c r="M20" s="69">
-        <v>0</v>
-      </c>
+      <c r="H19" s="69">
+        <v>0</v>
+      </c>
+      <c r="I19" s="69">
+        <v>0</v>
+      </c>
+      <c r="J19" s="69">
+        <v>0</v>
+      </c>
+      <c r="K19" s="69">
+        <v>0</v>
+      </c>
+      <c r="L19" s="69">
+        <v>0</v>
+      </c>
+      <c r="M19" s="69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="51"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="58"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="58"/>
+      <c r="K20" s="58"/>
+      <c r="L20" s="58"/>
+      <c r="M20" s="59"/>
     </row>
     <row r="21" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="51"/>
-      <c r="B21" s="58"/>
-      <c r="C21" s="58"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="58"/>
-      <c r="I21" s="58"/>
-      <c r="J21" s="58"/>
-      <c r="K21" s="58"/>
-      <c r="L21" s="58"/>
-      <c r="M21" s="59"/>
-    </row>
-    <row r="22" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="67" t="s">
+      <c r="A21" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="68">
-        <f>B23+B24+B25</f>
+      <c r="B21" s="68">
+        <f>B22+B23+B24</f>
         <v>1000</v>
       </c>
-      <c r="C22" s="68">
-        <f t="shared" ref="C22:M22" si="4">SUM(C23:C26)</f>
+      <c r="C21" s="68">
+        <f t="shared" ref="C21:M21" si="4">SUM(C22:C25)</f>
         <v>150</v>
       </c>
-      <c r="D22" s="68">
+      <c r="D21" s="68">
         <f t="shared" si="4"/>
         <v>450</v>
       </c>
-      <c r="E22" s="68">
+      <c r="E21" s="68">
         <f t="shared" si="4"/>
         <v>150</v>
       </c>
-      <c r="F22" s="68">
+      <c r="F21" s="68">
         <f t="shared" si="4"/>
         <v>150</v>
       </c>
-      <c r="G22" s="68">
+      <c r="G21" s="68">
         <f t="shared" si="4"/>
         <v>2353.2399999999998</v>
       </c>
-      <c r="H22" s="68">
+      <c r="H21" s="68">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I22" s="68">
+      <c r="I21" s="68">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J22" s="68">
+      <c r="J21" s="68">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K22" s="68">
+      <c r="K21" s="68">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L22" s="68">
+      <c r="L21" s="68">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M22" s="68">
+      <c r="M21" s="68">
         <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="70">
+        <v>0</v>
+      </c>
+      <c r="C22" s="69">
+        <v>0</v>
+      </c>
+      <c r="D22" s="69">
+        <v>300</v>
+      </c>
+      <c r="E22" s="69">
+        <v>0</v>
+      </c>
+      <c r="F22" s="69">
+        <v>0</v>
+      </c>
+      <c r="G22" s="69">
+        <f xml:space="preserve"> 1500 + 673.24</f>
+        <v>2173.2399999999998</v>
+      </c>
+      <c r="H22" s="69">
+        <v>0</v>
+      </c>
+      <c r="I22" s="69">
+        <v>0</v>
+      </c>
+      <c r="J22" s="69">
+        <v>0</v>
+      </c>
+      <c r="K22" s="69">
+        <v>0</v>
+      </c>
+      <c r="L22" s="69">
+        <v>0</v>
+      </c>
+      <c r="M22" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="62" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B23" s="70">
-        <v>0</v>
-      </c>
-      <c r="C23" s="69">
-        <v>0</v>
-      </c>
-      <c r="D23" s="69">
-        <v>300</v>
-      </c>
-      <c r="E23" s="69">
-        <v>0</v>
-      </c>
-      <c r="F23" s="69">
-        <v>0</v>
-      </c>
-      <c r="G23" s="69">
-        <f xml:space="preserve"> 1500 + 673.24</f>
-        <v>2173.2399999999998</v>
-      </c>
-      <c r="H23" s="69">
-        <v>0</v>
-      </c>
-      <c r="I23" s="69">
-        <v>0</v>
-      </c>
-      <c r="J23" s="69">
-        <v>0</v>
-      </c>
-      <c r="K23" s="69">
-        <v>0</v>
-      </c>
-      <c r="L23" s="69">
-        <v>0</v>
-      </c>
-      <c r="M23" s="69">
+        <v>850</v>
+      </c>
+      <c r="C23" s="70">
+        <v>0</v>
+      </c>
+      <c r="D23" s="70">
+        <v>0</v>
+      </c>
+      <c r="E23" s="70">
+        <v>0</v>
+      </c>
+      <c r="F23" s="70">
+        <v>0</v>
+      </c>
+      <c r="G23" s="70">
+        <v>180</v>
+      </c>
+      <c r="H23" s="70">
+        <v>0</v>
+      </c>
+      <c r="I23" s="70">
+        <v>0</v>
+      </c>
+      <c r="J23" s="70">
+        <v>0</v>
+      </c>
+      <c r="K23" s="70">
+        <v>0</v>
+      </c>
+      <c r="L23" s="70">
+        <v>0</v>
+      </c>
+      <c r="M23" s="70">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="62" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B24" s="70">
-        <v>850</v>
+        <v>150</v>
       </c>
       <c r="C24" s="70">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D24" s="70">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E24" s="70">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F24" s="70">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G24" s="70">
-        <v>180</v>
-      </c>
-      <c r="H24" s="70">
-        <v>0</v>
-      </c>
-      <c r="I24" s="70">
-        <v>0</v>
-      </c>
-      <c r="J24" s="70">
-        <v>0</v>
-      </c>
-      <c r="K24" s="70">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H24" s="70"/>
+      <c r="I24" s="70"/>
+      <c r="J24" s="70"/>
+      <c r="K24" s="70"/>
       <c r="L24" s="70">
         <v>0</v>
       </c>
@@ -8409,160 +8517,180 @@
       </c>
     </row>
     <row r="25" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="70">
-        <v>150</v>
-      </c>
-      <c r="C25" s="70">
-        <v>150</v>
-      </c>
-      <c r="D25" s="70">
-        <v>150</v>
-      </c>
-      <c r="E25" s="70">
-        <v>150</v>
-      </c>
-      <c r="F25" s="70">
-        <v>150</v>
-      </c>
-      <c r="G25" s="70">
-        <v>0</v>
-      </c>
-      <c r="H25" s="70"/>
-      <c r="I25" s="70"/>
-      <c r="J25" s="70"/>
-      <c r="K25" s="70"/>
-      <c r="L25" s="70">
-        <v>0</v>
-      </c>
-      <c r="M25" s="70">
-        <v>0</v>
-      </c>
+      <c r="A25" s="51"/>
+      <c r="B25" s="58"/>
+      <c r="C25" s="58"/>
+      <c r="D25" s="58"/>
+      <c r="E25" s="58"/>
+      <c r="F25" s="58"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="58"/>
+      <c r="I25" s="58"/>
+      <c r="J25" s="58"/>
+      <c r="K25" s="58"/>
+      <c r="L25" s="58"/>
+      <c r="M25" s="59"/>
     </row>
     <row r="26" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="51"/>
-      <c r="B26" s="58"/>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="58"/>
-      <c r="J26" s="58"/>
-      <c r="K26" s="58"/>
-      <c r="L26" s="58"/>
-      <c r="M26" s="59"/>
+      <c r="A26" s="71" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" s="72"/>
+      <c r="C26" s="72"/>
+      <c r="D26" s="72"/>
+      <c r="E26" s="72"/>
+      <c r="F26" s="72"/>
+      <c r="G26" s="72"/>
+      <c r="H26" s="72"/>
+      <c r="I26" s="72"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="72"/>
+      <c r="M26" s="72"/>
     </row>
     <row r="27" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="71" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" s="72"/>
-      <c r="C27" s="72"/>
-      <c r="D27" s="72"/>
-      <c r="E27" s="72"/>
-      <c r="F27" s="72"/>
-      <c r="G27" s="72"/>
-      <c r="H27" s="72"/>
-      <c r="I27" s="72"/>
-      <c r="J27" s="72"/>
-      <c r="K27" s="72"/>
-      <c r="L27" s="72"/>
-      <c r="M27" s="72"/>
+      <c r="A27" s="62" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="70">
+        <f>'Fluxo de caixa 2025'!M33+'Fluxo de caixa 2026'!B8</f>
+        <v>3980.1</v>
+      </c>
+      <c r="C27" s="70">
+        <f t="shared" ref="C27:H27" si="5">B32+C8</f>
+        <v>3234.45</v>
+      </c>
+      <c r="D27" s="70">
+        <f t="shared" si="5"/>
+        <v>3389.42</v>
+      </c>
+      <c r="E27" s="70">
+        <f t="shared" si="5"/>
+        <v>3419.26</v>
+      </c>
+      <c r="F27" s="70">
+        <f t="shared" si="5"/>
+        <v>3759.4700000000003</v>
+      </c>
+      <c r="G27" s="70">
+        <f t="shared" si="5"/>
+        <v>3241.2700000000004</v>
+      </c>
+      <c r="H27" s="70">
+        <f t="shared" si="5"/>
+        <v>442.07000000000062</v>
+      </c>
+      <c r="I27" s="70">
+        <v>0</v>
+      </c>
+      <c r="J27" s="70">
+        <v>0</v>
+      </c>
+      <c r="K27" s="70">
+        <v>0</v>
+      </c>
+      <c r="L27" s="70">
+        <v>0</v>
+      </c>
+      <c r="M27" s="70">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="62" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28" s="70">
-        <f>'Fluxo de caixa 2025'!M33+'Fluxo de caixa 2026'!B8</f>
-        <v>3980.1</v>
+        <f t="shared" ref="B28:H28" si="6">B10</f>
+        <v>36.1</v>
       </c>
       <c r="C28" s="70">
-        <f t="shared" ref="C28:H28" si="5">B33+C8</f>
-        <v>3234.45</v>
+        <f t="shared" si="6"/>
+        <v>27.74</v>
       </c>
       <c r="D28" s="70">
-        <f t="shared" si="5"/>
-        <v>3389.42</v>
+        <f t="shared" si="6"/>
+        <v>56.21</v>
       </c>
       <c r="E28" s="70">
-        <f t="shared" si="5"/>
-        <v>3419.26</v>
+        <f t="shared" si="6"/>
+        <v>24.97</v>
       </c>
       <c r="F28" s="70">
-        <f t="shared" si="5"/>
-        <v>3759.4700000000003</v>
+        <f t="shared" si="6"/>
+        <v>35.119999999999997</v>
       </c>
       <c r="G28" s="70">
-        <f t="shared" si="5"/>
-        <v>3238.7200000000003</v>
+        <f t="shared" si="6"/>
+        <v>8.11</v>
       </c>
       <c r="H28" s="70">
-        <f t="shared" si="5"/>
-        <v>439.52000000000044</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="I28" s="70">
+        <f>I12</f>
         <v>0</v>
       </c>
       <c r="J28" s="70">
+        <f>J10</f>
         <v>0</v>
       </c>
       <c r="K28" s="70">
+        <f>K10</f>
         <v>0</v>
       </c>
       <c r="L28" s="70">
+        <f>L10</f>
         <v>0</v>
       </c>
       <c r="M28" s="70">
+        <f>M10</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="62" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29" s="70">
-        <f t="shared" ref="B29:F29" si="6">B10</f>
-        <v>36.1</v>
+        <f t="shared" ref="B29:M29" si="7">B16</f>
+        <v>345.65</v>
       </c>
       <c r="C29" s="70">
-        <f t="shared" si="6"/>
-        <v>27.74</v>
+        <f t="shared" si="7"/>
+        <v>351.24</v>
       </c>
       <c r="D29" s="70">
-        <f t="shared" si="6"/>
-        <v>56.21</v>
+        <f t="shared" si="7"/>
+        <v>145.13</v>
       </c>
       <c r="E29" s="70">
-        <f t="shared" si="6"/>
-        <v>24.97</v>
+        <f t="shared" si="7"/>
+        <v>144.91</v>
       </c>
       <c r="F29" s="70">
-        <f t="shared" si="6"/>
-        <v>35.119999999999997</v>
+        <f t="shared" si="7"/>
+        <v>976.31</v>
       </c>
       <c r="G29" s="70">
-        <f>G10</f>
-        <v>5.56</v>
+        <f t="shared" si="7"/>
+        <v>445.96</v>
       </c>
       <c r="H29" s="70">
-        <f>H10</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I29" s="70">
-        <f>I13</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J29" s="70">
-        <f>J10</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K29" s="70">
-        <f t="shared" ref="K29:M29" si="7">K10</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L29" s="70">
@@ -8576,31 +8704,31 @@
     </row>
     <row r="30" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="62" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30" s="70">
-        <f t="shared" ref="B30:M30" si="8">B17</f>
-        <v>345.65</v>
+        <f t="shared" ref="B30:M31" si="8">B21</f>
+        <v>1000</v>
       </c>
       <c r="C30" s="70">
         <f t="shared" si="8"/>
-        <v>351.24</v>
+        <v>150</v>
       </c>
       <c r="D30" s="70">
         <f t="shared" si="8"/>
-        <v>145.13</v>
+        <v>450</v>
       </c>
       <c r="E30" s="70">
         <f t="shared" si="8"/>
-        <v>144.91</v>
+        <v>150</v>
       </c>
       <c r="F30" s="70">
         <f t="shared" si="8"/>
-        <v>976.31</v>
+        <v>150</v>
       </c>
       <c r="G30" s="70">
         <f t="shared" si="8"/>
-        <v>445.96</v>
+        <v>2353.2399999999998</v>
       </c>
       <c r="H30" s="70">
         <f t="shared" si="8"/>
@@ -8626,34 +8754,35 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
+      <c r="P30" s="118"/>
     </row>
     <row r="31" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="62" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="B31" s="70">
-        <f t="shared" ref="B31:M32" si="9">B22</f>
-        <v>1000</v>
+        <f>B12</f>
+        <v>0</v>
       </c>
       <c r="C31" s="70">
-        <f t="shared" si="9"/>
-        <v>150</v>
+        <f t="shared" ref="C31:L31" si="9">C12</f>
+        <v>0</v>
       </c>
       <c r="D31" s="70">
         <f t="shared" si="9"/>
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="E31" s="70">
         <f t="shared" si="9"/>
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F31" s="70">
         <f t="shared" si="9"/>
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="G31" s="70">
         <f t="shared" si="9"/>
-        <v>2353.2399999999998</v>
+        <v>0</v>
       </c>
       <c r="H31" s="70">
         <f t="shared" si="9"/>
@@ -8676,174 +8805,243 @@
         <v>0</v>
       </c>
       <c r="M31" s="70">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="P31" s="118"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="32" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="62" t="s">
-        <v>75</v>
-      </c>
-      <c r="B32" s="70">
-        <f>B13</f>
-        <v>0</v>
-      </c>
-      <c r="C32" s="70">
-        <f t="shared" ref="C32:L32" si="10">C13</f>
-        <v>0</v>
-      </c>
-      <c r="D32" s="70">
+        <v>41</v>
+      </c>
+      <c r="B32" s="73">
+        <f>B27-B29-B30-B31</f>
+        <v>2634.45</v>
+      </c>
+      <c r="C32" s="73">
+        <f t="shared" ref="C32:I32" si="10">C27-C29-C30-C31</f>
+        <v>2733.21</v>
+      </c>
+      <c r="D32" s="73">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="E32" s="70">
+        <v>2794.29</v>
+      </c>
+      <c r="E32" s="73">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F32" s="70">
+        <v>3124.3500000000004</v>
+      </c>
+      <c r="F32" s="73">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="G32" s="70">
+        <v>2633.1600000000003</v>
+      </c>
+      <c r="G32" s="73">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="H32" s="70">
+        <v>442.07000000000062</v>
+      </c>
+      <c r="H32" s="73">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="I32" s="70">
+        <v>442.07000000000062</v>
+      </c>
+      <c r="I32" s="73">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J32" s="70">
-        <f t="shared" si="10"/>
+        <f>J27-J29-J30</f>
         <v>0</v>
       </c>
       <c r="K32" s="70">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="L32" s="70">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="K32" si="11">K27+K28-K29-K30</f>
+        <v>0</v>
+      </c>
+      <c r="L32" s="117">
+        <f>L27+L28-L29-L30-L31</f>
         <v>0</v>
       </c>
       <c r="M32" s="70">
-        <f t="shared" si="9"/>
+        <f>M27-M29-M30</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="62" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="73">
-        <f>B28-B30-B31-B32</f>
-        <v>2634.45</v>
-      </c>
-      <c r="C33" s="73">
-        <f t="shared" ref="C33:I33" si="11">C28-C30-C31-C32</f>
-        <v>2733.21</v>
-      </c>
-      <c r="D33" s="73">
-        <f t="shared" si="11"/>
-        <v>2794.29</v>
-      </c>
-      <c r="E33" s="73">
-        <f t="shared" si="11"/>
-        <v>3124.3500000000004</v>
-      </c>
-      <c r="F33" s="73">
-        <f t="shared" si="11"/>
-        <v>2633.1600000000003</v>
-      </c>
-      <c r="G33" s="73">
-        <f t="shared" si="11"/>
-        <v>439.52000000000044</v>
-      </c>
-      <c r="H33" s="73">
-        <f t="shared" si="11"/>
-        <v>439.52000000000044</v>
-      </c>
-      <c r="I33" s="73">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J33" s="70">
-        <f>J28-J30-J31</f>
-        <v>0</v>
-      </c>
-      <c r="K33" s="70">
-        <f t="shared" ref="K33" si="12">K28+K29-K30-K31</f>
-        <v>0</v>
-      </c>
-      <c r="L33" s="117">
-        <f>L28+L29-L30-L31-L32</f>
-        <v>0</v>
-      </c>
-      <c r="M33" s="70">
-        <f>M28-M30-M31</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="A33" s="123"/>
+      <c r="B33" s="124"/>
+      <c r="C33" s="124"/>
+      <c r="D33" s="124"/>
+      <c r="E33" s="124"/>
+      <c r="F33" s="124"/>
+      <c r="G33" s="124"/>
+      <c r="H33" s="124"/>
+      <c r="I33" s="124"/>
+      <c r="J33" s="125"/>
+      <c r="K33" s="125"/>
+      <c r="L33" s="126"/>
+      <c r="M33" s="125"/>
+    </row>
+    <row r="34" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="71" t="s">
+        <v>76</v>
+      </c>
+      <c r="B34" s="72"/>
+      <c r="C34" s="72"/>
+      <c r="D34" s="72"/>
+      <c r="E34" s="72"/>
+      <c r="F34" s="72"/>
+      <c r="G34" s="72"/>
+      <c r="H34" s="72"/>
+      <c r="I34" s="72"/>
+      <c r="J34" s="72"/>
+      <c r="K34" s="72"/>
+      <c r="L34" s="72"/>
+      <c r="M34" s="72"/>
+    </row>
     <row r="35" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" s="119">
-        <f>'Fluxo de caixa 2025'!M35 + B25</f>
-        <v>-1500</v>
-      </c>
-      <c r="C35" s="119">
-        <f>B35+150</f>
-        <v>-1350</v>
-      </c>
-      <c r="D35" s="119">
-        <f t="shared" ref="D35:F35" si="13">C35+150</f>
-        <v>-1200</v>
-      </c>
-      <c r="E35" s="119">
-        <f t="shared" si="13"/>
-        <v>-1050</v>
-      </c>
-      <c r="F35" s="119">
-        <f t="shared" si="13"/>
-        <v>-900</v>
-      </c>
-      <c r="G35" s="121"/>
-      <c r="H35" s="119"/>
-      <c r="I35" s="119"/>
-      <c r="J35" s="119"/>
-      <c r="K35" s="119"/>
-      <c r="L35" s="119"/>
-      <c r="M35" s="119"/>
+      <c r="A35" s="62" t="s">
+        <v>77</v>
+      </c>
+      <c r="B35" s="70">
+        <v>1500</v>
+      </c>
+      <c r="C35" s="70">
+        <f>B35 - 150</f>
+        <v>1350</v>
+      </c>
+      <c r="D35" s="70">
+        <f t="shared" ref="D35:F35" si="12">C35 - 150</f>
+        <v>1200</v>
+      </c>
+      <c r="E35" s="70">
+        <f t="shared" si="12"/>
+        <v>1050</v>
+      </c>
+      <c r="F35" s="70">
+        <f t="shared" si="12"/>
+        <v>900</v>
+      </c>
+      <c r="G35" s="70">
+        <f>F35- 4521.24 - 200</f>
+        <v>-3821.24</v>
+      </c>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="70"/>
+      <c r="K35" s="70"/>
+      <c r="L35" s="70"/>
+      <c r="M35" s="70"/>
     </row>
     <row r="36" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D36" s="118"/>
-      <c r="I36" s="118"/>
+      <c r="A36" s="62" t="s">
+        <v>78</v>
+      </c>
+      <c r="B36" s="70">
+        <v>0</v>
+      </c>
+      <c r="C36" s="70">
+        <v>0</v>
+      </c>
+      <c r="D36" s="70">
+        <v>0</v>
+      </c>
+      <c r="E36" s="70">
+        <v>0</v>
+      </c>
+      <c r="F36" s="70">
+        <v>0</v>
+      </c>
+      <c r="G36" s="70">
+        <v>0</v>
+      </c>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="70"/>
+      <c r="K36" s="70"/>
+      <c r="L36" s="70"/>
+      <c r="M36" s="70"/>
     </row>
     <row r="37" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="N37" s="118"/>
-    </row>
-    <row r="38" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E38" s="116"/>
+      <c r="A37" s="62" t="s">
+        <v>79</v>
+      </c>
+      <c r="B37" s="70">
+        <v>0</v>
+      </c>
+      <c r="C37" s="70">
+        <v>0</v>
+      </c>
+      <c r="D37" s="70">
+        <v>0</v>
+      </c>
+      <c r="E37" s="70">
+        <v>0</v>
+      </c>
+      <c r="F37" s="70">
+        <v>0</v>
+      </c>
+      <c r="G37" s="70">
+        <v>0</v>
+      </c>
+      <c r="H37" s="70"/>
+      <c r="I37" s="70"/>
+      <c r="J37" s="70"/>
+      <c r="K37" s="70"/>
+      <c r="L37" s="70"/>
+      <c r="M37" s="70"/>
+    </row>
+    <row r="38" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="62" t="s">
+        <v>80</v>
+      </c>
+      <c r="B38" s="70">
+        <v>0</v>
+      </c>
+      <c r="C38" s="70">
+        <v>0</v>
+      </c>
+      <c r="D38" s="70">
+        <v>0</v>
+      </c>
+      <c r="E38" s="70">
+        <v>0</v>
+      </c>
+      <c r="F38" s="70">
+        <v>0</v>
+      </c>
+      <c r="G38" s="70">
+        <v>0</v>
+      </c>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="70"/>
+      <c r="K38" s="70"/>
+      <c r="L38" s="70"/>
+      <c r="M38" s="70"/>
     </row>
     <row r="39" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F39" s="118"/>
-      <c r="N39" s="116"/>
-    </row>
-    <row r="40" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="D39" s="118"/>
+      <c r="I39" s="118"/>
+      <c r="N39" s="118"/>
+    </row>
+    <row r="40" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N40" s="118"/>
+    </row>
     <row r="41" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="J41" s="118"/>
+      <c r="E41" s="116"/>
     </row>
     <row r="42" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G42" s="118"/>
+      <c r="G42" s="121"/>
+      <c r="H42" s="119"/>
+      <c r="I42" s="119"/>
+      <c r="J42" s="119"/>
+      <c r="K42" s="119"/>
+      <c r="L42" s="119"/>
+      <c r="M42" s="119"/>
     </row>
     <row r="43" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J44" s="118"/>
+    </row>
+    <row r="45" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G45" s="118"/>
+    </row>
     <row r="46" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="47" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="48" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -9801,6 +9999,9 @@
     <row r="1000" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1001" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1002" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1003" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1004" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1005" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:A4"/>
@@ -9812,11 +10013,21 @@
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="G3:H3"/>
   </mergeCells>
+  <phoneticPr fontId="34" type="noConversion"/>
+  <conditionalFormatting sqref="B35:M38">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>B35&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>B35&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{0BBF6038-DAD6-4ACD-B60D-5B091CBA3D12}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -9844,21 +10055,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="157" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="123"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="123"/>
-      <c r="E1" s="123"/>
-      <c r="F1" s="123"/>
-      <c r="G1" s="123"/>
-      <c r="H1" s="123"/>
-      <c r="I1" s="123"/>
-      <c r="J1" s="123"/>
-      <c r="K1" s="123"/>
-      <c r="L1" s="123"/>
-      <c r="M1" s="123"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="128"/>
+      <c r="M1" s="128"/>
       <c r="N1" s="79"/>
     </row>
     <row r="2" spans="1:39" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -10401,45 +10612,45 @@
       </c>
     </row>
     <row r="9" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="153"/>
-      <c r="B9" s="154"/>
-      <c r="C9" s="154"/>
-      <c r="D9" s="154"/>
-      <c r="E9" s="154"/>
-      <c r="F9" s="154"/>
-      <c r="G9" s="154"/>
-      <c r="H9" s="154"/>
-      <c r="I9" s="154"/>
-      <c r="J9" s="154"/>
-      <c r="K9" s="154"/>
-      <c r="L9" s="154"/>
-      <c r="M9" s="155"/>
-      <c r="N9" s="153"/>
-      <c r="O9" s="154"/>
-      <c r="P9" s="154"/>
-      <c r="Q9" s="154"/>
-      <c r="R9" s="154"/>
-      <c r="S9" s="154"/>
-      <c r="T9" s="154"/>
-      <c r="U9" s="154"/>
-      <c r="V9" s="154"/>
-      <c r="W9" s="154"/>
-      <c r="X9" s="154"/>
-      <c r="Y9" s="154"/>
-      <c r="Z9" s="155"/>
-      <c r="AA9" s="153"/>
-      <c r="AB9" s="154"/>
-      <c r="AC9" s="154"/>
-      <c r="AD9" s="154"/>
-      <c r="AE9" s="154"/>
-      <c r="AF9" s="154"/>
-      <c r="AG9" s="154"/>
-      <c r="AH9" s="154"/>
-      <c r="AI9" s="154"/>
-      <c r="AJ9" s="154"/>
-      <c r="AK9" s="154"/>
-      <c r="AL9" s="154"/>
-      <c r="AM9" s="155"/>
+      <c r="A9" s="158"/>
+      <c r="B9" s="159"/>
+      <c r="C9" s="159"/>
+      <c r="D9" s="159"/>
+      <c r="E9" s="159"/>
+      <c r="F9" s="159"/>
+      <c r="G9" s="159"/>
+      <c r="H9" s="159"/>
+      <c r="I9" s="159"/>
+      <c r="J9" s="159"/>
+      <c r="K9" s="159"/>
+      <c r="L9" s="159"/>
+      <c r="M9" s="160"/>
+      <c r="N9" s="158"/>
+      <c r="O9" s="159"/>
+      <c r="P9" s="159"/>
+      <c r="Q9" s="159"/>
+      <c r="R9" s="159"/>
+      <c r="S9" s="159"/>
+      <c r="T9" s="159"/>
+      <c r="U9" s="159"/>
+      <c r="V9" s="159"/>
+      <c r="W9" s="159"/>
+      <c r="X9" s="159"/>
+      <c r="Y9" s="159"/>
+      <c r="Z9" s="160"/>
+      <c r="AA9" s="158"/>
+      <c r="AB9" s="159"/>
+      <c r="AC9" s="159"/>
+      <c r="AD9" s="159"/>
+      <c r="AE9" s="159"/>
+      <c r="AF9" s="159"/>
+      <c r="AG9" s="159"/>
+      <c r="AH9" s="159"/>
+      <c r="AI9" s="159"/>
+      <c r="AJ9" s="159"/>
+      <c r="AK9" s="159"/>
+      <c r="AL9" s="159"/>
+      <c r="AM9" s="160"/>
     </row>
     <row r="10" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="78" t="s">
@@ -14750,13 +14961,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="156" t="s">
+      <c r="B1" s="161" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="134"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="139"/>
       <c r="G1" s="93"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
@@ -14782,11 +14993,11 @@
     </row>
     <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="97"/>
-      <c r="B3" s="157"/>
-      <c r="C3" s="158"/>
-      <c r="D3" s="158"/>
-      <c r="E3" s="158"/>
-      <c r="F3" s="159"/>
+      <c r="B3" s="162"/>
+      <c r="C3" s="163"/>
+      <c r="D3" s="163"/>
+      <c r="E3" s="163"/>
+      <c r="F3" s="164"/>
       <c r="G3" s="98"/>
     </row>
     <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">

--- a/planilhas/Contabilidade Condominio.xlsx
+++ b/planilhas/Contabilidade Condominio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Condominio\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED525A7-35D2-4EBD-B098-23A6C00310EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A8AF6D-DC81-405C-8B6F-2C5F1899A434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -141,10 +141,10 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={629604FD-A46D-4353-9480-10C9E82C566F}</author>
+    <author>tc={3CEF80CF-1AF7-4BD8-A8E0-70FD525073FA}</author>
   </authors>
   <commentList>
-    <comment ref="G35" authorId="0" shapeId="0" xr:uid="{629604FD-A46D-4353-9480-10C9E82C566F}">
+    <comment ref="G36" authorId="0" shapeId="0" xr:uid="{3CEF80CF-1AF7-4BD8-A8E0-70FD525073FA}">
       <text>
         <t>[Comentário encadeado]
 Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
@@ -414,7 +414,7 @@
     <numFmt numFmtId="165" formatCode="&quot;R$&quot;#,##0.00;[Red]&quot;R$&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="35" x14ac:knownFonts="1">
+  <fonts count="36" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -615,6 +615,12 @@
       <sz val="8"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Segoe UI"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="15">
@@ -1968,7 +1974,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="G35" dT="2026-06-18T12:37:56.77" personId="{94384591-832C-4E54-BCC6-025FEE2D32A2}" id="{629604FD-A46D-4353-9480-10C9E82C566F}">
+  <threadedComment ref="G36" dT="2026-06-18T12:37:56.77" personId="{94384591-832C-4E54-BCC6-025FEE2D32A2}" id="{3CEF80CF-1AF7-4BD8-A8E0-70FD525073FA}">
     <text>Definido em convenção do condominio que o valor do material perdido seria repassado como custos a ser coberto pelo AP01, o valor total dos materiais ficou em R$4.521,24, revertendo o crédito positivo de R$ 900,00 para R$ 3621,24. Taxa de Condominio não recolhida R$ 200,00</text>
   </threadedComment>
 </ThreadedComments>
@@ -8898,28 +8904,23 @@
       <c r="A35" s="62" t="s">
         <v>77</v>
       </c>
-      <c r="B35" s="70">
-        <v>1500</v>
-      </c>
-      <c r="C35" s="70">
-        <f>B35 - 150</f>
-        <v>1350</v>
-      </c>
-      <c r="D35" s="70">
-        <f t="shared" ref="D35:F35" si="12">C35 - 150</f>
-        <v>1200</v>
-      </c>
-      <c r="E35" s="70">
-        <f t="shared" si="12"/>
-        <v>1050</v>
-      </c>
-      <c r="F35" s="70">
-        <f t="shared" si="12"/>
-        <v>900</v>
-      </c>
-      <c r="G35" s="70">
-        <f>F35- 4521.24 - 200</f>
-        <v>-3821.24</v>
+      <c r="B35" s="115">
+        <v>0</v>
+      </c>
+      <c r="C35" s="115">
+        <v>0</v>
+      </c>
+      <c r="D35" s="115">
+        <v>0</v>
+      </c>
+      <c r="E35" s="115">
+        <v>0</v>
+      </c>
+      <c r="F35" s="115">
+        <v>0</v>
+      </c>
+      <c r="G35" s="115">
+        <v>0</v>
       </c>
       <c r="H35" s="70"/>
       <c r="I35" s="70"/>
@@ -8933,22 +8934,27 @@
         <v>78</v>
       </c>
       <c r="B36" s="70">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="C36" s="70">
-        <v>0</v>
+        <f>B36 - 150</f>
+        <v>1350</v>
       </c>
       <c r="D36" s="70">
-        <v>0</v>
+        <f t="shared" ref="D36" si="12">C36 - 150</f>
+        <v>1200</v>
       </c>
       <c r="E36" s="70">
-        <v>0</v>
+        <f t="shared" ref="E36" si="13">D36 - 150</f>
+        <v>1050</v>
       </c>
       <c r="F36" s="70">
-        <v>0</v>
+        <f t="shared" ref="F36" si="14">E36 - 150</f>
+        <v>900</v>
       </c>
       <c r="G36" s="70">
-        <v>0</v>
+        <f>F36- 4521.24 - 200</f>
+        <v>-3821.24</v>
       </c>
       <c r="H36" s="70"/>
       <c r="I36" s="70"/>
